--- a/data/rumah_makan.xlsx
+++ b/data/rumah_makan.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\SEMESTER 6\PRAK. SIGTER\PROJECT AKHIR\STUDENT SURVIVAL MAP\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19F27E75-7A38-48B7-BE13-81DFFA7D4F22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42ABA17B-03BF-49C9-8349-78970539F486}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{EBF2A29F-0C7E-4417-9F77-D4C323BFD0DA}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="431" uniqueCount="286">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="625" uniqueCount="420">
   <si>
     <t>Id</t>
   </si>
@@ -90,21 +90,9 @@
     <t>6:00 AM – 20:00 PM</t>
   </si>
   <si>
-    <t>Jl. Kuningan, Karang Malang, Caturtunggal, Kec. Depok, Kab. Sleman, DIY 55281</t>
-  </si>
-  <si>
-    <t>https://maps.app.goo.gl/iqZ4GBhxDdnmiKFh9</t>
-  </si>
-  <si>
-    <t>R001.jpg</t>
-  </si>
-  <si>
     <t>Tidak</t>
   </si>
   <si>
-    <t>RP 1-25.000</t>
-  </si>
-  <si>
     <t>R002</t>
   </si>
   <si>
@@ -117,15 +105,6 @@
     <t>11:00 AM – 23:00 PM</t>
   </si>
   <si>
-    <t>Jalan Tantular, Kaliwaru, Condongcatur, Kec. Depok, Kab. Sleman, DIY 55281</t>
-  </si>
-  <si>
-    <t>https://maps.app.goo.gl/RYeTdPUprhVZbWQj7</t>
-  </si>
-  <si>
-    <t>R002.jpg</t>
-  </si>
-  <si>
     <t>R003</t>
   </si>
   <si>
@@ -135,15 +114,6 @@
     <t>11:30 AM – 23:00 PM</t>
   </si>
   <si>
-    <t>Jl. Sengkan Gg. Sadewa No.02, Kocoran, Condongcatur, Kec. Depok, Kab. Sleman, DIY 55283</t>
-  </si>
-  <si>
-    <t>https://maps.app.goo.gl/dE8ZDETqJrKnrMYT7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">R003.jpg </t>
-  </si>
-  <si>
     <t>R004</t>
   </si>
   <si>
@@ -153,15 +123,6 @@
     <t>7:00 AM – 21:00 PM</t>
   </si>
   <si>
-    <t>Gg. Jemb. Merah No.116 D, Kaliwaru, Condongcatur, Kec. Depok, Kab. Sleman, DIY 55283</t>
-  </si>
-  <si>
-    <t>https://maps.app.goo.gl/4ZpaPxZ7B6SoaFbN7</t>
-  </si>
-  <si>
-    <t>R004.jpg</t>
-  </si>
-  <si>
     <t>R005</t>
   </si>
   <si>
@@ -171,15 +132,6 @@
     <t>8:00 AM – 20:00 PM</t>
   </si>
   <si>
-    <t>Blok B-5, Karangwuni, Manggung, Caturtunggal, Kec. Depok, Kab. Sleman, DIY 55281</t>
-  </si>
-  <si>
-    <t>https://maps.app.goo.gl/o6JYaCCD2E2qbBNu5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">R005.jpg </t>
-  </si>
-  <si>
     <t>R006</t>
   </si>
   <si>
@@ -189,15 +141,6 @@
     <t>9:00 AM – 23:00 PM</t>
   </si>
   <si>
-    <t>Dabag, Condongcatur, Kec. Depok, Kab. Sleman, DIY 55281</t>
-  </si>
-  <si>
-    <t>https://maps.app.goo.gl/jccDdukmCYNKPAUo8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">R006.jpg </t>
-  </si>
-  <si>
     <t>R007</t>
   </si>
   <si>
@@ -207,63 +150,24 @@
     <t>10:00 AM – 21:30 PM</t>
   </si>
   <si>
-    <t>Ruko Gorongan, Jl. Perumnas, Ngropoh, Condongcatur, Kec. Depok, Kab. Sleman, DIY 55283</t>
-  </si>
-  <si>
-    <t>https://maps.app.goo.gl/y2apQpo5v9a8eD8R7</t>
-  </si>
-  <si>
-    <t>R007.jpg</t>
-  </si>
-  <si>
     <t>R008</t>
   </si>
   <si>
-    <t>Warung Makan Mr. B</t>
-  </si>
-  <si>
     <t>8:00 AM – 21:00 PM</t>
   </si>
   <si>
-    <t>Jl. Cemp. No.231, Perumnas Condong Catur, Condongcatur, Kec. Depok, Kab. Sleman, DIY 55281</t>
-  </si>
-  <si>
-    <t>https://maps.app.goo.gl/JmsiDm3tz18g7duD8</t>
-  </si>
-  <si>
-    <t>R008.jpg</t>
-  </si>
-  <si>
     <t>R009</t>
   </si>
   <si>
     <t>Warung Makan Prasmanan Madonna</t>
   </si>
   <si>
-    <t>Ruko Babarsari, Jl. Raya Kledokan, Caturtunggal, Kec. Depok, Kab. Sleman, DIY 55281</t>
-  </si>
-  <si>
-    <t>https://maps.app.goo.gl/AVSE3ECfkHPPmucS8</t>
-  </si>
-  <si>
-    <t>R009.jpg</t>
-  </si>
-  <si>
     <t>R010</t>
   </si>
   <si>
     <t>Rumah Makan Padang Murah Babarsari</t>
   </si>
   <si>
-    <t>Ruko Babarsari, Jl. Babarsari, Tambak Bayan, Caturtunggal, Kec. Depok, Kab. Sleman, DIY 55281</t>
-  </si>
-  <si>
-    <t>https://maps.app.goo.gl/SWHzXXXf3SMQ8tA96</t>
-  </si>
-  <si>
-    <t>R010.jpg</t>
-  </si>
-  <si>
     <t>Ya</t>
   </si>
   <si>
@@ -273,18 +177,6 @@
     <t>Warung Makan Bu Ita</t>
   </si>
   <si>
-    <t>11:30 AM – 22.30 PM</t>
-  </si>
-  <si>
-    <t>Jl. Rusunawa Mranggen, Kutu Tegal, Sinduadi, Kec. Mlati, Kab. Sleman, DIY 55284</t>
-  </si>
-  <si>
-    <t>https://maps.app.goo.gl/945xB7PkevoCExYc8</t>
-  </si>
-  <si>
-    <t>R011.jpg</t>
-  </si>
-  <si>
     <t>R012</t>
   </si>
   <si>
@@ -297,30 +189,12 @@
     <t>11:00 AM – 20:00 PM</t>
   </si>
   <si>
-    <t>Jl. Babarsari I No.13, Janti, Caturtunggal, Kec. Depok, Kab. Sleman, DIY 55281</t>
-  </si>
-  <si>
-    <t>https://maps.app.goo.gl/rPTxmt9UDxHS23n19</t>
-  </si>
-  <si>
-    <t>R012.jpg</t>
-  </si>
-  <si>
     <t>R013</t>
   </si>
   <si>
     <t>Rumah Makan Rata-Rata</t>
   </si>
   <si>
-    <t>Ruko Babarsari BBC Plaza, Jl. Tambak Bayan, Janti, Caturtunggal, Kec. Depok, Kab. Sleman, DIY 55281</t>
-  </si>
-  <si>
-    <t>https://maps.app.goo.gl/L6iTqLFFDM966Tmd6</t>
-  </si>
-  <si>
-    <t>R013.jpg</t>
-  </si>
-  <si>
     <t>R014</t>
   </si>
   <si>
@@ -330,216 +204,84 @@
     <t>6:00 AM – 21:00 PM</t>
   </si>
   <si>
-    <t>Jl. Gambuh No.3, Manukan, Condongcatur, Kec. Depok, Kab. Sleman, DIY 52000</t>
-  </si>
-  <si>
-    <t>https://maps.app.goo.gl/fczoo46dnKmpCCLX7</t>
-  </si>
-  <si>
-    <t>R014.jpg</t>
-  </si>
-  <si>
     <t>R015</t>
   </si>
   <si>
     <t>Rizky Panghegar (Warmindo)</t>
   </si>
   <si>
-    <t>https://maps.app.goo.gl/frbqQuNvtPqtGRbZ9</t>
-  </si>
-  <si>
-    <t>R015.jpg</t>
-  </si>
-  <si>
     <t>R016</t>
   </si>
   <si>
     <t>Warung Parahyangan 2</t>
   </si>
   <si>
-    <t>https://maps.app.goo.gl/GyqJjnQwoYZo9MUv6</t>
-  </si>
-  <si>
-    <t>R016.jpg</t>
-  </si>
-  <si>
     <t>R017</t>
   </si>
   <si>
     <t>Ayam Bakar Warung Rizqi Agung</t>
   </si>
   <si>
-    <t>Karang Wuni, Caturtunggal, Kec. Depok, Kab. Sleman, DIY 55281</t>
-  </si>
-  <si>
-    <t>https://maps.app.goo.gl/fK5qaQbLaG5pV3qK7</t>
-  </si>
-  <si>
-    <t>R017.jpg</t>
-  </si>
-  <si>
     <t>R018</t>
   </si>
   <si>
     <t>Nomojowo 2</t>
   </si>
   <si>
-    <t>Jalan Kapulogo, Nologaten, Caturtunggal, Kec. Depok, Kab. Sleman, DIY 55281</t>
-  </si>
-  <si>
-    <t>https://maps.app.goo.gl/rfQ7La7Wdc5Ghyuw6</t>
-  </si>
-  <si>
-    <t>R018.jpg</t>
-  </si>
-  <si>
     <t>R019</t>
   </si>
   <si>
     <t>Warkop Agam Viral (Spesial Mie Bangladesh)</t>
   </si>
   <si>
-    <t>Ruko DTA Square, Jl. Seturan Raya, Kledokan, Caturtunggal, Kec. Depok, Kab. Sleman, DIY 55281</t>
-  </si>
-  <si>
-    <t>https://maps.app.goo.gl/Um2cFZ7P8u8Y3MLC9</t>
-  </si>
-  <si>
-    <t>R019.jpg</t>
-  </si>
-  <si>
     <t>R020</t>
   </si>
   <si>
     <t>Warteg 24</t>
   </si>
   <si>
-    <t>Jl. Kaliurang No.17 Km.6, Kentungan, Condongcatur, Kec. Depok, Kab. Sleman, DIY 55284</t>
-  </si>
-  <si>
-    <t>https://maps.app.goo.gl/8WpRE1ayxfZ9wkC86</t>
-  </si>
-  <si>
-    <t xml:space="preserve">R020.jpg </t>
-  </si>
-  <si>
     <t>R021</t>
   </si>
   <si>
     <t>WARMINDO PARADIS &amp; Nasi Goreng Barbar</t>
   </si>
   <si>
-    <t>Jl. Apokat, Perumnas Condong Catur, Condongcatur, Kec. Depok, Kab. Sleman, DIY 55283</t>
-  </si>
-  <si>
-    <t>https://maps.app.goo.gl/cAwMBmPVwPjQhV8b8</t>
-  </si>
-  <si>
-    <t>R021.jpg</t>
-  </si>
-  <si>
     <t>R022</t>
   </si>
   <si>
     <t>Motekar 12</t>
   </si>
   <si>
-    <t>Jl. Pintu Selatan UPN, Ngropoh, Condongcatur, Kec. Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
-  </si>
-  <si>
-    <t>https://maps.app.goo.gl/SQeZppWwHGojvCoYA</t>
-  </si>
-  <si>
-    <t>R022.jpg</t>
-  </si>
-  <si>
     <t>R023</t>
   </si>
   <si>
     <t>Warung Makan Putra Tunggal</t>
   </si>
   <si>
-    <t>9.00 AM - 21.00 PM</t>
-  </si>
-  <si>
-    <t>Jl. Perumnas Jl. Pintu Selatan UPN No.15, Ngropoh, Condongcatur, Kec. Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
-  </si>
-  <si>
-    <t>https://maps.app.goo.gl/MyMuo6xx6rSZSYn6A</t>
-  </si>
-  <si>
-    <t>R023.jpg</t>
-  </si>
-  <si>
     <t>R024</t>
   </si>
   <si>
     <t>Lesehan Pring Ori Sorowajan</t>
   </si>
   <si>
-    <t>9.00 AM - 23.30 PM</t>
-  </si>
-  <si>
-    <t>Jl. Sorowajan No.208, Sorowajan, Banguntapan, Kec. Banguntapan, Kabupaten Bantul, Daerah Istimewa Yogyakarta 55198</t>
-  </si>
-  <si>
-    <t>https://maps.app.goo.gl/GGv45FujGN5yNHwcA</t>
-  </si>
-  <si>
-    <t>R024.jpg</t>
-  </si>
-  <si>
     <t>R025</t>
   </si>
   <si>
     <t>Kantin Larasati</t>
   </si>
   <si>
-    <t xml:space="preserve">8.00 AM - 22.00 PM </t>
-  </si>
-  <si>
-    <t>Ruko Kelapa Hijau, Jl. Brojomulyo No.10, Gejayan, Condongcatur, Kec. Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
-  </si>
-  <si>
-    <t>https://maps.app.goo.gl/xKX6kRSfFGRUAG9A8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">R025.jpg </t>
-  </si>
-  <si>
     <t>R026</t>
   </si>
   <si>
     <t>Kantin Raya - Condong Catur</t>
   </si>
   <si>
-    <t xml:space="preserve">10.00 AM - 22.00 PM </t>
-  </si>
-  <si>
-    <t>Jl. Kemuning No.1b, Candok, Condongcatur, Kec. Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
-  </si>
-  <si>
-    <t>https://maps.app.goo.gl/Tm28gLkjwDSy5e776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">R026.jpg </t>
-  </si>
-  <si>
     <t>R027</t>
   </si>
   <si>
     <t xml:space="preserve">Bebek Disco Seturan </t>
   </si>
   <si>
-    <t>Jl. Seturan Raya, Kledokan, Caturtunggal, Kec. Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
-  </si>
-  <si>
-    <t>https://maps.app.goo.gl/8jP7p8idJp7mRe8E8</t>
-  </si>
-  <si>
-    <t>R027.jpg</t>
-  </si>
-  <si>
     <t>R028</t>
   </si>
   <si>
@@ -549,99 +291,33 @@
     <t xml:space="preserve">Selasa - Minggu </t>
   </si>
   <si>
-    <t xml:space="preserve"> Jl. Nusa Indah II, Dero, Condongcatur, Kec. Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
-  </si>
-  <si>
-    <t>https://maps.app.goo.gl/8AzpC7NaaWZVtmYx5</t>
-  </si>
-  <si>
-    <t>R028.jpg</t>
-  </si>
-  <si>
     <t>R029</t>
   </si>
   <si>
     <t xml:space="preserve">Soto Ayam Anton Khas Wonosari </t>
   </si>
   <si>
-    <t xml:space="preserve">7.00 AM - 12.00 PM </t>
-  </si>
-  <si>
-    <t>Komplek Ruko, Puluhdadi No.B 30, Kledokan, Caturtunggal, Kec. Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
-  </si>
-  <si>
-    <t>https://maps.app.goo.gl/Xvaw52o9zDGb7w1X6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">R029.jpg </t>
-  </si>
-  <si>
     <t>R030</t>
   </si>
   <si>
-    <t xml:space="preserve">11.00 AM - 03.00 AM </t>
-  </si>
-  <si>
-    <t>Gg. Puluhdadi Seturan Kios B28, Kledokan, Caturtunggal, Kec. Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
-  </si>
-  <si>
-    <t>https://maps.app.goo.gl/HtN9HV2g3EC2E6Yw6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">R030.jpg </t>
-  </si>
-  <si>
     <t>R031</t>
   </si>
   <si>
     <t>Soto Ayam "Simbok 1"</t>
   </si>
   <si>
-    <t xml:space="preserve">06.00 AM - 18.00 PM </t>
-  </si>
-  <si>
-    <t>Jl. Tasura, Jenengan, Maguwoharjo, Kec. Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55282</t>
-  </si>
-  <si>
-    <t>https://maps.app.goo.gl/RGsFBLKN9Tvhmdrh9</t>
-  </si>
-  <si>
-    <t>R031.jpg</t>
-  </si>
-  <si>
     <t>R032</t>
   </si>
   <si>
     <t xml:space="preserve">Padang Murah </t>
   </si>
   <si>
-    <t xml:space="preserve">08. 00 AM - 22.00 PM </t>
-  </si>
-  <si>
-    <t>Jl. Raya Kledokan No.23, Kledokan, Caturtunggal, Kec. Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
-  </si>
-  <si>
-    <t>https://maps.app.goo.gl/w3uwETVrBeL8kocJ8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">R032.jpg </t>
-  </si>
-  <si>
     <t>R033</t>
   </si>
   <si>
     <t>Sambel Cowek (Sambel Colek)</t>
   </si>
   <si>
-    <t xml:space="preserve">09.00 AM - 23.00 PM </t>
-  </si>
-  <si>
-    <t>Jl. Perumnas Seturan, Kledokan, Caturtunggal, Kec. Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
-  </si>
-  <si>
-    <t>https://maps.app.goo.gl/vByGQcCKFUbyUWs8A</t>
-  </si>
-  <si>
     <t xml:space="preserve">R033jpg </t>
   </si>
   <si>
@@ -651,254 +327,980 @@
     <t>Mie Ayam &amp; Bakso Sempurna Wonogiri</t>
   </si>
   <si>
-    <t xml:space="preserve">08.30 AM - 21.00 PM </t>
-  </si>
-  <si>
-    <t>Jl. Perumnas No.127, Tempel, Caturtunggal, Kec. Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
-  </si>
-  <si>
-    <t>https://maps.app.goo.gl/km35JL3uhPDCb4f26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">R034.jpg </t>
-  </si>
-  <si>
     <t>R035</t>
   </si>
   <si>
     <t>Nasi Telur Bahagia</t>
   </si>
   <si>
-    <t>09.30 AM - 10.00 PM</t>
-  </si>
-  <si>
-    <t>Jl. Perumnas No.141, Nologaten, Caturtunggal, Depok, Sleman Regency, Special Region of Yogyakarta 55281</t>
-  </si>
-  <si>
-    <t>https://maps.app.goo.gl/Me5yN67UAteqpGdY9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">R035.jpg </t>
-  </si>
-  <si>
-    <t>-7.774018451332347</t>
-  </si>
-  <si>
-    <t>110.38277142667721</t>
-  </si>
-  <si>
-    <t>-7.766598323121821</t>
-  </si>
-  <si>
-    <t>110.39630308280208</t>
-  </si>
-  <si>
-    <t>-7.748198351154356</t>
-  </si>
-  <si>
-    <t>110.39501674047217</t>
-  </si>
-  <si>
-    <t>-7.7649353526519755</t>
-  </si>
-  <si>
-    <t>110.3965513539671</t>
-  </si>
-  <si>
-    <t>-7.760414033672402</t>
-  </si>
-  <si>
-    <t>110.38289718095653</t>
-  </si>
-  <si>
-    <t>-7.767364427487958</t>
-  </si>
-  <si>
-    <t>110.40336234047223</t>
-  </si>
-  <si>
-    <t>-7.762219151339312</t>
-  </si>
-  <si>
-    <t>110.40609814061278</t>
-  </si>
-  <si>
-    <t>-7.758753747337649</t>
-  </si>
-  <si>
-    <t>110.40544786746183</t>
-  </si>
-  <si>
-    <t>-7.773185859499051</t>
-  </si>
-  <si>
-    <t>110.41127732513222</t>
-  </si>
-  <si>
-    <t>-7.773975478353483</t>
-  </si>
-  <si>
-    <t>110.41303351163725</t>
-  </si>
-  <si>
-    <t>-7.756148878671714</t>
-  </si>
-  <si>
-    <t>110.36666459445149</t>
-  </si>
-  <si>
-    <t>-7.78105070111518</t>
-  </si>
-  <si>
-    <t>110.41611792513211</t>
-  </si>
-  <si>
-    <t>-7.778998591556486</t>
-  </si>
-  <si>
-    <t>110.41645029860855</t>
-  </si>
-  <si>
-    <t>-7.744848444541496</t>
-  </si>
-  <si>
-    <t>110.39722782697724</t>
-  </si>
-  <si>
-    <t>-7.772147381587484</t>
-  </si>
-  <si>
-    <t>110.38255056017287</t>
-  </si>
-  <si>
-    <t>-7.773801908510043</t>
-  </si>
-  <si>
-    <t>110.38244608095673</t>
-  </si>
-  <si>
-    <t>-7.763588204383579</t>
-  </si>
-  <si>
-    <t>110.38656631163735</t>
-  </si>
-  <si>
-    <t>-7.778643299714027</t>
-  </si>
-  <si>
-    <t>110.40153840794645</t>
-  </si>
-  <si>
-    <t>-7.774072757500694</t>
-  </si>
-  <si>
-    <t>110.4089132386269</t>
-  </si>
-  <si>
-    <t>-7.7487586601315295</t>
-  </si>
-  <si>
-    <t>110.38680614047226</t>
-  </si>
-  <si>
-    <t>-7.755653254637142</t>
-  </si>
-  <si>
-    <t>110.40513369629689</t>
-  </si>
-  <si>
-    <t>-7.763446834820035</t>
-  </si>
-  <si>
-    <t>110.4074531962969</t>
-  </si>
-  <si>
-    <t>-7.763308506670925</t>
-  </si>
-  <si>
-    <t>110.40895518040409</t>
-  </si>
-  <si>
-    <t>-7.793779749086242</t>
-  </si>
-  <si>
-    <t>110.4066409251323</t>
-  </si>
-  <si>
-    <t>-7.755166261556854</t>
-  </si>
-  <si>
-    <t>110.39649766645391</t>
-  </si>
-  <si>
-    <t>-7.77696423193207</t>
-  </si>
-  <si>
-    <t>110.4082001376189</t>
-  </si>
-  <si>
-    <t>-7.773704851301657</t>
-  </si>
-  <si>
-    <t>110.408922011336</t>
-  </si>
-  <si>
-    <t>-7.755404200161589</t>
-  </si>
-  <si>
-    <t>110.40998792227738</t>
-  </si>
-  <si>
-    <t>-7.7650364676061825</t>
-  </si>
-  <si>
-    <t>110.41125753432115</t>
-  </si>
-  <si>
     <t xml:space="preserve">Bebek Senjay Seturan </t>
   </si>
   <si>
-    <t>-7.765137937154172</t>
-  </si>
-  <si>
-    <t>110.4111947343212</t>
-  </si>
-  <si>
-    <t>-7.762639622774797</t>
-  </si>
-  <si>
-    <t>110.42252795295988</t>
-  </si>
-  <si>
-    <t>-7.77473843142309</t>
-  </si>
-  <si>
-    <t>110.40866228736111</t>
-  </si>
-  <si>
-    <t>-7.77216168031367</t>
-  </si>
-  <si>
-    <t>110.40528626645401</t>
-  </si>
-  <si>
-    <t>-7.777458308996077</t>
-  </si>
-  <si>
-    <t>110.40528428637276</t>
-  </si>
-  <si>
-    <t>-7.776196931971200</t>
-  </si>
-  <si>
-    <t>110.4045624648450</t>
+    <t>Jl, Kuningan, Karang Malang, Caturtunggal, Kec, Depok, Kab, Sleman, DIY 55281</t>
+  </si>
+  <si>
+    <t>-7,774018451332347</t>
+  </si>
+  <si>
+    <t>110,38277142667721</t>
+  </si>
+  <si>
+    <t>https://maps,app,goo,gl/iqZ4GBhxDdnmiKFh9</t>
+  </si>
+  <si>
+    <t>R001,jpg</t>
+  </si>
+  <si>
+    <t>RP 1-25,000</t>
+  </si>
+  <si>
+    <t>Jalan Tantular, Kaliwaru, Condongcatur, Kec, Depok, Kab, Sleman, DIY 55281</t>
+  </si>
+  <si>
+    <t>-7,766598323121821</t>
+  </si>
+  <si>
+    <t>110,39630308280208</t>
+  </si>
+  <si>
+    <t>https://maps,app,goo,gl/RYeTdPUprhVZbWQj7</t>
+  </si>
+  <si>
+    <t>R002,jpg</t>
+  </si>
+  <si>
+    <t>Jl, Sengkan Gg, Sadewa No,02, Kocoran, Condongcatur, Kec, Depok, Kab, Sleman, DIY 55283</t>
+  </si>
+  <si>
+    <t>-7,748198351154356</t>
+  </si>
+  <si>
+    <t>110,39501674047217</t>
+  </si>
+  <si>
+    <t>https://maps,app,goo,gl/dE8ZDETqJrKnrMYT7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R003,jpg </t>
+  </si>
+  <si>
+    <t>Gg, Jemb, Merah No,116 D, Kaliwaru, Condongcatur, Kec, Depok, Kab, Sleman, DIY 55283</t>
+  </si>
+  <si>
+    <t>-7,7649353526519755</t>
+  </si>
+  <si>
+    <t>110,3965513539671</t>
+  </si>
+  <si>
+    <t>https://maps,app,goo,gl/4ZpaPxZ7B6SoaFbN7</t>
+  </si>
+  <si>
+    <t>R004,jpg</t>
+  </si>
+  <si>
+    <t>Blok B-5, Karangwuni, Manggung, Caturtunggal, Kec, Depok, Kab, Sleman, DIY 55281</t>
+  </si>
+  <si>
+    <t>-7,760414033672402</t>
+  </si>
+  <si>
+    <t>110,38289718095653</t>
+  </si>
+  <si>
+    <t>https://maps,app,goo,gl/o6JYaCCD2E2qbBNu5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R005,jpg </t>
+  </si>
+  <si>
+    <t>Dabag, Condongcatur, Kec, Depok, Kab, Sleman, DIY 55281</t>
+  </si>
+  <si>
+    <t>-7,767364427487958</t>
+  </si>
+  <si>
+    <t>110,40336234047223</t>
+  </si>
+  <si>
+    <t>https://maps,app,goo,gl/jccDdukmCYNKPAUo8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R006,jpg </t>
+  </si>
+  <si>
+    <t>Ruko Gorongan, Jl, Perumnas, Ngropoh, Condongcatur, Kec, Depok, Kab, Sleman, DIY 55283</t>
+  </si>
+  <si>
+    <t>-7,762219151339312</t>
+  </si>
+  <si>
+    <t>110,40609814061278</t>
+  </si>
+  <si>
+    <t>https://maps,app,goo,gl/y2apQpo5v9a8eD8R7</t>
+  </si>
+  <si>
+    <t>R007,jpg</t>
+  </si>
+  <si>
+    <t>Warung Makan Mr, B</t>
+  </si>
+  <si>
+    <t>Jl, Cemp, No,231, Perumnas Condong Catur, Condongcatur, Kec, Depok, Kab, Sleman, DIY 55281</t>
+  </si>
+  <si>
+    <t>-7,758753747337649</t>
+  </si>
+  <si>
+    <t>110,40544786746183</t>
+  </si>
+  <si>
+    <t>https://maps,app,goo,gl/JmsiDm3tz18g7duD8</t>
+  </si>
+  <si>
+    <t>R008,jpg</t>
+  </si>
+  <si>
+    <t>Ruko Babarsari, Jl, Raya Kledokan, Caturtunggal, Kec, Depok, Kab, Sleman, DIY 55281</t>
+  </si>
+  <si>
+    <t>-7,773185859499051</t>
+  </si>
+  <si>
+    <t>110,41127732513222</t>
+  </si>
+  <si>
+    <t>https://maps,app,goo,gl/AVSE3ECfkHPPmucS8</t>
+  </si>
+  <si>
+    <t>R009,jpg</t>
+  </si>
+  <si>
+    <t>Ruko Babarsari, Jl, Babarsari, Tambak Bayan, Caturtunggal, Kec, Depok, Kab, Sleman, DIY 55281</t>
+  </si>
+  <si>
+    <t>-7,773975478353483</t>
+  </si>
+  <si>
+    <t>110,41303351163725</t>
+  </si>
+  <si>
+    <t>https://maps,app,goo,gl/SWHzXXXf3SMQ8tA96</t>
+  </si>
+  <si>
+    <t>R010,jpg</t>
+  </si>
+  <si>
+    <t>11:30 AM – 22,30 PM</t>
+  </si>
+  <si>
+    <t>Jl, Rusunawa Mranggen, Kutu Tegal, Sinduadi, Kec, Mlati, Kab, Sleman, DIY 55284</t>
+  </si>
+  <si>
+    <t>-7,756148878671714</t>
+  </si>
+  <si>
+    <t>110,36666459445149</t>
+  </si>
+  <si>
+    <t>https://maps,app,goo,gl/945xB7PkevoCExYc8</t>
+  </si>
+  <si>
+    <t>R011,jpg</t>
+  </si>
+  <si>
+    <t>Jl, Babarsari I No,13, Janti, Caturtunggal, Kec, Depok, Kab, Sleman, DIY 55281</t>
+  </si>
+  <si>
+    <t>-7,78105070111518</t>
+  </si>
+  <si>
+    <t>110,41611792513211</t>
+  </si>
+  <si>
+    <t>https://maps,app,goo,gl/rPTxmt9UDxHS23n19</t>
+  </si>
+  <si>
+    <t>R012,jpg</t>
+  </si>
+  <si>
+    <t>Ruko Babarsari BBC Plaza, Jl, Tambak Bayan, Janti, Caturtunggal, Kec, Depok, Kab, Sleman, DIY 55281</t>
+  </si>
+  <si>
+    <t>-7,778998591556486</t>
+  </si>
+  <si>
+    <t>110,41645029860855</t>
+  </si>
+  <si>
+    <t>https://maps,app,goo,gl/L6iTqLFFDM966Tmd6</t>
+  </si>
+  <si>
+    <t>R013,jpg</t>
+  </si>
+  <si>
+    <t>Jl, Gambuh No,3, Manukan, Condongcatur, Kec, Depok, Kab, Sleman, DIY 52000</t>
+  </si>
+  <si>
+    <t>-7,744848444541496</t>
+  </si>
+  <si>
+    <t>110,39722782697724</t>
+  </si>
+  <si>
+    <t>https://maps,app,goo,gl/fczoo46dnKmpCCLX7</t>
+  </si>
+  <si>
+    <t>R014,jpg</t>
+  </si>
+  <si>
+    <t>-7,772147381587484</t>
+  </si>
+  <si>
+    <t>110,38255056017287</t>
+  </si>
+  <si>
+    <t>https://maps,app,goo,gl/frbqQuNvtPqtGRbZ9</t>
+  </si>
+  <si>
+    <t>R015,jpg</t>
+  </si>
+  <si>
+    <t>-7,773801908510043</t>
+  </si>
+  <si>
+    <t>110,38244608095673</t>
+  </si>
+  <si>
+    <t>https://maps,app,goo,gl/GyqJjnQwoYZo9MUv6</t>
+  </si>
+  <si>
+    <t>R016,jpg</t>
+  </si>
+  <si>
+    <t>Karang Wuni, Caturtunggal, Kec, Depok, Kab, Sleman, DIY 55281</t>
+  </si>
+  <si>
+    <t>-7,763588204383579</t>
+  </si>
+  <si>
+    <t>110,38656631163735</t>
+  </si>
+  <si>
+    <t>https://maps,app,goo,gl/fK5qaQbLaG5pV3qK7</t>
+  </si>
+  <si>
+    <t>R017,jpg</t>
+  </si>
+  <si>
+    <t>Jalan Kapulogo, Nologaten, Caturtunggal, Kec, Depok, Kab, Sleman, DIY 55281</t>
+  </si>
+  <si>
+    <t>-7,778643299714027</t>
+  </si>
+  <si>
+    <t>110,40153840794645</t>
+  </si>
+  <si>
+    <t>https://maps,app,goo,gl/rfQ7La7Wdc5Ghyuw6</t>
+  </si>
+  <si>
+    <t>R018,jpg</t>
+  </si>
+  <si>
+    <t>Ruko DTA Square, Jl, Seturan Raya, Kledokan, Caturtunggal, Kec, Depok, Kab, Sleman, DIY 55281</t>
+  </si>
+  <si>
+    <t>-7,774072757500694</t>
+  </si>
+  <si>
+    <t>110,4089132386269</t>
+  </si>
+  <si>
+    <t>https://maps,app,goo,gl/Um2cFZ7P8u8Y3MLC9</t>
+  </si>
+  <si>
+    <t>R019,jpg</t>
+  </si>
+  <si>
+    <t>Jl, Kaliurang No,17 Km,6, Kentungan, Condongcatur, Kec, Depok, Kab, Sleman, DIY 55284</t>
+  </si>
+  <si>
+    <t>-7,7487586601315295</t>
+  </si>
+  <si>
+    <t>110,38680614047226</t>
+  </si>
+  <si>
+    <t>https://maps,app,goo,gl/8WpRE1ayxfZ9wkC86</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R020,jpg </t>
+  </si>
+  <si>
+    <t>Jl, Apokat, Perumnas Condong Catur, Condongcatur, Kec, Depok, Kab, Sleman, DIY 55283</t>
+  </si>
+  <si>
+    <t>-7,755653254637142</t>
+  </si>
+  <si>
+    <t>110,40513369629689</t>
+  </si>
+  <si>
+    <t>https://maps,app,goo,gl/cAwMBmPVwPjQhV8b8</t>
+  </si>
+  <si>
+    <t>R021,jpg</t>
+  </si>
+  <si>
+    <t>Jl, Pintu Selatan UPN, Ngropoh, Condongcatur, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
+  </si>
+  <si>
+    <t>-7,763446834820035</t>
+  </si>
+  <si>
+    <t>110,4074531962969</t>
+  </si>
+  <si>
+    <t>https://maps,app,goo,gl/SQeZppWwHGojvCoYA</t>
+  </si>
+  <si>
+    <t>R022,jpg</t>
+  </si>
+  <si>
+    <t>9,00 AM - 21,00 PM</t>
+  </si>
+  <si>
+    <t>Jl, Perumnas Jl, Pintu Selatan UPN No,15, Ngropoh, Condongcatur, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
+  </si>
+  <si>
+    <t>-7.763824775595378</t>
+  </si>
+  <si>
+    <t>110.40860162599286</t>
+  </si>
+  <si>
+    <t>https://maps,app,goo,gl/MyMuo6xx6rSZSYn6A</t>
+  </si>
+  <si>
+    <t>R023,jpg</t>
+  </si>
+  <si>
+    <t>9,00 AM - 23,30 PM</t>
+  </si>
+  <si>
+    <t>Jl, Sorowajan No,208, Sorowajan, Banguntapan, Kec, Banguntapan, Kabupaten Bantul, Daerah Istimewa Yogyakarta 55198</t>
+  </si>
+  <si>
+    <t>-7,793779749086242</t>
+  </si>
+  <si>
+    <t>110,4066409251323</t>
+  </si>
+  <si>
+    <t>https://maps,app,goo,gl/GGv45FujGN5yNHwcA</t>
+  </si>
+  <si>
+    <t>R024,jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8,00 AM - 22,00 PM </t>
+  </si>
+  <si>
+    <t>Ruko Kelapa Hijau, Jl, Brojomulyo No,10, Gejayan, Condongcatur, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
+  </si>
+  <si>
+    <t>-7,755166261556854</t>
+  </si>
+  <si>
+    <t>110,39649766645391</t>
+  </si>
+  <si>
+    <t>https://maps,app,goo,gl/xKX6kRSfFGRUAG9A8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R025,jpg </t>
+  </si>
+  <si>
+    <t xml:space="preserve">10,00 AM - 22,00 PM </t>
+  </si>
+  <si>
+    <t>Jl, Kemuning No,1b, Candok, Condongcatur, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
+  </si>
+  <si>
+    <t>-7,77696423193207</t>
+  </si>
+  <si>
+    <t>110,4082001376189</t>
+  </si>
+  <si>
+    <t>https://maps,app,goo,gl/Tm28gLkjwDSy5e776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R026,jpg </t>
+  </si>
+  <si>
+    <t>Jl, Seturan Raya, Kledokan, Caturtunggal, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
+  </si>
+  <si>
+    <t>-7,773704851301657</t>
+  </si>
+  <si>
+    <t>110,408922011336</t>
+  </si>
+  <si>
+    <t>https://maps,app,goo,gl/8jP7p8idJp7mRe8E8</t>
+  </si>
+  <si>
+    <t>R027,jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Jl, Nusa Indah II, Dero, Condongcatur, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
+  </si>
+  <si>
+    <t>-7,755404200161589</t>
+  </si>
+  <si>
+    <t>110,40998792227738</t>
+  </si>
+  <si>
+    <t>https://maps,app,goo,gl/8AzpC7NaaWZVtmYx5</t>
+  </si>
+  <si>
+    <t>R028,jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7,00 AM - 12,00 PM </t>
+  </si>
+  <si>
+    <t>Komplek Ruko, Puluhdadi No,B 30, Kledokan, Caturtunggal, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
+  </si>
+  <si>
+    <t>-7,7650364676061825</t>
+  </si>
+  <si>
+    <t>110,41125753432115</t>
+  </si>
+  <si>
+    <t>https://maps,app,goo,gl/Xvaw52o9zDGb7w1X6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R029,jpg </t>
+  </si>
+  <si>
+    <t xml:space="preserve">11,00 AM - 03,00 AM </t>
+  </si>
+  <si>
+    <t>Gg, Puluhdadi Seturan Kios B28, Kledokan, Caturtunggal, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
+  </si>
+  <si>
+    <t>-7,765137937154172</t>
+  </si>
+  <si>
+    <t>110,4111947343212</t>
+  </si>
+  <si>
+    <t>https://maps,app,goo,gl/HtN9HV2g3EC2E6Yw6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R030,jpg </t>
+  </si>
+  <si>
+    <t xml:space="preserve">06,00 AM - 18,00 PM </t>
+  </si>
+  <si>
+    <t>Jl, Tasura, Jenengan, Maguwoharjo, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55282</t>
+  </si>
+  <si>
+    <t>-7,762639622774797</t>
+  </si>
+  <si>
+    <t>110,42252795295988</t>
+  </si>
+  <si>
+    <t>https://maps,app,goo,gl/RGsFBLKN9Tvhmdrh9</t>
+  </si>
+  <si>
+    <t>R031,jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">08, 00 AM - 22,00 PM </t>
+  </si>
+  <si>
+    <t>Jl, Raya Kledokan No,23, Kledokan, Caturtunggal, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
+  </si>
+  <si>
+    <t>-7,77473843142309</t>
+  </si>
+  <si>
+    <t>110,40866228736111</t>
+  </si>
+  <si>
+    <t>https://maps,app,goo,gl/w3uwETVrBeL8kocJ8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R032,jpg </t>
+  </si>
+  <si>
+    <t xml:space="preserve">09,00 AM - 23,00 PM </t>
+  </si>
+  <si>
+    <t>Jl, Perumnas Seturan, Kledokan, Caturtunggal, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
+  </si>
+  <si>
+    <t>-7,77216168031367</t>
+  </si>
+  <si>
+    <t>110,40528626645401</t>
+  </si>
+  <si>
+    <t>https://maps,app,goo,gl/vByGQcCKFUbyUWs8A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">08,30 AM - 21,00 PM </t>
+  </si>
+  <si>
+    <t>Jl, Perumnas No,127, Tempel, Caturtunggal, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
+  </si>
+  <si>
+    <t>-7,777458308996077</t>
+  </si>
+  <si>
+    <t>110,40528428637276</t>
+  </si>
+  <si>
+    <t>https://maps,app,goo,gl/km35JL3uhPDCb4f26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R034,jpg </t>
+  </si>
+  <si>
+    <t>09,30 AM - 10,00 PM</t>
+  </si>
+  <si>
+    <t>Jl, Perumnas No,141, Nologaten, Caturtunggal, Depok, Sleman Regency, Special Region of Yogyakarta 55281</t>
+  </si>
+  <si>
+    <t>-7,776196931971200</t>
+  </si>
+  <si>
+    <t>110,4045624648450</t>
+  </si>
+  <si>
+    <t>https://maps,app,goo,gl/Me5yN67UAteqpGdY9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R035,jpg </t>
+  </si>
+  <si>
+    <t>R036</t>
+  </si>
+  <si>
+    <t>Warung Makan Mahasiswa Ambarrukmo</t>
+  </si>
+  <si>
+    <t>08,00 - 19,00</t>
+  </si>
+  <si>
+    <t>Jl, Ambar Asri No,311, Ambarukmo, Caturtunggal, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
+  </si>
+  <si>
+    <t>-7,78261665177125</t>
+  </si>
+  <si>
+    <t>110,39953130466868</t>
+  </si>
+  <si>
+    <t>https://maps,app,goo,gl/7ZxoNc54UJ2ZkLf39</t>
+  </si>
+  <si>
+    <t>R036,jpg</t>
+  </si>
+  <si>
+    <t>R037</t>
+  </si>
+  <si>
+    <t>Mie Gacoan Babarsari</t>
+  </si>
+  <si>
+    <t>Ruko Rafflesia, Jl, Babarsari, Janti, Caturtunggal, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
+  </si>
+  <si>
+    <t>-7,779288337303048</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 110,41530143843262</t>
+  </si>
+  <si>
+    <t>https://maps,app,goo,gl/yYLSC9uJhWDgQUph8</t>
+  </si>
+  <si>
+    <t>R037,jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ya </t>
+  </si>
+  <si>
+    <t>R038</t>
+  </si>
+  <si>
+    <t>Warung Makan Depot Ibu Tiara</t>
+  </si>
+  <si>
+    <t>07,00 - 22,00</t>
+  </si>
+  <si>
+    <t>6CM6+85F, Jl, Seturan Raya, Kledokan, Caturtunggal, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
+  </si>
+  <si>
+    <t>-7,7667012046934865</t>
+  </si>
+  <si>
+    <t>110,41036731114856</t>
+  </si>
+  <si>
+    <t>https://maps,app,goo,gl/VzBnzzQmzfrSBWo9A</t>
+  </si>
+  <si>
+    <t>R038,jpg</t>
+  </si>
+  <si>
+    <t>R039</t>
+  </si>
+  <si>
+    <t>Surasa Kuliner (꧋ꦱꦸꦫꦱꦏꦸꦭꦶꦤꦺꦂ)</t>
+  </si>
+  <si>
+    <t>Senin - Sabtu</t>
+  </si>
+  <si>
+    <t>11,00 - 20,00</t>
+  </si>
+  <si>
+    <t>Jl, Babarsari I No,13, Janti, Caturtunggal, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
+  </si>
+  <si>
+    <t>-7,780851926155481</t>
+  </si>
+  <si>
+    <t>110,41606370772861</t>
+  </si>
+  <si>
+    <t>https://maps,app,goo,gl/bujMvFPKLoa6rspp7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R039,jpg </t>
+  </si>
+  <si>
+    <t>R040</t>
+  </si>
+  <si>
+    <t>Pecel Lele Bu Lestari</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rumah Makan,Lesehan </t>
+  </si>
+  <si>
+    <t>11,00 - 00,00</t>
+  </si>
+  <si>
+    <t>Gg, Shinta, Nayan, Maguwoharjo, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
+  </si>
+  <si>
+    <t>-7,77893232620335</t>
+  </si>
+  <si>
+    <t>110,42400796597617</t>
+  </si>
+  <si>
+    <t>https://maps,app,goo,gl/2RH5jEc9g64fvsgb7</t>
+  </si>
+  <si>
+    <t>R040,jpg</t>
+  </si>
+  <si>
+    <t>R041</t>
+  </si>
+  <si>
+    <t>Mie Ayam &amp; Bakso Purnami Jempol Sari Roso Jatiayu</t>
+  </si>
+  <si>
+    <t>10,00 - 18,00</t>
+  </si>
+  <si>
+    <t>Jl, P, Diponegoro, Sembego, Maguwoharjo, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
+  </si>
+  <si>
+    <t>-7,761847045353668</t>
+  </si>
+  <si>
+    <t>110,43943841946138</t>
+  </si>
+  <si>
+    <t>https://maps,app,goo,gl/4NFp2jRiWyogCHd3A</t>
+  </si>
+  <si>
+    <t>R041,jpg</t>
+  </si>
+  <si>
+    <t>R042</t>
+  </si>
+  <si>
+    <t>Tokyo Rock</t>
+  </si>
+  <si>
+    <t>Restoran Jepang</t>
+  </si>
+  <si>
+    <t>11,00 - 22,00</t>
+  </si>
+  <si>
+    <t>Jl, Palagan Tentara Pelajar No,59, Jongkang, Sariharjo, Kec, Ngaglik, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55581</t>
+  </si>
+  <si>
+    <t>-7,743,587,559,412,390</t>
+  </si>
+  <si>
+    <t>110,37401676139700</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/emcC92RrHoX8udwV7</t>
+  </si>
+  <si>
+    <t>R042,jpg</t>
+  </si>
+  <si>
+    <t>Rp 25–50 rb</t>
+  </si>
+  <si>
+    <t>R043</t>
+  </si>
+  <si>
+    <t>Sugoi Ramen Express</t>
+  </si>
+  <si>
+    <t>Restoran Ramen</t>
+  </si>
+  <si>
+    <t>11,00 - 23,30</t>
+  </si>
+  <si>
+    <t>Ruko Kelapa Hijau No, 18, Sanggrahan, Condongcatur, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55283</t>
+  </si>
+  <si>
+    <t>-7,7535380574479000</t>
+  </si>
+  <si>
+    <t>110,39710521673956</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/AvZHK7bAeCfGpBNJ7</t>
+  </si>
+  <si>
+    <t>R043,jpg</t>
+  </si>
+  <si>
+    <t>R044</t>
+  </si>
+  <si>
+    <t>Tottori_ID Japanese Fusion Food - Restaurant - Mrican</t>
+  </si>
+  <si>
+    <t>12,00 - 21,00</t>
+  </si>
+  <si>
+    <t>Jl, Gatotkaca No,1G, Santren, Caturtunggal, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
+  </si>
+  <si>
+    <t>-7,771694983656591</t>
+  </si>
+  <si>
+    <t>110,39133310283543</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/qytFbXEommQHkbe79</t>
+  </si>
+  <si>
+    <t>R044,jpg</t>
+  </si>
+  <si>
+    <t>R045</t>
+  </si>
+  <si>
+    <t>Sederhana Murah</t>
+  </si>
+  <si>
+    <t>Restoran Padang</t>
+  </si>
+  <si>
+    <t>08,30–22,00</t>
+  </si>
+  <si>
+    <t>Jl, Monjali No,99 49, Kutu Dukuh, Sinduadi, Kec, Mlati, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55284</t>
+  </si>
+  <si>
+    <t>-7,757918567368756</t>
+  </si>
+  <si>
+    <t>110,3693590993285</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/4JX1thPL8hmzb5FZ6</t>
+  </si>
+  <si>
+    <t>R045,jpg</t>
+  </si>
+  <si>
+    <t>R046</t>
+  </si>
+  <si>
+    <t>Ceplok Telor Babarsari</t>
+  </si>
+  <si>
+    <t>08,30–21,00</t>
+  </si>
+  <si>
+    <t>Jl, Babarsari No,15, Janti, Caturtunggal, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
+  </si>
+  <si>
+    <t>7,779724632145041</t>
+  </si>
+  <si>
+    <t>110,41522422762888</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/nXyZFaZFVdjNWZYcA</t>
+  </si>
+  <si>
+    <t>R046.jpg</t>
+  </si>
+  <si>
+    <t>R047</t>
+  </si>
+  <si>
+    <t>10.00 - 21.30</t>
+  </si>
+  <si>
+    <t>Ruko Gorongan, Jl. Perumnas, Ngropoh, Condongcatur, Kec. Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55283</t>
+  </si>
+  <si>
+    <t>-7.762796291952466</t>
+  </si>
+  <si>
+    <t>110.40641496098354</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/kYs4uBRbRfcX9mZAA</t>
+  </si>
+  <si>
+    <t>R047.jpg</t>
+  </si>
+  <si>
+    <t>R048</t>
+  </si>
+  <si>
+    <t>Dewi Ratih Lesehan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rumah Makan, Lesehan </t>
+  </si>
+  <si>
+    <t xml:space="preserve">07.00 - 22.00 </t>
+  </si>
+  <si>
+    <t>Jalan Apokat, Klebengan, Blok CT VIII, Kocoran, Caturtunggal, Kec. Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
+  </si>
+  <si>
+    <t>-7.764957074917656</t>
+  </si>
+  <si>
+    <t>110.3850257203493</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/cNotW79g7kypc9dM6</t>
+  </si>
+  <si>
+    <t>R048.jpg</t>
+  </si>
+  <si>
+    <t>R049</t>
+  </si>
+  <si>
+    <t>Warung Mie Ayam &amp; Bakso "Sumber Rejeki"</t>
+  </si>
+  <si>
+    <t>11.00 - 21.30</t>
+  </si>
+  <si>
+    <t>Jl. Utama Pugeran RT07 RW65, Pugeran, Maguwoharjo, Kec. Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55282</t>
+  </si>
+  <si>
+    <t>-7.766725321038907</t>
+  </si>
+  <si>
+    <t>110.42228570515304</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/oM63Gc12DbSpE7Ez6</t>
+  </si>
+  <si>
+    <t>R049.jpg</t>
+  </si>
+  <si>
+    <t>R050</t>
+  </si>
+  <si>
+    <t>Penyetan Mas Kobis</t>
+  </si>
+  <si>
+    <t>Rumah Makan</t>
+  </si>
+  <si>
+    <t>Jl. Nangka III Jl. Utama No.RT 7, Pugeran, Maguwoharjo, Kec. Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55282</t>
+  </si>
+  <si>
+    <t>-7.767939879922977</t>
+  </si>
+  <si>
+    <t>110.42454781844948</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/tTzzxmnLWbe9s5eo8</t>
+  </si>
+  <si>
+    <t>R050.jpg</t>
+  </si>
+  <si>
+    <t>R051</t>
+  </si>
+  <si>
+    <t>Warung Indomie Bersama WIB Tambakboyo (Warmindo)</t>
+  </si>
+  <si>
+    <t>17.00 - 02.00</t>
+  </si>
+  <si>
+    <t>Jl. Kaswari No.98, Ngringin, Condongcatur, Kec. Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55283</t>
+  </si>
+  <si>
+    <t>-7.756559272784034</t>
+  </si>
+  <si>
+    <t>110.41265205902258</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/UmdgsovKjfk3nhGT8</t>
+  </si>
+  <si>
+    <t>R051.jpg</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -960,6 +1362,12 @@
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF5E5E5E"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -985,16 +1393,16 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF000000"/>
+        <color indexed="64"/>
       </left>
       <right style="thin">
-        <color rgb="FF000000"/>
+        <color indexed="64"/>
       </right>
       <top style="thin">
-        <color rgb="FF000000"/>
+        <color indexed="64"/>
       </top>
       <bottom style="thin">
-        <color rgb="FF000000"/>
+        <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1003,23 +1411,25 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1029,6 +1439,31 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1344,7 +1779,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D2879120-B48A-4F1A-810E-C87B5DAC68ED}">
-  <dimension ref="A1:M36"/>
+  <dimension ref="A1:M52"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="5.77734375" bestFit="1" customWidth="1"/>
@@ -1420,77 +1855,77 @@
         <v>17</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>18</v>
+        <v>100</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>215</v>
+        <v>101</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>216</v>
+        <v>102</v>
       </c>
       <c r="I2" s="4">
         <v>4.8</v>
       </c>
       <c r="J2" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="K2" s="8" t="s">
-        <v>20</v>
+        <v>103</v>
+      </c>
+      <c r="K2" s="5" t="s">
+        <v>104</v>
       </c>
       <c r="L2" s="4" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="M2" s="4" t="s">
-        <v>22</v>
+        <v>105</v>
       </c>
     </row>
     <row r="3" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C3" s="5" t="s">
         <v>15</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>27</v>
+        <v>106</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>217</v>
+        <v>107</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>218</v>
+        <v>108</v>
       </c>
       <c r="I3" s="4">
         <v>4.5</v>
       </c>
       <c r="J3" s="7" t="s">
-        <v>28</v>
+        <v>109</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>29</v>
+        <v>110</v>
       </c>
       <c r="L3" s="4" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="M3" s="4" t="s">
-        <v>22</v>
+        <v>105</v>
       </c>
     </row>
     <row r="4" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C4" s="5" t="s">
         <v>15</v>
@@ -1499,39 +1934,39 @@
         <v>16</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>33</v>
+        <v>111</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>219</v>
+        <v>112</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>220</v>
+        <v>113</v>
       </c>
       <c r="I4" s="4">
         <v>4.7</v>
       </c>
       <c r="J4" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="K4" s="8" t="s">
-        <v>35</v>
+        <v>114</v>
+      </c>
+      <c r="K4" s="5" t="s">
+        <v>115</v>
       </c>
       <c r="L4" s="4" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="M4" s="4" t="s">
-        <v>22</v>
+        <v>105</v>
       </c>
     </row>
     <row r="5" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="C5" s="5" t="s">
         <v>15</v>
@@ -1540,39 +1975,39 @@
         <v>16</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>39</v>
+        <v>116</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>221</v>
+        <v>117</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>222</v>
+        <v>118</v>
       </c>
       <c r="I5" s="4">
         <v>4.5</v>
       </c>
       <c r="J5" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="K5" s="8" t="s">
-        <v>41</v>
+        <v>119</v>
+      </c>
+      <c r="K5" s="5" t="s">
+        <v>120</v>
       </c>
       <c r="L5" s="4" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="M5" s="4" t="s">
-        <v>22</v>
+        <v>105</v>
       </c>
     </row>
     <row r="6" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="C6" s="5" t="s">
         <v>15</v>
@@ -1581,39 +2016,39 @@
         <v>16</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>45</v>
+        <v>121</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>223</v>
+        <v>122</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>224</v>
-      </c>
-      <c r="I6" s="9">
+        <v>123</v>
+      </c>
+      <c r="I6" s="8">
         <v>5</v>
       </c>
       <c r="J6" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="K6" s="8" t="s">
-        <v>47</v>
+        <v>124</v>
+      </c>
+      <c r="K6" s="5" t="s">
+        <v>125</v>
       </c>
       <c r="L6" s="4" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="M6" s="4" t="s">
-        <v>22</v>
+        <v>105</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>15</v>
@@ -1622,39 +2057,39 @@
         <v>16</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>51</v>
+        <v>126</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>225</v>
+        <v>127</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>226</v>
+        <v>128</v>
       </c>
       <c r="I7" s="4">
         <v>4.7</v>
       </c>
       <c r="J7" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="K7" s="8" t="s">
-        <v>53</v>
+        <v>129</v>
+      </c>
+      <c r="K7" s="5" t="s">
+        <v>130</v>
       </c>
       <c r="L7" s="4" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="M7" s="4" t="s">
-        <v>22</v>
+        <v>105</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
-        <v>54</v>
+        <v>35</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="C8" s="5" t="s">
         <v>15</v>
@@ -1663,39 +2098,39 @@
         <v>16</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>56</v>
+        <v>37</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>57</v>
+        <v>131</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>227</v>
+        <v>132</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>228</v>
+        <v>133</v>
       </c>
       <c r="I8" s="4">
         <v>4.3</v>
       </c>
       <c r="J8" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="K8" s="8" t="s">
-        <v>59</v>
+        <v>134</v>
+      </c>
+      <c r="K8" s="5" t="s">
+        <v>135</v>
       </c>
       <c r="L8" s="4" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="M8" s="4" t="s">
-        <v>22</v>
+        <v>105</v>
       </c>
     </row>
     <row r="9" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
-        <v>60</v>
+        <v>38</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>61</v>
+        <v>136</v>
       </c>
       <c r="C9" s="5" t="s">
         <v>15</v>
@@ -1704,39 +2139,39 @@
         <v>16</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>62</v>
+        <v>39</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>63</v>
+        <v>137</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>229</v>
+        <v>138</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>230</v>
+        <v>139</v>
       </c>
       <c r="I9" s="4">
         <v>4.7</v>
       </c>
       <c r="J9" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="K9" s="8" t="s">
-        <v>65</v>
+        <v>140</v>
+      </c>
+      <c r="K9" s="5" t="s">
+        <v>141</v>
       </c>
       <c r="L9" s="4" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="M9" s="4" t="s">
-        <v>22</v>
+        <v>105</v>
       </c>
     </row>
     <row r="10" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
-        <v>66</v>
+        <v>40</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>67</v>
+        <v>41</v>
       </c>
       <c r="C10" s="5" t="s">
         <v>15</v>
@@ -1745,39 +2180,39 @@
         <v>16</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>68</v>
+        <v>142</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>231</v>
+        <v>143</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>232</v>
+        <v>144</v>
       </c>
       <c r="I10" s="4">
         <v>4.8</v>
       </c>
       <c r="J10" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="K10" s="8" t="s">
-        <v>70</v>
+        <v>145</v>
+      </c>
+      <c r="K10" s="5" t="s">
+        <v>146</v>
       </c>
       <c r="L10" s="4" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="M10" s="4" t="s">
-        <v>22</v>
+        <v>105</v>
       </c>
     </row>
     <row r="11" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
-        <v>71</v>
+        <v>42</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>72</v>
+        <v>43</v>
       </c>
       <c r="C11" s="5" t="s">
         <v>15</v>
@@ -1789,36 +2224,36 @@
         <v>11</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>73</v>
+        <v>147</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>233</v>
+        <v>148</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>234</v>
+        <v>149</v>
       </c>
       <c r="I11" s="4">
         <v>3.9</v>
       </c>
       <c r="J11" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="K11" s="8" t="s">
-        <v>75</v>
+        <v>150</v>
+      </c>
+      <c r="K11" s="5" t="s">
+        <v>151</v>
       </c>
       <c r="L11" s="4" t="s">
-        <v>76</v>
+        <v>44</v>
       </c>
       <c r="M11" s="4" t="s">
-        <v>22</v>
+        <v>105</v>
       </c>
     </row>
     <row r="12" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
-        <v>77</v>
+        <v>45</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>78</v>
+        <v>46</v>
       </c>
       <c r="C12" s="5" t="s">
         <v>15</v>
@@ -1827,80 +2262,80 @@
         <v>16</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>79</v>
+        <v>152</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>80</v>
+        <v>153</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>235</v>
+        <v>154</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>236</v>
+        <v>155</v>
       </c>
       <c r="I12" s="4">
         <v>4.4000000000000004</v>
       </c>
       <c r="J12" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="K12" s="8" t="s">
-        <v>82</v>
+        <v>156</v>
+      </c>
+      <c r="K12" s="5" t="s">
+        <v>157</v>
       </c>
       <c r="L12" s="4" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="M12" s="4" t="s">
-        <v>22</v>
+        <v>105</v>
       </c>
     </row>
     <row r="13" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
-        <v>83</v>
+        <v>47</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>84</v>
+        <v>48</v>
       </c>
       <c r="C13" s="5" t="s">
         <v>15</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>85</v>
+        <v>49</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>86</v>
+        <v>50</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>87</v>
+        <v>158</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>237</v>
+        <v>159</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>238</v>
+        <v>160</v>
       </c>
       <c r="I13" s="4">
         <v>4.9000000000000004</v>
       </c>
       <c r="J13" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="K13" s="8" t="s">
-        <v>89</v>
+        <v>161</v>
+      </c>
+      <c r="K13" s="5" t="s">
+        <v>162</v>
       </c>
       <c r="L13" s="4" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="M13" s="4" t="s">
-        <v>22</v>
+        <v>105</v>
       </c>
     </row>
     <row r="14" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
-        <v>90</v>
+        <v>51</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>91</v>
+        <v>52</v>
       </c>
       <c r="C14" s="5" t="s">
         <v>15</v>
@@ -1912,36 +2347,36 @@
         <v>17</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>92</v>
+        <v>163</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>239</v>
+        <v>164</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>240</v>
+        <v>165</v>
       </c>
       <c r="I14" s="4">
         <v>4.4000000000000004</v>
       </c>
       <c r="J14" s="7" t="s">
-        <v>93</v>
-      </c>
-      <c r="K14" s="8" t="s">
-        <v>94</v>
+        <v>166</v>
+      </c>
+      <c r="K14" s="5" t="s">
+        <v>167</v>
       </c>
       <c r="L14" s="4" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="M14" s="4" t="s">
-        <v>22</v>
+        <v>105</v>
       </c>
     </row>
     <row r="15" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A15" s="4" t="s">
-        <v>95</v>
+        <v>53</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>96</v>
+        <v>54</v>
       </c>
       <c r="C15" s="5" t="s">
         <v>15</v>
@@ -1950,39 +2385,39 @@
         <v>16</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>98</v>
+        <v>168</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>241</v>
+        <v>169</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>242</v>
+        <v>170</v>
       </c>
       <c r="I15" s="4">
         <v>4.5999999999999996</v>
       </c>
       <c r="J15" s="7" t="s">
-        <v>99</v>
-      </c>
-      <c r="K15" s="8" t="s">
-        <v>100</v>
+        <v>171</v>
+      </c>
+      <c r="K15" s="5" t="s">
+        <v>172</v>
       </c>
       <c r="L15" s="4" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="M15" s="4" t="s">
-        <v>22</v>
+        <v>105</v>
       </c>
     </row>
     <row r="16" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A16" s="4" t="s">
-        <v>101</v>
+        <v>56</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>102</v>
+        <v>57</v>
       </c>
       <c r="C16" s="5" t="s">
         <v>15</v>
@@ -1994,36 +2429,36 @@
         <v>11</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>18</v>
+        <v>100</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>243</v>
+        <v>173</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>244</v>
+        <v>174</v>
       </c>
       <c r="I16" s="4">
         <v>4.5999999999999996</v>
       </c>
       <c r="J16" s="7" t="s">
-        <v>103</v>
-      </c>
-      <c r="K16" s="8" t="s">
-        <v>104</v>
+        <v>175</v>
+      </c>
+      <c r="K16" s="5" t="s">
+        <v>176</v>
       </c>
       <c r="L16" s="4" t="s">
-        <v>76</v>
+        <v>44</v>
       </c>
       <c r="M16" s="4" t="s">
-        <v>22</v>
+        <v>105</v>
       </c>
     </row>
     <row r="17" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
-        <v>105</v>
+        <v>58</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>106</v>
+        <v>59</v>
       </c>
       <c r="C17" s="5" t="s">
         <v>15</v>
@@ -2035,36 +2470,36 @@
         <v>11</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>18</v>
+        <v>100</v>
       </c>
       <c r="G17" s="6" t="s">
-        <v>245</v>
+        <v>177</v>
       </c>
       <c r="H17" s="6" t="s">
-        <v>246</v>
+        <v>178</v>
       </c>
       <c r="I17" s="4">
         <v>4.5</v>
       </c>
       <c r="J17" s="7" t="s">
-        <v>107</v>
-      </c>
-      <c r="K17" s="8" t="s">
-        <v>108</v>
+        <v>179</v>
+      </c>
+      <c r="K17" s="5" t="s">
+        <v>180</v>
       </c>
       <c r="L17" s="4" t="s">
-        <v>76</v>
+        <v>44</v>
       </c>
       <c r="M17" s="4" t="s">
-        <v>22</v>
+        <v>105</v>
       </c>
     </row>
     <row r="18" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A18" s="4" t="s">
-        <v>109</v>
+        <v>60</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>110</v>
+        <v>61</v>
       </c>
       <c r="C18" s="5" t="s">
         <v>15</v>
@@ -2076,36 +2511,36 @@
         <v>11</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>111</v>
+        <v>181</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>247</v>
+        <v>182</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>248</v>
+        <v>183</v>
       </c>
       <c r="I18" s="4">
         <v>4.7</v>
       </c>
       <c r="J18" s="7" t="s">
-        <v>112</v>
-      </c>
-      <c r="K18" s="8" t="s">
-        <v>113</v>
+        <v>184</v>
+      </c>
+      <c r="K18" s="5" t="s">
+        <v>185</v>
       </c>
       <c r="L18" s="4" t="s">
-        <v>76</v>
+        <v>44</v>
       </c>
       <c r="M18" s="4" t="s">
-        <v>22</v>
+        <v>105</v>
       </c>
     </row>
     <row r="19" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A19" s="4" t="s">
-        <v>114</v>
+        <v>62</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>115</v>
+        <v>63</v>
       </c>
       <c r="C19" s="5" t="s">
         <v>15</v>
@@ -2117,36 +2552,36 @@
         <v>11</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>116</v>
+        <v>186</v>
       </c>
       <c r="G19" s="6" t="s">
-        <v>249</v>
+        <v>187</v>
       </c>
       <c r="H19" s="6" t="s">
-        <v>250</v>
+        <v>188</v>
       </c>
       <c r="I19" s="4">
         <v>4.7</v>
       </c>
       <c r="J19" s="7" t="s">
-        <v>117</v>
-      </c>
-      <c r="K19" s="8" t="s">
-        <v>118</v>
+        <v>189</v>
+      </c>
+      <c r="K19" s="5" t="s">
+        <v>190</v>
       </c>
       <c r="L19" s="4" t="s">
-        <v>76</v>
+        <v>44</v>
       </c>
       <c r="M19" s="4" t="s">
-        <v>22</v>
+        <v>105</v>
       </c>
     </row>
     <row r="20" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A20" s="4" t="s">
-        <v>119</v>
+        <v>64</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>120</v>
+        <v>65</v>
       </c>
       <c r="C20" s="5" t="s">
         <v>15</v>
@@ -2158,36 +2593,36 @@
         <v>11</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>121</v>
+        <v>191</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>251</v>
+        <v>192</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>252</v>
+        <v>193</v>
       </c>
       <c r="I20" s="4">
         <v>4.7</v>
       </c>
       <c r="J20" s="7" t="s">
-        <v>122</v>
-      </c>
-      <c r="K20" s="8" t="s">
-        <v>123</v>
+        <v>194</v>
+      </c>
+      <c r="K20" s="5" t="s">
+        <v>195</v>
       </c>
       <c r="L20" s="4" t="s">
-        <v>76</v>
+        <v>44</v>
       </c>
       <c r="M20" s="4" t="s">
-        <v>22</v>
+        <v>105</v>
       </c>
     </row>
     <row r="21" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A21" s="4" t="s">
-        <v>124</v>
+        <v>66</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>125</v>
+        <v>67</v>
       </c>
       <c r="C21" s="5" t="s">
         <v>15</v>
@@ -2199,36 +2634,36 @@
         <v>11</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>126</v>
+        <v>196</v>
       </c>
       <c r="G21" s="6" t="s">
-        <v>253</v>
+        <v>197</v>
       </c>
       <c r="H21" s="6" t="s">
-        <v>254</v>
+        <v>198</v>
       </c>
       <c r="I21" s="4">
         <v>4.3</v>
       </c>
       <c r="J21" s="7" t="s">
-        <v>127</v>
-      </c>
-      <c r="K21" s="8" t="s">
-        <v>128</v>
+        <v>199</v>
+      </c>
+      <c r="K21" s="5" t="s">
+        <v>200</v>
       </c>
       <c r="L21" s="4" t="s">
-        <v>76</v>
+        <v>44</v>
       </c>
       <c r="M21" s="4" t="s">
-        <v>22</v>
+        <v>105</v>
       </c>
     </row>
     <row r="22" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A22" s="4" t="s">
-        <v>129</v>
+        <v>68</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>130</v>
+        <v>69</v>
       </c>
       <c r="C22" s="5" t="s">
         <v>15</v>
@@ -2240,36 +2675,36 @@
         <v>11</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>131</v>
+        <v>201</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>255</v>
+        <v>202</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>256</v>
+        <v>203</v>
       </c>
       <c r="I22" s="4">
         <v>4.5</v>
       </c>
       <c r="J22" s="7" t="s">
-        <v>132</v>
-      </c>
-      <c r="K22" s="8" t="s">
-        <v>133</v>
+        <v>204</v>
+      </c>
+      <c r="K22" s="5" t="s">
+        <v>205</v>
       </c>
       <c r="L22" s="4" t="s">
-        <v>76</v>
+        <v>44</v>
       </c>
       <c r="M22" s="4" t="s">
-        <v>22</v>
+        <v>105</v>
       </c>
     </row>
     <row r="23" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A23" s="4" t="s">
-        <v>134</v>
+        <v>70</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>135</v>
+        <v>71</v>
       </c>
       <c r="C23" s="5" t="s">
         <v>15</v>
@@ -2281,36 +2716,36 @@
         <v>11</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>136</v>
+        <v>206</v>
       </c>
       <c r="G23" s="6" t="s">
-        <v>257</v>
+        <v>207</v>
       </c>
       <c r="H23" s="6" t="s">
-        <v>258</v>
+        <v>208</v>
       </c>
       <c r="I23" s="4">
         <v>4.0999999999999996</v>
       </c>
       <c r="J23" s="7" t="s">
-        <v>137</v>
-      </c>
-      <c r="K23" s="8" t="s">
-        <v>138</v>
+        <v>209</v>
+      </c>
+      <c r="K23" s="5" t="s">
+        <v>210</v>
       </c>
       <c r="L23" s="4" t="s">
-        <v>76</v>
+        <v>44</v>
       </c>
       <c r="M23" s="4" t="s">
-        <v>22</v>
+        <v>105</v>
       </c>
     </row>
     <row r="24" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A24" s="4" t="s">
-        <v>139</v>
+        <v>72</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>140</v>
+        <v>73</v>
       </c>
       <c r="C24" s="5" t="s">
         <v>15</v>
@@ -2319,39 +2754,39 @@
         <v>16</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>141</v>
+        <v>211</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="G24" s="6" t="s">
-        <v>259</v>
-      </c>
-      <c r="H24" s="6" t="s">
-        <v>260</v>
+        <v>212</v>
+      </c>
+      <c r="G24" s="9" t="s">
+        <v>213</v>
+      </c>
+      <c r="H24" s="9" t="s">
+        <v>214</v>
       </c>
       <c r="I24" s="4">
         <v>4.7</v>
       </c>
       <c r="J24" s="7" t="s">
-        <v>143</v>
-      </c>
-      <c r="K24" s="8" t="s">
-        <v>144</v>
+        <v>215</v>
+      </c>
+      <c r="K24" s="5" t="s">
+        <v>216</v>
       </c>
       <c r="L24" s="4" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="M24" s="4" t="s">
-        <v>22</v>
+        <v>105</v>
       </c>
     </row>
     <row r="25" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A25" s="4" t="s">
-        <v>145</v>
+        <v>74</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>146</v>
+        <v>75</v>
       </c>
       <c r="C25" s="5" t="s">
         <v>15</v>
@@ -2360,39 +2795,39 @@
         <v>16</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>147</v>
+        <v>217</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>148</v>
+        <v>218</v>
       </c>
       <c r="G25" s="6" t="s">
-        <v>261</v>
+        <v>219</v>
       </c>
       <c r="H25" s="6" t="s">
-        <v>262</v>
+        <v>220</v>
       </c>
       <c r="I25" s="4">
         <v>4.3</v>
       </c>
       <c r="J25" s="7" t="s">
-        <v>149</v>
-      </c>
-      <c r="K25" s="8" t="s">
-        <v>150</v>
+        <v>221</v>
+      </c>
+      <c r="K25" s="5" t="s">
+        <v>222</v>
       </c>
       <c r="L25" s="4" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="M25" s="4" t="s">
-        <v>22</v>
+        <v>105</v>
       </c>
     </row>
     <row r="26" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A26" s="4" t="s">
-        <v>151</v>
+        <v>76</v>
       </c>
       <c r="B26" s="10" t="s">
-        <v>152</v>
+        <v>77</v>
       </c>
       <c r="C26" s="5" t="s">
         <v>15</v>
@@ -2400,40 +2835,40 @@
       <c r="D26" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="E26" s="8" t="s">
-        <v>153</v>
-      </c>
-      <c r="F26" s="8" t="s">
-        <v>154</v>
+      <c r="E26" s="5" t="s">
+        <v>223</v>
+      </c>
+      <c r="F26" s="5" t="s">
+        <v>224</v>
       </c>
       <c r="G26" s="11" t="s">
-        <v>263</v>
+        <v>225</v>
       </c>
       <c r="H26" s="11" t="s">
-        <v>264</v>
-      </c>
-      <c r="I26" s="8">
+        <v>226</v>
+      </c>
+      <c r="I26" s="5">
         <v>4.7</v>
       </c>
       <c r="J26" s="12" t="s">
-        <v>155</v>
-      </c>
-      <c r="K26" s="8" t="s">
-        <v>156</v>
-      </c>
-      <c r="L26" s="8" t="s">
-        <v>21</v>
+        <v>227</v>
+      </c>
+      <c r="K26" s="5" t="s">
+        <v>228</v>
+      </c>
+      <c r="L26" s="5" t="s">
+        <v>18</v>
       </c>
       <c r="M26" s="4" t="s">
-        <v>22</v>
+        <v>105</v>
       </c>
     </row>
     <row r="27" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A27" s="4" t="s">
-        <v>157</v>
-      </c>
-      <c r="B27" s="8" t="s">
-        <v>158</v>
+        <v>78</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>79</v>
       </c>
       <c r="C27" s="5" t="s">
         <v>15</v>
@@ -2441,434 +2876,1112 @@
       <c r="D27" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="E27" s="8" t="s">
-        <v>159</v>
-      </c>
-      <c r="F27" s="8" t="s">
-        <v>160</v>
+      <c r="E27" s="5" t="s">
+        <v>229</v>
+      </c>
+      <c r="F27" s="5" t="s">
+        <v>230</v>
       </c>
       <c r="G27" s="11" t="s">
+        <v>231</v>
+      </c>
+      <c r="H27" s="11" t="s">
+        <v>232</v>
+      </c>
+      <c r="I27" s="5">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="J27" s="12" t="s">
+        <v>233</v>
+      </c>
+      <c r="K27" s="5" t="s">
+        <v>234</v>
+      </c>
+      <c r="L27" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="M27" s="4" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A28" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="B28" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="C28" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="D28" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="E28" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="F28" s="14" t="s">
+        <v>235</v>
+      </c>
+      <c r="G28" s="15" t="s">
+        <v>236</v>
+      </c>
+      <c r="H28" s="15" t="s">
+        <v>237</v>
+      </c>
+      <c r="I28" s="14">
+        <v>4.8</v>
+      </c>
+      <c r="J28" s="16" t="s">
+        <v>238</v>
+      </c>
+      <c r="K28" s="14" t="s">
+        <v>239</v>
+      </c>
+      <c r="L28" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="M28" s="14" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A29" s="13" t="s">
+        <v>82</v>
+      </c>
+      <c r="B29" s="14" t="s">
+        <v>83</v>
+      </c>
+      <c r="C29" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="D29" s="14" t="s">
+        <v>84</v>
+      </c>
+      <c r="E29" s="14" t="s">
+        <v>229</v>
+      </c>
+      <c r="F29" s="14" t="s">
+        <v>240</v>
+      </c>
+      <c r="G29" s="15" t="s">
+        <v>241</v>
+      </c>
+      <c r="H29" s="15" t="s">
+        <v>242</v>
+      </c>
+      <c r="I29" s="14">
+        <v>4.3</v>
+      </c>
+      <c r="J29" s="16" t="s">
+        <v>243</v>
+      </c>
+      <c r="K29" s="14" t="s">
+        <v>244</v>
+      </c>
+      <c r="L29" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="M29" s="14" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A30" s="13" t="s">
+        <v>85</v>
+      </c>
+      <c r="B30" s="14" t="s">
+        <v>86</v>
+      </c>
+      <c r="C30" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="D30" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="E30" s="14" t="s">
+        <v>245</v>
+      </c>
+      <c r="F30" s="14" t="s">
+        <v>246</v>
+      </c>
+      <c r="G30" s="15" t="s">
+        <v>247</v>
+      </c>
+      <c r="H30" s="15" t="s">
+        <v>248</v>
+      </c>
+      <c r="I30" s="14">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="J30" s="16" t="s">
+        <v>249</v>
+      </c>
+      <c r="K30" s="14" t="s">
+        <v>250</v>
+      </c>
+      <c r="L30" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="M30" s="14" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A31" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="B31" s="14" t="s">
+        <v>99</v>
+      </c>
+      <c r="C31" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="D31" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="E31" s="14" t="s">
+        <v>251</v>
+      </c>
+      <c r="F31" s="14" t="s">
+        <v>252</v>
+      </c>
+      <c r="G31" s="15" t="s">
+        <v>253</v>
+      </c>
+      <c r="H31" s="15" t="s">
+        <v>254</v>
+      </c>
+      <c r="I31" s="14">
+        <v>4.5</v>
+      </c>
+      <c r="J31" s="16" t="s">
+        <v>255</v>
+      </c>
+      <c r="K31" s="14" t="s">
+        <v>256</v>
+      </c>
+      <c r="L31" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="M31" s="14" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A32" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="B32" s="14" t="s">
+        <v>89</v>
+      </c>
+      <c r="C32" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="D32" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="E32" s="14" t="s">
+        <v>257</v>
+      </c>
+      <c r="F32" s="14" t="s">
+        <v>258</v>
+      </c>
+      <c r="G32" s="15" t="s">
+        <v>259</v>
+      </c>
+      <c r="H32" s="15" t="s">
+        <v>260</v>
+      </c>
+      <c r="I32" s="14">
+        <v>4.5</v>
+      </c>
+      <c r="J32" s="16" t="s">
+        <v>261</v>
+      </c>
+      <c r="K32" s="14" t="s">
+        <v>262</v>
+      </c>
+      <c r="L32" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="M32" s="14" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A33" s="13" t="s">
+        <v>90</v>
+      </c>
+      <c r="B33" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="C33" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="D33" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="E33" s="14" t="s">
+        <v>263</v>
+      </c>
+      <c r="F33" s="14" t="s">
+        <v>264</v>
+      </c>
+      <c r="G33" s="15" t="s">
         <v>265</v>
       </c>
-      <c r="H27" s="11" t="s">
+      <c r="H33" s="15" t="s">
         <v>266</v>
       </c>
-      <c r="I27" s="8">
+      <c r="I33" s="14">
+        <v>3.2</v>
+      </c>
+      <c r="J33" s="16" t="s">
+        <v>267</v>
+      </c>
+      <c r="K33" s="14" t="s">
+        <v>268</v>
+      </c>
+      <c r="L33" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="M33" s="14" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A34" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="B34" s="14" t="s">
+        <v>93</v>
+      </c>
+      <c r="C34" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="D34" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="E34" s="14" t="s">
+        <v>269</v>
+      </c>
+      <c r="F34" s="14" t="s">
+        <v>270</v>
+      </c>
+      <c r="G34" s="15" t="s">
+        <v>271</v>
+      </c>
+      <c r="H34" s="15" t="s">
+        <v>272</v>
+      </c>
+      <c r="I34" s="14">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="J34" s="16" t="s">
+        <v>273</v>
+      </c>
+      <c r="K34" s="14" t="s">
+        <v>94</v>
+      </c>
+      <c r="L34" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="M34" s="14" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A35" s="13" t="s">
+        <v>95</v>
+      </c>
+      <c r="B35" s="14" t="s">
+        <v>96</v>
+      </c>
+      <c r="C35" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="D35" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="E35" s="14" t="s">
+        <v>274</v>
+      </c>
+      <c r="F35" s="14" t="s">
+        <v>275</v>
+      </c>
+      <c r="G35" s="15" t="s">
+        <v>276</v>
+      </c>
+      <c r="H35" s="15" t="s">
+        <v>277</v>
+      </c>
+      <c r="I35" s="14">
         <v>4.5999999999999996</v>
       </c>
-      <c r="J27" s="12" t="s">
-        <v>161</v>
-      </c>
-      <c r="K27" s="8" t="s">
-        <v>162</v>
-      </c>
-      <c r="L27" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="M27" s="4" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="28" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A28" s="4" t="s">
-        <v>163</v>
-      </c>
-      <c r="B28" s="8" t="s">
-        <v>164</v>
-      </c>
-      <c r="C28" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D28" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="E28" s="8" t="s">
+      <c r="J35" s="16" t="s">
+        <v>278</v>
+      </c>
+      <c r="K35" s="14" t="s">
+        <v>279</v>
+      </c>
+      <c r="L35" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="M35" s="14" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A36" s="13" t="s">
+        <v>97</v>
+      </c>
+      <c r="B36" s="14" t="s">
+        <v>98</v>
+      </c>
+      <c r="C36" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="D36" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="E36" s="14" t="s">
+        <v>280</v>
+      </c>
+      <c r="F36" s="14" t="s">
+        <v>281</v>
+      </c>
+      <c r="G36" s="15" t="s">
+        <v>282</v>
+      </c>
+      <c r="H36" s="15" t="s">
+        <v>283</v>
+      </c>
+      <c r="I36" s="14">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="J36" s="16" t="s">
+        <v>284</v>
+      </c>
+      <c r="K36" s="14" t="s">
+        <v>285</v>
+      </c>
+      <c r="L36" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="M36" s="14" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A37" s="13" t="s">
+        <v>286</v>
+      </c>
+      <c r="B37" s="17" t="s">
+        <v>287</v>
+      </c>
+      <c r="C37" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="D37" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="E37" s="14" t="s">
+        <v>288</v>
+      </c>
+      <c r="F37" s="14" t="s">
+        <v>289</v>
+      </c>
+      <c r="G37" s="15" t="s">
+        <v>290</v>
+      </c>
+      <c r="H37" s="15" t="s">
+        <v>291</v>
+      </c>
+      <c r="I37" s="14">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="J37" s="16" t="s">
+        <v>292</v>
+      </c>
+      <c r="K37" s="14" t="s">
+        <v>293</v>
+      </c>
+      <c r="L37" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="M37" s="14" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A38" s="13" t="s">
+        <v>294</v>
+      </c>
+      <c r="B38" s="17" t="s">
+        <v>295</v>
+      </c>
+      <c r="C38" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="D38" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="E38" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="F28" s="8" t="s">
-        <v>165</v>
-      </c>
-      <c r="G28" s="11" t="s">
-        <v>267</v>
-      </c>
-      <c r="H28" s="11" t="s">
-        <v>268</v>
-      </c>
-      <c r="I28" s="8">
+      <c r="F38" s="14" t="s">
+        <v>296</v>
+      </c>
+      <c r="G38" s="15" t="s">
+        <v>297</v>
+      </c>
+      <c r="H38" s="15" t="s">
+        <v>298</v>
+      </c>
+      <c r="I38" s="14">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="J38" s="16" t="s">
+        <v>299</v>
+      </c>
+      <c r="K38" s="14" t="s">
+        <v>300</v>
+      </c>
+      <c r="L38" s="14" t="s">
+        <v>301</v>
+      </c>
+      <c r="M38" s="14" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A39" s="13" t="s">
+        <v>302</v>
+      </c>
+      <c r="B39" s="17" t="s">
+        <v>303</v>
+      </c>
+      <c r="C39" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="D39" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="E39" s="14" t="s">
+        <v>304</v>
+      </c>
+      <c r="F39" s="14" t="s">
+        <v>305</v>
+      </c>
+      <c r="G39" s="15" t="s">
+        <v>306</v>
+      </c>
+      <c r="H39" s="15" t="s">
+        <v>307</v>
+      </c>
+      <c r="I39" s="14">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="J39" s="16" t="s">
+        <v>308</v>
+      </c>
+      <c r="K39" s="14" t="s">
+        <v>309</v>
+      </c>
+      <c r="L39" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="M39" s="14" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A40" s="13" t="s">
+        <v>310</v>
+      </c>
+      <c r="B40" s="17" t="s">
+        <v>311</v>
+      </c>
+      <c r="C40" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="D40" s="13" t="s">
+        <v>312</v>
+      </c>
+      <c r="E40" s="14" t="s">
+        <v>313</v>
+      </c>
+      <c r="F40" s="14" t="s">
+        <v>314</v>
+      </c>
+      <c r="G40" s="15" t="s">
+        <v>315</v>
+      </c>
+      <c r="H40" s="15" t="s">
+        <v>316</v>
+      </c>
+      <c r="I40" s="14">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="J40" s="16" t="s">
+        <v>317</v>
+      </c>
+      <c r="K40" s="14" t="s">
+        <v>318</v>
+      </c>
+      <c r="L40" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="M40" s="14" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A41" s="13" t="s">
+        <v>319</v>
+      </c>
+      <c r="B41" s="17" t="s">
+        <v>320</v>
+      </c>
+      <c r="C41" s="14" t="s">
+        <v>321</v>
+      </c>
+      <c r="D41" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="E41" s="14" t="s">
+        <v>322</v>
+      </c>
+      <c r="F41" s="14" t="s">
+        <v>323</v>
+      </c>
+      <c r="G41" s="15" t="s">
+        <v>324</v>
+      </c>
+      <c r="H41" s="15" t="s">
+        <v>325</v>
+      </c>
+      <c r="I41" s="14">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="J41" s="16" t="s">
+        <v>326</v>
+      </c>
+      <c r="K41" s="14" t="s">
+        <v>327</v>
+      </c>
+      <c r="L41" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="M41" s="14" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A42" s="13" t="s">
+        <v>328</v>
+      </c>
+      <c r="B42" s="17" t="s">
+        <v>329</v>
+      </c>
+      <c r="C42" s="14" t="s">
+        <v>321</v>
+      </c>
+      <c r="D42" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="E42" s="14" t="s">
+        <v>330</v>
+      </c>
+      <c r="F42" s="14" t="s">
+        <v>331</v>
+      </c>
+      <c r="G42" s="15" t="s">
+        <v>332</v>
+      </c>
+      <c r="H42" s="15" t="s">
+        <v>333</v>
+      </c>
+      <c r="I42" s="14">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="J42" s="16" t="s">
+        <v>334</v>
+      </c>
+      <c r="K42" s="14" t="s">
+        <v>335</v>
+      </c>
+      <c r="L42" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="M42" s="14" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A43" s="13" t="s">
+        <v>336</v>
+      </c>
+      <c r="B43" s="17" t="s">
+        <v>337</v>
+      </c>
+      <c r="C43" s="18" t="s">
+        <v>338</v>
+      </c>
+      <c r="D43" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="E43" s="14" t="s">
+        <v>339</v>
+      </c>
+      <c r="F43" s="14" t="s">
+        <v>340</v>
+      </c>
+      <c r="G43" s="19" t="s">
+        <v>341</v>
+      </c>
+      <c r="H43" s="15" t="s">
+        <v>342</v>
+      </c>
+      <c r="I43" s="14">
         <v>4.8</v>
       </c>
-      <c r="J28" s="12" t="s">
-        <v>166</v>
-      </c>
-      <c r="K28" s="8" t="s">
-        <v>167</v>
-      </c>
-      <c r="L28" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="M28" s="8" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="29" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A29" s="4" t="s">
-        <v>168</v>
-      </c>
-      <c r="B29" s="8" t="s">
-        <v>169</v>
-      </c>
-      <c r="C29" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D29" s="8" t="s">
-        <v>170</v>
-      </c>
-      <c r="E29" s="8" t="s">
-        <v>159</v>
-      </c>
-      <c r="F29" s="8" t="s">
-        <v>171</v>
-      </c>
-      <c r="G29" s="11" t="s">
-        <v>269</v>
-      </c>
-      <c r="H29" s="11" t="s">
-        <v>270</v>
-      </c>
-      <c r="I29" s="8">
+      <c r="J43" s="16" t="s">
+        <v>343</v>
+      </c>
+      <c r="K43" s="14" t="s">
+        <v>344</v>
+      </c>
+      <c r="L43" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="M43" s="20" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A44" s="13" t="s">
+        <v>346</v>
+      </c>
+      <c r="B44" s="17" t="s">
+        <v>347</v>
+      </c>
+      <c r="C44" s="18" t="s">
+        <v>348</v>
+      </c>
+      <c r="D44" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="E44" s="14" t="s">
+        <v>349</v>
+      </c>
+      <c r="F44" s="14" t="s">
+        <v>350</v>
+      </c>
+      <c r="G44" s="15" t="s">
+        <v>351</v>
+      </c>
+      <c r="H44" s="15" t="s">
+        <v>352</v>
+      </c>
+      <c r="I44" s="14">
+        <v>4.5</v>
+      </c>
+      <c r="J44" s="16" t="s">
+        <v>353</v>
+      </c>
+      <c r="K44" s="14" t="s">
+        <v>354</v>
+      </c>
+      <c r="L44" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="M44" s="20" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A45" s="13" t="s">
+        <v>355</v>
+      </c>
+      <c r="B45" s="17" t="s">
+        <v>356</v>
+      </c>
+      <c r="C45" s="20" t="s">
+        <v>338</v>
+      </c>
+      <c r="D45" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="E45" s="14" t="s">
+        <v>357</v>
+      </c>
+      <c r="F45" s="14" t="s">
+        <v>358</v>
+      </c>
+      <c r="G45" s="15" t="s">
+        <v>359</v>
+      </c>
+      <c r="H45" s="15" t="s">
+        <v>360</v>
+      </c>
+      <c r="I45" s="14">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="J45" s="16" t="s">
+        <v>361</v>
+      </c>
+      <c r="K45" s="14" t="s">
+        <v>362</v>
+      </c>
+      <c r="L45" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="M45" s="20" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A46" s="13" t="s">
+        <v>363</v>
+      </c>
+      <c r="B46" s="17" t="s">
+        <v>364</v>
+      </c>
+      <c r="C46" s="20" t="s">
+        <v>365</v>
+      </c>
+      <c r="D46" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="E46" s="14" t="s">
+        <v>366</v>
+      </c>
+      <c r="F46" s="14" t="s">
+        <v>367</v>
+      </c>
+      <c r="G46" s="15" t="s">
+        <v>368</v>
+      </c>
+      <c r="H46" s="15" t="s">
+        <v>369</v>
+      </c>
+      <c r="I46" s="14">
+        <v>4.7</v>
+      </c>
+      <c r="J46" s="16" t="s">
+        <v>370</v>
+      </c>
+      <c r="K46" s="14" t="s">
+        <v>371</v>
+      </c>
+      <c r="L46" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="M46" s="14" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A47" s="13" t="s">
+        <v>372</v>
+      </c>
+      <c r="B47" s="17" t="s">
+        <v>373</v>
+      </c>
+      <c r="C47" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="D47" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="E47" s="14" t="s">
+        <v>374</v>
+      </c>
+      <c r="F47" s="14" t="s">
+        <v>375</v>
+      </c>
+      <c r="G47" s="15" t="s">
+        <v>376</v>
+      </c>
+      <c r="H47" s="15" t="s">
+        <v>377</v>
+      </c>
+      <c r="I47" s="14">
+        <v>4.7</v>
+      </c>
+      <c r="J47" s="16" t="s">
+        <v>378</v>
+      </c>
+      <c r="K47" s="14" t="s">
+        <v>379</v>
+      </c>
+      <c r="L47" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="M47" s="14" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="48" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A48" s="13" t="s">
+        <v>380</v>
+      </c>
+      <c r="B48" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="C48" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="D48" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="E48" s="5" t="s">
+        <v>381</v>
+      </c>
+      <c r="F48" s="5" t="s">
+        <v>382</v>
+      </c>
+      <c r="G48" s="21" t="s">
+        <v>383</v>
+      </c>
+      <c r="H48" s="21" t="s">
+        <v>384</v>
+      </c>
+      <c r="I48" s="5">
         <v>4.3</v>
       </c>
-      <c r="J29" s="12" t="s">
-        <v>172</v>
-      </c>
-      <c r="K29" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="L29" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="M29" s="8" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="30" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A30" s="4" t="s">
-        <v>174</v>
-      </c>
-      <c r="B30" s="8" t="s">
-        <v>175</v>
-      </c>
-      <c r="C30" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D30" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="E30" s="8" t="s">
-        <v>176</v>
-      </c>
-      <c r="F30" s="8" t="s">
-        <v>177</v>
-      </c>
-      <c r="G30" s="11" t="s">
-        <v>271</v>
-      </c>
-      <c r="H30" s="11" t="s">
-        <v>272</v>
-      </c>
-      <c r="I30" s="8">
+      <c r="J48" s="12" t="s">
+        <v>385</v>
+      </c>
+      <c r="K48" s="14" t="s">
+        <v>386</v>
+      </c>
+      <c r="L48" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="M48" s="5" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="49" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A49" s="13" t="s">
+        <v>387</v>
+      </c>
+      <c r="B49" s="10" t="s">
+        <v>388</v>
+      </c>
+      <c r="C49" s="5" t="s">
+        <v>389</v>
+      </c>
+      <c r="D49" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="E49" s="5" t="s">
+        <v>390</v>
+      </c>
+      <c r="F49" s="5" t="s">
+        <v>391</v>
+      </c>
+      <c r="G49" s="21" t="s">
+        <v>392</v>
+      </c>
+      <c r="H49" s="21" t="s">
+        <v>393</v>
+      </c>
+      <c r="I49" s="5">
+        <v>4.3</v>
+      </c>
+      <c r="J49" s="12" t="s">
+        <v>394</v>
+      </c>
+      <c r="K49" s="14" t="s">
+        <v>395</v>
+      </c>
+      <c r="L49" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="M49" s="5" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="50" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A50" s="13" t="s">
+        <v>396</v>
+      </c>
+      <c r="B50" s="10" t="s">
+        <v>397</v>
+      </c>
+      <c r="C50" s="5" t="s">
+        <v>389</v>
+      </c>
+      <c r="D50" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="E50" s="5" t="s">
+        <v>398</v>
+      </c>
+      <c r="F50" s="5" t="s">
+        <v>399</v>
+      </c>
+      <c r="G50" s="21" t="s">
+        <v>400</v>
+      </c>
+      <c r="H50" s="21" t="s">
+        <v>401</v>
+      </c>
+      <c r="I50" s="5">
         <v>4.5999999999999996</v>
       </c>
-      <c r="J30" s="12" t="s">
-        <v>178</v>
-      </c>
-      <c r="K30" s="8" t="s">
-        <v>179</v>
-      </c>
-      <c r="L30" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="M30" s="8" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="31" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A31" s="4" t="s">
-        <v>180</v>
-      </c>
-      <c r="B31" s="8" t="s">
-        <v>273</v>
-      </c>
-      <c r="C31" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D31" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="E31" s="8" t="s">
-        <v>181</v>
-      </c>
-      <c r="F31" s="8" t="s">
-        <v>182</v>
-      </c>
-      <c r="G31" s="11" t="s">
-        <v>274</v>
-      </c>
-      <c r="H31" s="11" t="s">
-        <v>275</v>
-      </c>
-      <c r="I31" s="8">
-        <v>4.5</v>
-      </c>
-      <c r="J31" s="12" t="s">
-        <v>183</v>
-      </c>
-      <c r="K31" s="8" t="s">
-        <v>184</v>
-      </c>
-      <c r="L31" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="M31" s="8" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="32" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A32" s="4" t="s">
-        <v>185</v>
-      </c>
-      <c r="B32" s="8" t="s">
-        <v>186</v>
-      </c>
-      <c r="C32" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D32" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="E32" s="8" t="s">
-        <v>187</v>
-      </c>
-      <c r="F32" s="8" t="s">
-        <v>188</v>
-      </c>
-      <c r="G32" s="11" t="s">
-        <v>276</v>
-      </c>
-      <c r="H32" s="11" t="s">
-        <v>277</v>
-      </c>
-      <c r="I32" s="8">
-        <v>4.5</v>
-      </c>
-      <c r="J32" s="12" t="s">
-        <v>189</v>
-      </c>
-      <c r="K32" s="8" t="s">
-        <v>190</v>
-      </c>
-      <c r="L32" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="M32" s="8" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="33" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A33" s="4" t="s">
-        <v>191</v>
-      </c>
-      <c r="B33" s="8" t="s">
-        <v>192</v>
-      </c>
-      <c r="C33" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D33" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="E33" s="8" t="s">
-        <v>193</v>
-      </c>
-      <c r="F33" s="8" t="s">
-        <v>194</v>
-      </c>
-      <c r="G33" s="11" t="s">
-        <v>278</v>
-      </c>
-      <c r="H33" s="11" t="s">
-        <v>279</v>
-      </c>
-      <c r="I33" s="8">
-        <v>3.2</v>
-      </c>
-      <c r="J33" s="12" t="s">
-        <v>195</v>
-      </c>
-      <c r="K33" s="8" t="s">
-        <v>196</v>
-      </c>
-      <c r="L33" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="M33" s="8" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="34" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A34" s="4" t="s">
-        <v>197</v>
-      </c>
-      <c r="B34" s="8" t="s">
-        <v>198</v>
-      </c>
-      <c r="C34" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D34" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="E34" s="8" t="s">
-        <v>199</v>
-      </c>
-      <c r="F34" s="8" t="s">
-        <v>200</v>
-      </c>
-      <c r="G34" s="11" t="s">
-        <v>280</v>
-      </c>
-      <c r="H34" s="11" t="s">
-        <v>281</v>
-      </c>
-      <c r="I34" s="8">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="J34" s="12" t="s">
-        <v>201</v>
-      </c>
-      <c r="K34" s="8" t="s">
-        <v>202</v>
-      </c>
-      <c r="L34" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="M34" s="8" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="35" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A35" s="4" t="s">
-        <v>203</v>
-      </c>
-      <c r="B35" s="8" t="s">
-        <v>204</v>
-      </c>
-      <c r="C35" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D35" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="E35" s="8" t="s">
-        <v>205</v>
-      </c>
-      <c r="F35" s="8" t="s">
-        <v>206</v>
-      </c>
-      <c r="G35" s="11" t="s">
-        <v>282</v>
-      </c>
-      <c r="H35" s="11" t="s">
-        <v>283</v>
-      </c>
-      <c r="I35" s="8">
-        <v>4.5999999999999996</v>
-      </c>
-      <c r="J35" s="12" t="s">
-        <v>207</v>
-      </c>
-      <c r="K35" s="8" t="s">
-        <v>208</v>
-      </c>
-      <c r="L35" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="M35" s="8" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="36" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A36" s="4" t="s">
-        <v>209</v>
-      </c>
-      <c r="B36" s="8" t="s">
-        <v>210</v>
-      </c>
-      <c r="E36" s="8" t="s">
-        <v>211</v>
-      </c>
-      <c r="F36" s="8" t="s">
-        <v>212</v>
-      </c>
-      <c r="G36" s="11" t="s">
-        <v>284</v>
-      </c>
-      <c r="H36" s="11" t="s">
-        <v>285</v>
-      </c>
-      <c r="I36" s="8">
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="J36" s="12" t="s">
-        <v>213</v>
-      </c>
-      <c r="K36" s="8" t="s">
-        <v>214</v>
-      </c>
-      <c r="L36" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="M36" s="8" t="s">
-        <v>22</v>
+      <c r="J50" s="12" t="s">
+        <v>402</v>
+      </c>
+      <c r="K50" s="14" t="s">
+        <v>403</v>
+      </c>
+      <c r="L50" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="M50" s="5" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="51" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A51" s="13" t="s">
+        <v>404</v>
+      </c>
+      <c r="B51" s="10" t="s">
+        <v>405</v>
+      </c>
+      <c r="C51" s="5" t="s">
+        <v>406</v>
+      </c>
+      <c r="D51" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="E51" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F51" s="5" t="s">
+        <v>407</v>
+      </c>
+      <c r="G51" s="21" t="s">
+        <v>408</v>
+      </c>
+      <c r="H51" s="21" t="s">
+        <v>409</v>
+      </c>
+      <c r="I51" s="5">
+        <v>4.3</v>
+      </c>
+      <c r="J51" s="12" t="s">
+        <v>410</v>
+      </c>
+      <c r="K51" s="14" t="s">
+        <v>411</v>
+      </c>
+      <c r="L51" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="M51" s="5" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="52" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A52" s="13" t="s">
+        <v>412</v>
+      </c>
+      <c r="B52" s="10" t="s">
+        <v>413</v>
+      </c>
+      <c r="C52" s="5" t="s">
+        <v>406</v>
+      </c>
+      <c r="D52" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="E52" s="5" t="s">
+        <v>414</v>
+      </c>
+      <c r="F52" s="5" t="s">
+        <v>415</v>
+      </c>
+      <c r="G52" s="21" t="s">
+        <v>416</v>
+      </c>
+      <c r="H52" s="21" t="s">
+        <v>417</v>
+      </c>
+      <c r="I52" s="5">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="J52" s="12" t="s">
+        <v>418</v>
+      </c>
+      <c r="K52" s="14" t="s">
+        <v>419</v>
+      </c>
+      <c r="L52" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="M52" s="5" t="s">
+        <v>105</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="J2" r:id="rId1" xr:uid="{C21EBE8A-FB28-456F-B43E-6C698CBB5919}"/>
-    <hyperlink ref="J3" r:id="rId2" xr:uid="{70E433A1-2F58-4944-BEDC-CE077ED6C42E}"/>
-    <hyperlink ref="J4" r:id="rId3" xr:uid="{AC88F184-BFE0-49DC-ABB3-9427022FCAAC}"/>
-    <hyperlink ref="J5" r:id="rId4" xr:uid="{7A94BDFC-6F1F-4024-9124-73C5A81747C3}"/>
-    <hyperlink ref="J6" r:id="rId5" xr:uid="{33315106-81B8-47AB-B625-7A058521D079}"/>
-    <hyperlink ref="J7" r:id="rId6" xr:uid="{5119EB0A-9C76-457F-98D8-346AD04EC4AA}"/>
-    <hyperlink ref="J8" r:id="rId7" xr:uid="{9027F35F-9189-44C9-B482-27A3ED1A4464}"/>
-    <hyperlink ref="J9" r:id="rId8" xr:uid="{DBA74C38-B338-479C-8D40-45D2561444B4}"/>
-    <hyperlink ref="J10" r:id="rId9" xr:uid="{B6B42EB7-C800-4474-B882-1611DD46ECAF}"/>
-    <hyperlink ref="J11" r:id="rId10" xr:uid="{EC893509-CDB2-4390-8F44-E861064F654C}"/>
-    <hyperlink ref="J12" r:id="rId11" xr:uid="{A80C2255-56A8-4D73-B91F-4F901E8E7739}"/>
-    <hyperlink ref="J13" r:id="rId12" xr:uid="{95827463-DAB7-463B-A809-786BFB1AC599}"/>
-    <hyperlink ref="J14" r:id="rId13" xr:uid="{E537E3E4-CDFD-4410-AD40-387117C027D0}"/>
-    <hyperlink ref="J15" r:id="rId14" xr:uid="{EE3AAC37-2CC5-49A1-89CE-180942695DC2}"/>
-    <hyperlink ref="J16" r:id="rId15" xr:uid="{8C85B041-5089-48BD-92E9-B5CB10D533B9}"/>
-    <hyperlink ref="J17" r:id="rId16" xr:uid="{6E60A05E-E715-4C7F-9FC2-EA425DE1024D}"/>
-    <hyperlink ref="J18" r:id="rId17" xr:uid="{64A90B58-5043-40C3-98AC-3FBC4DEB043B}"/>
-    <hyperlink ref="J19" r:id="rId18" xr:uid="{E028405A-212C-41FF-BE41-92FBB73E5E0F}"/>
-    <hyperlink ref="J20" r:id="rId19" xr:uid="{864E9055-06D8-444D-9B70-C57B16102ABA}"/>
-    <hyperlink ref="J21" r:id="rId20" xr:uid="{656CD8D4-659F-474B-B216-731E1DB0F050}"/>
-    <hyperlink ref="J22" r:id="rId21" xr:uid="{23389265-48C7-416D-8C2B-D224C5C33935}"/>
-    <hyperlink ref="J23" r:id="rId22" xr:uid="{EE734B35-CCB8-4453-92E0-3579CA90D9D9}"/>
-    <hyperlink ref="J24" r:id="rId23" xr:uid="{FF852A35-FE84-4CEC-9C1D-1A7A0EB48735}"/>
-    <hyperlink ref="J25" r:id="rId24" xr:uid="{679FEDFE-1492-4996-973C-A5F70F414912}"/>
-    <hyperlink ref="J26" r:id="rId25" xr:uid="{EBEDA7E3-EAB2-4836-A530-7B63C0BB6BCF}"/>
-    <hyperlink ref="J27" r:id="rId26" xr:uid="{6B8D15C7-30A5-498F-A6DA-9401152D1480}"/>
-    <hyperlink ref="J28" r:id="rId27" xr:uid="{532997D4-8957-4880-8021-D1430C4EDBD4}"/>
-    <hyperlink ref="J29" r:id="rId28" xr:uid="{0D3A94C5-CEEC-4AA0-9E53-289B39FEF639}"/>
-    <hyperlink ref="J30" r:id="rId29" xr:uid="{E9372452-BA02-4638-96EA-229EAD783F15}"/>
-    <hyperlink ref="J31" r:id="rId30" xr:uid="{94B6327F-3038-48CB-9D0F-4A9725929D01}"/>
-    <hyperlink ref="J32" r:id="rId31" xr:uid="{C705F3EA-4653-4441-99E4-A635F434736F}"/>
-    <hyperlink ref="J33" r:id="rId32" xr:uid="{B3100D91-EBDB-42EA-9077-BFE1B697DC42}"/>
-    <hyperlink ref="J34" r:id="rId33" xr:uid="{4EC06CB8-C118-4D93-B060-848F48F4A167}"/>
-    <hyperlink ref="J35" r:id="rId34" xr:uid="{C1F5CC9F-3F6C-4024-9519-3FBB3BBD6FB9}"/>
-    <hyperlink ref="J36" r:id="rId35" xr:uid="{FFE3C0EA-7293-4978-BDBE-F2CA38C28AB9}"/>
+    <hyperlink ref="J2" r:id="rId1" xr:uid="{CDCF929D-3F93-4EA6-89CE-DF0CD0B862CF}"/>
+    <hyperlink ref="J3" r:id="rId2" xr:uid="{5BA49BA5-F88B-4516-AD35-8DFFF1D23037}"/>
+    <hyperlink ref="J4" r:id="rId3" xr:uid="{3505B3D9-4186-445D-B5D0-0BA970259669}"/>
+    <hyperlink ref="J5" r:id="rId4" xr:uid="{7D087BEC-941E-45AE-929A-93D3709BD73A}"/>
+    <hyperlink ref="J6" r:id="rId5" xr:uid="{FF854E6C-30E5-47F8-BA6B-0794BAABDD9D}"/>
+    <hyperlink ref="J7" r:id="rId6" xr:uid="{0646CCB0-1850-476F-9CCA-22088FD55B26}"/>
+    <hyperlink ref="J8" r:id="rId7" xr:uid="{6AAB5585-437C-4F79-A572-A26CBC85200E}"/>
+    <hyperlink ref="J9" r:id="rId8" xr:uid="{C5DDB248-97FB-48D0-860C-775F2ABAAA9D}"/>
+    <hyperlink ref="J10" r:id="rId9" xr:uid="{FAFE970F-33B1-43B1-B427-3C3C9C93C011}"/>
+    <hyperlink ref="J11" r:id="rId10" xr:uid="{FC2166CF-C102-464D-9FDA-3AF98F5B3601}"/>
+    <hyperlink ref="J12" r:id="rId11" xr:uid="{D934C074-F0B2-4832-9905-BDB7ACD89F4D}"/>
+    <hyperlink ref="J13" r:id="rId12" xr:uid="{CB03D343-C5D9-4B9C-8D8E-7017BFA29723}"/>
+    <hyperlink ref="J14" r:id="rId13" xr:uid="{26A1A466-D2C3-4D2D-8262-4EB197949143}"/>
+    <hyperlink ref="J15" r:id="rId14" xr:uid="{88E8932E-E209-4A53-B071-69E593060BC3}"/>
+    <hyperlink ref="J16" r:id="rId15" xr:uid="{5CB1469D-9F5E-48F3-83EC-6883B62AB633}"/>
+    <hyperlink ref="J17" r:id="rId16" xr:uid="{2F85593E-C13F-4594-B04E-88FCB963CCCE}"/>
+    <hyperlink ref="J18" r:id="rId17" xr:uid="{D612EFF9-F7BE-4156-915F-B22987B28735}"/>
+    <hyperlink ref="J19" r:id="rId18" xr:uid="{F562A984-5FFE-460B-94D4-35AD273F963E}"/>
+    <hyperlink ref="J20" r:id="rId19" xr:uid="{4AB5CC22-DAE1-4791-9026-3A567339DCE6}"/>
+    <hyperlink ref="J21" r:id="rId20" xr:uid="{990BA7A4-3757-42BE-B370-3D01A51F580C}"/>
+    <hyperlink ref="J22" r:id="rId21" xr:uid="{D98E8F97-F38F-42C0-BD84-0AAD85E3B361}"/>
+    <hyperlink ref="J23" r:id="rId22" xr:uid="{3610F491-7A36-4926-B819-63C44CD43004}"/>
+    <hyperlink ref="J24" r:id="rId23" xr:uid="{8A9FF99F-A69E-4CBE-B5B5-80440BC425A1}"/>
+    <hyperlink ref="J25" r:id="rId24" xr:uid="{50C1AF6C-85E6-48D3-96EF-102D78E50B9E}"/>
+    <hyperlink ref="J26" r:id="rId25" xr:uid="{8C858C36-0CBA-4511-8D39-473E87625719}"/>
+    <hyperlink ref="J27" r:id="rId26" xr:uid="{92DFC153-D576-4B27-A38D-6DF4A9496B8E}"/>
+    <hyperlink ref="J28" r:id="rId27" xr:uid="{6C149969-4FA3-4768-83AD-E36022E8F721}"/>
+    <hyperlink ref="J29" r:id="rId28" xr:uid="{B5744B9D-E017-429F-BA8A-F1554EA2B3FE}"/>
+    <hyperlink ref="J30" r:id="rId29" xr:uid="{FE25A4D6-6B54-4F63-BFE7-963CA9C10B15}"/>
+    <hyperlink ref="J31" r:id="rId30" xr:uid="{00CDC88B-7042-4B31-8291-600F7D6CD655}"/>
+    <hyperlink ref="J32" r:id="rId31" xr:uid="{143A7AA9-AAFA-4E2F-9D21-FFD620CFF49C}"/>
+    <hyperlink ref="J33" r:id="rId32" xr:uid="{8ADB1B85-9BCB-4381-933E-BBB67AFD66E4}"/>
+    <hyperlink ref="J34" r:id="rId33" xr:uid="{8FF141DA-03A6-4F2C-B3C3-3DB90E38D290}"/>
+    <hyperlink ref="J35" r:id="rId34" xr:uid="{E3D318B9-9E05-4C0E-914A-7535DC6FEDDF}"/>
+    <hyperlink ref="J36" r:id="rId35" xr:uid="{DAD7E640-4AE8-4247-BCF0-25907DE8A5E4}"/>
+    <hyperlink ref="J37" r:id="rId36" xr:uid="{83972A79-BC5A-415D-96C0-085346578A15}"/>
+    <hyperlink ref="J38" r:id="rId37" xr:uid="{88E4C936-E737-4511-8005-70E818C200B7}"/>
+    <hyperlink ref="J39" r:id="rId38" xr:uid="{16F0E6E5-3889-49C9-A085-FC0C15873B60}"/>
+    <hyperlink ref="J40" r:id="rId39" xr:uid="{5DA1450F-8C32-467E-B455-4BF7A8143424}"/>
+    <hyperlink ref="J41" r:id="rId40" xr:uid="{3F0F4B36-D3C7-4EE6-94A8-0775A37C3CEA}"/>
+    <hyperlink ref="J42" r:id="rId41" xr:uid="{C3C44677-EDCC-4112-ACD4-8AED04CA76A7}"/>
+    <hyperlink ref="J43" r:id="rId42" xr:uid="{68206919-E5D5-4CFB-B69A-468DB6E28C8F}"/>
+    <hyperlink ref="J44" r:id="rId43" xr:uid="{7E6B6096-597A-4175-8A12-83122297AB9D}"/>
+    <hyperlink ref="J45" r:id="rId44" xr:uid="{BB3ADCF2-C3A4-49F0-BA18-596C360CD12C}"/>
+    <hyperlink ref="J46" r:id="rId45" xr:uid="{80E5AFE5-F3E0-4DEB-901C-9BE910BD7CBA}"/>
+    <hyperlink ref="J47" r:id="rId46" xr:uid="{374385D1-CFA5-4159-8019-AF5029D51208}"/>
+    <hyperlink ref="J48" r:id="rId47" xr:uid="{F2520922-FE1E-401F-9467-864DD4F0EEBD}"/>
+    <hyperlink ref="J49" r:id="rId48" xr:uid="{3B6C46D2-9F7A-4E3C-81EA-121BE0DF0DFD}"/>
+    <hyperlink ref="J50" r:id="rId49" xr:uid="{398975A2-9140-477E-A029-5D9B4437FB28}"/>
+    <hyperlink ref="J51" r:id="rId50" xr:uid="{FD381196-4532-4514-8C5A-009B3A74855E}"/>
+    <hyperlink ref="J52" r:id="rId51" xr:uid="{304FDA02-FD8D-4F5B-A6AE-4AF4BD75F69B}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/rumah_makan.xlsx
+++ b/data/rumah_makan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\SEMESTER 6\PRAK. SIGTER\PROJECT AKHIR\STUDENT SURVIVAL MAP\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42ABA17B-03BF-49C9-8349-78970539F486}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{252047F2-4305-431E-A324-B905F78C588C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{EBF2A29F-0C7E-4417-9F77-D4C323BFD0DA}"/>
   </bookViews>
@@ -318,9 +318,6 @@
     <t>Sambel Cowek (Sambel Colek)</t>
   </si>
   <si>
-    <t xml:space="preserve">R033jpg </t>
-  </si>
-  <si>
     <t>R034</t>
   </si>
   <si>
@@ -348,7 +345,7 @@
     <t>https://maps,app,goo,gl/iqZ4GBhxDdnmiKFh9</t>
   </si>
   <si>
-    <t>R001,jpg</t>
+    <t>images\R001,jpg</t>
   </si>
   <si>
     <t>RP 1-25,000</t>
@@ -366,7 +363,7 @@
     <t>https://maps,app,goo,gl/RYeTdPUprhVZbWQj7</t>
   </si>
   <si>
-    <t>R002,jpg</t>
+    <t>images\R002,jpg</t>
   </si>
   <si>
     <t>Jl, Sengkan Gg, Sadewa No,02, Kocoran, Condongcatur, Kec, Depok, Kab, Sleman, DIY 55283</t>
@@ -381,7 +378,7 @@
     <t>https://maps,app,goo,gl/dE8ZDETqJrKnrMYT7</t>
   </si>
   <si>
-    <t xml:space="preserve">R003,jpg </t>
+    <t xml:space="preserve">images\R003,jpg </t>
   </si>
   <si>
     <t>Gg, Jemb, Merah No,116 D, Kaliwaru, Condongcatur, Kec, Depok, Kab, Sleman, DIY 55283</t>
@@ -396,7 +393,7 @@
     <t>https://maps,app,goo,gl/4ZpaPxZ7B6SoaFbN7</t>
   </si>
   <si>
-    <t>R004,jpg</t>
+    <t>images\R004,jpg</t>
   </si>
   <si>
     <t>Blok B-5, Karangwuni, Manggung, Caturtunggal, Kec, Depok, Kab, Sleman, DIY 55281</t>
@@ -411,7 +408,7 @@
     <t>https://maps,app,goo,gl/o6JYaCCD2E2qbBNu5</t>
   </si>
   <si>
-    <t xml:space="preserve">R005,jpg </t>
+    <t xml:space="preserve">images\R005,jpg </t>
   </si>
   <si>
     <t>Dabag, Condongcatur, Kec, Depok, Kab, Sleman, DIY 55281</t>
@@ -426,7 +423,7 @@
     <t>https://maps,app,goo,gl/jccDdukmCYNKPAUo8</t>
   </si>
   <si>
-    <t xml:space="preserve">R006,jpg </t>
+    <t xml:space="preserve">images\R006,jpg </t>
   </si>
   <si>
     <t>Ruko Gorongan, Jl, Perumnas, Ngropoh, Condongcatur, Kec, Depok, Kab, Sleman, DIY 55283</t>
@@ -441,7 +438,7 @@
     <t>https://maps,app,goo,gl/y2apQpo5v9a8eD8R7</t>
   </si>
   <si>
-    <t>R007,jpg</t>
+    <t>images\R007,jpg</t>
   </si>
   <si>
     <t>Warung Makan Mr, B</t>
@@ -459,7 +456,7 @@
     <t>https://maps,app,goo,gl/JmsiDm3tz18g7duD8</t>
   </si>
   <si>
-    <t>R008,jpg</t>
+    <t>images\R008,jpg</t>
   </si>
   <si>
     <t>Ruko Babarsari, Jl, Raya Kledokan, Caturtunggal, Kec, Depok, Kab, Sleman, DIY 55281</t>
@@ -474,7 +471,7 @@
     <t>https://maps,app,goo,gl/AVSE3ECfkHPPmucS8</t>
   </si>
   <si>
-    <t>R009,jpg</t>
+    <t>images\R009,jpg</t>
   </si>
   <si>
     <t>Ruko Babarsari, Jl, Babarsari, Tambak Bayan, Caturtunggal, Kec, Depok, Kab, Sleman, DIY 55281</t>
@@ -489,7 +486,7 @@
     <t>https://maps,app,goo,gl/SWHzXXXf3SMQ8tA96</t>
   </si>
   <si>
-    <t>R010,jpg</t>
+    <t>images\R010,jpg</t>
   </si>
   <si>
     <t>11:30 AM – 22,30 PM</t>
@@ -507,7 +504,7 @@
     <t>https://maps,app,goo,gl/945xB7PkevoCExYc8</t>
   </si>
   <si>
-    <t>R011,jpg</t>
+    <t>images\R011,jpg</t>
   </si>
   <si>
     <t>Jl, Babarsari I No,13, Janti, Caturtunggal, Kec, Depok, Kab, Sleman, DIY 55281</t>
@@ -522,7 +519,7 @@
     <t>https://maps,app,goo,gl/rPTxmt9UDxHS23n19</t>
   </si>
   <si>
-    <t>R012,jpg</t>
+    <t>images\R012,jpg</t>
   </si>
   <si>
     <t>Ruko Babarsari BBC Plaza, Jl, Tambak Bayan, Janti, Caturtunggal, Kec, Depok, Kab, Sleman, DIY 55281</t>
@@ -537,7 +534,7 @@
     <t>https://maps,app,goo,gl/L6iTqLFFDM966Tmd6</t>
   </si>
   <si>
-    <t>R013,jpg</t>
+    <t>images\R013,jpg</t>
   </si>
   <si>
     <t>Jl, Gambuh No,3, Manukan, Condongcatur, Kec, Depok, Kab, Sleman, DIY 52000</t>
@@ -552,7 +549,7 @@
     <t>https://maps,app,goo,gl/fczoo46dnKmpCCLX7</t>
   </si>
   <si>
-    <t>R014,jpg</t>
+    <t>images\R014,jpg</t>
   </si>
   <si>
     <t>-7,772147381587484</t>
@@ -564,7 +561,7 @@
     <t>https://maps,app,goo,gl/frbqQuNvtPqtGRbZ9</t>
   </si>
   <si>
-    <t>R015,jpg</t>
+    <t>images\R015,jpg</t>
   </si>
   <si>
     <t>-7,773801908510043</t>
@@ -576,7 +573,7 @@
     <t>https://maps,app,goo,gl/GyqJjnQwoYZo9MUv6</t>
   </si>
   <si>
-    <t>R016,jpg</t>
+    <t>images\R016,jpg</t>
   </si>
   <si>
     <t>Karang Wuni, Caturtunggal, Kec, Depok, Kab, Sleman, DIY 55281</t>
@@ -591,7 +588,7 @@
     <t>https://maps,app,goo,gl/fK5qaQbLaG5pV3qK7</t>
   </si>
   <si>
-    <t>R017,jpg</t>
+    <t>images\R017,jpg</t>
   </si>
   <si>
     <t>Jalan Kapulogo, Nologaten, Caturtunggal, Kec, Depok, Kab, Sleman, DIY 55281</t>
@@ -606,7 +603,7 @@
     <t>https://maps,app,goo,gl/rfQ7La7Wdc5Ghyuw6</t>
   </si>
   <si>
-    <t>R018,jpg</t>
+    <t>images\R018,jpg</t>
   </si>
   <si>
     <t>Ruko DTA Square, Jl, Seturan Raya, Kledokan, Caturtunggal, Kec, Depok, Kab, Sleman, DIY 55281</t>
@@ -621,7 +618,7 @@
     <t>https://maps,app,goo,gl/Um2cFZ7P8u8Y3MLC9</t>
   </si>
   <si>
-    <t>R019,jpg</t>
+    <t>images\R019,jpg</t>
   </si>
   <si>
     <t>Jl, Kaliurang No,17 Km,6, Kentungan, Condongcatur, Kec, Depok, Kab, Sleman, DIY 55284</t>
@@ -636,7 +633,7 @@
     <t>https://maps,app,goo,gl/8WpRE1ayxfZ9wkC86</t>
   </si>
   <si>
-    <t xml:space="preserve">R020,jpg </t>
+    <t xml:space="preserve">images\R020,jpg </t>
   </si>
   <si>
     <t>Jl, Apokat, Perumnas Condong Catur, Condongcatur, Kec, Depok, Kab, Sleman, DIY 55283</t>
@@ -651,7 +648,7 @@
     <t>https://maps,app,goo,gl/cAwMBmPVwPjQhV8b8</t>
   </si>
   <si>
-    <t>R021,jpg</t>
+    <t>images\R021,jpg</t>
   </si>
   <si>
     <t>Jl, Pintu Selatan UPN, Ngropoh, Condongcatur, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
@@ -666,7 +663,7 @@
     <t>https://maps,app,goo,gl/SQeZppWwHGojvCoYA</t>
   </si>
   <si>
-    <t>R022,jpg</t>
+    <t>images\R022,jpg</t>
   </si>
   <si>
     <t>9,00 AM - 21,00 PM</t>
@@ -684,7 +681,7 @@
     <t>https://maps,app,goo,gl/MyMuo6xx6rSZSYn6A</t>
   </si>
   <si>
-    <t>R023,jpg</t>
+    <t>images\R023,jpg</t>
   </si>
   <si>
     <t>9,00 AM - 23,30 PM</t>
@@ -702,7 +699,7 @@
     <t>https://maps,app,goo,gl/GGv45FujGN5yNHwcA</t>
   </si>
   <si>
-    <t>R024,jpg</t>
+    <t>images\R024,jpg</t>
   </si>
   <si>
     <t xml:space="preserve">8,00 AM - 22,00 PM </t>
@@ -720,7 +717,7 @@
     <t>https://maps,app,goo,gl/xKX6kRSfFGRUAG9A8</t>
   </si>
   <si>
-    <t xml:space="preserve">R025,jpg </t>
+    <t xml:space="preserve">images\R025,jpg </t>
   </si>
   <si>
     <t xml:space="preserve">10,00 AM - 22,00 PM </t>
@@ -738,7 +735,7 @@
     <t>https://maps,app,goo,gl/Tm28gLkjwDSy5e776</t>
   </si>
   <si>
-    <t xml:space="preserve">R026,jpg </t>
+    <t xml:space="preserve">images\R026,jpg </t>
   </si>
   <si>
     <t>Jl, Seturan Raya, Kledokan, Caturtunggal, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
@@ -753,7 +750,7 @@
     <t>https://maps,app,goo,gl/8jP7p8idJp7mRe8E8</t>
   </si>
   <si>
-    <t>R027,jpg</t>
+    <t>images\R027,jpg</t>
   </si>
   <si>
     <t xml:space="preserve"> Jl, Nusa Indah II, Dero, Condongcatur, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
@@ -768,7 +765,7 @@
     <t>https://maps,app,goo,gl/8AzpC7NaaWZVtmYx5</t>
   </si>
   <si>
-    <t>R028,jpg</t>
+    <t>images\R028,jpg</t>
   </si>
   <si>
     <t xml:space="preserve">7,00 AM - 12,00 PM </t>
@@ -786,7 +783,7 @@
     <t>https://maps,app,goo,gl/Xvaw52o9zDGb7w1X6</t>
   </si>
   <si>
-    <t xml:space="preserve">R029,jpg </t>
+    <t xml:space="preserve">images\R029,jpg </t>
   </si>
   <si>
     <t xml:space="preserve">11,00 AM - 03,00 AM </t>
@@ -804,7 +801,7 @@
     <t>https://maps,app,goo,gl/HtN9HV2g3EC2E6Yw6</t>
   </si>
   <si>
-    <t xml:space="preserve">R030,jpg </t>
+    <t xml:space="preserve">images\R030,jpg </t>
   </si>
   <si>
     <t xml:space="preserve">06,00 AM - 18,00 PM </t>
@@ -822,7 +819,7 @@
     <t>https://maps,app,goo,gl/RGsFBLKN9Tvhmdrh9</t>
   </si>
   <si>
-    <t>R031,jpg</t>
+    <t>images\R031,jpg</t>
   </si>
   <si>
     <t xml:space="preserve">08, 00 AM - 22,00 PM </t>
@@ -840,7 +837,7 @@
     <t>https://maps,app,goo,gl/w3uwETVrBeL8kocJ8</t>
   </si>
   <si>
-    <t xml:space="preserve">R032,jpg </t>
+    <t xml:space="preserve">images\R032,jpg </t>
   </si>
   <si>
     <t xml:space="preserve">09,00 AM - 23,00 PM </t>
@@ -858,6 +855,9 @@
     <t>https://maps,app,goo,gl/vByGQcCKFUbyUWs8A</t>
   </si>
   <si>
+    <t xml:space="preserve">images\R033jpg </t>
+  </si>
+  <si>
     <t xml:space="preserve">08,30 AM - 21,00 PM </t>
   </si>
   <si>
@@ -873,7 +873,7 @@
     <t>https://maps,app,goo,gl/km35JL3uhPDCb4f26</t>
   </si>
   <si>
-    <t xml:space="preserve">R034,jpg </t>
+    <t xml:space="preserve">images\R034,jpg </t>
   </si>
   <si>
     <t>09,30 AM - 10,00 PM</t>
@@ -891,7 +891,7 @@
     <t>https://maps,app,goo,gl/Me5yN67UAteqpGdY9</t>
   </si>
   <si>
-    <t xml:space="preserve">R035,jpg </t>
+    <t xml:space="preserve">images\R035,jpg </t>
   </si>
   <si>
     <t>R036</t>
@@ -915,7 +915,7 @@
     <t>https://maps,app,goo,gl/7ZxoNc54UJ2ZkLf39</t>
   </si>
   <si>
-    <t>R036,jpg</t>
+    <t>images\R036,jpg</t>
   </si>
   <si>
     <t>R037</t>
@@ -936,7 +936,7 @@
     <t>https://maps,app,goo,gl/yYLSC9uJhWDgQUph8</t>
   </si>
   <si>
-    <t>R037,jpg</t>
+    <t>images\R037,jpg</t>
   </si>
   <si>
     <t xml:space="preserve">Ya </t>
@@ -963,7 +963,7 @@
     <t>https://maps,app,goo,gl/VzBnzzQmzfrSBWo9A</t>
   </si>
   <si>
-    <t>R038,jpg</t>
+    <t>images\R038,jpg</t>
   </si>
   <si>
     <t>R039</t>
@@ -990,7 +990,7 @@
     <t>https://maps,app,goo,gl/bujMvFPKLoa6rspp7</t>
   </si>
   <si>
-    <t xml:space="preserve">R039,jpg </t>
+    <t xml:space="preserve">images\R039,jpg </t>
   </si>
   <si>
     <t>R040</t>
@@ -1017,7 +1017,7 @@
     <t>https://maps,app,goo,gl/2RH5jEc9g64fvsgb7</t>
   </si>
   <si>
-    <t>R040,jpg</t>
+    <t>images\R040,jpg</t>
   </si>
   <si>
     <t>R041</t>
@@ -1041,7 +1041,7 @@
     <t>https://maps,app,goo,gl/4NFp2jRiWyogCHd3A</t>
   </si>
   <si>
-    <t>R041,jpg</t>
+    <t>images\R041,jpg</t>
   </si>
   <si>
     <t>R042</t>
@@ -1068,7 +1068,7 @@
     <t>https://maps.app.goo.gl/emcC92RrHoX8udwV7</t>
   </si>
   <si>
-    <t>R042,jpg</t>
+    <t>images\R042,jpg</t>
   </si>
   <si>
     <t>Rp 25–50 rb</t>
@@ -1098,7 +1098,7 @@
     <t>https://maps.app.goo.gl/AvZHK7bAeCfGpBNJ7</t>
   </si>
   <si>
-    <t>R043,jpg</t>
+    <t>images\R043,jpg</t>
   </si>
   <si>
     <t>R044</t>
@@ -1122,7 +1122,7 @@
     <t>https://maps.app.goo.gl/qytFbXEommQHkbe79</t>
   </si>
   <si>
-    <t>R044,jpg</t>
+    <t>images\R044,jpg</t>
   </si>
   <si>
     <t>R045</t>
@@ -1149,7 +1149,7 @@
     <t>https://maps.app.goo.gl/4JX1thPL8hmzb5FZ6</t>
   </si>
   <si>
-    <t>R045,jpg</t>
+    <t>images\R045,jpg</t>
   </si>
   <si>
     <t>R046</t>
@@ -1173,7 +1173,7 @@
     <t>https://maps.app.goo.gl/nXyZFaZFVdjNWZYcA</t>
   </si>
   <si>
-    <t>R046.jpg</t>
+    <t>images\R046.jpg</t>
   </si>
   <si>
     <t>R047</t>
@@ -1194,7 +1194,7 @@
     <t>https://maps.app.goo.gl/kYs4uBRbRfcX9mZAA</t>
   </si>
   <si>
-    <t>R047.jpg</t>
+    <t>images\R047.jpg</t>
   </si>
   <si>
     <t>R048</t>
@@ -1221,7 +1221,7 @@
     <t>https://maps.app.goo.gl/cNotW79g7kypc9dM6</t>
   </si>
   <si>
-    <t>R048.jpg</t>
+    <t>images\R048.jpg</t>
   </si>
   <si>
     <t>R049</t>
@@ -1245,7 +1245,7 @@
     <t>https://maps.app.goo.gl/oM63Gc12DbSpE7Ez6</t>
   </si>
   <si>
-    <t>R049.jpg</t>
+    <t>images\R049.jpg</t>
   </si>
   <si>
     <t>R050</t>
@@ -1269,7 +1269,7 @@
     <t>https://maps.app.goo.gl/tTzzxmnLWbe9s5eo8</t>
   </si>
   <si>
-    <t>R050.jpg</t>
+    <t>images\R050.jpg</t>
   </si>
   <si>
     <t>R051</t>
@@ -1293,14 +1293,14 @@
     <t>https://maps.app.goo.gl/UmdgsovKjfk3nhGT8</t>
   </si>
   <si>
-    <t>R051.jpg</t>
+    <t>images\R051.jpg</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="12">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1363,10 +1363,20 @@
       <family val="1"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF5E5E5E"/>
+      <name val="&quot;Google Sans&quot;"/>
+    </font>
+    <font>
       <sz val="12"/>
       <color rgb="FF5E5E5E"/>
       <name val="Times New Roman"/>
       <family val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="&quot;Google Sans&quot;"/>
     </font>
   </fonts>
   <fills count="3">
@@ -1393,16 +1403,16 @@
     </border>
     <border>
       <left style="thin">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </left>
       <right style="thin">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </right>
       <top style="thin">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </top>
       <bottom style="thin">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1411,25 +1421,23 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1439,6 +1447,9 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1463,7 +1474,14 @@
     <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1780,7 +1798,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D2879120-B48A-4F1A-810E-C87B5DAC68ED}">
   <dimension ref="A1:M52"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="5.77734375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="44.44140625" bestFit="1" customWidth="1"/>
@@ -1797,7 +1815,7 @@
     <col min="13" max="13" width="12.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" ht="15.6">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1838,7 +1856,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:13" ht="15.6">
       <c r="A2" s="4" t="s">
         <v>13</v>
       </c>
@@ -1855,31 +1873,31 @@
         <v>17</v>
       </c>
       <c r="F2" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="G2" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="G2" s="6" t="s">
+      <c r="H2" s="6" t="s">
         <v>101</v>
-      </c>
-      <c r="H2" s="6" t="s">
-        <v>102</v>
       </c>
       <c r="I2" s="4">
         <v>4.8</v>
       </c>
       <c r="J2" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="K2" s="8" t="s">
         <v>103</v>
-      </c>
-      <c r="K2" s="5" t="s">
-        <v>104</v>
       </c>
       <c r="L2" s="4" t="s">
         <v>18</v>
       </c>
       <c r="M2" s="4" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" ht="15.6">
       <c r="A3" s="4" t="s">
         <v>19</v>
       </c>
@@ -1896,31 +1914,31 @@
         <v>22</v>
       </c>
       <c r="F3" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="G3" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="G3" s="6" t="s">
+      <c r="H3" s="6" t="s">
         <v>107</v>
-      </c>
-      <c r="H3" s="6" t="s">
-        <v>108</v>
       </c>
       <c r="I3" s="4">
         <v>4.5</v>
       </c>
       <c r="J3" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="K3" s="4" t="s">
         <v>109</v>
-      </c>
-      <c r="K3" s="4" t="s">
-        <v>110</v>
       </c>
       <c r="L3" s="4" t="s">
         <v>18</v>
       </c>
       <c r="M3" s="4" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" ht="15.6">
       <c r="A4" s="4" t="s">
         <v>23</v>
       </c>
@@ -1937,31 +1955,31 @@
         <v>25</v>
       </c>
       <c r="F4" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="G4" s="6" t="s">
         <v>111</v>
       </c>
-      <c r="G4" s="6" t="s">
+      <c r="H4" s="6" t="s">
         <v>112</v>
-      </c>
-      <c r="H4" s="6" t="s">
-        <v>113</v>
       </c>
       <c r="I4" s="4">
         <v>4.7</v>
       </c>
       <c r="J4" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="K4" s="8" t="s">
         <v>114</v>
-      </c>
-      <c r="K4" s="5" t="s">
-        <v>115</v>
       </c>
       <c r="L4" s="4" t="s">
         <v>18</v>
       </c>
       <c r="M4" s="4" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" ht="15.6">
       <c r="A5" s="4" t="s">
         <v>26</v>
       </c>
@@ -1978,31 +1996,31 @@
         <v>28</v>
       </c>
       <c r="F5" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="G5" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="G5" s="6" t="s">
+      <c r="H5" s="6" t="s">
         <v>117</v>
-      </c>
-      <c r="H5" s="6" t="s">
-        <v>118</v>
       </c>
       <c r="I5" s="4">
         <v>4.5</v>
       </c>
       <c r="J5" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="K5" s="8" t="s">
         <v>119</v>
-      </c>
-      <c r="K5" s="5" t="s">
-        <v>120</v>
       </c>
       <c r="L5" s="4" t="s">
         <v>18</v>
       </c>
       <c r="M5" s="4" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" ht="15.6">
       <c r="A6" s="4" t="s">
         <v>29</v>
       </c>
@@ -2019,31 +2037,31 @@
         <v>31</v>
       </c>
       <c r="F6" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="G6" s="6" t="s">
         <v>121</v>
       </c>
-      <c r="G6" s="6" t="s">
+      <c r="H6" s="6" t="s">
         <v>122</v>
       </c>
-      <c r="H6" s="6" t="s">
+      <c r="I6" s="9">
+        <v>5</v>
+      </c>
+      <c r="J6" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="I6" s="8">
-        <v>5</v>
-      </c>
-      <c r="J6" s="7" t="s">
+      <c r="K6" s="8" t="s">
         <v>124</v>
-      </c>
-      <c r="K6" s="5" t="s">
-        <v>125</v>
       </c>
       <c r="L6" s="4" t="s">
         <v>18</v>
       </c>
       <c r="M6" s="4" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="15.6">
       <c r="A7" s="4" t="s">
         <v>32</v>
       </c>
@@ -2060,31 +2078,31 @@
         <v>34</v>
       </c>
       <c r="F7" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="G7" s="6" t="s">
         <v>126</v>
       </c>
-      <c r="G7" s="6" t="s">
+      <c r="H7" s="6" t="s">
         <v>127</v>
-      </c>
-      <c r="H7" s="6" t="s">
-        <v>128</v>
       </c>
       <c r="I7" s="4">
         <v>4.7</v>
       </c>
       <c r="J7" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="K7" s="8" t="s">
         <v>129</v>
-      </c>
-      <c r="K7" s="5" t="s">
-        <v>130</v>
       </c>
       <c r="L7" s="4" t="s">
         <v>18</v>
       </c>
       <c r="M7" s="4" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" ht="15.6">
       <c r="A8" s="4" t="s">
         <v>35</v>
       </c>
@@ -2101,36 +2119,36 @@
         <v>37</v>
       </c>
       <c r="F8" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="G8" s="6" t="s">
         <v>131</v>
       </c>
-      <c r="G8" s="6" t="s">
+      <c r="H8" s="6" t="s">
         <v>132</v>
-      </c>
-      <c r="H8" s="6" t="s">
-        <v>133</v>
       </c>
       <c r="I8" s="4">
         <v>4.3</v>
       </c>
       <c r="J8" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="K8" s="8" t="s">
         <v>134</v>
-      </c>
-      <c r="K8" s="5" t="s">
-        <v>135</v>
       </c>
       <c r="L8" s="4" t="s">
         <v>18</v>
       </c>
       <c r="M8" s="4" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" ht="15.6">
       <c r="A9" s="4" t="s">
         <v>38</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C9" s="5" t="s">
         <v>15</v>
@@ -2142,31 +2160,31 @@
         <v>39</v>
       </c>
       <c r="F9" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="G9" s="6" t="s">
         <v>137</v>
       </c>
-      <c r="G9" s="6" t="s">
+      <c r="H9" s="6" t="s">
         <v>138</v>
-      </c>
-      <c r="H9" s="6" t="s">
-        <v>139</v>
       </c>
       <c r="I9" s="4">
         <v>4.7</v>
       </c>
       <c r="J9" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="K9" s="8" t="s">
         <v>140</v>
-      </c>
-      <c r="K9" s="5" t="s">
-        <v>141</v>
       </c>
       <c r="L9" s="4" t="s">
         <v>18</v>
       </c>
       <c r="M9" s="4" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" ht="15.6">
       <c r="A10" s="4" t="s">
         <v>40</v>
       </c>
@@ -2183,31 +2201,31 @@
         <v>28</v>
       </c>
       <c r="F10" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="G10" s="6" t="s">
         <v>142</v>
       </c>
-      <c r="G10" s="6" t="s">
+      <c r="H10" s="6" t="s">
         <v>143</v>
-      </c>
-      <c r="H10" s="6" t="s">
-        <v>144</v>
       </c>
       <c r="I10" s="4">
         <v>4.8</v>
       </c>
       <c r="J10" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="K10" s="8" t="s">
         <v>145</v>
-      </c>
-      <c r="K10" s="5" t="s">
-        <v>146</v>
       </c>
       <c r="L10" s="4" t="s">
         <v>18</v>
       </c>
       <c r="M10" s="4" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" ht="15.6">
       <c r="A11" s="4" t="s">
         <v>42</v>
       </c>
@@ -2224,31 +2242,31 @@
         <v>11</v>
       </c>
       <c r="F11" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="G11" s="6" t="s">
         <v>147</v>
       </c>
-      <c r="G11" s="6" t="s">
+      <c r="H11" s="6" t="s">
         <v>148</v>
-      </c>
-      <c r="H11" s="6" t="s">
-        <v>149</v>
       </c>
       <c r="I11" s="4">
         <v>3.9</v>
       </c>
       <c r="J11" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="K11" s="8" t="s">
         <v>150</v>
-      </c>
-      <c r="K11" s="5" t="s">
-        <v>151</v>
       </c>
       <c r="L11" s="4" t="s">
         <v>44</v>
       </c>
       <c r="M11" s="4" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" ht="15.6">
       <c r="A12" s="4" t="s">
         <v>45</v>
       </c>
@@ -2262,34 +2280,34 @@
         <v>16</v>
       </c>
       <c r="E12" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="F12" s="4" t="s">
         <v>152</v>
       </c>
-      <c r="F12" s="4" t="s">
+      <c r="G12" s="6" t="s">
         <v>153</v>
       </c>
-      <c r="G12" s="6" t="s">
+      <c r="H12" s="6" t="s">
         <v>154</v>
-      </c>
-      <c r="H12" s="6" t="s">
-        <v>155</v>
       </c>
       <c r="I12" s="4">
         <v>4.4000000000000004</v>
       </c>
       <c r="J12" s="7" t="s">
+        <v>155</v>
+      </c>
+      <c r="K12" s="8" t="s">
         <v>156</v>
-      </c>
-      <c r="K12" s="5" t="s">
-        <v>157</v>
       </c>
       <c r="L12" s="4" t="s">
         <v>18</v>
       </c>
       <c r="M12" s="4" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" ht="15.6">
       <c r="A13" s="4" t="s">
         <v>47</v>
       </c>
@@ -2306,31 +2324,31 @@
         <v>50</v>
       </c>
       <c r="F13" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="G13" s="6" t="s">
         <v>158</v>
       </c>
-      <c r="G13" s="6" t="s">
+      <c r="H13" s="6" t="s">
         <v>159</v>
-      </c>
-      <c r="H13" s="6" t="s">
-        <v>160</v>
       </c>
       <c r="I13" s="4">
         <v>4.9000000000000004</v>
       </c>
       <c r="J13" s="7" t="s">
+        <v>160</v>
+      </c>
+      <c r="K13" s="8" t="s">
         <v>161</v>
-      </c>
-      <c r="K13" s="5" t="s">
-        <v>162</v>
       </c>
       <c r="L13" s="4" t="s">
         <v>18</v>
       </c>
       <c r="M13" s="4" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" ht="15.6">
       <c r="A14" s="4" t="s">
         <v>51</v>
       </c>
@@ -2347,31 +2365,31 @@
         <v>17</v>
       </c>
       <c r="F14" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="G14" s="6" t="s">
         <v>163</v>
       </c>
-      <c r="G14" s="6" t="s">
+      <c r="H14" s="6" t="s">
         <v>164</v>
-      </c>
-      <c r="H14" s="6" t="s">
-        <v>165</v>
       </c>
       <c r="I14" s="4">
         <v>4.4000000000000004</v>
       </c>
       <c r="J14" s="7" t="s">
+        <v>165</v>
+      </c>
+      <c r="K14" s="8" t="s">
         <v>166</v>
-      </c>
-      <c r="K14" s="5" t="s">
-        <v>167</v>
       </c>
       <c r="L14" s="4" t="s">
         <v>18</v>
       </c>
       <c r="M14" s="4" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" ht="15.6">
       <c r="A15" s="4" t="s">
         <v>53</v>
       </c>
@@ -2388,31 +2406,31 @@
         <v>55</v>
       </c>
       <c r="F15" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="G15" s="6" t="s">
         <v>168</v>
       </c>
-      <c r="G15" s="6" t="s">
+      <c r="H15" s="6" t="s">
         <v>169</v>
-      </c>
-      <c r="H15" s="6" t="s">
-        <v>170</v>
       </c>
       <c r="I15" s="4">
         <v>4.5999999999999996</v>
       </c>
       <c r="J15" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="K15" s="8" t="s">
         <v>171</v>
-      </c>
-      <c r="K15" s="5" t="s">
-        <v>172</v>
       </c>
       <c r="L15" s="4" t="s">
         <v>18</v>
       </c>
       <c r="M15" s="4" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" ht="15.6">
       <c r="A16" s="4" t="s">
         <v>56</v>
       </c>
@@ -2429,31 +2447,31 @@
         <v>11</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="G16" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="H16" s="6" t="s">
         <v>173</v>
-      </c>
-      <c r="H16" s="6" t="s">
-        <v>174</v>
       </c>
       <c r="I16" s="4">
         <v>4.5999999999999996</v>
       </c>
       <c r="J16" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="K16" s="8" t="s">
         <v>175</v>
-      </c>
-      <c r="K16" s="5" t="s">
-        <v>176</v>
       </c>
       <c r="L16" s="4" t="s">
         <v>44</v>
       </c>
       <c r="M16" s="4" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" ht="15.6">
       <c r="A17" s="4" t="s">
         <v>58</v>
       </c>
@@ -2470,31 +2488,31 @@
         <v>11</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="G17" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="H17" s="6" t="s">
         <v>177</v>
-      </c>
-      <c r="H17" s="6" t="s">
-        <v>178</v>
       </c>
       <c r="I17" s="4">
         <v>4.5</v>
       </c>
       <c r="J17" s="7" t="s">
+        <v>178</v>
+      </c>
+      <c r="K17" s="8" t="s">
         <v>179</v>
-      </c>
-      <c r="K17" s="5" t="s">
-        <v>180</v>
       </c>
       <c r="L17" s="4" t="s">
         <v>44</v>
       </c>
       <c r="M17" s="4" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" ht="15.6">
       <c r="A18" s="4" t="s">
         <v>60</v>
       </c>
@@ -2511,31 +2529,31 @@
         <v>11</v>
       </c>
       <c r="F18" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="G18" s="6" t="s">
         <v>181</v>
       </c>
-      <c r="G18" s="6" t="s">
+      <c r="H18" s="6" t="s">
         <v>182</v>
-      </c>
-      <c r="H18" s="6" t="s">
-        <v>183</v>
       </c>
       <c r="I18" s="4">
         <v>4.7</v>
       </c>
       <c r="J18" s="7" t="s">
+        <v>183</v>
+      </c>
+      <c r="K18" s="8" t="s">
         <v>184</v>
-      </c>
-      <c r="K18" s="5" t="s">
-        <v>185</v>
       </c>
       <c r="L18" s="4" t="s">
         <v>44</v>
       </c>
       <c r="M18" s="4" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" ht="15.6">
       <c r="A19" s="4" t="s">
         <v>62</v>
       </c>
@@ -2552,31 +2570,31 @@
         <v>11</v>
       </c>
       <c r="F19" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="G19" s="6" t="s">
         <v>186</v>
       </c>
-      <c r="G19" s="6" t="s">
+      <c r="H19" s="6" t="s">
         <v>187</v>
-      </c>
-      <c r="H19" s="6" t="s">
-        <v>188</v>
       </c>
       <c r="I19" s="4">
         <v>4.7</v>
       </c>
       <c r="J19" s="7" t="s">
+        <v>188</v>
+      </c>
+      <c r="K19" s="8" t="s">
         <v>189</v>
-      </c>
-      <c r="K19" s="5" t="s">
-        <v>190</v>
       </c>
       <c r="L19" s="4" t="s">
         <v>44</v>
       </c>
       <c r="M19" s="4" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="20" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" ht="15.6">
       <c r="A20" s="4" t="s">
         <v>64</v>
       </c>
@@ -2593,31 +2611,31 @@
         <v>11</v>
       </c>
       <c r="F20" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="G20" s="6" t="s">
         <v>191</v>
       </c>
-      <c r="G20" s="6" t="s">
+      <c r="H20" s="6" t="s">
         <v>192</v>
-      </c>
-      <c r="H20" s="6" t="s">
-        <v>193</v>
       </c>
       <c r="I20" s="4">
         <v>4.7</v>
       </c>
       <c r="J20" s="7" t="s">
+        <v>193</v>
+      </c>
+      <c r="K20" s="8" t="s">
         <v>194</v>
-      </c>
-      <c r="K20" s="5" t="s">
-        <v>195</v>
       </c>
       <c r="L20" s="4" t="s">
         <v>44</v>
       </c>
       <c r="M20" s="4" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="21" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" ht="15.6">
       <c r="A21" s="4" t="s">
         <v>66</v>
       </c>
@@ -2634,31 +2652,31 @@
         <v>11</v>
       </c>
       <c r="F21" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="G21" s="6" t="s">
         <v>196</v>
       </c>
-      <c r="G21" s="6" t="s">
+      <c r="H21" s="6" t="s">
         <v>197</v>
-      </c>
-      <c r="H21" s="6" t="s">
-        <v>198</v>
       </c>
       <c r="I21" s="4">
         <v>4.3</v>
       </c>
       <c r="J21" s="7" t="s">
+        <v>198</v>
+      </c>
+      <c r="K21" s="8" t="s">
         <v>199</v>
-      </c>
-      <c r="K21" s="5" t="s">
-        <v>200</v>
       </c>
       <c r="L21" s="4" t="s">
         <v>44</v>
       </c>
       <c r="M21" s="4" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="22" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" ht="15.6">
       <c r="A22" s="4" t="s">
         <v>68</v>
       </c>
@@ -2675,31 +2693,31 @@
         <v>11</v>
       </c>
       <c r="F22" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="G22" s="6" t="s">
         <v>201</v>
       </c>
-      <c r="G22" s="6" t="s">
+      <c r="H22" s="6" t="s">
         <v>202</v>
-      </c>
-      <c r="H22" s="6" t="s">
-        <v>203</v>
       </c>
       <c r="I22" s="4">
         <v>4.5</v>
       </c>
       <c r="J22" s="7" t="s">
+        <v>203</v>
+      </c>
+      <c r="K22" s="8" t="s">
         <v>204</v>
-      </c>
-      <c r="K22" s="5" t="s">
-        <v>205</v>
       </c>
       <c r="L22" s="4" t="s">
         <v>44</v>
       </c>
       <c r="M22" s="4" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="23" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" ht="15.6">
       <c r="A23" s="4" t="s">
         <v>70</v>
       </c>
@@ -2716,31 +2734,31 @@
         <v>11</v>
       </c>
       <c r="F23" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="G23" s="6" t="s">
         <v>206</v>
       </c>
-      <c r="G23" s="6" t="s">
+      <c r="H23" s="6" t="s">
         <v>207</v>
-      </c>
-      <c r="H23" s="6" t="s">
-        <v>208</v>
       </c>
       <c r="I23" s="4">
         <v>4.0999999999999996</v>
       </c>
       <c r="J23" s="7" t="s">
+        <v>208</v>
+      </c>
+      <c r="K23" s="8" t="s">
         <v>209</v>
-      </c>
-      <c r="K23" s="5" t="s">
-        <v>210</v>
       </c>
       <c r="L23" s="4" t="s">
         <v>44</v>
       </c>
       <c r="M23" s="4" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="24" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" ht="15.6">
       <c r="A24" s="4" t="s">
         <v>72</v>
       </c>
@@ -2754,34 +2772,34 @@
         <v>16</v>
       </c>
       <c r="E24" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="F24" s="4" t="s">
         <v>211</v>
       </c>
-      <c r="F24" s="4" t="s">
+      <c r="G24" s="13" t="s">
         <v>212</v>
       </c>
-      <c r="G24" s="9" t="s">
+      <c r="H24" s="13" t="s">
         <v>213</v>
-      </c>
-      <c r="H24" s="9" t="s">
-        <v>214</v>
       </c>
       <c r="I24" s="4">
         <v>4.7</v>
       </c>
       <c r="J24" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="K24" s="8" t="s">
         <v>215</v>
-      </c>
-      <c r="K24" s="5" t="s">
-        <v>216</v>
       </c>
       <c r="L24" s="4" t="s">
         <v>18</v>
       </c>
       <c r="M24" s="4" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="25" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" ht="15.6">
       <c r="A25" s="4" t="s">
         <v>74</v>
       </c>
@@ -2795,34 +2813,34 @@
         <v>16</v>
       </c>
       <c r="E25" s="4" t="s">
+        <v>216</v>
+      </c>
+      <c r="F25" s="4" t="s">
         <v>217</v>
       </c>
-      <c r="F25" s="4" t="s">
+      <c r="G25" s="6" t="s">
         <v>218</v>
       </c>
-      <c r="G25" s="6" t="s">
+      <c r="H25" s="6" t="s">
         <v>219</v>
-      </c>
-      <c r="H25" s="6" t="s">
-        <v>220</v>
       </c>
       <c r="I25" s="4">
         <v>4.3</v>
       </c>
       <c r="J25" s="7" t="s">
+        <v>220</v>
+      </c>
+      <c r="K25" s="8" t="s">
         <v>221</v>
-      </c>
-      <c r="K25" s="5" t="s">
-        <v>222</v>
       </c>
       <c r="L25" s="4" t="s">
         <v>18</v>
       </c>
       <c r="M25" s="4" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="26" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" ht="15.6">
       <c r="A26" s="4" t="s">
         <v>76</v>
       </c>
@@ -2835,39 +2853,39 @@
       <c r="D26" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="E26" s="5" t="s">
+      <c r="E26" s="8" t="s">
+        <v>222</v>
+      </c>
+      <c r="F26" s="8" t="s">
         <v>223</v>
       </c>
-      <c r="F26" s="5" t="s">
+      <c r="G26" s="11" t="s">
         <v>224</v>
       </c>
-      <c r="G26" s="11" t="s">
+      <c r="H26" s="11" t="s">
         <v>225</v>
       </c>
-      <c r="H26" s="11" t="s">
+      <c r="I26" s="8">
+        <v>4.7</v>
+      </c>
+      <c r="J26" s="12" t="s">
         <v>226</v>
       </c>
-      <c r="I26" s="5">
-        <v>4.7</v>
-      </c>
-      <c r="J26" s="12" t="s">
+      <c r="K26" s="8" t="s">
         <v>227</v>
       </c>
-      <c r="K26" s="5" t="s">
-        <v>228</v>
-      </c>
-      <c r="L26" s="5" t="s">
+      <c r="L26" s="8" t="s">
         <v>18</v>
       </c>
       <c r="M26" s="4" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="27" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" ht="15.6">
       <c r="A27" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="B27" s="5" t="s">
+      <c r="B27" s="8" t="s">
         <v>79</v>
       </c>
       <c r="C27" s="5" t="s">
@@ -2876,865 +2894,865 @@
       <c r="D27" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="E27" s="5" t="s">
+      <c r="E27" s="8" t="s">
+        <v>228</v>
+      </c>
+      <c r="F27" s="8" t="s">
         <v>229</v>
       </c>
-      <c r="F27" s="5" t="s">
+      <c r="G27" s="11" t="s">
         <v>230</v>
       </c>
-      <c r="G27" s="11" t="s">
+      <c r="H27" s="11" t="s">
         <v>231</v>
       </c>
-      <c r="H27" s="11" t="s">
+      <c r="I27" s="8">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="J27" s="12" t="s">
         <v>232</v>
       </c>
-      <c r="I27" s="5">
+      <c r="K27" s="8" t="s">
+        <v>233</v>
+      </c>
+      <c r="L27" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="M27" s="4" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" ht="15.6">
+      <c r="A28" s="14" t="s">
+        <v>80</v>
+      </c>
+      <c r="B28" s="15" t="s">
+        <v>81</v>
+      </c>
+      <c r="C28" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="D28" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="E28" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="F28" s="15" t="s">
+        <v>234</v>
+      </c>
+      <c r="G28" s="16" t="s">
+        <v>235</v>
+      </c>
+      <c r="H28" s="16" t="s">
+        <v>236</v>
+      </c>
+      <c r="I28" s="15">
+        <v>4.8</v>
+      </c>
+      <c r="J28" s="17" t="s">
+        <v>237</v>
+      </c>
+      <c r="K28" s="15" t="s">
+        <v>238</v>
+      </c>
+      <c r="L28" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="M28" s="15" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" ht="15.6">
+      <c r="A29" s="14" t="s">
+        <v>82</v>
+      </c>
+      <c r="B29" s="15" t="s">
+        <v>83</v>
+      </c>
+      <c r="C29" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="D29" s="15" t="s">
+        <v>84</v>
+      </c>
+      <c r="E29" s="15" t="s">
+        <v>228</v>
+      </c>
+      <c r="F29" s="15" t="s">
+        <v>239</v>
+      </c>
+      <c r="G29" s="16" t="s">
+        <v>240</v>
+      </c>
+      <c r="H29" s="16" t="s">
+        <v>241</v>
+      </c>
+      <c r="I29" s="15">
+        <v>4.3</v>
+      </c>
+      <c r="J29" s="17" t="s">
+        <v>242</v>
+      </c>
+      <c r="K29" s="15" t="s">
+        <v>243</v>
+      </c>
+      <c r="L29" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="M29" s="15" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" ht="15.6">
+      <c r="A30" s="14" t="s">
+        <v>85</v>
+      </c>
+      <c r="B30" s="15" t="s">
+        <v>86</v>
+      </c>
+      <c r="C30" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="D30" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="E30" s="15" t="s">
+        <v>244</v>
+      </c>
+      <c r="F30" s="15" t="s">
+        <v>245</v>
+      </c>
+      <c r="G30" s="16" t="s">
+        <v>246</v>
+      </c>
+      <c r="H30" s="16" t="s">
+        <v>247</v>
+      </c>
+      <c r="I30" s="15">
         <v>4.5999999999999996</v>
       </c>
-      <c r="J27" s="12" t="s">
-        <v>233</v>
-      </c>
-      <c r="K27" s="5" t="s">
-        <v>234</v>
-      </c>
-      <c r="L27" s="5" t="s">
+      <c r="J30" s="17" t="s">
+        <v>248</v>
+      </c>
+      <c r="K30" s="15" t="s">
+        <v>249</v>
+      </c>
+      <c r="L30" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="M27" s="4" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="28" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A28" s="13" t="s">
-        <v>80</v>
-      </c>
-      <c r="B28" s="14" t="s">
-        <v>81</v>
-      </c>
-      <c r="C28" s="14" t="s">
+      <c r="M30" s="15" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" ht="15.6">
+      <c r="A31" s="14" t="s">
+        <v>87</v>
+      </c>
+      <c r="B31" s="15" t="s">
+        <v>98</v>
+      </c>
+      <c r="C31" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="D28" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="E28" s="14" t="s">
+      <c r="D31" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="E31" s="15" t="s">
+        <v>250</v>
+      </c>
+      <c r="F31" s="15" t="s">
+        <v>251</v>
+      </c>
+      <c r="G31" s="16" t="s">
+        <v>252</v>
+      </c>
+      <c r="H31" s="16" t="s">
+        <v>253</v>
+      </c>
+      <c r="I31" s="15">
+        <v>4.5</v>
+      </c>
+      <c r="J31" s="17" t="s">
+        <v>254</v>
+      </c>
+      <c r="K31" s="15" t="s">
+        <v>255</v>
+      </c>
+      <c r="L31" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="M31" s="15" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" ht="15.6">
+      <c r="A32" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="B32" s="15" t="s">
+        <v>89</v>
+      </c>
+      <c r="C32" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="D32" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="E32" s="15" t="s">
+        <v>256</v>
+      </c>
+      <c r="F32" s="15" t="s">
+        <v>257</v>
+      </c>
+      <c r="G32" s="16" t="s">
+        <v>258</v>
+      </c>
+      <c r="H32" s="16" t="s">
+        <v>259</v>
+      </c>
+      <c r="I32" s="15">
+        <v>4.5</v>
+      </c>
+      <c r="J32" s="17" t="s">
+        <v>260</v>
+      </c>
+      <c r="K32" s="15" t="s">
+        <v>261</v>
+      </c>
+      <c r="L32" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="M32" s="15" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" ht="15.6">
+      <c r="A33" s="14" t="s">
+        <v>90</v>
+      </c>
+      <c r="B33" s="15" t="s">
+        <v>91</v>
+      </c>
+      <c r="C33" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="D33" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="E33" s="15" t="s">
+        <v>262</v>
+      </c>
+      <c r="F33" s="15" t="s">
+        <v>263</v>
+      </c>
+      <c r="G33" s="16" t="s">
+        <v>264</v>
+      </c>
+      <c r="H33" s="16" t="s">
+        <v>265</v>
+      </c>
+      <c r="I33" s="15">
+        <v>3.2</v>
+      </c>
+      <c r="J33" s="17" t="s">
+        <v>266</v>
+      </c>
+      <c r="K33" s="15" t="s">
+        <v>267</v>
+      </c>
+      <c r="L33" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="M33" s="15" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" ht="15.6">
+      <c r="A34" s="14" t="s">
+        <v>92</v>
+      </c>
+      <c r="B34" s="15" t="s">
+        <v>93</v>
+      </c>
+      <c r="C34" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="D34" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="E34" s="15" t="s">
+        <v>268</v>
+      </c>
+      <c r="F34" s="15" t="s">
+        <v>269</v>
+      </c>
+      <c r="G34" s="16" t="s">
+        <v>270</v>
+      </c>
+      <c r="H34" s="16" t="s">
+        <v>271</v>
+      </c>
+      <c r="I34" s="15">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="J34" s="17" t="s">
+        <v>272</v>
+      </c>
+      <c r="K34" s="15" t="s">
+        <v>273</v>
+      </c>
+      <c r="L34" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="M34" s="15" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" ht="15.6">
+      <c r="A35" s="14" t="s">
+        <v>94</v>
+      </c>
+      <c r="B35" s="15" t="s">
+        <v>95</v>
+      </c>
+      <c r="C35" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="D35" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="E35" s="15" t="s">
+        <v>274</v>
+      </c>
+      <c r="F35" s="15" t="s">
+        <v>275</v>
+      </c>
+      <c r="G35" s="16" t="s">
+        <v>276</v>
+      </c>
+      <c r="H35" s="16" t="s">
+        <v>277</v>
+      </c>
+      <c r="I35" s="15">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="J35" s="17" t="s">
+        <v>278</v>
+      </c>
+      <c r="K35" s="15" t="s">
+        <v>279</v>
+      </c>
+      <c r="L35" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="M35" s="15" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" ht="15.6">
+      <c r="A36" s="14" t="s">
+        <v>96</v>
+      </c>
+      <c r="B36" s="15" t="s">
+        <v>97</v>
+      </c>
+      <c r="C36" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="D36" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="E36" s="15" t="s">
+        <v>280</v>
+      </c>
+      <c r="F36" s="15" t="s">
+        <v>281</v>
+      </c>
+      <c r="G36" s="16" t="s">
+        <v>282</v>
+      </c>
+      <c r="H36" s="16" t="s">
+        <v>283</v>
+      </c>
+      <c r="I36" s="15">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="J36" s="17" t="s">
+        <v>284</v>
+      </c>
+      <c r="K36" s="15" t="s">
+        <v>285</v>
+      </c>
+      <c r="L36" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="M36" s="15" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" ht="15.6">
+      <c r="A37" s="14" t="s">
+        <v>286</v>
+      </c>
+      <c r="B37" s="18" t="s">
+        <v>287</v>
+      </c>
+      <c r="C37" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="D37" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="E37" s="15" t="s">
+        <v>288</v>
+      </c>
+      <c r="F37" s="15" t="s">
+        <v>289</v>
+      </c>
+      <c r="G37" s="16" t="s">
+        <v>290</v>
+      </c>
+      <c r="H37" s="16" t="s">
+        <v>291</v>
+      </c>
+      <c r="I37" s="15">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="J37" s="17" t="s">
+        <v>292</v>
+      </c>
+      <c r="K37" s="15" t="s">
+        <v>293</v>
+      </c>
+      <c r="L37" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="M37" s="15" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" ht="15.6">
+      <c r="A38" s="14" t="s">
+        <v>294</v>
+      </c>
+      <c r="B38" s="18" t="s">
+        <v>295</v>
+      </c>
+      <c r="C38" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="D38" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="E38" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="F28" s="14" t="s">
-        <v>235</v>
-      </c>
-      <c r="G28" s="15" t="s">
-        <v>236</v>
-      </c>
-      <c r="H28" s="15" t="s">
-        <v>237</v>
-      </c>
-      <c r="I28" s="14">
+      <c r="F38" s="15" t="s">
+        <v>296</v>
+      </c>
+      <c r="G38" s="16" t="s">
+        <v>297</v>
+      </c>
+      <c r="H38" s="16" t="s">
+        <v>298</v>
+      </c>
+      <c r="I38" s="15">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="J38" s="17" t="s">
+        <v>299</v>
+      </c>
+      <c r="K38" s="15" t="s">
+        <v>300</v>
+      </c>
+      <c r="L38" s="15" t="s">
+        <v>301</v>
+      </c>
+      <c r="M38" s="15" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" ht="15.6">
+      <c r="A39" s="14" t="s">
+        <v>302</v>
+      </c>
+      <c r="B39" s="18" t="s">
+        <v>303</v>
+      </c>
+      <c r="C39" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="D39" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="E39" s="15" t="s">
+        <v>304</v>
+      </c>
+      <c r="F39" s="15" t="s">
+        <v>305</v>
+      </c>
+      <c r="G39" s="16" t="s">
+        <v>306</v>
+      </c>
+      <c r="H39" s="16" t="s">
+        <v>307</v>
+      </c>
+      <c r="I39" s="15">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="J39" s="17" t="s">
+        <v>308</v>
+      </c>
+      <c r="K39" s="15" t="s">
+        <v>309</v>
+      </c>
+      <c r="L39" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="M39" s="15" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" ht="15.6">
+      <c r="A40" s="14" t="s">
+        <v>310</v>
+      </c>
+      <c r="B40" s="18" t="s">
+        <v>311</v>
+      </c>
+      <c r="C40" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="D40" s="14" t="s">
+        <v>312</v>
+      </c>
+      <c r="E40" s="15" t="s">
+        <v>313</v>
+      </c>
+      <c r="F40" s="15" t="s">
+        <v>314</v>
+      </c>
+      <c r="G40" s="16" t="s">
+        <v>315</v>
+      </c>
+      <c r="H40" s="16" t="s">
+        <v>316</v>
+      </c>
+      <c r="I40" s="15">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="J40" s="17" t="s">
+        <v>317</v>
+      </c>
+      <c r="K40" s="15" t="s">
+        <v>318</v>
+      </c>
+      <c r="L40" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="M40" s="15" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" ht="15.6">
+      <c r="A41" s="14" t="s">
+        <v>319</v>
+      </c>
+      <c r="B41" s="18" t="s">
+        <v>320</v>
+      </c>
+      <c r="C41" s="15" t="s">
+        <v>321</v>
+      </c>
+      <c r="D41" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="E41" s="15" t="s">
+        <v>322</v>
+      </c>
+      <c r="F41" s="15" t="s">
+        <v>323</v>
+      </c>
+      <c r="G41" s="16" t="s">
+        <v>324</v>
+      </c>
+      <c r="H41" s="16" t="s">
+        <v>325</v>
+      </c>
+      <c r="I41" s="15">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="J41" s="17" t="s">
+        <v>326</v>
+      </c>
+      <c r="K41" s="15" t="s">
+        <v>327</v>
+      </c>
+      <c r="L41" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="M41" s="15" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13" ht="15.6">
+      <c r="A42" s="14" t="s">
+        <v>328</v>
+      </c>
+      <c r="B42" s="18" t="s">
+        <v>329</v>
+      </c>
+      <c r="C42" s="15" t="s">
+        <v>321</v>
+      </c>
+      <c r="D42" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="E42" s="15" t="s">
+        <v>330</v>
+      </c>
+      <c r="F42" s="15" t="s">
+        <v>331</v>
+      </c>
+      <c r="G42" s="16" t="s">
+        <v>332</v>
+      </c>
+      <c r="H42" s="16" t="s">
+        <v>333</v>
+      </c>
+      <c r="I42" s="15">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="J42" s="17" t="s">
+        <v>334</v>
+      </c>
+      <c r="K42" s="15" t="s">
+        <v>335</v>
+      </c>
+      <c r="L42" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="M42" s="15" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13" ht="15.6">
+      <c r="A43" s="14" t="s">
+        <v>336</v>
+      </c>
+      <c r="B43" s="18" t="s">
+        <v>337</v>
+      </c>
+      <c r="C43" s="19" t="s">
+        <v>338</v>
+      </c>
+      <c r="D43" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="E43" s="15" t="s">
+        <v>339</v>
+      </c>
+      <c r="F43" s="15" t="s">
+        <v>340</v>
+      </c>
+      <c r="G43" s="20" t="s">
+        <v>341</v>
+      </c>
+      <c r="H43" s="16" t="s">
+        <v>342</v>
+      </c>
+      <c r="I43" s="15">
         <v>4.8</v>
       </c>
-      <c r="J28" s="16" t="s">
-        <v>238</v>
-      </c>
-      <c r="K28" s="14" t="s">
-        <v>239</v>
-      </c>
-      <c r="L28" s="14" t="s">
-        <v>44</v>
-      </c>
-      <c r="M28" s="14" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="29" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A29" s="13" t="s">
-        <v>82</v>
-      </c>
-      <c r="B29" s="14" t="s">
-        <v>83</v>
-      </c>
-      <c r="C29" s="14" t="s">
+      <c r="J43" s="17" t="s">
+        <v>343</v>
+      </c>
+      <c r="K43" s="15" t="s">
+        <v>344</v>
+      </c>
+      <c r="L43" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="M43" s="21" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13" ht="15.6">
+      <c r="A44" s="14" t="s">
+        <v>346</v>
+      </c>
+      <c r="B44" s="18" t="s">
+        <v>347</v>
+      </c>
+      <c r="C44" s="19" t="s">
+        <v>348</v>
+      </c>
+      <c r="D44" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="E44" s="15" t="s">
+        <v>349</v>
+      </c>
+      <c r="F44" s="15" t="s">
+        <v>350</v>
+      </c>
+      <c r="G44" s="16" t="s">
+        <v>351</v>
+      </c>
+      <c r="H44" s="16" t="s">
+        <v>352</v>
+      </c>
+      <c r="I44" s="15">
+        <v>4.5</v>
+      </c>
+      <c r="J44" s="17" t="s">
+        <v>353</v>
+      </c>
+      <c r="K44" s="15" t="s">
+        <v>354</v>
+      </c>
+      <c r="L44" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="M44" s="21" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13" ht="15.6">
+      <c r="A45" s="14" t="s">
+        <v>355</v>
+      </c>
+      <c r="B45" s="18" t="s">
+        <v>356</v>
+      </c>
+      <c r="C45" s="22" t="s">
+        <v>338</v>
+      </c>
+      <c r="D45" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="E45" s="15" t="s">
+        <v>357</v>
+      </c>
+      <c r="F45" s="15" t="s">
+        <v>358</v>
+      </c>
+      <c r="G45" s="16" t="s">
+        <v>359</v>
+      </c>
+      <c r="H45" s="16" t="s">
+        <v>360</v>
+      </c>
+      <c r="I45" s="15">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="J45" s="17" t="s">
+        <v>361</v>
+      </c>
+      <c r="K45" s="15" t="s">
+        <v>362</v>
+      </c>
+      <c r="L45" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="M45" s="21" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13" ht="15.6">
+      <c r="A46" s="14" t="s">
+        <v>363</v>
+      </c>
+      <c r="B46" s="18" t="s">
+        <v>364</v>
+      </c>
+      <c r="C46" s="22" t="s">
+        <v>365</v>
+      </c>
+      <c r="D46" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="E46" s="15" t="s">
+        <v>366</v>
+      </c>
+      <c r="F46" s="15" t="s">
+        <v>367</v>
+      </c>
+      <c r="G46" s="16" t="s">
+        <v>368</v>
+      </c>
+      <c r="H46" s="16" t="s">
+        <v>369</v>
+      </c>
+      <c r="I46" s="15">
+        <v>4.7</v>
+      </c>
+      <c r="J46" s="17" t="s">
+        <v>370</v>
+      </c>
+      <c r="K46" s="15" t="s">
+        <v>371</v>
+      </c>
+      <c r="L46" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="M46" s="15" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13" ht="15.6">
+      <c r="A47" s="14" t="s">
+        <v>372</v>
+      </c>
+      <c r="B47" s="18" t="s">
+        <v>373</v>
+      </c>
+      <c r="C47" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="D29" s="14" t="s">
-        <v>84</v>
-      </c>
-      <c r="E29" s="14" t="s">
-        <v>229</v>
-      </c>
-      <c r="F29" s="14" t="s">
-        <v>240</v>
-      </c>
-      <c r="G29" s="15" t="s">
-        <v>241</v>
-      </c>
-      <c r="H29" s="15" t="s">
-        <v>242</v>
-      </c>
-      <c r="I29" s="14">
-        <v>4.3</v>
-      </c>
-      <c r="J29" s="16" t="s">
-        <v>243</v>
-      </c>
-      <c r="K29" s="14" t="s">
-        <v>244</v>
-      </c>
-      <c r="L29" s="14" t="s">
+      <c r="D47" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="E47" s="15" t="s">
+        <v>374</v>
+      </c>
+      <c r="F47" s="15" t="s">
+        <v>375</v>
+      </c>
+      <c r="G47" s="16" t="s">
+        <v>376</v>
+      </c>
+      <c r="H47" s="16" t="s">
+        <v>377</v>
+      </c>
+      <c r="I47" s="15">
+        <v>4.7</v>
+      </c>
+      <c r="J47" s="17" t="s">
+        <v>378</v>
+      </c>
+      <c r="K47" s="15" t="s">
+        <v>379</v>
+      </c>
+      <c r="L47" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="M29" s="14" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="30" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A30" s="13" t="s">
-        <v>85</v>
-      </c>
-      <c r="B30" s="14" t="s">
-        <v>86</v>
-      </c>
-      <c r="C30" s="14" t="s">
+      <c r="M47" s="15" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="48" spans="1:13" ht="15.6">
+      <c r="A48" s="14" t="s">
+        <v>380</v>
+      </c>
+      <c r="B48" s="23" t="s">
+        <v>36</v>
+      </c>
+      <c r="C48" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="D30" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="E30" s="14" t="s">
-        <v>245</v>
-      </c>
-      <c r="F30" s="14" t="s">
-        <v>246</v>
-      </c>
-      <c r="G30" s="15" t="s">
-        <v>247</v>
-      </c>
-      <c r="H30" s="15" t="s">
-        <v>248</v>
-      </c>
-      <c r="I30" s="14">
-        <v>4.5999999999999996</v>
-      </c>
-      <c r="J30" s="16" t="s">
-        <v>249</v>
-      </c>
-      <c r="K30" s="14" t="s">
-        <v>250</v>
-      </c>
-      <c r="L30" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="M30" s="14" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="31" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A31" s="13" t="s">
-        <v>87</v>
-      </c>
-      <c r="B31" s="14" t="s">
-        <v>99</v>
-      </c>
-      <c r="C31" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="D31" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="E31" s="14" t="s">
-        <v>251</v>
-      </c>
-      <c r="F31" s="14" t="s">
-        <v>252</v>
-      </c>
-      <c r="G31" s="15" t="s">
-        <v>253</v>
-      </c>
-      <c r="H31" s="15" t="s">
-        <v>254</v>
-      </c>
-      <c r="I31" s="14">
-        <v>4.5</v>
-      </c>
-      <c r="J31" s="16" t="s">
-        <v>255</v>
-      </c>
-      <c r="K31" s="14" t="s">
-        <v>256</v>
-      </c>
-      <c r="L31" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="M31" s="14" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="32" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A32" s="13" t="s">
-        <v>88</v>
-      </c>
-      <c r="B32" s="14" t="s">
-        <v>89</v>
-      </c>
-      <c r="C32" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="D32" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="E32" s="14" t="s">
-        <v>257</v>
-      </c>
-      <c r="F32" s="14" t="s">
-        <v>258</v>
-      </c>
-      <c r="G32" s="15" t="s">
-        <v>259</v>
-      </c>
-      <c r="H32" s="15" t="s">
-        <v>260</v>
-      </c>
-      <c r="I32" s="14">
-        <v>4.5</v>
-      </c>
-      <c r="J32" s="16" t="s">
-        <v>261</v>
-      </c>
-      <c r="K32" s="14" t="s">
-        <v>262</v>
-      </c>
-      <c r="L32" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="M32" s="14" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="33" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A33" s="13" t="s">
-        <v>90</v>
-      </c>
-      <c r="B33" s="14" t="s">
-        <v>91</v>
-      </c>
-      <c r="C33" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="D33" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="E33" s="14" t="s">
-        <v>263</v>
-      </c>
-      <c r="F33" s="14" t="s">
-        <v>264</v>
-      </c>
-      <c r="G33" s="15" t="s">
-        <v>265</v>
-      </c>
-      <c r="H33" s="15" t="s">
-        <v>266</v>
-      </c>
-      <c r="I33" s="14">
-        <v>3.2</v>
-      </c>
-      <c r="J33" s="16" t="s">
-        <v>267</v>
-      </c>
-      <c r="K33" s="14" t="s">
-        <v>268</v>
-      </c>
-      <c r="L33" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="M33" s="14" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="34" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A34" s="13" t="s">
-        <v>92</v>
-      </c>
-      <c r="B34" s="14" t="s">
-        <v>93</v>
-      </c>
-      <c r="C34" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="D34" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="E34" s="14" t="s">
-        <v>269</v>
-      </c>
-      <c r="F34" s="14" t="s">
-        <v>270</v>
-      </c>
-      <c r="G34" s="15" t="s">
-        <v>271</v>
-      </c>
-      <c r="H34" s="15" t="s">
-        <v>272</v>
-      </c>
-      <c r="I34" s="14">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="J34" s="16" t="s">
-        <v>273</v>
-      </c>
-      <c r="K34" s="14" t="s">
-        <v>94</v>
-      </c>
-      <c r="L34" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="M34" s="14" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="35" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A35" s="13" t="s">
-        <v>95</v>
-      </c>
-      <c r="B35" s="14" t="s">
-        <v>96</v>
-      </c>
-      <c r="C35" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="D35" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="E35" s="14" t="s">
-        <v>274</v>
-      </c>
-      <c r="F35" s="14" t="s">
-        <v>275</v>
-      </c>
-      <c r="G35" s="15" t="s">
-        <v>276</v>
-      </c>
-      <c r="H35" s="15" t="s">
-        <v>277</v>
-      </c>
-      <c r="I35" s="14">
-        <v>4.5999999999999996</v>
-      </c>
-      <c r="J35" s="16" t="s">
-        <v>278</v>
-      </c>
-      <c r="K35" s="14" t="s">
-        <v>279</v>
-      </c>
-      <c r="L35" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="M35" s="14" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="36" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A36" s="13" t="s">
-        <v>97</v>
-      </c>
-      <c r="B36" s="14" t="s">
-        <v>98</v>
-      </c>
-      <c r="C36" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="D36" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="E36" s="14" t="s">
-        <v>280</v>
-      </c>
-      <c r="F36" s="14" t="s">
-        <v>281</v>
-      </c>
-      <c r="G36" s="15" t="s">
-        <v>282</v>
-      </c>
-      <c r="H36" s="15" t="s">
-        <v>283</v>
-      </c>
-      <c r="I36" s="14">
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="J36" s="16" t="s">
-        <v>284</v>
-      </c>
-      <c r="K36" s="14" t="s">
-        <v>285</v>
-      </c>
-      <c r="L36" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="M36" s="14" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="37" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A37" s="13" t="s">
-        <v>286</v>
-      </c>
-      <c r="B37" s="17" t="s">
-        <v>287</v>
-      </c>
-      <c r="C37" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="D37" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="E37" s="14" t="s">
-        <v>288</v>
-      </c>
-      <c r="F37" s="14" t="s">
-        <v>289</v>
-      </c>
-      <c r="G37" s="15" t="s">
-        <v>290</v>
-      </c>
-      <c r="H37" s="15" t="s">
-        <v>291</v>
-      </c>
-      <c r="I37" s="14">
-        <v>4.5999999999999996</v>
-      </c>
-      <c r="J37" s="16" t="s">
-        <v>292</v>
-      </c>
-      <c r="K37" s="14" t="s">
-        <v>293</v>
-      </c>
-      <c r="L37" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="M37" s="14" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="38" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A38" s="13" t="s">
-        <v>294</v>
-      </c>
-      <c r="B38" s="17" t="s">
-        <v>295</v>
-      </c>
-      <c r="C38" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="D38" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="E38" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="F38" s="14" t="s">
-        <v>296</v>
-      </c>
-      <c r="G38" s="15" t="s">
-        <v>297</v>
-      </c>
-      <c r="H38" s="15" t="s">
-        <v>298</v>
-      </c>
-      <c r="I38" s="14">
-        <v>4.5999999999999996</v>
-      </c>
-      <c r="J38" s="16" t="s">
-        <v>299</v>
-      </c>
-      <c r="K38" s="14" t="s">
-        <v>300</v>
-      </c>
-      <c r="L38" s="14" t="s">
-        <v>301</v>
-      </c>
-      <c r="M38" s="14" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="39" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A39" s="13" t="s">
-        <v>302</v>
-      </c>
-      <c r="B39" s="17" t="s">
-        <v>303</v>
-      </c>
-      <c r="C39" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="D39" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="E39" s="14" t="s">
-        <v>304</v>
-      </c>
-      <c r="F39" s="14" t="s">
-        <v>305</v>
-      </c>
-      <c r="G39" s="15" t="s">
-        <v>306</v>
-      </c>
-      <c r="H39" s="15" t="s">
-        <v>307</v>
-      </c>
-      <c r="I39" s="14">
-        <v>4.9000000000000004</v>
-      </c>
-      <c r="J39" s="16" t="s">
-        <v>308</v>
-      </c>
-      <c r="K39" s="14" t="s">
-        <v>309</v>
-      </c>
-      <c r="L39" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="M39" s="14" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="40" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A40" s="13" t="s">
-        <v>310</v>
-      </c>
-      <c r="B40" s="17" t="s">
-        <v>311</v>
-      </c>
-      <c r="C40" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="D40" s="13" t="s">
-        <v>312</v>
-      </c>
-      <c r="E40" s="14" t="s">
-        <v>313</v>
-      </c>
-      <c r="F40" s="14" t="s">
-        <v>314</v>
-      </c>
-      <c r="G40" s="15" t="s">
-        <v>315</v>
-      </c>
-      <c r="H40" s="15" t="s">
-        <v>316</v>
-      </c>
-      <c r="I40" s="14">
-        <v>4.9000000000000004</v>
-      </c>
-      <c r="J40" s="16" t="s">
-        <v>317</v>
-      </c>
-      <c r="K40" s="14" t="s">
-        <v>318</v>
-      </c>
-      <c r="L40" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="M40" s="14" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="41" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A41" s="13" t="s">
-        <v>319</v>
-      </c>
-      <c r="B41" s="17" t="s">
-        <v>320</v>
-      </c>
-      <c r="C41" s="14" t="s">
-        <v>321</v>
-      </c>
-      <c r="D41" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="E41" s="14" t="s">
-        <v>322</v>
-      </c>
-      <c r="F41" s="14" t="s">
-        <v>323</v>
-      </c>
-      <c r="G41" s="15" t="s">
-        <v>324</v>
-      </c>
-      <c r="H41" s="15" t="s">
-        <v>325</v>
-      </c>
-      <c r="I41" s="14">
-        <v>4.9000000000000004</v>
-      </c>
-      <c r="J41" s="16" t="s">
-        <v>326</v>
-      </c>
-      <c r="K41" s="14" t="s">
-        <v>327</v>
-      </c>
-      <c r="L41" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="M41" s="14" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="42" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A42" s="13" t="s">
-        <v>328</v>
-      </c>
-      <c r="B42" s="17" t="s">
-        <v>329</v>
-      </c>
-      <c r="C42" s="14" t="s">
-        <v>321</v>
-      </c>
-      <c r="D42" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="E42" s="14" t="s">
-        <v>330</v>
-      </c>
-      <c r="F42" s="14" t="s">
-        <v>331</v>
-      </c>
-      <c r="G42" s="15" t="s">
-        <v>332</v>
-      </c>
-      <c r="H42" s="15" t="s">
-        <v>333</v>
-      </c>
-      <c r="I42" s="14">
-        <v>4.5999999999999996</v>
-      </c>
-      <c r="J42" s="16" t="s">
-        <v>334</v>
-      </c>
-      <c r="K42" s="14" t="s">
-        <v>335</v>
-      </c>
-      <c r="L42" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="M42" s="14" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="43" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A43" s="13" t="s">
-        <v>336</v>
-      </c>
-      <c r="B43" s="17" t="s">
-        <v>337</v>
-      </c>
-      <c r="C43" s="18" t="s">
-        <v>338</v>
-      </c>
-      <c r="D43" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="E43" s="14" t="s">
-        <v>339</v>
-      </c>
-      <c r="F43" s="14" t="s">
-        <v>340</v>
-      </c>
-      <c r="G43" s="19" t="s">
-        <v>341</v>
-      </c>
-      <c r="H43" s="15" t="s">
-        <v>342</v>
-      </c>
-      <c r="I43" s="14">
-        <v>4.8</v>
-      </c>
-      <c r="J43" s="16" t="s">
-        <v>343</v>
-      </c>
-      <c r="K43" s="14" t="s">
-        <v>344</v>
-      </c>
-      <c r="L43" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="M43" s="20" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="44" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A44" s="13" t="s">
-        <v>346</v>
-      </c>
-      <c r="B44" s="17" t="s">
-        <v>347</v>
-      </c>
-      <c r="C44" s="18" t="s">
-        <v>348</v>
-      </c>
-      <c r="D44" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="E44" s="14" t="s">
-        <v>349</v>
-      </c>
-      <c r="F44" s="14" t="s">
-        <v>350</v>
-      </c>
-      <c r="G44" s="15" t="s">
-        <v>351</v>
-      </c>
-      <c r="H44" s="15" t="s">
-        <v>352</v>
-      </c>
-      <c r="I44" s="14">
-        <v>4.5</v>
-      </c>
-      <c r="J44" s="16" t="s">
-        <v>353</v>
-      </c>
-      <c r="K44" s="14" t="s">
-        <v>354</v>
-      </c>
-      <c r="L44" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="M44" s="20" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="45" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A45" s="13" t="s">
-        <v>355</v>
-      </c>
-      <c r="B45" s="17" t="s">
-        <v>356</v>
-      </c>
-      <c r="C45" s="20" t="s">
-        <v>338</v>
-      </c>
-      <c r="D45" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="E45" s="14" t="s">
-        <v>357</v>
-      </c>
-      <c r="F45" s="14" t="s">
-        <v>358</v>
-      </c>
-      <c r="G45" s="15" t="s">
-        <v>359</v>
-      </c>
-      <c r="H45" s="15" t="s">
-        <v>360</v>
-      </c>
-      <c r="I45" s="14">
-        <v>4.9000000000000004</v>
-      </c>
-      <c r="J45" s="16" t="s">
-        <v>361</v>
-      </c>
-      <c r="K45" s="14" t="s">
-        <v>362</v>
-      </c>
-      <c r="L45" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="M45" s="20" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="46" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A46" s="13" t="s">
-        <v>363</v>
-      </c>
-      <c r="B46" s="17" t="s">
-        <v>364</v>
-      </c>
-      <c r="C46" s="20" t="s">
-        <v>365</v>
-      </c>
-      <c r="D46" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="E46" s="14" t="s">
-        <v>366</v>
-      </c>
-      <c r="F46" s="14" t="s">
-        <v>367</v>
-      </c>
-      <c r="G46" s="15" t="s">
-        <v>368</v>
-      </c>
-      <c r="H46" s="15" t="s">
-        <v>369</v>
-      </c>
-      <c r="I46" s="14">
-        <v>4.7</v>
-      </c>
-      <c r="J46" s="16" t="s">
-        <v>370</v>
-      </c>
-      <c r="K46" s="14" t="s">
-        <v>371</v>
-      </c>
-      <c r="L46" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="M46" s="14" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="47" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A47" s="13" t="s">
-        <v>372</v>
-      </c>
-      <c r="B47" s="17" t="s">
-        <v>373</v>
-      </c>
-      <c r="C47" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="D47" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="E47" s="14" t="s">
-        <v>374</v>
-      </c>
-      <c r="F47" s="14" t="s">
-        <v>375</v>
-      </c>
-      <c r="G47" s="15" t="s">
-        <v>376</v>
-      </c>
-      <c r="H47" s="15" t="s">
-        <v>377</v>
-      </c>
-      <c r="I47" s="14">
-        <v>4.7</v>
-      </c>
-      <c r="J47" s="16" t="s">
-        <v>378</v>
-      </c>
-      <c r="K47" s="14" t="s">
-        <v>379</v>
-      </c>
-      <c r="L47" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="M47" s="14" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="48" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A48" s="13" t="s">
-        <v>380</v>
-      </c>
-      <c r="B48" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="C48" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="D48" s="13" t="s">
+      <c r="D48" s="14" t="s">
         <v>16</v>
       </c>
       <c r="E48" s="5" t="s">
@@ -3743,39 +3761,39 @@
       <c r="F48" s="5" t="s">
         <v>382</v>
       </c>
-      <c r="G48" s="21" t="s">
+      <c r="G48" s="24" t="s">
         <v>383</v>
       </c>
-      <c r="H48" s="21" t="s">
+      <c r="H48" s="24" t="s">
         <v>384</v>
       </c>
       <c r="I48" s="5">
         <v>4.3</v>
       </c>
-      <c r="J48" s="12" t="s">
+      <c r="J48" s="25" t="s">
         <v>385</v>
       </c>
-      <c r="K48" s="14" t="s">
+      <c r="K48" s="15" t="s">
         <v>386</v>
       </c>
-      <c r="L48" s="14" t="s">
+      <c r="L48" s="15" t="s">
         <v>18</v>
       </c>
       <c r="M48" s="5" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="49" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A49" s="13" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="49" spans="1:13" ht="15.6">
+      <c r="A49" s="14" t="s">
         <v>387</v>
       </c>
-      <c r="B49" s="10" t="s">
+      <c r="B49" s="23" t="s">
         <v>388</v>
       </c>
       <c r="C49" s="5" t="s">
         <v>389</v>
       </c>
-      <c r="D49" s="13" t="s">
+      <c r="D49" s="14" t="s">
         <v>16</v>
       </c>
       <c r="E49" s="5" t="s">
@@ -3784,39 +3802,39 @@
       <c r="F49" s="5" t="s">
         <v>391</v>
       </c>
-      <c r="G49" s="21" t="s">
+      <c r="G49" s="24" t="s">
         <v>392</v>
       </c>
-      <c r="H49" s="21" t="s">
+      <c r="H49" s="24" t="s">
         <v>393</v>
       </c>
       <c r="I49" s="5">
         <v>4.3</v>
       </c>
-      <c r="J49" s="12" t="s">
+      <c r="J49" s="25" t="s">
         <v>394</v>
       </c>
-      <c r="K49" s="14" t="s">
+      <c r="K49" s="15" t="s">
         <v>395</v>
       </c>
-      <c r="L49" s="14" t="s">
+      <c r="L49" s="15" t="s">
         <v>18</v>
       </c>
       <c r="M49" s="5" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="50" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A50" s="13" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="50" spans="1:13" ht="15.6">
+      <c r="A50" s="14" t="s">
         <v>396</v>
       </c>
-      <c r="B50" s="10" t="s">
+      <c r="B50" s="23" t="s">
         <v>397</v>
       </c>
       <c r="C50" s="5" t="s">
         <v>389</v>
       </c>
-      <c r="D50" s="13" t="s">
+      <c r="D50" s="14" t="s">
         <v>16</v>
       </c>
       <c r="E50" s="5" t="s">
@@ -3825,39 +3843,39 @@
       <c r="F50" s="5" t="s">
         <v>399</v>
       </c>
-      <c r="G50" s="21" t="s">
+      <c r="G50" s="24" t="s">
         <v>400</v>
       </c>
-      <c r="H50" s="21" t="s">
+      <c r="H50" s="24" t="s">
         <v>401</v>
       </c>
       <c r="I50" s="5">
         <v>4.5999999999999996</v>
       </c>
-      <c r="J50" s="12" t="s">
+      <c r="J50" s="25" t="s">
         <v>402</v>
       </c>
-      <c r="K50" s="14" t="s">
+      <c r="K50" s="15" t="s">
         <v>403</v>
       </c>
-      <c r="L50" s="14" t="s">
+      <c r="L50" s="15" t="s">
         <v>18</v>
       </c>
       <c r="M50" s="5" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="51" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A51" s="13" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="51" spans="1:13" ht="15.6">
+      <c r="A51" s="14" t="s">
         <v>404</v>
       </c>
-      <c r="B51" s="10" t="s">
+      <c r="B51" s="23" t="s">
         <v>405</v>
       </c>
       <c r="C51" s="5" t="s">
         <v>406</v>
       </c>
-      <c r="D51" s="13" t="s">
+      <c r="D51" s="14" t="s">
         <v>16</v>
       </c>
       <c r="E51" s="5" t="s">
@@ -3866,39 +3884,39 @@
       <c r="F51" s="5" t="s">
         <v>407</v>
       </c>
-      <c r="G51" s="21" t="s">
+      <c r="G51" s="24" t="s">
         <v>408</v>
       </c>
-      <c r="H51" s="21" t="s">
+      <c r="H51" s="24" t="s">
         <v>409</v>
       </c>
       <c r="I51" s="5">
         <v>4.3</v>
       </c>
-      <c r="J51" s="12" t="s">
+      <c r="J51" s="25" t="s">
         <v>410</v>
       </c>
-      <c r="K51" s="14" t="s">
+      <c r="K51" s="15" t="s">
         <v>411</v>
       </c>
       <c r="L51" s="5" t="s">
         <v>44</v>
       </c>
       <c r="M51" s="5" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="52" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A52" s="13" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="52" spans="1:13" ht="15.6">
+      <c r="A52" s="14" t="s">
         <v>412</v>
       </c>
-      <c r="B52" s="10" t="s">
+      <c r="B52" s="23" t="s">
         <v>413</v>
       </c>
       <c r="C52" s="5" t="s">
         <v>406</v>
       </c>
-      <c r="D52" s="13" t="s">
+      <c r="D52" s="14" t="s">
         <v>16</v>
       </c>
       <c r="E52" s="5" t="s">
@@ -3907,81 +3925,81 @@
       <c r="F52" s="5" t="s">
         <v>415</v>
       </c>
-      <c r="G52" s="21" t="s">
+      <c r="G52" s="24" t="s">
         <v>416</v>
       </c>
-      <c r="H52" s="21" t="s">
+      <c r="H52" s="24" t="s">
         <v>417</v>
       </c>
       <c r="I52" s="5">
         <v>4.9000000000000004</v>
       </c>
-      <c r="J52" s="12" t="s">
+      <c r="J52" s="25" t="s">
         <v>418</v>
       </c>
-      <c r="K52" s="14" t="s">
+      <c r="K52" s="15" t="s">
         <v>419</v>
       </c>
-      <c r="L52" s="14" t="s">
+      <c r="L52" s="15" t="s">
         <v>18</v>
       </c>
       <c r="M52" s="5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="J2" r:id="rId1" xr:uid="{CDCF929D-3F93-4EA6-89CE-DF0CD0B862CF}"/>
-    <hyperlink ref="J3" r:id="rId2" xr:uid="{5BA49BA5-F88B-4516-AD35-8DFFF1D23037}"/>
-    <hyperlink ref="J4" r:id="rId3" xr:uid="{3505B3D9-4186-445D-B5D0-0BA970259669}"/>
-    <hyperlink ref="J5" r:id="rId4" xr:uid="{7D087BEC-941E-45AE-929A-93D3709BD73A}"/>
-    <hyperlink ref="J6" r:id="rId5" xr:uid="{FF854E6C-30E5-47F8-BA6B-0794BAABDD9D}"/>
-    <hyperlink ref="J7" r:id="rId6" xr:uid="{0646CCB0-1850-476F-9CCA-22088FD55B26}"/>
-    <hyperlink ref="J8" r:id="rId7" xr:uid="{6AAB5585-437C-4F79-A572-A26CBC85200E}"/>
-    <hyperlink ref="J9" r:id="rId8" xr:uid="{C5DDB248-97FB-48D0-860C-775F2ABAAA9D}"/>
-    <hyperlink ref="J10" r:id="rId9" xr:uid="{FAFE970F-33B1-43B1-B427-3C3C9C93C011}"/>
-    <hyperlink ref="J11" r:id="rId10" xr:uid="{FC2166CF-C102-464D-9FDA-3AF98F5B3601}"/>
-    <hyperlink ref="J12" r:id="rId11" xr:uid="{D934C074-F0B2-4832-9905-BDB7ACD89F4D}"/>
-    <hyperlink ref="J13" r:id="rId12" xr:uid="{CB03D343-C5D9-4B9C-8D8E-7017BFA29723}"/>
-    <hyperlink ref="J14" r:id="rId13" xr:uid="{26A1A466-D2C3-4D2D-8262-4EB197949143}"/>
-    <hyperlink ref="J15" r:id="rId14" xr:uid="{88E8932E-E209-4A53-B071-69E593060BC3}"/>
-    <hyperlink ref="J16" r:id="rId15" xr:uid="{5CB1469D-9F5E-48F3-83EC-6883B62AB633}"/>
-    <hyperlink ref="J17" r:id="rId16" xr:uid="{2F85593E-C13F-4594-B04E-88FCB963CCCE}"/>
-    <hyperlink ref="J18" r:id="rId17" xr:uid="{D612EFF9-F7BE-4156-915F-B22987B28735}"/>
-    <hyperlink ref="J19" r:id="rId18" xr:uid="{F562A984-5FFE-460B-94D4-35AD273F963E}"/>
-    <hyperlink ref="J20" r:id="rId19" xr:uid="{4AB5CC22-DAE1-4791-9026-3A567339DCE6}"/>
-    <hyperlink ref="J21" r:id="rId20" xr:uid="{990BA7A4-3757-42BE-B370-3D01A51F580C}"/>
-    <hyperlink ref="J22" r:id="rId21" xr:uid="{D98E8F97-F38F-42C0-BD84-0AAD85E3B361}"/>
-    <hyperlink ref="J23" r:id="rId22" xr:uid="{3610F491-7A36-4926-B819-63C44CD43004}"/>
-    <hyperlink ref="J24" r:id="rId23" xr:uid="{8A9FF99F-A69E-4CBE-B5B5-80440BC425A1}"/>
-    <hyperlink ref="J25" r:id="rId24" xr:uid="{50C1AF6C-85E6-48D3-96EF-102D78E50B9E}"/>
-    <hyperlink ref="J26" r:id="rId25" xr:uid="{8C858C36-0CBA-4511-8D39-473E87625719}"/>
-    <hyperlink ref="J27" r:id="rId26" xr:uid="{92DFC153-D576-4B27-A38D-6DF4A9496B8E}"/>
-    <hyperlink ref="J28" r:id="rId27" xr:uid="{6C149969-4FA3-4768-83AD-E36022E8F721}"/>
-    <hyperlink ref="J29" r:id="rId28" xr:uid="{B5744B9D-E017-429F-BA8A-F1554EA2B3FE}"/>
-    <hyperlink ref="J30" r:id="rId29" xr:uid="{FE25A4D6-6B54-4F63-BFE7-963CA9C10B15}"/>
-    <hyperlink ref="J31" r:id="rId30" xr:uid="{00CDC88B-7042-4B31-8291-600F7D6CD655}"/>
-    <hyperlink ref="J32" r:id="rId31" xr:uid="{143A7AA9-AAFA-4E2F-9D21-FFD620CFF49C}"/>
-    <hyperlink ref="J33" r:id="rId32" xr:uid="{8ADB1B85-9BCB-4381-933E-BBB67AFD66E4}"/>
-    <hyperlink ref="J34" r:id="rId33" xr:uid="{8FF141DA-03A6-4F2C-B3C3-3DB90E38D290}"/>
-    <hyperlink ref="J35" r:id="rId34" xr:uid="{E3D318B9-9E05-4C0E-914A-7535DC6FEDDF}"/>
-    <hyperlink ref="J36" r:id="rId35" xr:uid="{DAD7E640-4AE8-4247-BCF0-25907DE8A5E4}"/>
-    <hyperlink ref="J37" r:id="rId36" xr:uid="{83972A79-BC5A-415D-96C0-085346578A15}"/>
-    <hyperlink ref="J38" r:id="rId37" xr:uid="{88E4C936-E737-4511-8005-70E818C200B7}"/>
-    <hyperlink ref="J39" r:id="rId38" xr:uid="{16F0E6E5-3889-49C9-A085-FC0C15873B60}"/>
-    <hyperlink ref="J40" r:id="rId39" xr:uid="{5DA1450F-8C32-467E-B455-4BF7A8143424}"/>
-    <hyperlink ref="J41" r:id="rId40" xr:uid="{3F0F4B36-D3C7-4EE6-94A8-0775A37C3CEA}"/>
-    <hyperlink ref="J42" r:id="rId41" xr:uid="{C3C44677-EDCC-4112-ACD4-8AED04CA76A7}"/>
-    <hyperlink ref="J43" r:id="rId42" xr:uid="{68206919-E5D5-4CFB-B69A-468DB6E28C8F}"/>
-    <hyperlink ref="J44" r:id="rId43" xr:uid="{7E6B6096-597A-4175-8A12-83122297AB9D}"/>
-    <hyperlink ref="J45" r:id="rId44" xr:uid="{BB3ADCF2-C3A4-49F0-BA18-596C360CD12C}"/>
-    <hyperlink ref="J46" r:id="rId45" xr:uid="{80E5AFE5-F3E0-4DEB-901C-9BE910BD7CBA}"/>
-    <hyperlink ref="J47" r:id="rId46" xr:uid="{374385D1-CFA5-4159-8019-AF5029D51208}"/>
-    <hyperlink ref="J48" r:id="rId47" xr:uid="{F2520922-FE1E-401F-9467-864DD4F0EEBD}"/>
-    <hyperlink ref="J49" r:id="rId48" xr:uid="{3B6C46D2-9F7A-4E3C-81EA-121BE0DF0DFD}"/>
-    <hyperlink ref="J50" r:id="rId49" xr:uid="{398975A2-9140-477E-A029-5D9B4437FB28}"/>
-    <hyperlink ref="J51" r:id="rId50" xr:uid="{FD381196-4532-4514-8C5A-009B3A74855E}"/>
-    <hyperlink ref="J52" r:id="rId51" xr:uid="{304FDA02-FD8D-4F5B-A6AE-4AF4BD75F69B}"/>
+    <hyperlink ref="J2" r:id="rId1" xr:uid="{5F28E9F7-69B5-4D2E-8916-93933A28ED1B}"/>
+    <hyperlink ref="J3" r:id="rId2" xr:uid="{4C4C617C-03A6-499D-9E2A-4911AAE17DD5}"/>
+    <hyperlink ref="J4" r:id="rId3" xr:uid="{A9A97CD1-D680-47CF-89A0-0B1168691561}"/>
+    <hyperlink ref="J5" r:id="rId4" xr:uid="{68D56107-09D0-4B41-B8ED-982531F7A091}"/>
+    <hyperlink ref="J6" r:id="rId5" xr:uid="{C4C7B9C0-1C91-4560-BFE4-C8AF085A2643}"/>
+    <hyperlink ref="J7" r:id="rId6" xr:uid="{EA7BA35A-A6FD-439F-865A-CA2D902BB11E}"/>
+    <hyperlink ref="J8" r:id="rId7" xr:uid="{EA90B8BC-FA9F-4D03-AD25-E3151EE8C5FD}"/>
+    <hyperlink ref="J9" r:id="rId8" xr:uid="{D832E135-915C-4E16-BDFE-71BAAFEA8959}"/>
+    <hyperlink ref="J10" r:id="rId9" xr:uid="{747792A3-AC9A-4DA7-A606-52AE60FC9328}"/>
+    <hyperlink ref="J11" r:id="rId10" xr:uid="{C193871D-D723-4BFB-B0A9-A51F20F53D1C}"/>
+    <hyperlink ref="J12" r:id="rId11" xr:uid="{20A97227-27E9-4410-B2D5-733B8745BBB5}"/>
+    <hyperlink ref="J13" r:id="rId12" xr:uid="{AD84EF3F-3284-422B-BF67-D869F19CE3BA}"/>
+    <hyperlink ref="J14" r:id="rId13" xr:uid="{F74680C4-6364-4DB3-8454-A23C935089F0}"/>
+    <hyperlink ref="J15" r:id="rId14" xr:uid="{4C988495-994B-47B2-BA46-0001CA2D1395}"/>
+    <hyperlink ref="J16" r:id="rId15" xr:uid="{E473E2A1-1F7C-4DAF-B6F4-582364D857AD}"/>
+    <hyperlink ref="J17" r:id="rId16" xr:uid="{B45DC2DE-8EB7-43E6-883A-A3AF46EC6FC2}"/>
+    <hyperlink ref="J18" r:id="rId17" xr:uid="{BE45B744-753D-40C1-8DED-9E8CA21A7746}"/>
+    <hyperlink ref="J19" r:id="rId18" xr:uid="{93E95BB0-EE23-48CA-A665-E67AB93FEDAF}"/>
+    <hyperlink ref="J20" r:id="rId19" xr:uid="{8BC2BA43-5906-4390-94E9-9517343FA102}"/>
+    <hyperlink ref="J21" r:id="rId20" xr:uid="{7BB9FC83-2F4E-451C-8912-3E4278980B47}"/>
+    <hyperlink ref="J22" r:id="rId21" xr:uid="{22FF56D8-A0BF-4A01-BAA4-29F375D5A1CA}"/>
+    <hyperlink ref="J23" r:id="rId22" xr:uid="{54BB3D09-7D5D-4D95-A093-8D8F5E9363F1}"/>
+    <hyperlink ref="J24" r:id="rId23" xr:uid="{7127EC8E-F1D1-4E0D-A0E3-D08156C4759D}"/>
+    <hyperlink ref="J25" r:id="rId24" xr:uid="{A48FB8E3-23A7-4891-B045-0E0CBD04D32C}"/>
+    <hyperlink ref="J26" r:id="rId25" xr:uid="{3872151D-30BA-4203-BE96-28E663814D2B}"/>
+    <hyperlink ref="J27" r:id="rId26" xr:uid="{AEBB5678-C409-4010-8258-0B84F8681C12}"/>
+    <hyperlink ref="J28" r:id="rId27" xr:uid="{36675695-2279-4D53-BE05-9114FF4E183F}"/>
+    <hyperlink ref="J29" r:id="rId28" xr:uid="{DA7AFC30-C0BE-4D6A-9364-A044C990A057}"/>
+    <hyperlink ref="J30" r:id="rId29" xr:uid="{E99C6923-6BE9-4CE1-961D-A7EA4F689E12}"/>
+    <hyperlink ref="J31" r:id="rId30" xr:uid="{5EFF5CD3-C163-4668-836D-5300D2280660}"/>
+    <hyperlink ref="J32" r:id="rId31" xr:uid="{EE41788C-1A8A-477E-9B87-B94ACB891B04}"/>
+    <hyperlink ref="J33" r:id="rId32" xr:uid="{06A89AE1-36C0-4056-97A5-F2B1EC55FADA}"/>
+    <hyperlink ref="J34" r:id="rId33" xr:uid="{0EF695BA-D2D1-42F8-8F67-DBD1AAA1F539}"/>
+    <hyperlink ref="J35" r:id="rId34" xr:uid="{65DEAC6F-4D4F-4886-8349-3261847B7014}"/>
+    <hyperlink ref="J36" r:id="rId35" xr:uid="{A825F428-A5DB-428E-86D3-338A90FBB5E5}"/>
+    <hyperlink ref="J37" r:id="rId36" xr:uid="{CF7E82BB-4DFE-4BCF-A21E-091318196BD7}"/>
+    <hyperlink ref="J38" r:id="rId37" xr:uid="{84489530-2C94-4D8A-AE8B-CE8B6E515674}"/>
+    <hyperlink ref="J39" r:id="rId38" xr:uid="{A72EE316-33B8-4BCB-B2BA-05A96BB0E6E5}"/>
+    <hyperlink ref="J40" r:id="rId39" xr:uid="{D87B545B-0A3F-4CF4-8D05-D359159DFF6C}"/>
+    <hyperlink ref="J41" r:id="rId40" xr:uid="{8619918B-C06B-4AD7-96B0-B05613CBAE25}"/>
+    <hyperlink ref="J42" r:id="rId41" xr:uid="{72199441-FA17-42A3-A206-E092478BB3B2}"/>
+    <hyperlink ref="J43" r:id="rId42" xr:uid="{CB7331E9-A16A-459A-BA6F-9F7E4B1801DA}"/>
+    <hyperlink ref="J44" r:id="rId43" xr:uid="{CAB536DE-9C14-43E2-A412-A12C72236CE5}"/>
+    <hyperlink ref="J45" r:id="rId44" xr:uid="{F41B9216-44DE-4440-A530-ED55D61A8498}"/>
+    <hyperlink ref="J46" r:id="rId45" xr:uid="{F1987741-8B2C-4CE0-8100-AB94165FD7D4}"/>
+    <hyperlink ref="J47" r:id="rId46" xr:uid="{10ADB5AC-A40E-4B3F-8196-43317CE743CF}"/>
+    <hyperlink ref="J48" r:id="rId47" xr:uid="{59156857-A9DC-45FA-A39E-1B4DBD81161C}"/>
+    <hyperlink ref="J49" r:id="rId48" xr:uid="{41F052BE-FB0D-4E4F-B05F-2887343785DD}"/>
+    <hyperlink ref="J50" r:id="rId49" xr:uid="{3FA739B9-1F6A-4725-9B6A-71234F2AF51D}"/>
+    <hyperlink ref="J51" r:id="rId50" xr:uid="{B8CE2F49-6087-4F0F-8E1F-A6DCDA166183}"/>
+    <hyperlink ref="J52" r:id="rId51" xr:uid="{A3936BD9-40E8-4500-ABB8-EA8E13C0BDCE}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/rumah_makan.xlsx
+++ b/data/rumah_makan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\SEMESTER 6\PRAK. SIGTER\PROJECT AKHIR\STUDENT SURVIVAL MAP\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBCFB7D2-1849-48F2-90BD-4DE12737607B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6229B7D5-F278-405D-ADF2-53F71BF55471}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{EBF2A29F-0C7E-4417-9F77-D4C323BFD0DA}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="625" uniqueCount="421">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="622" uniqueCount="418">
   <si>
     <t>Id</t>
   </si>
@@ -75,9 +75,6 @@
     <t>Senin - Minggu</t>
   </si>
   <si>
-    <t>6:00 AM – 20:00 PM</t>
-  </si>
-  <si>
     <t>Tidak</t>
   </si>
   <si>
@@ -90,60 +87,39 @@
     <t>Kecuali Senin</t>
   </si>
   <si>
-    <t>11:00 AM – 23:00 PM</t>
-  </si>
-  <si>
     <t>R003</t>
   </si>
   <si>
     <t>Warung Makan 4T</t>
   </si>
   <si>
-    <t>11:30 AM – 23:00 PM</t>
-  </si>
-  <si>
     <t>R004</t>
   </si>
   <si>
     <t>Kindai Warung Masakan Banjar</t>
   </si>
   <si>
-    <t>7:00 AM – 21:00 PM</t>
-  </si>
-  <si>
     <t>R005</t>
   </si>
   <si>
     <t>Warung Makan Murah Neng Sari</t>
   </si>
   <si>
-    <t>8:00 AM – 20:00 PM</t>
-  </si>
-  <si>
     <t>R006</t>
   </si>
   <si>
     <t>Warung "Ijo" Mami</t>
   </si>
   <si>
-    <t>9:00 AM – 23:00 PM</t>
-  </si>
-  <si>
     <t>R007</t>
   </si>
   <si>
     <t>Warung Makan Kita</t>
   </si>
   <si>
-    <t>10:00 AM – 21:30 PM</t>
-  </si>
-  <si>
     <t>R008</t>
   </si>
   <si>
-    <t>8:00 AM – 21:00 PM</t>
-  </si>
-  <si>
     <t>R009</t>
   </si>
   <si>
@@ -174,9 +150,6 @@
     <t>Kecuali Minggu</t>
   </si>
   <si>
-    <t>11:00 AM – 20:00 PM</t>
-  </si>
-  <si>
     <t>R013</t>
   </si>
   <si>
@@ -189,9 +162,6 @@
     <t>Rumah Makan Omah Abah</t>
   </si>
   <si>
-    <t>6:00 AM – 21:00 PM</t>
-  </si>
-  <si>
     <t>R015</t>
   </si>
   <si>
@@ -321,612 +291,24 @@
     <t xml:space="preserve">Bebek Senjay Seturan </t>
   </si>
   <si>
-    <t>Jl, Kuningan, Karang Malang, Caturtunggal, Kec, Depok, Kab, Sleman, DIY 55281</t>
-  </si>
-  <si>
-    <t>-7,774018451332347</t>
-  </si>
-  <si>
-    <t>110,38277142667721</t>
-  </si>
-  <si>
-    <t>https://maps,app,goo,gl/iqZ4GBhxDdnmiKFh9</t>
-  </si>
-  <si>
-    <t>images\R001,jpg</t>
-  </si>
-  <si>
-    <t>RP 1-25,000</t>
-  </si>
-  <si>
-    <t>Jalan Tantular, Kaliwaru, Condongcatur, Kec, Depok, Kab, Sleman, DIY 55281</t>
-  </si>
-  <si>
-    <t>-7,766598323121821</t>
-  </si>
-  <si>
-    <t>110,39630308280208</t>
-  </si>
-  <si>
-    <t>https://maps,app,goo,gl/RYeTdPUprhVZbWQj7</t>
-  </si>
-  <si>
-    <t>images\R002,jpg</t>
-  </si>
-  <si>
-    <t>Jl, Sengkan Gg, Sadewa No,02, Kocoran, Condongcatur, Kec, Depok, Kab, Sleman, DIY 55283</t>
-  </si>
-  <si>
-    <t>-7,748198351154356</t>
-  </si>
-  <si>
-    <t>110,39501674047217</t>
-  </si>
-  <si>
-    <t>https://maps,app,goo,gl/dE8ZDETqJrKnrMYT7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">images\R003,jpg </t>
-  </si>
-  <si>
-    <t>Gg, Jemb, Merah No,116 D, Kaliwaru, Condongcatur, Kec, Depok, Kab, Sleman, DIY 55283</t>
-  </si>
-  <si>
-    <t>-7,7649353526519755</t>
-  </si>
-  <si>
-    <t>110,3965513539671</t>
-  </si>
-  <si>
-    <t>https://maps,app,goo,gl/4ZpaPxZ7B6SoaFbN7</t>
-  </si>
-  <si>
-    <t>images\R004,jpg</t>
-  </si>
-  <si>
-    <t>Blok B-5, Karangwuni, Manggung, Caturtunggal, Kec, Depok, Kab, Sleman, DIY 55281</t>
-  </si>
-  <si>
-    <t>-7,760414033672402</t>
-  </si>
-  <si>
-    <t>110,38289718095653</t>
-  </si>
-  <si>
-    <t>https://maps,app,goo,gl/o6JYaCCD2E2qbBNu5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">images\R005,jpg </t>
-  </si>
-  <si>
-    <t>Dabag, Condongcatur, Kec, Depok, Kab, Sleman, DIY 55281</t>
-  </si>
-  <si>
-    <t>-7,767364427487958</t>
-  </si>
-  <si>
-    <t>110,40336234047223</t>
-  </si>
-  <si>
-    <t>https://maps,app,goo,gl/jccDdukmCYNKPAUo8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">images\R006,jpg </t>
-  </si>
-  <si>
-    <t>Ruko Gorongan, Jl, Perumnas, Ngropoh, Condongcatur, Kec, Depok, Kab, Sleman, DIY 55283</t>
-  </si>
-  <si>
-    <t>-7,762219151339312</t>
-  </si>
-  <si>
-    <t>110,40609814061278</t>
-  </si>
-  <si>
-    <t>https://maps,app,goo,gl/y2apQpo5v9a8eD8R7</t>
-  </si>
-  <si>
-    <t>images\R007,jpg</t>
-  </si>
-  <si>
-    <t>Warung Makan Mr, B</t>
-  </si>
-  <si>
-    <t>Jl, Cemp, No,231, Perumnas Condong Catur, Condongcatur, Kec, Depok, Kab, Sleman, DIY 55281</t>
-  </si>
-  <si>
-    <t>-7,758753747337649</t>
-  </si>
-  <si>
-    <t>110,40544786746183</t>
-  </si>
-  <si>
-    <t>https://maps,app,goo,gl/JmsiDm3tz18g7duD8</t>
-  </si>
-  <si>
-    <t>images\R008,jpg</t>
-  </si>
-  <si>
-    <t>Ruko Babarsari, Jl, Raya Kledokan, Caturtunggal, Kec, Depok, Kab, Sleman, DIY 55281</t>
-  </si>
-  <si>
-    <t>-7,773185859499051</t>
-  </si>
-  <si>
-    <t>110,41127732513222</t>
-  </si>
-  <si>
-    <t>https://maps,app,goo,gl/AVSE3ECfkHPPmucS8</t>
-  </si>
-  <si>
-    <t>images\R009,jpg</t>
-  </si>
-  <si>
-    <t>Ruko Babarsari, Jl, Babarsari, Tambak Bayan, Caturtunggal, Kec, Depok, Kab, Sleman, DIY 55281</t>
-  </si>
-  <si>
-    <t>-7,773975478353483</t>
-  </si>
-  <si>
-    <t>110,41303351163725</t>
-  </si>
-  <si>
-    <t>https://maps,app,goo,gl/SWHzXXXf3SMQ8tA96</t>
-  </si>
-  <si>
-    <t>images\R010,jpg</t>
-  </si>
-  <si>
-    <t>11:30 AM – 22,30 PM</t>
-  </si>
-  <si>
-    <t>Jl, Rusunawa Mranggen, Kutu Tegal, Sinduadi, Kec, Mlati, Kab, Sleman, DIY 55284</t>
-  </si>
-  <si>
-    <t>-7,756148878671714</t>
-  </si>
-  <si>
-    <t>110,36666459445149</t>
-  </si>
-  <si>
-    <t>https://maps,app,goo,gl/945xB7PkevoCExYc8</t>
-  </si>
-  <si>
-    <t>images\R011,jpg</t>
-  </si>
-  <si>
-    <t>Jl, Babarsari I No,13, Janti, Caturtunggal, Kec, Depok, Kab, Sleman, DIY 55281</t>
-  </si>
-  <si>
-    <t>-7,78105070111518</t>
-  </si>
-  <si>
-    <t>110,41611792513211</t>
-  </si>
-  <si>
-    <t>https://maps,app,goo,gl/rPTxmt9UDxHS23n19</t>
-  </si>
-  <si>
-    <t>images\R012,jpg</t>
-  </si>
-  <si>
-    <t>Ruko Babarsari BBC Plaza, Jl, Tambak Bayan, Janti, Caturtunggal, Kec, Depok, Kab, Sleman, DIY 55281</t>
-  </si>
-  <si>
-    <t>-7,778998591556486</t>
-  </si>
-  <si>
-    <t>110,41645029860855</t>
-  </si>
-  <si>
-    <t>https://maps,app,goo,gl/L6iTqLFFDM966Tmd6</t>
-  </si>
-  <si>
-    <t>images\R013,jpg</t>
-  </si>
-  <si>
-    <t>Jl, Gambuh No,3, Manukan, Condongcatur, Kec, Depok, Kab, Sleman, DIY 52000</t>
-  </si>
-  <si>
-    <t>-7,744848444541496</t>
-  </si>
-  <si>
-    <t>110,39722782697724</t>
-  </si>
-  <si>
-    <t>https://maps,app,goo,gl/fczoo46dnKmpCCLX7</t>
-  </si>
-  <si>
-    <t>images\R014,jpg</t>
-  </si>
-  <si>
-    <t>-7,772147381587484</t>
-  </si>
-  <si>
-    <t>110,38255056017287</t>
-  </si>
-  <si>
-    <t>https://maps,app,goo,gl/frbqQuNvtPqtGRbZ9</t>
-  </si>
-  <si>
-    <t>images\R015,jpg</t>
-  </si>
-  <si>
-    <t>-7,773801908510043</t>
-  </si>
-  <si>
-    <t>110,38244608095673</t>
-  </si>
-  <si>
-    <t>https://maps,app,goo,gl/GyqJjnQwoYZo9MUv6</t>
-  </si>
-  <si>
-    <t>images\R016,jpg</t>
-  </si>
-  <si>
-    <t>Karang Wuni, Caturtunggal, Kec, Depok, Kab, Sleman, DIY 55281</t>
-  </si>
-  <si>
-    <t>-7,763588204383579</t>
-  </si>
-  <si>
-    <t>110,38656631163735</t>
-  </si>
-  <si>
-    <t>https://maps,app,goo,gl/fK5qaQbLaG5pV3qK7</t>
-  </si>
-  <si>
-    <t>images\R017,jpg</t>
-  </si>
-  <si>
-    <t>Jalan Kapulogo, Nologaten, Caturtunggal, Kec, Depok, Kab, Sleman, DIY 55281</t>
-  </si>
-  <si>
-    <t>-7,778643299714027</t>
-  </si>
-  <si>
-    <t>110,40153840794645</t>
-  </si>
-  <si>
-    <t>https://maps,app,goo,gl/rfQ7La7Wdc5Ghyuw6</t>
-  </si>
-  <si>
-    <t>images\R018,jpg</t>
-  </si>
-  <si>
-    <t>Ruko DTA Square, Jl, Seturan Raya, Kledokan, Caturtunggal, Kec, Depok, Kab, Sleman, DIY 55281</t>
-  </si>
-  <si>
-    <t>-7,774072757500694</t>
-  </si>
-  <si>
-    <t>110,4089132386269</t>
-  </si>
-  <si>
-    <t>https://maps,app,goo,gl/Um2cFZ7P8u8Y3MLC9</t>
-  </si>
-  <si>
-    <t>images\R019,jpg</t>
-  </si>
-  <si>
-    <t>Jl, Kaliurang No,17 Km,6, Kentungan, Condongcatur, Kec, Depok, Kab, Sleman, DIY 55284</t>
-  </si>
-  <si>
-    <t>-7,7487586601315295</t>
-  </si>
-  <si>
-    <t>110,38680614047226</t>
-  </si>
-  <si>
-    <t>https://maps,app,goo,gl/8WpRE1ayxfZ9wkC86</t>
-  </si>
-  <si>
-    <t xml:space="preserve">images\R020,jpg </t>
-  </si>
-  <si>
-    <t>Jl, Apokat, Perumnas Condong Catur, Condongcatur, Kec, Depok, Kab, Sleman, DIY 55283</t>
-  </si>
-  <si>
-    <t>-7,755653254637142</t>
-  </si>
-  <si>
-    <t>110,40513369629689</t>
-  </si>
-  <si>
-    <t>https://maps,app,goo,gl/cAwMBmPVwPjQhV8b8</t>
-  </si>
-  <si>
-    <t>images\R021,jpg</t>
-  </si>
-  <si>
-    <t>Jl, Pintu Selatan UPN, Ngropoh, Condongcatur, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
-  </si>
-  <si>
-    <t>-7,763446834820035</t>
-  </si>
-  <si>
-    <t>110,4074531962969</t>
-  </si>
-  <si>
-    <t>https://maps,app,goo,gl/SQeZppWwHGojvCoYA</t>
-  </si>
-  <si>
-    <t>images\R022,jpg</t>
-  </si>
-  <si>
-    <t>9,00 AM - 21,00 PM</t>
-  </si>
-  <si>
-    <t>Jl, Perumnas Jl, Pintu Selatan UPN No,15, Ngropoh, Condongcatur, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
-  </si>
-  <si>
-    <t>-7.763824775595378</t>
-  </si>
-  <si>
     <t>110.40860162599286</t>
   </si>
   <si>
-    <t>https://maps,app,goo,gl/MyMuo6xx6rSZSYn6A</t>
-  </si>
-  <si>
-    <t>images\R023,jpg</t>
-  </si>
-  <si>
-    <t>9,00 AM - 23,30 PM</t>
-  </si>
-  <si>
-    <t>Jl, Sorowajan No,208, Sorowajan, Banguntapan, Kec, Banguntapan, Kabupaten Bantul, Daerah Istimewa Yogyakarta 55198</t>
-  </si>
-  <si>
-    <t>-7,793779749086242</t>
-  </si>
-  <si>
-    <t>110,4066409251323</t>
-  </si>
-  <si>
-    <t>https://maps,app,goo,gl/GGv45FujGN5yNHwcA</t>
-  </si>
-  <si>
-    <t>images\R024,jpg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8,00 AM - 22,00 PM </t>
-  </si>
-  <si>
-    <t>Ruko Kelapa Hijau, Jl, Brojomulyo No,10, Gejayan, Condongcatur, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
-  </si>
-  <si>
-    <t>-7,755166261556854</t>
-  </si>
-  <si>
-    <t>110,39649766645391</t>
-  </si>
-  <si>
-    <t>https://maps,app,goo,gl/xKX6kRSfFGRUAG9A8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">images\R025,jpg </t>
-  </si>
-  <si>
-    <t xml:space="preserve">10,00 AM - 22,00 PM </t>
-  </si>
-  <si>
-    <t>Jl, Kemuning No,1b, Candok, Condongcatur, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
-  </si>
-  <si>
-    <t>-7,77696423193207</t>
-  </si>
-  <si>
-    <t>110,4082001376189</t>
-  </si>
-  <si>
-    <t>https://maps,app,goo,gl/Tm28gLkjwDSy5e776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">images\R026,jpg </t>
-  </si>
-  <si>
-    <t>Jl, Seturan Raya, Kledokan, Caturtunggal, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
-  </si>
-  <si>
-    <t>-7,773704851301657</t>
-  </si>
-  <si>
-    <t>110,408922011336</t>
-  </si>
-  <si>
-    <t>https://maps,app,goo,gl/8jP7p8idJp7mRe8E8</t>
-  </si>
-  <si>
-    <t>images\R027,jpg</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Jl, Nusa Indah II, Dero, Condongcatur, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
-  </si>
-  <si>
-    <t>-7,755404200161589</t>
-  </si>
-  <si>
-    <t>110,40998792227738</t>
-  </si>
-  <si>
-    <t>https://maps,app,goo,gl/8AzpC7NaaWZVtmYx5</t>
-  </si>
-  <si>
-    <t>images\R028,jpg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7,00 AM - 12,00 PM </t>
-  </si>
-  <si>
-    <t>Komplek Ruko, Puluhdadi No,B 30, Kledokan, Caturtunggal, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
-  </si>
-  <si>
-    <t>-7,7650364676061825</t>
-  </si>
-  <si>
-    <t>110,41125753432115</t>
-  </si>
-  <si>
-    <t>https://maps,app,goo,gl/Xvaw52o9zDGb7w1X6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">images\R029,jpg </t>
-  </si>
-  <si>
-    <t xml:space="preserve">11,00 AM - 03,00 AM </t>
-  </si>
-  <si>
-    <t>Gg, Puluhdadi Seturan Kios B28, Kledokan, Caturtunggal, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
-  </si>
-  <si>
-    <t>-7,765137937154172</t>
-  </si>
-  <si>
-    <t>110,4111947343212</t>
-  </si>
-  <si>
-    <t>https://maps,app,goo,gl/HtN9HV2g3EC2E6Yw6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">images\R030,jpg </t>
-  </si>
-  <si>
-    <t xml:space="preserve">06,00 AM - 18,00 PM </t>
-  </si>
-  <si>
-    <t>Jl, Tasura, Jenengan, Maguwoharjo, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55282</t>
-  </si>
-  <si>
-    <t>-7,762639622774797</t>
-  </si>
-  <si>
-    <t>110,42252795295988</t>
-  </si>
-  <si>
-    <t>https://maps,app,goo,gl/RGsFBLKN9Tvhmdrh9</t>
-  </si>
-  <si>
-    <t>images\R031,jpg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">08, 00 AM - 22,00 PM </t>
-  </si>
-  <si>
-    <t>Jl, Raya Kledokan No,23, Kledokan, Caturtunggal, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
-  </si>
-  <si>
-    <t>-7,77473843142309</t>
-  </si>
-  <si>
-    <t>110,40866228736111</t>
-  </si>
-  <si>
-    <t>https://maps,app,goo,gl/w3uwETVrBeL8kocJ8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">images\R032,jpg </t>
-  </si>
-  <si>
-    <t xml:space="preserve">09,00 AM - 23,00 PM </t>
-  </si>
-  <si>
-    <t>Jl, Perumnas Seturan, Kledokan, Caturtunggal, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
-  </si>
-  <si>
-    <t>-7,77216168031367</t>
-  </si>
-  <si>
-    <t>110,40528626645401</t>
-  </si>
-  <si>
-    <t>https://maps,app,goo,gl/vByGQcCKFUbyUWs8A</t>
-  </si>
-  <si>
     <t xml:space="preserve">images\R033jpg </t>
   </si>
   <si>
-    <t xml:space="preserve">08,30 AM - 21,00 PM </t>
-  </si>
-  <si>
-    <t>Jl, Perumnas No,127, Tempel, Caturtunggal, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
-  </si>
-  <si>
-    <t>-7,777458308996077</t>
-  </si>
-  <si>
-    <t>110,40528428637276</t>
-  </si>
-  <si>
-    <t>https://maps,app,goo,gl/km35JL3uhPDCb4f26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">images\R034,jpg </t>
-  </si>
-  <si>
-    <t>09,30 AM - 10,00 PM</t>
-  </si>
-  <si>
-    <t>Jl, Perumnas No,141, Nologaten, Caturtunggal, Depok, Sleman Regency, Special Region of Yogyakarta 55281</t>
-  </si>
-  <si>
-    <t>-7,776196931971200</t>
-  </si>
-  <si>
-    <t>110,4045624648450</t>
-  </si>
-  <si>
-    <t>https://maps,app,goo,gl/Me5yN67UAteqpGdY9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">images\R035,jpg </t>
-  </si>
-  <si>
     <t>R036</t>
   </si>
   <si>
     <t>Warung Makan Mahasiswa Ambarrukmo</t>
   </si>
   <si>
-    <t>08,00 - 19,00</t>
-  </si>
-  <si>
-    <t>Jl, Ambar Asri No,311, Ambarukmo, Caturtunggal, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
-  </si>
-  <si>
-    <t>-7,78261665177125</t>
-  </si>
-  <si>
-    <t>110,39953130466868</t>
-  </si>
-  <si>
-    <t>https://maps,app,goo,gl/7ZxoNc54UJ2ZkLf39</t>
-  </si>
-  <si>
-    <t>images\R036,jpg</t>
-  </si>
-  <si>
     <t>R037</t>
   </si>
   <si>
     <t>Mie Gacoan Babarsari</t>
   </si>
   <si>
-    <t>Ruko Rafflesia, Jl, Babarsari, Janti, Caturtunggal, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
-  </si>
-  <si>
-    <t>-7,779288337303048</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 110,41530143843262</t>
-  </si>
-  <si>
-    <t>https://maps,app,goo,gl/yYLSC9uJhWDgQUph8</t>
-  </si>
-  <si>
-    <t>images\R037,jpg</t>
-  </si>
-  <si>
     <t xml:space="preserve">Ya </t>
   </si>
   <si>
@@ -936,24 +318,6 @@
     <t>Warung Makan Depot Ibu Tiara</t>
   </si>
   <si>
-    <t>07,00 - 22,00</t>
-  </si>
-  <si>
-    <t>6CM6+85F, Jl, Seturan Raya, Kledokan, Caturtunggal, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
-  </si>
-  <si>
-    <t>-7,7667012046934865</t>
-  </si>
-  <si>
-    <t>110,41036731114856</t>
-  </si>
-  <si>
-    <t>https://maps,app,goo,gl/VzBnzzQmzfrSBWo9A</t>
-  </si>
-  <si>
-    <t>images\R038,jpg</t>
-  </si>
-  <si>
     <t>R039</t>
   </si>
   <si>
@@ -963,75 +327,18 @@
     <t>Senin - Sabtu</t>
   </si>
   <si>
-    <t>11,00 - 20,00</t>
-  </si>
-  <si>
-    <t>Jl, Babarsari I No,13, Janti, Caturtunggal, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
-  </si>
-  <si>
-    <t>-7,780851926155481</t>
-  </si>
-  <si>
-    <t>110,41606370772861</t>
-  </si>
-  <si>
-    <t>https://maps,app,goo,gl/bujMvFPKLoa6rspp7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">images\R039,jpg </t>
-  </si>
-  <si>
     <t>R040</t>
   </si>
   <si>
     <t>Pecel Lele Bu Lestari</t>
   </si>
   <si>
-    <t xml:space="preserve">Rumah Makan,Lesehan </t>
-  </si>
-  <si>
-    <t>11,00 - 00,00</t>
-  </si>
-  <si>
-    <t>Gg, Shinta, Nayan, Maguwoharjo, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
-  </si>
-  <si>
-    <t>-7,77893232620335</t>
-  </si>
-  <si>
-    <t>110,42400796597617</t>
-  </si>
-  <si>
-    <t>https://maps,app,goo,gl/2RH5jEc9g64fvsgb7</t>
-  </si>
-  <si>
-    <t>images\R040,jpg</t>
-  </si>
-  <si>
     <t>R041</t>
   </si>
   <si>
     <t>Mie Ayam &amp; Bakso Purnami Jempol Sari Roso Jatiayu</t>
   </si>
   <si>
-    <t>10,00 - 18,00</t>
-  </si>
-  <si>
-    <t>Jl, P, Diponegoro, Sembego, Maguwoharjo, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
-  </si>
-  <si>
-    <t>-7,761847045353668</t>
-  </si>
-  <si>
-    <t>110,43943841946138</t>
-  </si>
-  <si>
-    <t>https://maps,app,goo,gl/4NFp2jRiWyogCHd3A</t>
-  </si>
-  <si>
-    <t>images\R041,jpg</t>
-  </si>
-  <si>
     <t>R042</t>
   </si>
   <si>
@@ -1041,24 +348,9 @@
     <t>Restoran Jepang</t>
   </si>
   <si>
-    <t>11,00 - 22,00</t>
-  </si>
-  <si>
-    <t>Jl, Palagan Tentara Pelajar No,59, Jongkang, Sariharjo, Kec, Ngaglik, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55581</t>
-  </si>
-  <si>
-    <t>-7,743,587,559,412,390</t>
-  </si>
-  <si>
-    <t>110,37401676139700</t>
-  </si>
-  <si>
     <t>https://maps.app.goo.gl/emcC92RrHoX8udwV7</t>
   </si>
   <si>
-    <t>images\R042,jpg</t>
-  </si>
-  <si>
     <t>Rp 25–50 rb</t>
   </si>
   <si>
@@ -1071,48 +363,18 @@
     <t>Restoran Ramen</t>
   </si>
   <si>
-    <t>11,00 - 23,30</t>
-  </si>
-  <si>
-    <t>Ruko Kelapa Hijau No, 18, Sanggrahan, Condongcatur, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55283</t>
-  </si>
-  <si>
-    <t>-7,7535380574479000</t>
-  </si>
-  <si>
-    <t>110,39710521673956</t>
-  </si>
-  <si>
     <t>https://maps.app.goo.gl/AvZHK7bAeCfGpBNJ7</t>
   </si>
   <si>
-    <t>images\R043,jpg</t>
-  </si>
-  <si>
     <t>R044</t>
   </si>
   <si>
     <t>Tottori_ID Japanese Fusion Food - Restaurant - Mrican</t>
   </si>
   <si>
-    <t>12,00 - 21,00</t>
-  </si>
-  <si>
-    <t>Jl, Gatotkaca No,1G, Santren, Caturtunggal, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
-  </si>
-  <si>
-    <t>-7,771694983656591</t>
-  </si>
-  <si>
-    <t>110,39133310283543</t>
-  </si>
-  <si>
     <t>https://maps.app.goo.gl/qytFbXEommQHkbe79</t>
   </si>
   <si>
-    <t>images\R044,jpg</t>
-  </si>
-  <si>
     <t>R045</t>
   </si>
   <si>
@@ -1122,42 +384,15 @@
     <t>Restoran Padang</t>
   </si>
   <si>
-    <t>08,30–22,00</t>
-  </si>
-  <si>
-    <t>Jl, Monjali No,99 49, Kutu Dukuh, Sinduadi, Kec, Mlati, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55284</t>
-  </si>
-  <si>
-    <t>-7,757918567368756</t>
-  </si>
-  <si>
-    <t>110,3693590993285</t>
-  </si>
-  <si>
     <t>https://maps.app.goo.gl/4JX1thPL8hmzb5FZ6</t>
   </si>
   <si>
-    <t>images\R045,jpg</t>
-  </si>
-  <si>
     <t>R046</t>
   </si>
   <si>
     <t>Ceplok Telor Babarsari</t>
   </si>
   <si>
-    <t>08,30–21,00</t>
-  </si>
-  <si>
-    <t>Jl, Babarsari No,15, Janti, Caturtunggal, Kec, Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
-  </si>
-  <si>
-    <t>7,779724632145041</t>
-  </si>
-  <si>
-    <t>110,41522422762888</t>
-  </si>
-  <si>
     <t>https://maps.app.goo.gl/nXyZFaZFVdjNWZYcA</t>
   </si>
   <si>
@@ -1170,9 +405,6 @@
     <t>10.00 - 21.30</t>
   </si>
   <si>
-    <t>Ruko Gorongan, Jl. Perumnas, Ngropoh, Condongcatur, Kec. Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55283</t>
-  </si>
-  <si>
     <t>-7.762796291952466</t>
   </si>
   <si>
@@ -1191,15 +423,9 @@
     <t>Dewi Ratih Lesehan</t>
   </si>
   <si>
-    <t xml:space="preserve">Rumah Makan, Lesehan </t>
-  </si>
-  <si>
     <t xml:space="preserve">07.00 - 22.00 </t>
   </si>
   <si>
-    <t>Jalan Apokat, Klebengan, Blok CT VIII, Kocoran, Caturtunggal, Kec. Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55281</t>
-  </si>
-  <si>
     <t>-7.764957074917656</t>
   </si>
   <si>
@@ -1221,9 +447,6 @@
     <t>11.00 - 21.30</t>
   </si>
   <si>
-    <t>Jl. Utama Pugeran RT07 RW65, Pugeran, Maguwoharjo, Kec. Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55282</t>
-  </si>
-  <si>
     <t>-7.766725321038907</t>
   </si>
   <si>
@@ -1245,9 +468,6 @@
     <t>Rumah Makan</t>
   </si>
   <si>
-    <t>Jl. Nangka III Jl. Utama No.RT 7, Pugeran, Maguwoharjo, Kec. Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55282</t>
-  </si>
-  <si>
     <t>-7.767939879922977</t>
   </si>
   <si>
@@ -1269,9 +489,6 @@
     <t>17.00 - 02.00</t>
   </si>
   <si>
-    <t>Jl. Kaswari No.98, Ngringin, Condongcatur, Kec. Depok, Kabupaten Sleman, Daerah Istimewa Yogyakarta 55283</t>
-  </si>
-  <si>
     <t>-7.756559272784034</t>
   </si>
   <si>
@@ -1297,6 +514,780 @@
   </si>
   <si>
     <t>Buka_24_jam</t>
+  </si>
+  <si>
+    <t>6.00 AM – 20.00 PM</t>
+  </si>
+  <si>
+    <t>11.00 AM – 23.00 PM</t>
+  </si>
+  <si>
+    <t>11.30 AM – 23.00 PM</t>
+  </si>
+  <si>
+    <t>7.00 AM – 21.00 PM</t>
+  </si>
+  <si>
+    <t>8.00 AM – 20.00 PM</t>
+  </si>
+  <si>
+    <t>9.00 AM – 23.00 PM</t>
+  </si>
+  <si>
+    <t>10.00 AM – 21.30 PM</t>
+  </si>
+  <si>
+    <t>8.00 AM – 21.00 PM</t>
+  </si>
+  <si>
+    <t>11.00 AM – 20.00 PM</t>
+  </si>
+  <si>
+    <t>6.00 AM – 21.00 PM</t>
+  </si>
+  <si>
+    <t>Jl. Kuningan. Karang Malang. Caturtunggal. Kec. Depok. Kab. Sleman. DIY 55281</t>
+  </si>
+  <si>
+    <t>-7.774018451332347</t>
+  </si>
+  <si>
+    <t>110.38277142667721</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/iqZ4GBhxDdnmiKFh9</t>
+  </si>
+  <si>
+    <t>images\R001.jpg</t>
+  </si>
+  <si>
+    <t>RP 1-25.000</t>
+  </si>
+  <si>
+    <t>Jalan Tantular. Kaliwaru. Condongcatur. Kec. Depok. Kab. Sleman. DIY 55281</t>
+  </si>
+  <si>
+    <t>-7.766598323121821</t>
+  </si>
+  <si>
+    <t>110.39630308280208</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/RYeTdPUprhVZbWQj7</t>
+  </si>
+  <si>
+    <t>images\R002.jpg</t>
+  </si>
+  <si>
+    <t>Jl. Sengkan Gg. Sadewa No.02. Kocoran. Condongcatur. Kec. Depok. Kab. Sleman. DIY 55283</t>
+  </si>
+  <si>
+    <t>-7.748198351154356</t>
+  </si>
+  <si>
+    <t>110.39501674047217</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/dE8ZDETqJrKnrMYT7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">images\R003.jpg </t>
+  </si>
+  <si>
+    <t>Gg. Jemb. Merah No.116 D. Kaliwaru. Condongcatur. Kec. Depok. Kab. Sleman. DIY 55283</t>
+  </si>
+  <si>
+    <t>-7.7649353526519755</t>
+  </si>
+  <si>
+    <t>110.3965513539671</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/4ZpaPxZ7B6SoaFbN7</t>
+  </si>
+  <si>
+    <t>images\R004.jpg</t>
+  </si>
+  <si>
+    <t>Blok B-5. Karangwuni. Manggung. Caturtunggal. Kec. Depok. Kab. Sleman. DIY 55281</t>
+  </si>
+  <si>
+    <t>-7.760414033672402</t>
+  </si>
+  <si>
+    <t>110.38289718095653</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/o6JYaCCD2E2qbBNu5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">images\R005.jpg </t>
+  </si>
+  <si>
+    <t>Dabag. Condongcatur. Kec. Depok. Kab. Sleman. DIY 55281</t>
+  </si>
+  <si>
+    <t>-7.767364427487958</t>
+  </si>
+  <si>
+    <t>110.40336234047223</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/jccDdukmCYNKPAUo8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">images\R006.jpg </t>
+  </si>
+  <si>
+    <t>Ruko Gorongan. Jl. Perumnas. Ngropoh. Condongcatur. Kec. Depok. Kab. Sleman. DIY 55283</t>
+  </si>
+  <si>
+    <t>-7.762219151339312</t>
+  </si>
+  <si>
+    <t>110.40609814061278</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/y2apQpo5v9a8eD8R7</t>
+  </si>
+  <si>
+    <t>images\R007.jpg</t>
+  </si>
+  <si>
+    <t>Warung Makan Mr. B</t>
+  </si>
+  <si>
+    <t>Jl. Cemp. No.231. Perumnas Condong Catur. Condongcatur. Kec. Depok. Kab. Sleman. DIY 55281</t>
+  </si>
+  <si>
+    <t>-7.758753747337649</t>
+  </si>
+  <si>
+    <t>110.40544786746183</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/JmsiDm3tz18g7duD8</t>
+  </si>
+  <si>
+    <t>images\R008.jpg</t>
+  </si>
+  <si>
+    <t>Ruko Babarsari. Jl. Raya Kledokan. Caturtunggal. Kec. Depok. Kab. Sleman. DIY 55281</t>
+  </si>
+  <si>
+    <t>-7.773185859499051</t>
+  </si>
+  <si>
+    <t>110.41127732513222</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/AVSE3ECfkHPPmucS8</t>
+  </si>
+  <si>
+    <t>images\R009.jpg</t>
+  </si>
+  <si>
+    <t>Ruko Babarsari. Jl. Babarsari. Tambak Bayan. Caturtunggal. Kec. Depok. Kab. Sleman. DIY 55281</t>
+  </si>
+  <si>
+    <t>-7.773975478353483</t>
+  </si>
+  <si>
+    <t>110.41303351163725</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/SWHzXXXf3SMQ8tA96</t>
+  </si>
+  <si>
+    <t>images\R010.jpg</t>
+  </si>
+  <si>
+    <t>11.30 AM – 22.30 PM</t>
+  </si>
+  <si>
+    <t>Jl. Rusunawa Mranggen. Kutu Tegal. Sinduadi. Kec. Mlati. Kab. Sleman. DIY 55284</t>
+  </si>
+  <si>
+    <t>-7.756148878671714</t>
+  </si>
+  <si>
+    <t>110.36666459445149</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/945xB7PkevoCExYc8</t>
+  </si>
+  <si>
+    <t>images\R011.jpg</t>
+  </si>
+  <si>
+    <t>Jl. Babarsari I No.13. Janti. Caturtunggal. Kec. Depok. Kab. Sleman. DIY 55281</t>
+  </si>
+  <si>
+    <t>-7.78105070111518</t>
+  </si>
+  <si>
+    <t>110.41611792513211</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/rPTxmt9UDxHS23n19</t>
+  </si>
+  <si>
+    <t>images\R012.jpg</t>
+  </si>
+  <si>
+    <t>Ruko Babarsari BBC Plaza. Jl. Tambak Bayan. Janti. Caturtunggal. Kec. Depok. Kab. Sleman. DIY 55281</t>
+  </si>
+  <si>
+    <t>-7.778998591556486</t>
+  </si>
+  <si>
+    <t>110.41645029860855</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/L6iTqLFFDM966Tmd6</t>
+  </si>
+  <si>
+    <t>images\R013.jpg</t>
+  </si>
+  <si>
+    <t>Jl. Gambuh No.3. Manukan. Condongcatur. Kec. Depok. Kab. Sleman. DIY 52000</t>
+  </si>
+  <si>
+    <t>-7.744848444541496</t>
+  </si>
+  <si>
+    <t>110.39722782697724</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/fczoo46dnKmpCCLX7</t>
+  </si>
+  <si>
+    <t>images\R014.jpg</t>
+  </si>
+  <si>
+    <t>-7.772147381587484</t>
+  </si>
+  <si>
+    <t>110.38255056017287</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/frbqQuNvtPqtGRbZ9</t>
+  </si>
+  <si>
+    <t>images\R015.jpg</t>
+  </si>
+  <si>
+    <t>-7.773801908510043</t>
+  </si>
+  <si>
+    <t>110.38244608095673</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/GyqJjnQwoYZo9MUv6</t>
+  </si>
+  <si>
+    <t>images\R016.jpg</t>
+  </si>
+  <si>
+    <t>Karang Wuni. Caturtunggal. Kec. Depok. Kab. Sleman. DIY 55281</t>
+  </si>
+  <si>
+    <t>-7.763588204383579</t>
+  </si>
+  <si>
+    <t>110.38656631163735</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/fK5qaQbLaG5pV3qK7</t>
+  </si>
+  <si>
+    <t>images\R017.jpg</t>
+  </si>
+  <si>
+    <t>Jalan Kapulogo. Nologaten. Caturtunggal. Kec. Depok. Kab. Sleman. DIY 55281</t>
+  </si>
+  <si>
+    <t>-7.778643299714027</t>
+  </si>
+  <si>
+    <t>110.40153840794645</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/rfQ7La7Wdc5Ghyuw6</t>
+  </si>
+  <si>
+    <t>images\R018.jpg</t>
+  </si>
+  <si>
+    <t>Ruko DTA Square. Jl. Seturan Raya. Kledokan. Caturtunggal. Kec. Depok. Kab. Sleman. DIY 55281</t>
+  </si>
+  <si>
+    <t>-7.774072757500694</t>
+  </si>
+  <si>
+    <t>110.4089132386269</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/Um2cFZ7P8u8Y3MLC9</t>
+  </si>
+  <si>
+    <t>images\R019.jpg</t>
+  </si>
+  <si>
+    <t>Jl. Kaliurang No.17 Km.6. Kentungan. Condongcatur. Kec. Depok. Kab. Sleman. DIY 55284</t>
+  </si>
+  <si>
+    <t>-7.7487586601315295</t>
+  </si>
+  <si>
+    <t>110.38680614047226</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/8WpRE1ayxfZ9wkC86</t>
+  </si>
+  <si>
+    <t xml:space="preserve">images\R020.jpg </t>
+  </si>
+  <si>
+    <t>Jl. Apokat. Perumnas Condong Catur. Condongcatur. Kec. Depok. Kab. Sleman. DIY 55283</t>
+  </si>
+  <si>
+    <t>-7.755653254637142</t>
+  </si>
+  <si>
+    <t>110.40513369629689</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/cAwMBmPVwPjQhV8b8</t>
+  </si>
+  <si>
+    <t>images\R021.jpg</t>
+  </si>
+  <si>
+    <t>Jl. Pintu Selatan UPN. Ngropoh. Condongcatur. Kec. Depok. Kabupaten Sleman. Daerah Istimewa Yogyakarta 55281</t>
+  </si>
+  <si>
+    <t>-7.763446834820035</t>
+  </si>
+  <si>
+    <t>110.4074531962969</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/SQeZppWwHGojvCoYA</t>
+  </si>
+  <si>
+    <t>images\R022.jpg</t>
+  </si>
+  <si>
+    <t>9.00 AM - 21.00 PM</t>
+  </si>
+  <si>
+    <t>Jl. Perumnas Jl. Pintu Selatan UPN No.15. Ngropoh. Condongcatur. Kec. Depok. Kabupaten Sleman. Daerah Istimewa Yogyakarta 55281</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/MyMuo6xx6rSZSYn6A</t>
+  </si>
+  <si>
+    <t>images\R023.jpg</t>
+  </si>
+  <si>
+    <t>9.00 AM - 23.30 PM</t>
+  </si>
+  <si>
+    <t>Jl. Sorowajan No.208. Sorowajan. Banguntapan. Kec. Banguntapan. Kabupaten Bantul. Daerah Istimewa Yogyakarta 55198</t>
+  </si>
+  <si>
+    <t>-7.793779749086242</t>
+  </si>
+  <si>
+    <t>110.4066409251323</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/GGv45FujGN5yNHwcA</t>
+  </si>
+  <si>
+    <t>images\R024.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00 AM - 22.00 PM </t>
+  </si>
+  <si>
+    <t>Ruko Kelapa Hijau. Jl. Brojomulyo No.10. Gejayan. Condongcatur. Kec. Depok. Kabupaten Sleman. Daerah Istimewa Yogyakarta 55281</t>
+  </si>
+  <si>
+    <t>-7.755166261556854</t>
+  </si>
+  <si>
+    <t>110.39649766645391</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/xKX6kRSfFGRUAG9A8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">images\R025.jpg </t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.00 AM - 22.00 PM </t>
+  </si>
+  <si>
+    <t>Jl. Kemuning No.1b. Candok. Condongcatur. Kec. Depok. Kabupaten Sleman. Daerah Istimewa Yogyakarta 55281</t>
+  </si>
+  <si>
+    <t>-7.77696423193207</t>
+  </si>
+  <si>
+    <t>110.4082001376189</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/Tm28gLkjwDSy5e776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">images\R026.jpg </t>
+  </si>
+  <si>
+    <t>Jl. Seturan Raya. Kledokan. Caturtunggal. Kec. Depok. Kabupaten Sleman. Daerah Istimewa Yogyakarta 55281</t>
+  </si>
+  <si>
+    <t>-7.773704851301657</t>
+  </si>
+  <si>
+    <t>110.408922011336</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/8jP7p8idJp7mRe8E8</t>
+  </si>
+  <si>
+    <t>images\R027.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Jl. Nusa Indah II. Dero. Condongcatur. Kec. Depok. Kabupaten Sleman. Daerah Istimewa Yogyakarta 55281</t>
+  </si>
+  <si>
+    <t>-7.755404200161589</t>
+  </si>
+  <si>
+    <t>110.40998792227738</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/8AzpC7NaaWZVtmYx5</t>
+  </si>
+  <si>
+    <t>images\R028.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00 AM - 12.00 PM </t>
+  </si>
+  <si>
+    <t>Komplek Ruko. Puluhdadi No.B 30. Kledokan. Caturtunggal. Kec. Depok. Kabupaten Sleman. Daerah Istimewa Yogyakarta 55281</t>
+  </si>
+  <si>
+    <t>-7.7650364676061825</t>
+  </si>
+  <si>
+    <t>110.41125753432115</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/Xvaw52o9zDGb7w1X6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">images\R029.jpg </t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.00 AM - 03.00 AM </t>
+  </si>
+  <si>
+    <t>Gg. Puluhdadi Seturan Kios B28. Kledokan. Caturtunggal. Kec. Depok. Kabupaten Sleman. Daerah Istimewa Yogyakarta 55281</t>
+  </si>
+  <si>
+    <t>-7.765137937154172</t>
+  </si>
+  <si>
+    <t>110.4111947343212</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/HtN9HV2g3EC2E6Yw6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">images\R030.jpg </t>
+  </si>
+  <si>
+    <t xml:space="preserve">06.00 AM - 18.00 PM </t>
+  </si>
+  <si>
+    <t>Jl. Tasura. Jenengan. Maguwoharjo. Kec. Depok. Kabupaten Sleman. Daerah Istimewa Yogyakarta 55282</t>
+  </si>
+  <si>
+    <t>-7.762639622774797</t>
+  </si>
+  <si>
+    <t>110.42252795295988</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/RGsFBLKN9Tvhmdrh9</t>
+  </si>
+  <si>
+    <t>images\R031.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">08. 00 AM - 22.00 PM </t>
+  </si>
+  <si>
+    <t>Jl. Raya Kledokan No.23. Kledokan. Caturtunggal. Kec. Depok. Kabupaten Sleman. Daerah Istimewa Yogyakarta 55281</t>
+  </si>
+  <si>
+    <t>-7.77473843142309</t>
+  </si>
+  <si>
+    <t>110.40866228736111</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/w3uwETVrBeL8kocJ8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">images\R032.jpg </t>
+  </si>
+  <si>
+    <t xml:space="preserve">09.00 AM - 23.00 PM </t>
+  </si>
+  <si>
+    <t>Jl. Perumnas Seturan. Kledokan. Caturtunggal. Kec. Depok. Kabupaten Sleman. Daerah Istimewa Yogyakarta 55281</t>
+  </si>
+  <si>
+    <t>-7.77216168031367</t>
+  </si>
+  <si>
+    <t>110.40528626645401</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/vByGQcCKFUbyUWs8A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">08.30 AM - 21.00 PM </t>
+  </si>
+  <si>
+    <t>Jl. Perumnas No.127. Tempel. Caturtunggal. Kec. Depok. Kabupaten Sleman. Daerah Istimewa Yogyakarta 55281</t>
+  </si>
+  <si>
+    <t>-7.777458308996077</t>
+  </si>
+  <si>
+    <t>110.40528428637276</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/km35JL3uhPDCb4f26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">images\R034.jpg </t>
+  </si>
+  <si>
+    <t>09.30 AM - 10.00 PM</t>
+  </si>
+  <si>
+    <t>Jl. Perumnas No.141. Nologaten. Caturtunggal. Depok. Sleman Regency. Special Region of Yogyakarta 55281</t>
+  </si>
+  <si>
+    <t>-7.776196931971200</t>
+  </si>
+  <si>
+    <t>110.4045624648450</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/Me5yN67UAteqpGdY9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">images\R035.jpg </t>
+  </si>
+  <si>
+    <t>08.00 - 19.00</t>
+  </si>
+  <si>
+    <t>Jl. Ambar Asri No.311. Ambarukmo. Caturtunggal. Kec. Depok. Kabupaten Sleman. Daerah Istimewa Yogyakarta 55281</t>
+  </si>
+  <si>
+    <t>-7.78261665177125</t>
+  </si>
+  <si>
+    <t>110.39953130466868</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/7ZxoNc54UJ2ZkLf39</t>
+  </si>
+  <si>
+    <t>images\R036.jpg</t>
+  </si>
+  <si>
+    <t>Ruko Rafflesia. Jl. Babarsari. Janti. Caturtunggal. Kec. Depok. Kabupaten Sleman. Daerah Istimewa Yogyakarta 55281</t>
+  </si>
+  <si>
+    <t>-7.779288337303048</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 110.41530143843262</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/yYLSC9uJhWDgQUph8</t>
+  </si>
+  <si>
+    <t>images\R037.jpg</t>
+  </si>
+  <si>
+    <t>07.00 - 22.00</t>
+  </si>
+  <si>
+    <t>6CM6+85F. Jl. Seturan Raya. Kledokan. Caturtunggal. Kec. Depok. Kabupaten Sleman. Daerah Istimewa Yogyakarta 55281</t>
+  </si>
+  <si>
+    <t>-7.7667012046934865</t>
+  </si>
+  <si>
+    <t>110.41036731114856</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/VzBnzzQmzfrSBWo9A</t>
+  </si>
+  <si>
+    <t>images\R038.jpg</t>
+  </si>
+  <si>
+    <t>11.00 - 20.00</t>
+  </si>
+  <si>
+    <t>Jl. Babarsari I No.13. Janti. Caturtunggal. Kec. Depok. Kabupaten Sleman. Daerah Istimewa Yogyakarta 55281</t>
+  </si>
+  <si>
+    <t>-7.780851926155481</t>
+  </si>
+  <si>
+    <t>110.41606370772861</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/bujMvFPKLoa6rspp7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">images\R039.jpg </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rumah Makan.Lesehan </t>
+  </si>
+  <si>
+    <t>11.00 - 00.00</t>
+  </si>
+  <si>
+    <t>Gg. Shinta. Nayan. Maguwoharjo. Kec. Depok. Kabupaten Sleman. Daerah Istimewa Yogyakarta 55281</t>
+  </si>
+  <si>
+    <t>-7.77893232620335</t>
+  </si>
+  <si>
+    <t>110.42400796597617</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/2RH5jEc9g64fvsgb7</t>
+  </si>
+  <si>
+    <t>images\R040.jpg</t>
+  </si>
+  <si>
+    <t>10.00 - 18.00</t>
+  </si>
+  <si>
+    <t>Jl. P. Diponegoro. Sembego. Maguwoharjo. Kec. Depok. Kabupaten Sleman. Daerah Istimewa Yogyakarta 55281</t>
+  </si>
+  <si>
+    <t>-7.761847045353668</t>
+  </si>
+  <si>
+    <t>110.43943841946138</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/4NFp2jRiWyogCHd3A</t>
+  </si>
+  <si>
+    <t>images\R041.jpg</t>
+  </si>
+  <si>
+    <t>11.00 - 22.00</t>
+  </si>
+  <si>
+    <t>Jl. Palagan Tentara Pelajar No.59. Jongkang. Sariharjo. Kec. Ngaglik. Kabupaten Sleman. Daerah Istimewa Yogyakarta 55581</t>
+  </si>
+  <si>
+    <t>110.37401676139700</t>
+  </si>
+  <si>
+    <t>images\R042.jpg</t>
+  </si>
+  <si>
+    <t>11.00 - 23.30</t>
+  </si>
+  <si>
+    <t>Ruko Kelapa Hijau No. 18. Sanggrahan. Condongcatur. Kec. Depok. Kabupaten Sleman. Daerah Istimewa Yogyakarta 55283</t>
+  </si>
+  <si>
+    <t>-7.7535380574479000</t>
+  </si>
+  <si>
+    <t>110.39710521673956</t>
+  </si>
+  <si>
+    <t>images\R043.jpg</t>
+  </si>
+  <si>
+    <t>12.00 - 21.00</t>
+  </si>
+  <si>
+    <t>Jl. Gatotkaca No.1G. Santren. Caturtunggal. Kec. Depok. Kabupaten Sleman. Daerah Istimewa Yogyakarta 55281</t>
+  </si>
+  <si>
+    <t>-7.771694983656591</t>
+  </si>
+  <si>
+    <t>110.39133310283543</t>
+  </si>
+  <si>
+    <t>images\R044.jpg</t>
+  </si>
+  <si>
+    <t>08.30–22.00</t>
+  </si>
+  <si>
+    <t>Jl. Monjali No.99 49. Kutu Dukuh. Sinduadi. Kec. Mlati. Kabupaten Sleman. Daerah Istimewa Yogyakarta 55284</t>
+  </si>
+  <si>
+    <t>-7.757918567368756</t>
+  </si>
+  <si>
+    <t>110.3693590993285</t>
+  </si>
+  <si>
+    <t>images\R045.jpg</t>
+  </si>
+  <si>
+    <t>08.30–21.00</t>
+  </si>
+  <si>
+    <t>Jl. Babarsari No.15. Janti. Caturtunggal. Kec. Depok. Kabupaten Sleman. Daerah Istimewa Yogyakarta 55281</t>
+  </si>
+  <si>
+    <t>110.41522422762888</t>
+  </si>
+  <si>
+    <t>Ruko Gorongan. Jl. Perumnas. Ngropoh. Condongcatur. Kec. Depok. Kabupaten Sleman. Daerah Istimewa Yogyakarta 55283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rumah Makan. Lesehan </t>
+  </si>
+  <si>
+    <t>Jalan Apokat. Klebengan. Blok CT VIII. Kocoran. Caturtunggal. Kec. Depok. Kabupaten Sleman. Daerah Istimewa Yogyakarta 55281</t>
+  </si>
+  <si>
+    <t>Jl. Utama Pugeran RT07 RW65. Pugeran. Maguwoharjo. Kec. Depok. Kabupaten Sleman. Daerah Istimewa Yogyakarta 55282</t>
+  </si>
+  <si>
+    <t>Jl. Nangka III Jl. Utama No.RT 7. Pugeran. Maguwoharjo. Kec. Depok. Kabupaten Sleman. Daerah Istimewa Yogyakarta 55282</t>
+  </si>
+  <si>
+    <t>Jl. Kaswari No.98. Ngringin. Condongcatur. Kec. Depok. Kabupaten Sleman. Daerah Istimewa Yogyakarta 55283</t>
   </si>
 </sst>
 </file>
@@ -1416,7 +1407,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1472,14 +1463,31 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="3" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1799,17 +1807,17 @@
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="5.77734375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="44.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="50.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.21875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="22" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="124.44140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.5546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="22.6640625" style="33" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="21.33203125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="7.21875" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="45.6640625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="13.88671875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.21875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="16.44140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="12.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1818,21 +1826,21 @@
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>416</v>
+        <v>155</v>
       </c>
       <c r="C1" s="4" t="s">
         <v>1</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>417</v>
+        <v>156</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>418</v>
+        <v>157</v>
       </c>
       <c r="F1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="26" t="s">
         <v>3</v>
       </c>
       <c r="H1" s="3" t="s">
@@ -1842,13 +1850,13 @@
         <v>5</v>
       </c>
       <c r="J1" s="5" t="s">
-        <v>419</v>
+        <v>158</v>
       </c>
       <c r="K1" s="6" t="s">
         <v>6</v>
       </c>
       <c r="L1" s="3" t="s">
-        <v>420</v>
+        <v>159</v>
       </c>
       <c r="M1" s="3" t="s">
         <v>8</v>
@@ -1868,80 +1876,80 @@
         <v>12</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>13</v>
+        <v>160</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>95</v>
-      </c>
-      <c r="G2" s="9" t="s">
-        <v>96</v>
+        <v>170</v>
+      </c>
+      <c r="G2" s="27" t="s">
+        <v>171</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>97</v>
+        <v>172</v>
       </c>
       <c r="I2" s="7">
         <v>4.8</v>
       </c>
       <c r="J2" s="10" t="s">
-        <v>98</v>
+        <v>173</v>
       </c>
       <c r="K2" s="11" t="s">
-        <v>99</v>
+        <v>174</v>
       </c>
       <c r="L2" s="7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M2" s="7" t="s">
-        <v>100</v>
+        <v>175</v>
       </c>
     </row>
     <row r="3" spans="1:13" ht="15.6">
       <c r="A3" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" s="7" t="s">
         <v>15</v>
-      </c>
-      <c r="B3" s="7" t="s">
-        <v>16</v>
       </c>
       <c r="C3" s="8" t="s">
         <v>11</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>18</v>
+        <v>161</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>101</v>
-      </c>
-      <c r="G3" s="9" t="s">
-        <v>102</v>
+        <v>176</v>
+      </c>
+      <c r="G3" s="27" t="s">
+        <v>177</v>
       </c>
       <c r="H3" s="9" t="s">
-        <v>103</v>
+        <v>178</v>
       </c>
       <c r="I3" s="7">
         <v>4.5</v>
       </c>
       <c r="J3" s="10" t="s">
-        <v>104</v>
+        <v>179</v>
       </c>
       <c r="K3" s="7" t="s">
-        <v>105</v>
+        <v>180</v>
       </c>
       <c r="L3" s="7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M3" s="7" t="s">
-        <v>100</v>
+        <v>175</v>
       </c>
     </row>
     <row r="4" spans="1:13" ht="15.6">
       <c r="A4" s="7" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C4" s="8" t="s">
         <v>11</v>
@@ -1950,39 +1958,39 @@
         <v>12</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>21</v>
+        <v>162</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>106</v>
-      </c>
-      <c r="G4" s="9" t="s">
-        <v>107</v>
+        <v>181</v>
+      </c>
+      <c r="G4" s="27" t="s">
+        <v>182</v>
       </c>
       <c r="H4" s="9" t="s">
-        <v>108</v>
+        <v>183</v>
       </c>
       <c r="I4" s="7">
         <v>4.7</v>
       </c>
       <c r="J4" s="10" t="s">
-        <v>109</v>
+        <v>184</v>
       </c>
       <c r="K4" s="11" t="s">
-        <v>110</v>
+        <v>185</v>
       </c>
       <c r="L4" s="7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M4" s="7" t="s">
-        <v>100</v>
+        <v>175</v>
       </c>
     </row>
     <row r="5" spans="1:13" ht="15.6">
       <c r="A5" s="7" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C5" s="8" t="s">
         <v>11</v>
@@ -1991,39 +1999,39 @@
         <v>12</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>24</v>
+        <v>163</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>111</v>
-      </c>
-      <c r="G5" s="9" t="s">
-        <v>112</v>
+        <v>186</v>
+      </c>
+      <c r="G5" s="27" t="s">
+        <v>187</v>
       </c>
       <c r="H5" s="9" t="s">
-        <v>113</v>
+        <v>188</v>
       </c>
       <c r="I5" s="7">
         <v>4.5</v>
       </c>
       <c r="J5" s="10" t="s">
-        <v>114</v>
+        <v>189</v>
       </c>
       <c r="K5" s="11" t="s">
-        <v>115</v>
+        <v>190</v>
       </c>
       <c r="L5" s="7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M5" s="7" t="s">
-        <v>100</v>
+        <v>175</v>
       </c>
     </row>
     <row r="6" spans="1:13" ht="15.6">
       <c r="A6" s="7" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="C6" s="8" t="s">
         <v>11</v>
@@ -2032,39 +2040,39 @@
         <v>12</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>27</v>
+        <v>164</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>116</v>
-      </c>
-      <c r="G6" s="9" t="s">
-        <v>117</v>
+        <v>191</v>
+      </c>
+      <c r="G6" s="27" t="s">
+        <v>192</v>
       </c>
       <c r="H6" s="9" t="s">
-        <v>118</v>
+        <v>193</v>
       </c>
       <c r="I6" s="12">
         <v>5</v>
       </c>
       <c r="J6" s="10" t="s">
-        <v>119</v>
+        <v>194</v>
       </c>
       <c r="K6" s="11" t="s">
-        <v>120</v>
+        <v>195</v>
       </c>
       <c r="L6" s="7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M6" s="7" t="s">
-        <v>100</v>
+        <v>175</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="15.6">
       <c r="A7" s="7" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C7" s="8" t="s">
         <v>11</v>
@@ -2073,39 +2081,39 @@
         <v>12</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>30</v>
+        <v>165</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>121</v>
-      </c>
-      <c r="G7" s="9" t="s">
-        <v>122</v>
+        <v>196</v>
+      </c>
+      <c r="G7" s="27" t="s">
+        <v>197</v>
       </c>
       <c r="H7" s="9" t="s">
-        <v>123</v>
+        <v>198</v>
       </c>
       <c r="I7" s="7">
         <v>4.7</v>
       </c>
       <c r="J7" s="10" t="s">
-        <v>124</v>
+        <v>199</v>
       </c>
       <c r="K7" s="11" t="s">
-        <v>125</v>
+        <v>200</v>
       </c>
       <c r="L7" s="7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M7" s="7" t="s">
-        <v>100</v>
+        <v>175</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="15.6">
       <c r="A8" s="7" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="C8" s="8" t="s">
         <v>11</v>
@@ -2114,39 +2122,39 @@
         <v>12</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>33</v>
+        <v>166</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>126</v>
-      </c>
-      <c r="G8" s="9" t="s">
-        <v>127</v>
+        <v>201</v>
+      </c>
+      <c r="G8" s="27" t="s">
+        <v>202</v>
       </c>
       <c r="H8" s="9" t="s">
-        <v>128</v>
+        <v>203</v>
       </c>
       <c r="I8" s="7">
         <v>4.3</v>
       </c>
       <c r="J8" s="10" t="s">
-        <v>129</v>
+        <v>204</v>
       </c>
       <c r="K8" s="11" t="s">
-        <v>130</v>
+        <v>205</v>
       </c>
       <c r="L8" s="7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M8" s="7" t="s">
-        <v>100</v>
+        <v>175</v>
       </c>
     </row>
     <row r="9" spans="1:13" ht="15.6">
       <c r="A9" s="7" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>131</v>
+        <v>206</v>
       </c>
       <c r="C9" s="8" t="s">
         <v>11</v>
@@ -2155,39 +2163,39 @@
         <v>12</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>35</v>
+        <v>167</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>132</v>
-      </c>
-      <c r="G9" s="9" t="s">
-        <v>133</v>
+        <v>207</v>
+      </c>
+      <c r="G9" s="27" t="s">
+        <v>208</v>
       </c>
       <c r="H9" s="9" t="s">
-        <v>134</v>
+        <v>209</v>
       </c>
       <c r="I9" s="7">
         <v>4.7</v>
       </c>
       <c r="J9" s="10" t="s">
-        <v>135</v>
+        <v>210</v>
       </c>
       <c r="K9" s="11" t="s">
-        <v>136</v>
+        <v>211</v>
       </c>
       <c r="L9" s="7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M9" s="7" t="s">
-        <v>100</v>
+        <v>175</v>
       </c>
     </row>
     <row r="10" spans="1:13" ht="15.6">
       <c r="A10" s="7" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="C10" s="8" t="s">
         <v>11</v>
@@ -2196,39 +2204,39 @@
         <v>12</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>24</v>
+        <v>163</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>137</v>
-      </c>
-      <c r="G10" s="9" t="s">
-        <v>138</v>
+        <v>212</v>
+      </c>
+      <c r="G10" s="27" t="s">
+        <v>213</v>
       </c>
       <c r="H10" s="9" t="s">
-        <v>139</v>
+        <v>214</v>
       </c>
       <c r="I10" s="7">
         <v>4.8</v>
       </c>
       <c r="J10" s="10" t="s">
-        <v>140</v>
+        <v>215</v>
       </c>
       <c r="K10" s="11" t="s">
-        <v>141</v>
+        <v>216</v>
       </c>
       <c r="L10" s="7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M10" s="7" t="s">
-        <v>100</v>
+        <v>175</v>
       </c>
     </row>
     <row r="11" spans="1:13" ht="15.6">
       <c r="A11" s="7" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="C11" s="8" t="s">
         <v>11</v>
@@ -2240,36 +2248,36 @@
         <v>7</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>142</v>
-      </c>
-      <c r="G11" s="9" t="s">
-        <v>143</v>
+        <v>217</v>
+      </c>
+      <c r="G11" s="27" t="s">
+        <v>218</v>
       </c>
       <c r="H11" s="9" t="s">
-        <v>144</v>
+        <v>219</v>
       </c>
       <c r="I11" s="7">
         <v>3.9</v>
       </c>
       <c r="J11" s="10" t="s">
-        <v>145</v>
+        <v>220</v>
       </c>
       <c r="K11" s="11" t="s">
-        <v>146</v>
+        <v>221</v>
       </c>
       <c r="L11" s="7" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="M11" s="7" t="s">
-        <v>100</v>
+        <v>175</v>
       </c>
     </row>
     <row r="12" spans="1:13" ht="15.6">
       <c r="A12" s="7" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="C12" s="8" t="s">
         <v>11</v>
@@ -2278,80 +2286,80 @@
         <v>12</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>147</v>
+        <v>222</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>148</v>
-      </c>
-      <c r="G12" s="9" t="s">
-        <v>149</v>
+        <v>223</v>
+      </c>
+      <c r="G12" s="27" t="s">
+        <v>224</v>
       </c>
       <c r="H12" s="9" t="s">
-        <v>150</v>
+        <v>225</v>
       </c>
       <c r="I12" s="7">
         <v>4.4000000000000004</v>
       </c>
       <c r="J12" s="10" t="s">
-        <v>151</v>
+        <v>226</v>
       </c>
       <c r="K12" s="11" t="s">
-        <v>152</v>
+        <v>227</v>
       </c>
       <c r="L12" s="7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M12" s="7" t="s">
-        <v>100</v>
+        <v>175</v>
       </c>
     </row>
     <row r="13" spans="1:13" ht="15.6">
       <c r="A13" s="7" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="C13" s="8" t="s">
         <v>11</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>46</v>
+        <v>168</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>153</v>
-      </c>
-      <c r="G13" s="9" t="s">
-        <v>154</v>
+        <v>228</v>
+      </c>
+      <c r="G13" s="27" t="s">
+        <v>229</v>
       </c>
       <c r="H13" s="9" t="s">
-        <v>155</v>
+        <v>230</v>
       </c>
       <c r="I13" s="7">
         <v>4.9000000000000004</v>
       </c>
       <c r="J13" s="10" t="s">
-        <v>156</v>
+        <v>231</v>
       </c>
       <c r="K13" s="11" t="s">
-        <v>157</v>
+        <v>232</v>
       </c>
       <c r="L13" s="7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M13" s="7" t="s">
-        <v>100</v>
+        <v>175</v>
       </c>
     </row>
     <row r="14" spans="1:13" ht="15.6">
       <c r="A14" s="7" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="C14" s="8" t="s">
         <v>11</v>
@@ -2360,39 +2368,39 @@
         <v>12</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>13</v>
+        <v>160</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>158</v>
-      </c>
-      <c r="G14" s="9" t="s">
-        <v>159</v>
+        <v>233</v>
+      </c>
+      <c r="G14" s="27" t="s">
+        <v>234</v>
       </c>
       <c r="H14" s="9" t="s">
-        <v>160</v>
+        <v>235</v>
       </c>
       <c r="I14" s="7">
         <v>4.4000000000000004</v>
       </c>
       <c r="J14" s="10" t="s">
-        <v>161</v>
+        <v>236</v>
       </c>
       <c r="K14" s="11" t="s">
-        <v>162</v>
+        <v>237</v>
       </c>
       <c r="L14" s="7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M14" s="7" t="s">
-        <v>100</v>
+        <v>175</v>
       </c>
     </row>
     <row r="15" spans="1:13" ht="15.6">
       <c r="A15" s="7" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="C15" s="8" t="s">
         <v>11</v>
@@ -2401,39 +2409,39 @@
         <v>12</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>51</v>
+        <v>169</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>163</v>
-      </c>
-      <c r="G15" s="9" t="s">
-        <v>164</v>
+        <v>238</v>
+      </c>
+      <c r="G15" s="27" t="s">
+        <v>239</v>
       </c>
       <c r="H15" s="9" t="s">
-        <v>165</v>
+        <v>240</v>
       </c>
       <c r="I15" s="7">
         <v>4.5999999999999996</v>
       </c>
       <c r="J15" s="10" t="s">
-        <v>166</v>
+        <v>241</v>
       </c>
       <c r="K15" s="11" t="s">
-        <v>167</v>
+        <v>242</v>
       </c>
       <c r="L15" s="7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M15" s="7" t="s">
-        <v>100</v>
+        <v>175</v>
       </c>
     </row>
     <row r="16" spans="1:13" ht="15.6">
       <c r="A16" s="7" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="C16" s="8" t="s">
         <v>11</v>
@@ -2445,36 +2453,36 @@
         <v>7</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>95</v>
-      </c>
-      <c r="G16" s="9" t="s">
-        <v>168</v>
+        <v>170</v>
+      </c>
+      <c r="G16" s="27" t="s">
+        <v>243</v>
       </c>
       <c r="H16" s="9" t="s">
-        <v>169</v>
+        <v>244</v>
       </c>
       <c r="I16" s="7">
         <v>4.5999999999999996</v>
       </c>
       <c r="J16" s="10" t="s">
-        <v>170</v>
+        <v>245</v>
       </c>
       <c r="K16" s="11" t="s">
-        <v>171</v>
+        <v>246</v>
       </c>
       <c r="L16" s="7" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="M16" s="7" t="s">
-        <v>100</v>
+        <v>175</v>
       </c>
     </row>
     <row r="17" spans="1:13" ht="15.6">
       <c r="A17" s="7" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="C17" s="8" t="s">
         <v>11</v>
@@ -2486,36 +2494,36 @@
         <v>7</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>95</v>
-      </c>
-      <c r="G17" s="9" t="s">
-        <v>172</v>
+        <v>170</v>
+      </c>
+      <c r="G17" s="27" t="s">
+        <v>247</v>
       </c>
       <c r="H17" s="9" t="s">
-        <v>173</v>
+        <v>248</v>
       </c>
       <c r="I17" s="7">
         <v>4.5</v>
       </c>
       <c r="J17" s="10" t="s">
-        <v>174</v>
+        <v>249</v>
       </c>
       <c r="K17" s="11" t="s">
-        <v>175</v>
+        <v>250</v>
       </c>
       <c r="L17" s="7" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="M17" s="7" t="s">
-        <v>100</v>
+        <v>175</v>
       </c>
     </row>
     <row r="18" spans="1:13" ht="15.6">
       <c r="A18" s="7" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="C18" s="8" t="s">
         <v>11</v>
@@ -2527,36 +2535,36 @@
         <v>7</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>176</v>
-      </c>
-      <c r="G18" s="9" t="s">
-        <v>177</v>
+        <v>251</v>
+      </c>
+      <c r="G18" s="27" t="s">
+        <v>252</v>
       </c>
       <c r="H18" s="9" t="s">
-        <v>178</v>
+        <v>253</v>
       </c>
       <c r="I18" s="7">
         <v>4.7</v>
       </c>
       <c r="J18" s="10" t="s">
-        <v>179</v>
+        <v>254</v>
       </c>
       <c r="K18" s="11" t="s">
-        <v>180</v>
+        <v>255</v>
       </c>
       <c r="L18" s="7" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="M18" s="7" t="s">
-        <v>100</v>
+        <v>175</v>
       </c>
     </row>
     <row r="19" spans="1:13" ht="15.6">
       <c r="A19" s="7" t="s">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="C19" s="8" t="s">
         <v>11</v>
@@ -2568,36 +2576,36 @@
         <v>7</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>181</v>
-      </c>
-      <c r="G19" s="9" t="s">
-        <v>182</v>
+        <v>256</v>
+      </c>
+      <c r="G19" s="27" t="s">
+        <v>257</v>
       </c>
       <c r="H19" s="9" t="s">
-        <v>183</v>
+        <v>258</v>
       </c>
       <c r="I19" s="7">
         <v>4.7</v>
       </c>
       <c r="J19" s="10" t="s">
-        <v>184</v>
+        <v>259</v>
       </c>
       <c r="K19" s="11" t="s">
-        <v>185</v>
+        <v>260</v>
       </c>
       <c r="L19" s="7" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="M19" s="7" t="s">
-        <v>100</v>
+        <v>175</v>
       </c>
     </row>
     <row r="20" spans="1:13" ht="15.6">
       <c r="A20" s="7" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="C20" s="8" t="s">
         <v>11</v>
@@ -2609,36 +2617,36 @@
         <v>7</v>
       </c>
       <c r="F20" s="7" t="s">
-        <v>186</v>
-      </c>
-      <c r="G20" s="9" t="s">
-        <v>187</v>
+        <v>261</v>
+      </c>
+      <c r="G20" s="27" t="s">
+        <v>262</v>
       </c>
       <c r="H20" s="9" t="s">
-        <v>188</v>
+        <v>263</v>
       </c>
       <c r="I20" s="7">
         <v>4.7</v>
       </c>
       <c r="J20" s="10" t="s">
-        <v>189</v>
+        <v>264</v>
       </c>
       <c r="K20" s="11" t="s">
-        <v>190</v>
+        <v>265</v>
       </c>
       <c r="L20" s="7" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="M20" s="7" t="s">
-        <v>100</v>
+        <v>175</v>
       </c>
     </row>
     <row r="21" spans="1:13" ht="15.6">
       <c r="A21" s="7" t="s">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="C21" s="8" t="s">
         <v>11</v>
@@ -2650,36 +2658,36 @@
         <v>7</v>
       </c>
       <c r="F21" s="7" t="s">
-        <v>191</v>
-      </c>
-      <c r="G21" s="9" t="s">
-        <v>192</v>
+        <v>266</v>
+      </c>
+      <c r="G21" s="27" t="s">
+        <v>267</v>
       </c>
       <c r="H21" s="9" t="s">
-        <v>193</v>
+        <v>268</v>
       </c>
       <c r="I21" s="7">
         <v>4.3</v>
       </c>
       <c r="J21" s="10" t="s">
-        <v>194</v>
+        <v>269</v>
       </c>
       <c r="K21" s="11" t="s">
-        <v>195</v>
+        <v>270</v>
       </c>
       <c r="L21" s="7" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="M21" s="7" t="s">
-        <v>100</v>
+        <v>175</v>
       </c>
     </row>
     <row r="22" spans="1:13" ht="15.6">
       <c r="A22" s="7" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="C22" s="8" t="s">
         <v>11</v>
@@ -2691,36 +2699,36 @@
         <v>7</v>
       </c>
       <c r="F22" s="7" t="s">
-        <v>196</v>
-      </c>
-      <c r="G22" s="9" t="s">
-        <v>197</v>
+        <v>271</v>
+      </c>
+      <c r="G22" s="27" t="s">
+        <v>272</v>
       </c>
       <c r="H22" s="9" t="s">
-        <v>198</v>
+        <v>273</v>
       </c>
       <c r="I22" s="7">
         <v>4.5</v>
       </c>
       <c r="J22" s="10" t="s">
-        <v>199</v>
+        <v>274</v>
       </c>
       <c r="K22" s="11" t="s">
-        <v>200</v>
+        <v>275</v>
       </c>
       <c r="L22" s="7" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="M22" s="7" t="s">
-        <v>100</v>
+        <v>175</v>
       </c>
     </row>
     <row r="23" spans="1:13" ht="15.6">
       <c r="A23" s="7" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="C23" s="8" t="s">
         <v>11</v>
@@ -2732,36 +2740,36 @@
         <v>7</v>
       </c>
       <c r="F23" s="7" t="s">
-        <v>201</v>
-      </c>
-      <c r="G23" s="9" t="s">
-        <v>202</v>
+        <v>276</v>
+      </c>
+      <c r="G23" s="27" t="s">
+        <v>277</v>
       </c>
       <c r="H23" s="9" t="s">
-        <v>203</v>
+        <v>278</v>
       </c>
       <c r="I23" s="7">
         <v>4.0999999999999996</v>
       </c>
       <c r="J23" s="10" t="s">
-        <v>204</v>
+        <v>279</v>
       </c>
       <c r="K23" s="11" t="s">
-        <v>205</v>
+        <v>280</v>
       </c>
       <c r="L23" s="7" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="M23" s="7" t="s">
-        <v>100</v>
+        <v>175</v>
       </c>
     </row>
     <row r="24" spans="1:13" ht="15.6">
       <c r="A24" s="7" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="C24" s="8" t="s">
         <v>11</v>
@@ -2770,39 +2778,39 @@
         <v>12</v>
       </c>
       <c r="E24" s="7" t="s">
-        <v>206</v>
+        <v>281</v>
       </c>
       <c r="F24" s="7" t="s">
-        <v>207</v>
-      </c>
-      <c r="G24" s="13" t="s">
-        <v>208</v>
+        <v>282</v>
+      </c>
+      <c r="G24" s="28">
+        <v>-7.7638247755953698</v>
       </c>
       <c r="H24" s="13" t="s">
-        <v>209</v>
+        <v>85</v>
       </c>
       <c r="I24" s="7">
         <v>4.7</v>
       </c>
       <c r="J24" s="10" t="s">
-        <v>210</v>
+        <v>283</v>
       </c>
       <c r="K24" s="11" t="s">
-        <v>211</v>
+        <v>284</v>
       </c>
       <c r="L24" s="7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M24" s="7" t="s">
-        <v>100</v>
+        <v>175</v>
       </c>
     </row>
     <row r="25" spans="1:13" ht="15.6">
       <c r="A25" s="7" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="C25" s="8" t="s">
         <v>11</v>
@@ -2811,39 +2819,39 @@
         <v>12</v>
       </c>
       <c r="E25" s="7" t="s">
-        <v>212</v>
+        <v>285</v>
       </c>
       <c r="F25" s="7" t="s">
-        <v>213</v>
-      </c>
-      <c r="G25" s="9" t="s">
-        <v>214</v>
+        <v>286</v>
+      </c>
+      <c r="G25" s="27" t="s">
+        <v>287</v>
       </c>
       <c r="H25" s="9" t="s">
-        <v>215</v>
+        <v>288</v>
       </c>
       <c r="I25" s="7">
         <v>4.3</v>
       </c>
       <c r="J25" s="10" t="s">
-        <v>216</v>
+        <v>289</v>
       </c>
       <c r="K25" s="11" t="s">
-        <v>217</v>
+        <v>290</v>
       </c>
       <c r="L25" s="7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M25" s="7" t="s">
-        <v>100</v>
+        <v>175</v>
       </c>
     </row>
     <row r="26" spans="1:13" ht="15.6">
       <c r="A26" s="7" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="B26" s="14" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="C26" s="8" t="s">
         <v>11</v>
@@ -2852,39 +2860,39 @@
         <v>12</v>
       </c>
       <c r="E26" s="11" t="s">
-        <v>218</v>
+        <v>291</v>
       </c>
       <c r="F26" s="11" t="s">
-        <v>219</v>
-      </c>
-      <c r="G26" s="15" t="s">
-        <v>220</v>
+        <v>292</v>
+      </c>
+      <c r="G26" s="29" t="s">
+        <v>293</v>
       </c>
       <c r="H26" s="15" t="s">
-        <v>221</v>
+        <v>294</v>
       </c>
       <c r="I26" s="11">
         <v>4.7</v>
       </c>
       <c r="J26" s="16" t="s">
-        <v>222</v>
+        <v>295</v>
       </c>
       <c r="K26" s="11" t="s">
-        <v>223</v>
+        <v>296</v>
       </c>
       <c r="L26" s="11" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M26" s="7" t="s">
-        <v>100</v>
+        <v>175</v>
       </c>
     </row>
     <row r="27" spans="1:13" ht="15.6">
       <c r="A27" s="7" t="s">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="B27" s="11" t="s">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="C27" s="8" t="s">
         <v>11</v>
@@ -2893,39 +2901,39 @@
         <v>12</v>
       </c>
       <c r="E27" s="11" t="s">
-        <v>224</v>
+        <v>297</v>
       </c>
       <c r="F27" s="11" t="s">
-        <v>225</v>
-      </c>
-      <c r="G27" s="15" t="s">
-        <v>226</v>
+        <v>298</v>
+      </c>
+      <c r="G27" s="29" t="s">
+        <v>299</v>
       </c>
       <c r="H27" s="15" t="s">
-        <v>227</v>
+        <v>300</v>
       </c>
       <c r="I27" s="11">
         <v>4.5999999999999996</v>
       </c>
       <c r="J27" s="16" t="s">
-        <v>228</v>
+        <v>301</v>
       </c>
       <c r="K27" s="11" t="s">
-        <v>229</v>
+        <v>302</v>
       </c>
       <c r="L27" s="11" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M27" s="7" t="s">
-        <v>100</v>
+        <v>175</v>
       </c>
     </row>
     <row r="28" spans="1:13" ht="15.6">
       <c r="A28" s="17" t="s">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="B28" s="18" t="s">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="C28" s="18" t="s">
         <v>11</v>
@@ -2937,77 +2945,77 @@
         <v>7</v>
       </c>
       <c r="F28" s="18" t="s">
-        <v>230</v>
-      </c>
-      <c r="G28" s="19" t="s">
-        <v>231</v>
+        <v>303</v>
+      </c>
+      <c r="G28" s="30" t="s">
+        <v>304</v>
       </c>
       <c r="H28" s="19" t="s">
-        <v>232</v>
+        <v>305</v>
       </c>
       <c r="I28" s="18">
         <v>4.8</v>
       </c>
       <c r="J28" s="20" t="s">
-        <v>233</v>
+        <v>306</v>
       </c>
       <c r="K28" s="18" t="s">
-        <v>234</v>
+        <v>307</v>
       </c>
       <c r="L28" s="18" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="M28" s="18" t="s">
-        <v>100</v>
+        <v>175</v>
       </c>
     </row>
     <row r="29" spans="1:13" ht="15.6">
       <c r="A29" s="17" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="B29" s="18" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="C29" s="18" t="s">
         <v>11</v>
       </c>
       <c r="D29" s="18" t="s">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="E29" s="18" t="s">
-        <v>224</v>
+        <v>297</v>
       </c>
       <c r="F29" s="18" t="s">
-        <v>235</v>
-      </c>
-      <c r="G29" s="19" t="s">
-        <v>236</v>
+        <v>308</v>
+      </c>
+      <c r="G29" s="30" t="s">
+        <v>309</v>
       </c>
       <c r="H29" s="19" t="s">
-        <v>237</v>
+        <v>310</v>
       </c>
       <c r="I29" s="18">
         <v>4.3</v>
       </c>
       <c r="J29" s="20" t="s">
-        <v>238</v>
+        <v>311</v>
       </c>
       <c r="K29" s="18" t="s">
-        <v>239</v>
+        <v>312</v>
       </c>
       <c r="L29" s="18" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M29" s="18" t="s">
-        <v>100</v>
+        <v>175</v>
       </c>
     </row>
     <row r="30" spans="1:13" ht="15.6">
       <c r="A30" s="17" t="s">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="B30" s="18" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="C30" s="18" t="s">
         <v>11</v>
@@ -3016,39 +3024,39 @@
         <v>12</v>
       </c>
       <c r="E30" s="18" t="s">
-        <v>240</v>
+        <v>313</v>
       </c>
       <c r="F30" s="18" t="s">
-        <v>241</v>
-      </c>
-      <c r="G30" s="19" t="s">
-        <v>242</v>
+        <v>314</v>
+      </c>
+      <c r="G30" s="30" t="s">
+        <v>315</v>
       </c>
       <c r="H30" s="19" t="s">
-        <v>243</v>
+        <v>316</v>
       </c>
       <c r="I30" s="18">
         <v>4.5999999999999996</v>
       </c>
       <c r="J30" s="20" t="s">
-        <v>244</v>
+        <v>317</v>
       </c>
       <c r="K30" s="18" t="s">
-        <v>245</v>
+        <v>318</v>
       </c>
       <c r="L30" s="18" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M30" s="18" t="s">
-        <v>100</v>
+        <v>175</v>
       </c>
     </row>
     <row r="31" spans="1:13" ht="15.6">
       <c r="A31" s="17" t="s">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="B31" s="18" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="C31" s="18" t="s">
         <v>11</v>
@@ -3057,39 +3065,39 @@
         <v>12</v>
       </c>
       <c r="E31" s="18" t="s">
-        <v>246</v>
+        <v>319</v>
       </c>
       <c r="F31" s="18" t="s">
-        <v>247</v>
-      </c>
-      <c r="G31" s="19" t="s">
-        <v>248</v>
+        <v>320</v>
+      </c>
+      <c r="G31" s="30" t="s">
+        <v>321</v>
       </c>
       <c r="H31" s="19" t="s">
-        <v>249</v>
+        <v>322</v>
       </c>
       <c r="I31" s="18">
         <v>4.5</v>
       </c>
       <c r="J31" s="20" t="s">
-        <v>250</v>
+        <v>323</v>
       </c>
       <c r="K31" s="18" t="s">
-        <v>251</v>
+        <v>324</v>
       </c>
       <c r="L31" s="18" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M31" s="18" t="s">
-        <v>100</v>
+        <v>175</v>
       </c>
     </row>
     <row r="32" spans="1:13" ht="15.6">
       <c r="A32" s="17" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="B32" s="18" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="C32" s="18" t="s">
         <v>11</v>
@@ -3098,39 +3106,39 @@
         <v>12</v>
       </c>
       <c r="E32" s="18" t="s">
-        <v>252</v>
+        <v>325</v>
       </c>
       <c r="F32" s="18" t="s">
-        <v>253</v>
-      </c>
-      <c r="G32" s="19" t="s">
-        <v>254</v>
+        <v>326</v>
+      </c>
+      <c r="G32" s="30" t="s">
+        <v>327</v>
       </c>
       <c r="H32" s="19" t="s">
-        <v>255</v>
+        <v>328</v>
       </c>
       <c r="I32" s="18">
         <v>4.5</v>
       </c>
       <c r="J32" s="20" t="s">
-        <v>256</v>
+        <v>329</v>
       </c>
       <c r="K32" s="18" t="s">
-        <v>257</v>
+        <v>330</v>
       </c>
       <c r="L32" s="18" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M32" s="18" t="s">
-        <v>100</v>
+        <v>175</v>
       </c>
     </row>
     <row r="33" spans="1:13" ht="15.6">
       <c r="A33" s="17" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="B33" s="18" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="C33" s="18" t="s">
         <v>11</v>
@@ -3139,39 +3147,39 @@
         <v>12</v>
       </c>
       <c r="E33" s="18" t="s">
-        <v>258</v>
+        <v>331</v>
       </c>
       <c r="F33" s="18" t="s">
-        <v>259</v>
-      </c>
-      <c r="G33" s="19" t="s">
-        <v>260</v>
+        <v>332</v>
+      </c>
+      <c r="G33" s="30" t="s">
+        <v>333</v>
       </c>
       <c r="H33" s="19" t="s">
-        <v>261</v>
+        <v>334</v>
       </c>
       <c r="I33" s="18">
         <v>3.2</v>
       </c>
       <c r="J33" s="20" t="s">
-        <v>262</v>
+        <v>335</v>
       </c>
       <c r="K33" s="18" t="s">
-        <v>263</v>
+        <v>336</v>
       </c>
       <c r="L33" s="18" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M33" s="18" t="s">
-        <v>100</v>
+        <v>175</v>
       </c>
     </row>
     <row r="34" spans="1:13" ht="15.6">
       <c r="A34" s="17" t="s">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="B34" s="18" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="C34" s="18" t="s">
         <v>11</v>
@@ -3180,39 +3188,39 @@
         <v>12</v>
       </c>
       <c r="E34" s="18" t="s">
-        <v>264</v>
+        <v>337</v>
       </c>
       <c r="F34" s="18" t="s">
-        <v>265</v>
-      </c>
-      <c r="G34" s="19" t="s">
-        <v>266</v>
+        <v>338</v>
+      </c>
+      <c r="G34" s="30" t="s">
+        <v>339</v>
       </c>
       <c r="H34" s="19" t="s">
-        <v>267</v>
+        <v>340</v>
       </c>
       <c r="I34" s="18">
         <v>4.0999999999999996</v>
       </c>
       <c r="J34" s="20" t="s">
-        <v>268</v>
+        <v>341</v>
       </c>
       <c r="K34" s="18" t="s">
-        <v>269</v>
+        <v>86</v>
       </c>
       <c r="L34" s="18" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M34" s="18" t="s">
-        <v>100</v>
+        <v>175</v>
       </c>
     </row>
     <row r="35" spans="1:13" ht="15.6">
       <c r="A35" s="17" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="B35" s="18" t="s">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="C35" s="18" t="s">
         <v>11</v>
@@ -3221,39 +3229,39 @@
         <v>12</v>
       </c>
       <c r="E35" s="18" t="s">
-        <v>270</v>
+        <v>342</v>
       </c>
       <c r="F35" s="18" t="s">
-        <v>271</v>
-      </c>
-      <c r="G35" s="19" t="s">
-        <v>272</v>
+        <v>343</v>
+      </c>
+      <c r="G35" s="30" t="s">
+        <v>344</v>
       </c>
       <c r="H35" s="19" t="s">
-        <v>273</v>
+        <v>345</v>
       </c>
       <c r="I35" s="18">
         <v>4.5999999999999996</v>
       </c>
       <c r="J35" s="20" t="s">
-        <v>274</v>
+        <v>346</v>
       </c>
       <c r="K35" s="18" t="s">
-        <v>275</v>
+        <v>347</v>
       </c>
       <c r="L35" s="18" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M35" s="18" t="s">
-        <v>100</v>
+        <v>175</v>
       </c>
     </row>
     <row r="36" spans="1:13" ht="15.6">
       <c r="A36" s="17" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="B36" s="18" t="s">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="C36" s="18" t="s">
         <v>11</v>
@@ -3262,39 +3270,39 @@
         <v>12</v>
       </c>
       <c r="E36" s="18" t="s">
-        <v>276</v>
+        <v>348</v>
       </c>
       <c r="F36" s="18" t="s">
-        <v>277</v>
-      </c>
-      <c r="G36" s="19" t="s">
-        <v>278</v>
+        <v>349</v>
+      </c>
+      <c r="G36" s="30" t="s">
+        <v>350</v>
       </c>
       <c r="H36" s="19" t="s">
-        <v>279</v>
+        <v>351</v>
       </c>
       <c r="I36" s="18">
         <v>4.4000000000000004</v>
       </c>
       <c r="J36" s="20" t="s">
-        <v>280</v>
+        <v>352</v>
       </c>
       <c r="K36" s="18" t="s">
-        <v>281</v>
+        <v>353</v>
       </c>
       <c r="L36" s="18" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M36" s="18" t="s">
-        <v>100</v>
+        <v>175</v>
       </c>
     </row>
     <row r="37" spans="1:13" ht="15.6">
       <c r="A37" s="17" t="s">
-        <v>282</v>
+        <v>87</v>
       </c>
       <c r="B37" s="21" t="s">
-        <v>283</v>
+        <v>88</v>
       </c>
       <c r="C37" s="18" t="s">
         <v>11</v>
@@ -3303,39 +3311,39 @@
         <v>12</v>
       </c>
       <c r="E37" s="18" t="s">
-        <v>284</v>
+        <v>354</v>
       </c>
       <c r="F37" s="18" t="s">
-        <v>285</v>
-      </c>
-      <c r="G37" s="19" t="s">
-        <v>286</v>
+        <v>355</v>
+      </c>
+      <c r="G37" s="30" t="s">
+        <v>356</v>
       </c>
       <c r="H37" s="19" t="s">
-        <v>287</v>
+        <v>357</v>
       </c>
       <c r="I37" s="18">
         <v>4.5999999999999996</v>
       </c>
       <c r="J37" s="20" t="s">
-        <v>288</v>
+        <v>358</v>
       </c>
       <c r="K37" s="18" t="s">
-        <v>289</v>
+        <v>359</v>
       </c>
       <c r="L37" s="18" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M37" s="18" t="s">
-        <v>100</v>
+        <v>175</v>
       </c>
     </row>
     <row r="38" spans="1:13" ht="15.6">
       <c r="A38" s="17" t="s">
-        <v>290</v>
+        <v>89</v>
       </c>
       <c r="B38" s="21" t="s">
-        <v>291</v>
+        <v>90</v>
       </c>
       <c r="C38" s="18" t="s">
         <v>11</v>
@@ -3347,36 +3355,36 @@
         <v>7</v>
       </c>
       <c r="F38" s="18" t="s">
-        <v>292</v>
-      </c>
-      <c r="G38" s="19" t="s">
-        <v>293</v>
+        <v>360</v>
+      </c>
+      <c r="G38" s="30" t="s">
+        <v>361</v>
       </c>
       <c r="H38" s="19" t="s">
-        <v>294</v>
+        <v>362</v>
       </c>
       <c r="I38" s="18">
         <v>4.5999999999999996</v>
       </c>
       <c r="J38" s="20" t="s">
-        <v>295</v>
+        <v>363</v>
       </c>
       <c r="K38" s="18" t="s">
-        <v>296</v>
+        <v>364</v>
       </c>
       <c r="L38" s="18" t="s">
-        <v>297</v>
+        <v>91</v>
       </c>
       <c r="M38" s="18" t="s">
-        <v>100</v>
+        <v>175</v>
       </c>
     </row>
     <row r="39" spans="1:13" ht="15.6">
       <c r="A39" s="17" t="s">
-        <v>298</v>
+        <v>92</v>
       </c>
       <c r="B39" s="21" t="s">
-        <v>299</v>
+        <v>93</v>
       </c>
       <c r="C39" s="18" t="s">
         <v>11</v>
@@ -3385,326 +3393,326 @@
         <v>12</v>
       </c>
       <c r="E39" s="18" t="s">
-        <v>300</v>
+        <v>365</v>
       </c>
       <c r="F39" s="18" t="s">
-        <v>301</v>
-      </c>
-      <c r="G39" s="19" t="s">
-        <v>302</v>
+        <v>366</v>
+      </c>
+      <c r="G39" s="30" t="s">
+        <v>367</v>
       </c>
       <c r="H39" s="19" t="s">
-        <v>303</v>
+        <v>368</v>
       </c>
       <c r="I39" s="18">
         <v>4.9000000000000004</v>
       </c>
       <c r="J39" s="20" t="s">
-        <v>304</v>
+        <v>369</v>
       </c>
       <c r="K39" s="18" t="s">
-        <v>305</v>
+        <v>370</v>
       </c>
       <c r="L39" s="18" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M39" s="18" t="s">
-        <v>100</v>
+        <v>175</v>
       </c>
     </row>
     <row r="40" spans="1:13" ht="15.6">
       <c r="A40" s="17" t="s">
-        <v>306</v>
+        <v>94</v>
       </c>
       <c r="B40" s="21" t="s">
-        <v>307</v>
+        <v>95</v>
       </c>
       <c r="C40" s="18" t="s">
         <v>11</v>
       </c>
       <c r="D40" s="17" t="s">
-        <v>308</v>
+        <v>96</v>
       </c>
       <c r="E40" s="18" t="s">
-        <v>309</v>
+        <v>371</v>
       </c>
       <c r="F40" s="18" t="s">
-        <v>310</v>
-      </c>
-      <c r="G40" s="19" t="s">
-        <v>311</v>
+        <v>372</v>
+      </c>
+      <c r="G40" s="30" t="s">
+        <v>373</v>
       </c>
       <c r="H40" s="19" t="s">
-        <v>312</v>
+        <v>374</v>
       </c>
       <c r="I40" s="18">
         <v>4.9000000000000004</v>
       </c>
       <c r="J40" s="20" t="s">
-        <v>313</v>
+        <v>375</v>
       </c>
       <c r="K40" s="18" t="s">
-        <v>314</v>
+        <v>376</v>
       </c>
       <c r="L40" s="18" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M40" s="18" t="s">
-        <v>100</v>
+        <v>175</v>
       </c>
     </row>
     <row r="41" spans="1:13" ht="15.6">
       <c r="A41" s="17" t="s">
-        <v>315</v>
+        <v>97</v>
       </c>
       <c r="B41" s="21" t="s">
-        <v>316</v>
+        <v>98</v>
       </c>
       <c r="C41" s="18" t="s">
-        <v>317</v>
+        <v>377</v>
       </c>
       <c r="D41" s="17" t="s">
         <v>12</v>
       </c>
       <c r="E41" s="18" t="s">
-        <v>318</v>
+        <v>378</v>
       </c>
       <c r="F41" s="18" t="s">
-        <v>319</v>
-      </c>
-      <c r="G41" s="19" t="s">
-        <v>320</v>
+        <v>379</v>
+      </c>
+      <c r="G41" s="30" t="s">
+        <v>380</v>
       </c>
       <c r="H41" s="19" t="s">
-        <v>321</v>
+        <v>381</v>
       </c>
       <c r="I41" s="18">
         <v>4.9000000000000004</v>
       </c>
       <c r="J41" s="20" t="s">
-        <v>322</v>
+        <v>382</v>
       </c>
       <c r="K41" s="18" t="s">
-        <v>323</v>
+        <v>383</v>
       </c>
       <c r="L41" s="18" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M41" s="18" t="s">
-        <v>100</v>
+        <v>175</v>
       </c>
     </row>
     <row r="42" spans="1:13" ht="15.6">
       <c r="A42" s="17" t="s">
-        <v>324</v>
+        <v>99</v>
       </c>
       <c r="B42" s="21" t="s">
-        <v>325</v>
+        <v>100</v>
       </c>
       <c r="C42" s="18" t="s">
-        <v>317</v>
+        <v>377</v>
       </c>
       <c r="D42" s="17" t="s">
         <v>12</v>
       </c>
       <c r="E42" s="18" t="s">
-        <v>326</v>
+        <v>384</v>
       </c>
       <c r="F42" s="18" t="s">
-        <v>327</v>
-      </c>
-      <c r="G42" s="19" t="s">
-        <v>328</v>
+        <v>385</v>
+      </c>
+      <c r="G42" s="30" t="s">
+        <v>386</v>
       </c>
       <c r="H42" s="19" t="s">
-        <v>329</v>
+        <v>387</v>
       </c>
       <c r="I42" s="18">
         <v>4.5999999999999996</v>
       </c>
       <c r="J42" s="20" t="s">
-        <v>330</v>
+        <v>388</v>
       </c>
       <c r="K42" s="18" t="s">
-        <v>331</v>
+        <v>389</v>
       </c>
       <c r="L42" s="18" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M42" s="18" t="s">
-        <v>100</v>
+        <v>175</v>
       </c>
     </row>
     <row r="43" spans="1:13" ht="15.6">
       <c r="A43" s="17" t="s">
-        <v>332</v>
+        <v>101</v>
       </c>
       <c r="B43" s="21" t="s">
-        <v>333</v>
+        <v>102</v>
       </c>
       <c r="C43" s="22" t="s">
-        <v>334</v>
+        <v>103</v>
       </c>
       <c r="D43" s="17" t="s">
         <v>12</v>
       </c>
       <c r="E43" s="18" t="s">
-        <v>335</v>
+        <v>390</v>
       </c>
       <c r="F43" s="18" t="s">
-        <v>336</v>
-      </c>
-      <c r="G43" s="23" t="s">
-        <v>337</v>
+        <v>391</v>
+      </c>
+      <c r="G43" s="31">
+        <v>-7.74358755941239</v>
       </c>
       <c r="H43" s="19" t="s">
-        <v>338</v>
+        <v>392</v>
       </c>
       <c r="I43" s="18">
         <v>4.8</v>
       </c>
       <c r="J43" s="20" t="s">
-        <v>339</v>
+        <v>104</v>
       </c>
       <c r="K43" s="18" t="s">
-        <v>340</v>
+        <v>393</v>
       </c>
       <c r="L43" s="18" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M43" s="1" t="s">
-        <v>341</v>
+        <v>105</v>
       </c>
     </row>
     <row r="44" spans="1:13" ht="15.6">
       <c r="A44" s="17" t="s">
-        <v>342</v>
+        <v>106</v>
       </c>
       <c r="B44" s="21" t="s">
-        <v>343</v>
+        <v>107</v>
       </c>
       <c r="C44" s="22" t="s">
-        <v>344</v>
+        <v>108</v>
       </c>
       <c r="D44" s="17" t="s">
         <v>12</v>
       </c>
       <c r="E44" s="18" t="s">
-        <v>345</v>
+        <v>394</v>
       </c>
       <c r="F44" s="18" t="s">
-        <v>346</v>
-      </c>
-      <c r="G44" s="19" t="s">
-        <v>347</v>
+        <v>395</v>
+      </c>
+      <c r="G44" s="30" t="s">
+        <v>396</v>
       </c>
       <c r="H44" s="19" t="s">
-        <v>348</v>
+        <v>397</v>
       </c>
       <c r="I44" s="18">
         <v>4.5</v>
       </c>
       <c r="J44" s="20" t="s">
-        <v>349</v>
+        <v>109</v>
       </c>
       <c r="K44" s="18" t="s">
-        <v>350</v>
+        <v>398</v>
       </c>
       <c r="L44" s="18" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M44" s="1" t="s">
-        <v>341</v>
+        <v>105</v>
       </c>
     </row>
     <row r="45" spans="1:13" ht="15.6">
       <c r="A45" s="17" t="s">
-        <v>351</v>
+        <v>110</v>
       </c>
       <c r="B45" s="21" t="s">
-        <v>352</v>
-      </c>
-      <c r="C45" s="24" t="s">
-        <v>334</v>
+        <v>111</v>
+      </c>
+      <c r="C45" s="23" t="s">
+        <v>103</v>
       </c>
       <c r="D45" s="17" t="s">
         <v>12</v>
       </c>
       <c r="E45" s="18" t="s">
-        <v>353</v>
+        <v>399</v>
       </c>
       <c r="F45" s="18" t="s">
-        <v>354</v>
-      </c>
-      <c r="G45" s="19" t="s">
-        <v>355</v>
+        <v>400</v>
+      </c>
+      <c r="G45" s="30" t="s">
+        <v>401</v>
       </c>
       <c r="H45" s="19" t="s">
-        <v>356</v>
+        <v>402</v>
       </c>
       <c r="I45" s="18">
         <v>4.9000000000000004</v>
       </c>
       <c r="J45" s="20" t="s">
-        <v>357</v>
+        <v>112</v>
       </c>
       <c r="K45" s="18" t="s">
-        <v>358</v>
+        <v>403</v>
       </c>
       <c r="L45" s="18" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M45" s="1" t="s">
-        <v>341</v>
+        <v>105</v>
       </c>
     </row>
     <row r="46" spans="1:13" ht="15.6">
       <c r="A46" s="17" t="s">
-        <v>359</v>
+        <v>113</v>
       </c>
       <c r="B46" s="21" t="s">
-        <v>360</v>
-      </c>
-      <c r="C46" s="24" t="s">
-        <v>361</v>
+        <v>114</v>
+      </c>
+      <c r="C46" s="23" t="s">
+        <v>115</v>
       </c>
       <c r="D46" s="17" t="s">
         <v>12</v>
       </c>
       <c r="E46" s="18" t="s">
-        <v>362</v>
+        <v>404</v>
       </c>
       <c r="F46" s="18" t="s">
-        <v>363</v>
-      </c>
-      <c r="G46" s="19" t="s">
-        <v>364</v>
+        <v>405</v>
+      </c>
+      <c r="G46" s="30" t="s">
+        <v>406</v>
       </c>
       <c r="H46" s="19" t="s">
-        <v>365</v>
+        <v>407</v>
       </c>
       <c r="I46" s="18">
         <v>4.7</v>
       </c>
       <c r="J46" s="20" t="s">
-        <v>366</v>
+        <v>116</v>
       </c>
       <c r="K46" s="18" t="s">
-        <v>367</v>
+        <v>408</v>
       </c>
       <c r="L46" s="18" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M46" s="18" t="s">
-        <v>100</v>
+        <v>175</v>
       </c>
     </row>
     <row r="47" spans="1:13" ht="15.6">
       <c r="A47" s="17" t="s">
-        <v>368</v>
+        <v>117</v>
       </c>
       <c r="B47" s="21" t="s">
-        <v>369</v>
+        <v>118</v>
       </c>
       <c r="C47" s="18" t="s">
         <v>11</v>
@@ -3713,39 +3721,39 @@
         <v>12</v>
       </c>
       <c r="E47" s="18" t="s">
-        <v>370</v>
+        <v>409</v>
       </c>
       <c r="F47" s="18" t="s">
-        <v>371</v>
-      </c>
-      <c r="G47" s="19" t="s">
-        <v>372</v>
+        <v>410</v>
+      </c>
+      <c r="G47" s="30">
+        <v>-7.7797246321450402</v>
       </c>
       <c r="H47" s="19" t="s">
-        <v>373</v>
+        <v>411</v>
       </c>
       <c r="I47" s="18">
         <v>4.7</v>
       </c>
       <c r="J47" s="20" t="s">
-        <v>374</v>
+        <v>119</v>
       </c>
       <c r="K47" s="18" t="s">
-        <v>375</v>
+        <v>120</v>
       </c>
       <c r="L47" s="18" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M47" s="18" t="s">
-        <v>100</v>
+        <v>175</v>
       </c>
     </row>
     <row r="48" spans="1:13" ht="15.6">
       <c r="A48" s="17" t="s">
-        <v>376</v>
+        <v>121</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="C48" s="18" t="s">
         <v>11</v>
@@ -3754,124 +3762,124 @@
         <v>12</v>
       </c>
       <c r="E48" s="8" t="s">
-        <v>377</v>
+        <v>122</v>
       </c>
       <c r="F48" s="8" t="s">
-        <v>378</v>
-      </c>
-      <c r="G48" s="25" t="s">
-        <v>379</v>
-      </c>
-      <c r="H48" s="25" t="s">
-        <v>380</v>
+        <v>412</v>
+      </c>
+      <c r="G48" s="32" t="s">
+        <v>123</v>
+      </c>
+      <c r="H48" s="24" t="s">
+        <v>124</v>
       </c>
       <c r="I48" s="8">
         <v>4.3</v>
       </c>
-      <c r="J48" s="26" t="s">
-        <v>381</v>
+      <c r="J48" s="25" t="s">
+        <v>125</v>
       </c>
       <c r="K48" s="18" t="s">
-        <v>382</v>
+        <v>126</v>
       </c>
       <c r="L48" s="18" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M48" s="8" t="s">
-        <v>100</v>
+        <v>175</v>
       </c>
     </row>
     <row r="49" spans="1:13" ht="15.6">
       <c r="A49" s="17" t="s">
-        <v>383</v>
+        <v>127</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>384</v>
+        <v>128</v>
       </c>
       <c r="C49" s="8" t="s">
-        <v>385</v>
+        <v>413</v>
       </c>
       <c r="D49" s="17" t="s">
         <v>12</v>
       </c>
       <c r="E49" s="8" t="s">
-        <v>386</v>
+        <v>129</v>
       </c>
       <c r="F49" s="8" t="s">
-        <v>387</v>
-      </c>
-      <c r="G49" s="25" t="s">
-        <v>388</v>
-      </c>
-      <c r="H49" s="25" t="s">
-        <v>389</v>
+        <v>414</v>
+      </c>
+      <c r="G49" s="32" t="s">
+        <v>130</v>
+      </c>
+      <c r="H49" s="24" t="s">
+        <v>131</v>
       </c>
       <c r="I49" s="8">
         <v>4.3</v>
       </c>
-      <c r="J49" s="26" t="s">
-        <v>390</v>
+      <c r="J49" s="25" t="s">
+        <v>132</v>
       </c>
       <c r="K49" s="18" t="s">
-        <v>391</v>
+        <v>133</v>
       </c>
       <c r="L49" s="18" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M49" s="8" t="s">
-        <v>100</v>
+        <v>175</v>
       </c>
     </row>
     <row r="50" spans="1:13" ht="15.6">
       <c r="A50" s="17" t="s">
-        <v>392</v>
+        <v>134</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>393</v>
+        <v>135</v>
       </c>
       <c r="C50" s="8" t="s">
-        <v>385</v>
+        <v>413</v>
       </c>
       <c r="D50" s="17" t="s">
         <v>12</v>
       </c>
       <c r="E50" s="8" t="s">
-        <v>394</v>
+        <v>136</v>
       </c>
       <c r="F50" s="8" t="s">
-        <v>395</v>
-      </c>
-      <c r="G50" s="25" t="s">
-        <v>396</v>
-      </c>
-      <c r="H50" s="25" t="s">
-        <v>397</v>
+        <v>415</v>
+      </c>
+      <c r="G50" s="32" t="s">
+        <v>137</v>
+      </c>
+      <c r="H50" s="24" t="s">
+        <v>138</v>
       </c>
       <c r="I50" s="8">
         <v>4.5999999999999996</v>
       </c>
-      <c r="J50" s="26" t="s">
-        <v>398</v>
+      <c r="J50" s="25" t="s">
+        <v>139</v>
       </c>
       <c r="K50" s="18" t="s">
-        <v>399</v>
+        <v>140</v>
       </c>
       <c r="L50" s="18" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M50" s="8" t="s">
-        <v>100</v>
+        <v>175</v>
       </c>
     </row>
     <row r="51" spans="1:13" ht="15.6">
       <c r="A51" s="17" t="s">
-        <v>400</v>
+        <v>141</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>401</v>
+        <v>142</v>
       </c>
       <c r="C51" s="8" t="s">
-        <v>402</v>
+        <v>143</v>
       </c>
       <c r="D51" s="17" t="s">
         <v>12</v>
@@ -3880,114 +3888,114 @@
         <v>7</v>
       </c>
       <c r="F51" s="8" t="s">
-        <v>403</v>
-      </c>
-      <c r="G51" s="25" t="s">
-        <v>404</v>
-      </c>
-      <c r="H51" s="25" t="s">
-        <v>405</v>
+        <v>416</v>
+      </c>
+      <c r="G51" s="32" t="s">
+        <v>144</v>
+      </c>
+      <c r="H51" s="24" t="s">
+        <v>145</v>
       </c>
       <c r="I51" s="8">
         <v>4.3</v>
       </c>
-      <c r="J51" s="26" t="s">
-        <v>406</v>
+      <c r="J51" s="25" t="s">
+        <v>146</v>
       </c>
       <c r="K51" s="18" t="s">
-        <v>407</v>
+        <v>147</v>
       </c>
       <c r="L51" s="8" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="M51" s="8" t="s">
-        <v>100</v>
+        <v>175</v>
       </c>
     </row>
     <row r="52" spans="1:13" ht="15.6">
       <c r="A52" s="17" t="s">
-        <v>408</v>
+        <v>148</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>409</v>
+        <v>149</v>
       </c>
       <c r="C52" s="8" t="s">
-        <v>402</v>
+        <v>143</v>
       </c>
       <c r="D52" s="17" t="s">
         <v>12</v>
       </c>
       <c r="E52" s="8" t="s">
-        <v>410</v>
+        <v>150</v>
       </c>
       <c r="F52" s="8" t="s">
-        <v>411</v>
-      </c>
-      <c r="G52" s="25" t="s">
-        <v>412</v>
-      </c>
-      <c r="H52" s="25" t="s">
-        <v>413</v>
+        <v>417</v>
+      </c>
+      <c r="G52" s="32" t="s">
+        <v>151</v>
+      </c>
+      <c r="H52" s="24" t="s">
+        <v>152</v>
       </c>
       <c r="I52" s="8">
         <v>4.9000000000000004</v>
       </c>
-      <c r="J52" s="26" t="s">
-        <v>414</v>
+      <c r="J52" s="25" t="s">
+        <v>153</v>
       </c>
       <c r="K52" s="18" t="s">
-        <v>415</v>
+        <v>154</v>
       </c>
       <c r="L52" s="18" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M52" s="8" t="s">
-        <v>100</v>
+        <v>175</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="J2" r:id="rId1" xr:uid="{CE36CA00-A6BF-4AAB-B6C5-44962FC36003}"/>
-    <hyperlink ref="J3" r:id="rId2" xr:uid="{8057D4F4-5BFC-4452-A91C-DC5703FAECB8}"/>
-    <hyperlink ref="J4" r:id="rId3" xr:uid="{F904D503-2E10-4E57-B75B-A8A69DAA99AC}"/>
-    <hyperlink ref="J5" r:id="rId4" xr:uid="{EE9CA8E6-0197-49ED-B5B1-C6A5C74478AE}"/>
-    <hyperlink ref="J6" r:id="rId5" xr:uid="{882673DE-C8D0-40A7-AF9C-38A0E598E0FD}"/>
-    <hyperlink ref="J7" r:id="rId6" xr:uid="{B9D7202B-76BB-4617-985A-E07B6C43860A}"/>
-    <hyperlink ref="J8" r:id="rId7" xr:uid="{15A7BAEC-BBF0-4442-B043-5B3F3D6B801F}"/>
-    <hyperlink ref="J9" r:id="rId8" xr:uid="{798F3B9C-BFE7-4D89-ACD8-C84BEA75BCBD}"/>
-    <hyperlink ref="J10" r:id="rId9" xr:uid="{7F9A602E-E203-4C49-AE09-DD17C3E1802E}"/>
-    <hyperlink ref="J11" r:id="rId10" xr:uid="{E36B4D7D-26DA-443D-8A9E-A738223C713B}"/>
-    <hyperlink ref="J12" r:id="rId11" xr:uid="{7FEE1438-2B19-427E-898D-DB8271442A22}"/>
-    <hyperlink ref="J13" r:id="rId12" xr:uid="{F130B874-88BE-4A5E-9A44-EEEA49DFB806}"/>
-    <hyperlink ref="J14" r:id="rId13" xr:uid="{E006C1A7-AC6B-4017-887A-DC5E7916F38E}"/>
-    <hyperlink ref="J15" r:id="rId14" xr:uid="{AD6E7590-08D3-4CA0-827A-4DEE1033B8FA}"/>
-    <hyperlink ref="J16" r:id="rId15" xr:uid="{942FBC13-AB50-4C24-BAD8-F27520219896}"/>
-    <hyperlink ref="J17" r:id="rId16" xr:uid="{47CA89FF-1F50-4A02-BA83-1539A6F73345}"/>
-    <hyperlink ref="J18" r:id="rId17" xr:uid="{ECEBCF49-E889-4534-82DC-2F804160DF23}"/>
-    <hyperlink ref="J19" r:id="rId18" xr:uid="{3F2FED4B-5E07-4648-B42E-3E11483F3CE7}"/>
-    <hyperlink ref="J20" r:id="rId19" xr:uid="{52B755C7-03DD-4309-902B-B4BEAC1DCDEC}"/>
-    <hyperlink ref="J21" r:id="rId20" xr:uid="{FC487693-D61C-4DCE-8707-E753C696E70E}"/>
-    <hyperlink ref="J22" r:id="rId21" xr:uid="{D6B51B4E-32C6-4D4E-ABDB-90D19F129D97}"/>
-    <hyperlink ref="J23" r:id="rId22" xr:uid="{DB808F08-B054-496A-8694-3198944C8277}"/>
-    <hyperlink ref="J24" r:id="rId23" xr:uid="{66C24FEC-8BD2-4056-89AC-E255AB928D5A}"/>
-    <hyperlink ref="J25" r:id="rId24" xr:uid="{223D442C-F685-4A6D-936E-061C8109B6A7}"/>
-    <hyperlink ref="J26" r:id="rId25" xr:uid="{F1A17DFC-9523-4457-B9A2-A8FBD5EE9C9B}"/>
-    <hyperlink ref="J27" r:id="rId26" xr:uid="{1DF2EE09-82D1-49A8-A6AB-09D17DA070E9}"/>
-    <hyperlink ref="J28" r:id="rId27" xr:uid="{D9527C73-A6D8-4D66-949B-4C50774795BC}"/>
-    <hyperlink ref="J29" r:id="rId28" xr:uid="{77993E83-8E1A-4B79-A6AE-838731318CE3}"/>
-    <hyperlink ref="J30" r:id="rId29" xr:uid="{B6F2C167-D0F0-4841-8227-95174DC8E4C0}"/>
-    <hyperlink ref="J31" r:id="rId30" xr:uid="{3E1B7946-9D48-4626-A2E0-9271EFA781BB}"/>
-    <hyperlink ref="J32" r:id="rId31" xr:uid="{B3937310-346F-4083-98A8-EE922BE256E2}"/>
-    <hyperlink ref="J33" r:id="rId32" xr:uid="{D2853EDE-EA8D-4159-B08E-E7F293BF381B}"/>
-    <hyperlink ref="J34" r:id="rId33" xr:uid="{41D8F148-B33B-43DA-8C29-0681FAA8CE4D}"/>
-    <hyperlink ref="J35" r:id="rId34" xr:uid="{AEFC594C-3F42-4232-849F-D933F5AD24E6}"/>
-    <hyperlink ref="J36" r:id="rId35" xr:uid="{32BC42A5-5D78-495B-8BE7-82308B1A0B1A}"/>
-    <hyperlink ref="J37" r:id="rId36" xr:uid="{4301C117-A2EF-4FFE-ACDF-9A10EAF47248}"/>
-    <hyperlink ref="J38" r:id="rId37" xr:uid="{60D36F47-AFA9-4676-A54D-F021B6C0B123}"/>
-    <hyperlink ref="J39" r:id="rId38" xr:uid="{A2028B25-7760-42DF-B076-DE06376ECE0F}"/>
-    <hyperlink ref="J40" r:id="rId39" xr:uid="{5AB510FC-7FB1-476D-B99D-90B0F8C284E6}"/>
-    <hyperlink ref="J41" r:id="rId40" xr:uid="{1B066515-BE1C-4EAD-B29B-3F89E8C2096F}"/>
-    <hyperlink ref="J42" r:id="rId41" xr:uid="{167835A6-0B90-4D90-817D-4F7DDEC8FCBA}"/>
+    <hyperlink ref="J2" r:id="rId1" display="https://maps,app,goo,gl/iqZ4GBhxDdnmiKFh9" xr:uid="{CE36CA00-A6BF-4AAB-B6C5-44962FC36003}"/>
+    <hyperlink ref="J3" r:id="rId2" display="https://maps,app,goo,gl/RYeTdPUprhVZbWQj7" xr:uid="{8057D4F4-5BFC-4452-A91C-DC5703FAECB8}"/>
+    <hyperlink ref="J4" r:id="rId3" display="https://maps,app,goo,gl/dE8ZDETqJrKnrMYT7" xr:uid="{F904D503-2E10-4E57-B75B-A8A69DAA99AC}"/>
+    <hyperlink ref="J5" r:id="rId4" display="https://maps,app,goo,gl/4ZpaPxZ7B6SoaFbN7" xr:uid="{EE9CA8E6-0197-49ED-B5B1-C6A5C74478AE}"/>
+    <hyperlink ref="J6" r:id="rId5" display="https://maps,app,goo,gl/o6JYaCCD2E2qbBNu5" xr:uid="{882673DE-C8D0-40A7-AF9C-38A0E598E0FD}"/>
+    <hyperlink ref="J7" r:id="rId6" display="https://maps,app,goo,gl/jccDdukmCYNKPAUo8" xr:uid="{B9D7202B-76BB-4617-985A-E07B6C43860A}"/>
+    <hyperlink ref="J8" r:id="rId7" display="https://maps,app,goo,gl/y2apQpo5v9a8eD8R7" xr:uid="{15A7BAEC-BBF0-4442-B043-5B3F3D6B801F}"/>
+    <hyperlink ref="J9" r:id="rId8" display="https://maps,app,goo,gl/JmsiDm3tz18g7duD8" xr:uid="{798F3B9C-BFE7-4D89-ACD8-C84BEA75BCBD}"/>
+    <hyperlink ref="J10" r:id="rId9" display="https://maps,app,goo,gl/AVSE3ECfkHPPmucS8" xr:uid="{7F9A602E-E203-4C49-AE09-DD17C3E1802E}"/>
+    <hyperlink ref="J11" r:id="rId10" display="https://maps,app,goo,gl/SWHzXXXf3SMQ8tA96" xr:uid="{E36B4D7D-26DA-443D-8A9E-A738223C713B}"/>
+    <hyperlink ref="J12" r:id="rId11" display="https://maps,app,goo,gl/945xB7PkevoCExYc8" xr:uid="{7FEE1438-2B19-427E-898D-DB8271442A22}"/>
+    <hyperlink ref="J13" r:id="rId12" display="https://maps,app,goo,gl/rPTxmt9UDxHS23n19" xr:uid="{F130B874-88BE-4A5E-9A44-EEEA49DFB806}"/>
+    <hyperlink ref="J14" r:id="rId13" display="https://maps,app,goo,gl/L6iTqLFFDM966Tmd6" xr:uid="{E006C1A7-AC6B-4017-887A-DC5E7916F38E}"/>
+    <hyperlink ref="J15" r:id="rId14" display="https://maps,app,goo,gl/fczoo46dnKmpCCLX7" xr:uid="{AD6E7590-08D3-4CA0-827A-4DEE1033B8FA}"/>
+    <hyperlink ref="J16" r:id="rId15" display="https://maps,app,goo,gl/frbqQuNvtPqtGRbZ9" xr:uid="{942FBC13-AB50-4C24-BAD8-F27520219896}"/>
+    <hyperlink ref="J17" r:id="rId16" display="https://maps,app,goo,gl/GyqJjnQwoYZo9MUv6" xr:uid="{47CA89FF-1F50-4A02-BA83-1539A6F73345}"/>
+    <hyperlink ref="J18" r:id="rId17" display="https://maps,app,goo,gl/fK5qaQbLaG5pV3qK7" xr:uid="{ECEBCF49-E889-4534-82DC-2F804160DF23}"/>
+    <hyperlink ref="J19" r:id="rId18" display="https://maps,app,goo,gl/rfQ7La7Wdc5Ghyuw6" xr:uid="{3F2FED4B-5E07-4648-B42E-3E11483F3CE7}"/>
+    <hyperlink ref="J20" r:id="rId19" display="https://maps,app,goo,gl/Um2cFZ7P8u8Y3MLC9" xr:uid="{52B755C7-03DD-4309-902B-B4BEAC1DCDEC}"/>
+    <hyperlink ref="J21" r:id="rId20" display="https://maps,app,goo,gl/8WpRE1ayxfZ9wkC86" xr:uid="{FC487693-D61C-4DCE-8707-E753C696E70E}"/>
+    <hyperlink ref="J22" r:id="rId21" display="https://maps,app,goo,gl/cAwMBmPVwPjQhV8b8" xr:uid="{D6B51B4E-32C6-4D4E-ABDB-90D19F129D97}"/>
+    <hyperlink ref="J23" r:id="rId22" display="https://maps,app,goo,gl/SQeZppWwHGojvCoYA" xr:uid="{DB808F08-B054-496A-8694-3198944C8277}"/>
+    <hyperlink ref="J24" r:id="rId23" display="https://maps,app,goo,gl/MyMuo6xx6rSZSYn6A" xr:uid="{66C24FEC-8BD2-4056-89AC-E255AB928D5A}"/>
+    <hyperlink ref="J25" r:id="rId24" display="https://maps,app,goo,gl/GGv45FujGN5yNHwcA" xr:uid="{223D442C-F685-4A6D-936E-061C8109B6A7}"/>
+    <hyperlink ref="J26" r:id="rId25" display="https://maps,app,goo,gl/xKX6kRSfFGRUAG9A8" xr:uid="{F1A17DFC-9523-4457-B9A2-A8FBD5EE9C9B}"/>
+    <hyperlink ref="J27" r:id="rId26" display="https://maps,app,goo,gl/Tm28gLkjwDSy5e776" xr:uid="{1DF2EE09-82D1-49A8-A6AB-09D17DA070E9}"/>
+    <hyperlink ref="J28" r:id="rId27" display="https://maps,app,goo,gl/8jP7p8idJp7mRe8E8" xr:uid="{D9527C73-A6D8-4D66-949B-4C50774795BC}"/>
+    <hyperlink ref="J29" r:id="rId28" display="https://maps,app,goo,gl/8AzpC7NaaWZVtmYx5" xr:uid="{77993E83-8E1A-4B79-A6AE-838731318CE3}"/>
+    <hyperlink ref="J30" r:id="rId29" display="https://maps,app,goo,gl/Xvaw52o9zDGb7w1X6" xr:uid="{B6F2C167-D0F0-4841-8227-95174DC8E4C0}"/>
+    <hyperlink ref="J31" r:id="rId30" display="https://maps,app,goo,gl/HtN9HV2g3EC2E6Yw6" xr:uid="{3E1B7946-9D48-4626-A2E0-9271EFA781BB}"/>
+    <hyperlink ref="J32" r:id="rId31" display="https://maps,app,goo,gl/RGsFBLKN9Tvhmdrh9" xr:uid="{B3937310-346F-4083-98A8-EE922BE256E2}"/>
+    <hyperlink ref="J33" r:id="rId32" display="https://maps,app,goo,gl/w3uwETVrBeL8kocJ8" xr:uid="{D2853EDE-EA8D-4159-B08E-E7F293BF381B}"/>
+    <hyperlink ref="J34" r:id="rId33" display="https://maps,app,goo,gl/vByGQcCKFUbyUWs8A" xr:uid="{41D8F148-B33B-43DA-8C29-0681FAA8CE4D}"/>
+    <hyperlink ref="J35" r:id="rId34" display="https://maps,app,goo,gl/km35JL3uhPDCb4f26" xr:uid="{AEFC594C-3F42-4232-849F-D933F5AD24E6}"/>
+    <hyperlink ref="J36" r:id="rId35" display="https://maps,app,goo,gl/Me5yN67UAteqpGdY9" xr:uid="{32BC42A5-5D78-495B-8BE7-82308B1A0B1A}"/>
+    <hyperlink ref="J37" r:id="rId36" display="https://maps,app,goo,gl/7ZxoNc54UJ2ZkLf39" xr:uid="{4301C117-A2EF-4FFE-ACDF-9A10EAF47248}"/>
+    <hyperlink ref="J38" r:id="rId37" display="https://maps,app,goo,gl/yYLSC9uJhWDgQUph8" xr:uid="{60D36F47-AFA9-4676-A54D-F021B6C0B123}"/>
+    <hyperlink ref="J39" r:id="rId38" display="https://maps,app,goo,gl/VzBnzzQmzfrSBWo9A" xr:uid="{A2028B25-7760-42DF-B076-DE06376ECE0F}"/>
+    <hyperlink ref="J40" r:id="rId39" display="https://maps,app,goo,gl/bujMvFPKLoa6rspp7" xr:uid="{5AB510FC-7FB1-476D-B99D-90B0F8C284E6}"/>
+    <hyperlink ref="J41" r:id="rId40" display="https://maps,app,goo,gl/2RH5jEc9g64fvsgb7" xr:uid="{1B066515-BE1C-4EAD-B29B-3F89E8C2096F}"/>
+    <hyperlink ref="J42" r:id="rId41" display="https://maps,app,goo,gl/4NFp2jRiWyogCHd3A" xr:uid="{167835A6-0B90-4D90-817D-4F7DDEC8FCBA}"/>
     <hyperlink ref="J43" r:id="rId42" xr:uid="{7A4C07BE-0CC6-4709-B048-2B99515331E3}"/>
     <hyperlink ref="J44" r:id="rId43" xr:uid="{C215FBFE-935F-4C81-84AB-EEF3C4A3C15D}"/>
     <hyperlink ref="J45" r:id="rId44" xr:uid="{860FEF54-7560-4430-BBE1-62AE389CA776}"/>

--- a/data/rumah_makan.xlsx
+++ b/data/rumah_makan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\SEMESTER 6\PRAK. SIGTER\PROJECT AKHIR\STUDENT SURVIVAL MAP\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6229B7D5-F278-405D-ADF2-53F71BF55471}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8E9A5EF-C5C4-4458-890A-C71EDD041B8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{EBF2A29F-0C7E-4417-9F77-D4C323BFD0DA}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="622" uniqueCount="418">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="674" uniqueCount="421">
   <si>
     <t>Id</t>
   </si>
@@ -1288,13 +1288,22 @@
   </si>
   <si>
     <t>Jl. Kaswari No.98. Ngringin. Condongcatur. Kec. Depok. Kabupaten Sleman. Daerah Istimewa Yogyakarta 55283</t>
+  </si>
+  <si>
+    <t>Kategori Harga</t>
+  </si>
+  <si>
+    <t>Murah</t>
+  </si>
+  <si>
+    <t>Menengah</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="12">
+  <fonts count="15">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1364,6 +1373,25 @@
       <color rgb="FF5E5E5E"/>
       <name val="Times New Roman"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -1379,7 +1407,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -1402,12 +1430,57 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFCCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1468,26 +1541,21 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1803,7 +1871,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D2879120-B48A-4F1A-810E-C87B5DAC68ED}">
-  <dimension ref="A1:M52"/>
+  <dimension ref="A1:N999"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="5.77734375" bestFit="1" customWidth="1"/>
@@ -1812,16 +1880,17 @@
     <col min="4" max="4" width="17.21875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="22" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="124.44140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="22.6640625" style="33" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="22.6640625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="21.33203125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="7.21875" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="45.6640625" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="16.44140625" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="14" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="12.21875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="15.6">
+    <row r="1" spans="1:14" ht="31.8" thickBot="1">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1840,7 +1909,7 @@
       <c r="F1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="26" t="s">
+      <c r="G1" s="3" t="s">
         <v>3</v>
       </c>
       <c r="H1" s="3" t="s">
@@ -1861,8 +1930,11 @@
       <c r="M1" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="2" spans="1:13" ht="15.6">
+      <c r="N1" s="28" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" ht="16.2" thickBot="1">
       <c r="A2" s="7" t="s">
         <v>9</v>
       </c>
@@ -1881,7 +1953,7 @@
       <c r="F2" s="7" t="s">
         <v>170</v>
       </c>
-      <c r="G2" s="27" t="s">
+      <c r="G2" s="26" t="s">
         <v>171</v>
       </c>
       <c r="H2" s="9" t="s">
@@ -1902,8 +1974,11 @@
       <c r="M2" s="7" t="s">
         <v>175</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="15.6">
+      <c r="N2" s="29" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" ht="16.2" thickBot="1">
       <c r="A3" s="7" t="s">
         <v>14</v>
       </c>
@@ -1922,7 +1997,7 @@
       <c r="F3" s="7" t="s">
         <v>176</v>
       </c>
-      <c r="G3" s="27" t="s">
+      <c r="G3" s="26" t="s">
         <v>177</v>
       </c>
       <c r="H3" s="9" t="s">
@@ -1943,8 +2018,11 @@
       <c r="M3" s="7" t="s">
         <v>175</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="15.6">
+      <c r="N3" s="29" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" ht="16.2" thickBot="1">
       <c r="A4" s="7" t="s">
         <v>17</v>
       </c>
@@ -1963,7 +2041,7 @@
       <c r="F4" s="7" t="s">
         <v>181</v>
       </c>
-      <c r="G4" s="27" t="s">
+      <c r="G4" s="26" t="s">
         <v>182</v>
       </c>
       <c r="H4" s="9" t="s">
@@ -1984,8 +2062,11 @@
       <c r="M4" s="7" t="s">
         <v>175</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="15.6">
+      <c r="N4" s="29" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" ht="16.2" thickBot="1">
       <c r="A5" s="7" t="s">
         <v>19</v>
       </c>
@@ -2004,7 +2085,7 @@
       <c r="F5" s="7" t="s">
         <v>186</v>
       </c>
-      <c r="G5" s="27" t="s">
+      <c r="G5" s="26" t="s">
         <v>187</v>
       </c>
       <c r="H5" s="9" t="s">
@@ -2025,8 +2106,11 @@
       <c r="M5" s="7" t="s">
         <v>175</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" ht="15.6">
+      <c r="N5" s="29" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" ht="16.2" thickBot="1">
       <c r="A6" s="7" t="s">
         <v>21</v>
       </c>
@@ -2045,7 +2129,7 @@
       <c r="F6" s="7" t="s">
         <v>191</v>
       </c>
-      <c r="G6" s="27" t="s">
+      <c r="G6" s="26" t="s">
         <v>192</v>
       </c>
       <c r="H6" s="9" t="s">
@@ -2066,8 +2150,11 @@
       <c r="M6" s="7" t="s">
         <v>175</v>
       </c>
-    </row>
-    <row r="7" spans="1:13" ht="15.6">
+      <c r="N6" s="29" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" ht="16.2" thickBot="1">
       <c r="A7" s="7" t="s">
         <v>23</v>
       </c>
@@ -2086,7 +2173,7 @@
       <c r="F7" s="7" t="s">
         <v>196</v>
       </c>
-      <c r="G7" s="27" t="s">
+      <c r="G7" s="26" t="s">
         <v>197</v>
       </c>
       <c r="H7" s="9" t="s">
@@ -2107,8 +2194,11 @@
       <c r="M7" s="7" t="s">
         <v>175</v>
       </c>
-    </row>
-    <row r="8" spans="1:13" ht="15.6">
+      <c r="N7" s="29" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" ht="16.2" thickBot="1">
       <c r="A8" s="7" t="s">
         <v>25</v>
       </c>
@@ -2127,7 +2217,7 @@
       <c r="F8" s="7" t="s">
         <v>201</v>
       </c>
-      <c r="G8" s="27" t="s">
+      <c r="G8" s="26" t="s">
         <v>202</v>
       </c>
       <c r="H8" s="9" t="s">
@@ -2148,8 +2238,11 @@
       <c r="M8" s="7" t="s">
         <v>175</v>
       </c>
-    </row>
-    <row r="9" spans="1:13" ht="15.6">
+      <c r="N8" s="29" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" ht="16.2" thickBot="1">
       <c r="A9" s="7" t="s">
         <v>27</v>
       </c>
@@ -2168,7 +2261,7 @@
       <c r="F9" s="7" t="s">
         <v>207</v>
       </c>
-      <c r="G9" s="27" t="s">
+      <c r="G9" s="26" t="s">
         <v>208</v>
       </c>
       <c r="H9" s="9" t="s">
@@ -2189,8 +2282,11 @@
       <c r="M9" s="7" t="s">
         <v>175</v>
       </c>
-    </row>
-    <row r="10" spans="1:13" ht="15.6">
+      <c r="N9" s="29" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" ht="16.2" thickBot="1">
       <c r="A10" s="7" t="s">
         <v>28</v>
       </c>
@@ -2209,7 +2305,7 @@
       <c r="F10" s="7" t="s">
         <v>212</v>
       </c>
-      <c r="G10" s="27" t="s">
+      <c r="G10" s="26" t="s">
         <v>213</v>
       </c>
       <c r="H10" s="9" t="s">
@@ -2230,8 +2326,11 @@
       <c r="M10" s="7" t="s">
         <v>175</v>
       </c>
-    </row>
-    <row r="11" spans="1:13" ht="15.6">
+      <c r="N10" s="29" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" ht="16.2" thickBot="1">
       <c r="A11" s="7" t="s">
         <v>30</v>
       </c>
@@ -2250,7 +2349,7 @@
       <c r="F11" s="7" t="s">
         <v>217</v>
       </c>
-      <c r="G11" s="27" t="s">
+      <c r="G11" s="26" t="s">
         <v>218</v>
       </c>
       <c r="H11" s="9" t="s">
@@ -2271,8 +2370,11 @@
       <c r="M11" s="7" t="s">
         <v>175</v>
       </c>
-    </row>
-    <row r="12" spans="1:13" ht="15.6">
+      <c r="N11" s="29" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" ht="16.2" thickBot="1">
       <c r="A12" s="7" t="s">
         <v>33</v>
       </c>
@@ -2291,7 +2393,7 @@
       <c r="F12" s="7" t="s">
         <v>223</v>
       </c>
-      <c r="G12" s="27" t="s">
+      <c r="G12" s="26" t="s">
         <v>224</v>
       </c>
       <c r="H12" s="9" t="s">
@@ -2312,8 +2414,11 @@
       <c r="M12" s="7" t="s">
         <v>175</v>
       </c>
-    </row>
-    <row r="13" spans="1:13" ht="15.6">
+      <c r="N12" s="29" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" ht="16.2" thickBot="1">
       <c r="A13" s="7" t="s">
         <v>35</v>
       </c>
@@ -2332,7 +2437,7 @@
       <c r="F13" s="7" t="s">
         <v>228</v>
       </c>
-      <c r="G13" s="27" t="s">
+      <c r="G13" s="26" t="s">
         <v>229</v>
       </c>
       <c r="H13" s="9" t="s">
@@ -2353,8 +2458,11 @@
       <c r="M13" s="7" t="s">
         <v>175</v>
       </c>
-    </row>
-    <row r="14" spans="1:13" ht="15.6">
+      <c r="N13" s="29" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" ht="16.2" thickBot="1">
       <c r="A14" s="7" t="s">
         <v>38</v>
       </c>
@@ -2373,7 +2481,7 @@
       <c r="F14" s="7" t="s">
         <v>233</v>
       </c>
-      <c r="G14" s="27" t="s">
+      <c r="G14" s="26" t="s">
         <v>234</v>
       </c>
       <c r="H14" s="9" t="s">
@@ -2394,8 +2502,11 @@
       <c r="M14" s="7" t="s">
         <v>175</v>
       </c>
-    </row>
-    <row r="15" spans="1:13" ht="15.6">
+      <c r="N14" s="29" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" ht="16.2" thickBot="1">
       <c r="A15" s="7" t="s">
         <v>40</v>
       </c>
@@ -2414,7 +2525,7 @@
       <c r="F15" s="7" t="s">
         <v>238</v>
       </c>
-      <c r="G15" s="27" t="s">
+      <c r="G15" s="26" t="s">
         <v>239</v>
       </c>
       <c r="H15" s="9" t="s">
@@ -2435,8 +2546,11 @@
       <c r="M15" s="7" t="s">
         <v>175</v>
       </c>
-    </row>
-    <row r="16" spans="1:13" ht="15.6">
+      <c r="N15" s="29" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" ht="16.2" thickBot="1">
       <c r="A16" s="7" t="s">
         <v>42</v>
       </c>
@@ -2455,7 +2569,7 @@
       <c r="F16" s="7" t="s">
         <v>170</v>
       </c>
-      <c r="G16" s="27" t="s">
+      <c r="G16" s="26" t="s">
         <v>243</v>
       </c>
       <c r="H16" s="9" t="s">
@@ -2476,8 +2590,11 @@
       <c r="M16" s="7" t="s">
         <v>175</v>
       </c>
-    </row>
-    <row r="17" spans="1:13" ht="15.6">
+      <c r="N16" s="29" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" ht="16.2" thickBot="1">
       <c r="A17" s="7" t="s">
         <v>44</v>
       </c>
@@ -2496,7 +2613,7 @@
       <c r="F17" s="7" t="s">
         <v>170</v>
       </c>
-      <c r="G17" s="27" t="s">
+      <c r="G17" s="26" t="s">
         <v>247</v>
       </c>
       <c r="H17" s="9" t="s">
@@ -2517,8 +2634,11 @@
       <c r="M17" s="7" t="s">
         <v>175</v>
       </c>
-    </row>
-    <row r="18" spans="1:13" ht="15.6">
+      <c r="N17" s="29" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" ht="16.2" thickBot="1">
       <c r="A18" s="7" t="s">
         <v>46</v>
       </c>
@@ -2537,7 +2657,7 @@
       <c r="F18" s="7" t="s">
         <v>251</v>
       </c>
-      <c r="G18" s="27" t="s">
+      <c r="G18" s="26" t="s">
         <v>252</v>
       </c>
       <c r="H18" s="9" t="s">
@@ -2558,8 +2678,11 @@
       <c r="M18" s="7" t="s">
         <v>175</v>
       </c>
-    </row>
-    <row r="19" spans="1:13" ht="15.6">
+      <c r="N18" s="29" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" ht="16.2" thickBot="1">
       <c r="A19" s="7" t="s">
         <v>48</v>
       </c>
@@ -2578,7 +2701,7 @@
       <c r="F19" s="7" t="s">
         <v>256</v>
       </c>
-      <c r="G19" s="27" t="s">
+      <c r="G19" s="26" t="s">
         <v>257</v>
       </c>
       <c r="H19" s="9" t="s">
@@ -2599,8 +2722,11 @@
       <c r="M19" s="7" t="s">
         <v>175</v>
       </c>
-    </row>
-    <row r="20" spans="1:13" ht="15.6">
+      <c r="N19" s="29" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" ht="16.2" thickBot="1">
       <c r="A20" s="7" t="s">
         <v>50</v>
       </c>
@@ -2619,7 +2745,7 @@
       <c r="F20" s="7" t="s">
         <v>261</v>
       </c>
-      <c r="G20" s="27" t="s">
+      <c r="G20" s="26" t="s">
         <v>262</v>
       </c>
       <c r="H20" s="9" t="s">
@@ -2640,8 +2766,11 @@
       <c r="M20" s="7" t="s">
         <v>175</v>
       </c>
-    </row>
-    <row r="21" spans="1:13" ht="15.6">
+      <c r="N20" s="29" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" ht="16.2" thickBot="1">
       <c r="A21" s="7" t="s">
         <v>52</v>
       </c>
@@ -2660,7 +2789,7 @@
       <c r="F21" s="7" t="s">
         <v>266</v>
       </c>
-      <c r="G21" s="27" t="s">
+      <c r="G21" s="26" t="s">
         <v>267</v>
       </c>
       <c r="H21" s="9" t="s">
@@ -2681,8 +2810,11 @@
       <c r="M21" s="7" t="s">
         <v>175</v>
       </c>
-    </row>
-    <row r="22" spans="1:13" ht="15.6">
+      <c r="N21" s="29" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" ht="16.2" thickBot="1">
       <c r="A22" s="7" t="s">
         <v>54</v>
       </c>
@@ -2701,7 +2833,7 @@
       <c r="F22" s="7" t="s">
         <v>271</v>
       </c>
-      <c r="G22" s="27" t="s">
+      <c r="G22" s="26" t="s">
         <v>272</v>
       </c>
       <c r="H22" s="9" t="s">
@@ -2722,8 +2854,11 @@
       <c r="M22" s="7" t="s">
         <v>175</v>
       </c>
-    </row>
-    <row r="23" spans="1:13" ht="15.6">
+      <c r="N22" s="29" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" ht="16.2" thickBot="1">
       <c r="A23" s="7" t="s">
         <v>56</v>
       </c>
@@ -2742,7 +2877,7 @@
       <c r="F23" s="7" t="s">
         <v>276</v>
       </c>
-      <c r="G23" s="27" t="s">
+      <c r="G23" s="26" t="s">
         <v>277</v>
       </c>
       <c r="H23" s="9" t="s">
@@ -2763,8 +2898,11 @@
       <c r="M23" s="7" t="s">
         <v>175</v>
       </c>
-    </row>
-    <row r="24" spans="1:13" ht="15.6">
+      <c r="N23" s="29" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" ht="16.2" thickBot="1">
       <c r="A24" s="7" t="s">
         <v>58</v>
       </c>
@@ -2783,7 +2921,7 @@
       <c r="F24" s="7" t="s">
         <v>282</v>
       </c>
-      <c r="G24" s="28">
+      <c r="G24" s="27">
         <v>-7.7638247755953698</v>
       </c>
       <c r="H24" s="13" t="s">
@@ -2804,8 +2942,11 @@
       <c r="M24" s="7" t="s">
         <v>175</v>
       </c>
-    </row>
-    <row r="25" spans="1:13" ht="15.6">
+      <c r="N24" s="29" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" ht="16.2" thickBot="1">
       <c r="A25" s="7" t="s">
         <v>60</v>
       </c>
@@ -2824,7 +2965,7 @@
       <c r="F25" s="7" t="s">
         <v>286</v>
       </c>
-      <c r="G25" s="27" t="s">
+      <c r="G25" s="26" t="s">
         <v>287</v>
       </c>
       <c r="H25" s="9" t="s">
@@ -2845,8 +2986,11 @@
       <c r="M25" s="7" t="s">
         <v>175</v>
       </c>
-    </row>
-    <row r="26" spans="1:13" ht="15.6">
+      <c r="N25" s="29" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14" ht="16.2" thickBot="1">
       <c r="A26" s="7" t="s">
         <v>62</v>
       </c>
@@ -2865,7 +3009,7 @@
       <c r="F26" s="11" t="s">
         <v>292</v>
       </c>
-      <c r="G26" s="29" t="s">
+      <c r="G26" s="15" t="s">
         <v>293</v>
       </c>
       <c r="H26" s="15" t="s">
@@ -2886,8 +3030,11 @@
       <c r="M26" s="7" t="s">
         <v>175</v>
       </c>
-    </row>
-    <row r="27" spans="1:13" ht="15.6">
+      <c r="N26" s="29" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" ht="16.2" thickBot="1">
       <c r="A27" s="7" t="s">
         <v>64</v>
       </c>
@@ -2906,7 +3053,7 @@
       <c r="F27" s="11" t="s">
         <v>298</v>
       </c>
-      <c r="G27" s="29" t="s">
+      <c r="G27" s="15" t="s">
         <v>299</v>
       </c>
       <c r="H27" s="15" t="s">
@@ -2927,8 +3074,11 @@
       <c r="M27" s="7" t="s">
         <v>175</v>
       </c>
-    </row>
-    <row r="28" spans="1:13" ht="15.6">
+      <c r="N27" s="29" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14" ht="16.2" thickBot="1">
       <c r="A28" s="17" t="s">
         <v>66</v>
       </c>
@@ -2947,7 +3097,7 @@
       <c r="F28" s="18" t="s">
         <v>303</v>
       </c>
-      <c r="G28" s="30" t="s">
+      <c r="G28" s="19" t="s">
         <v>304</v>
       </c>
       <c r="H28" s="19" t="s">
@@ -2968,8 +3118,11 @@
       <c r="M28" s="18" t="s">
         <v>175</v>
       </c>
-    </row>
-    <row r="29" spans="1:13" ht="15.6">
+      <c r="N28" s="29" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14" ht="16.2" thickBot="1">
       <c r="A29" s="17" t="s">
         <v>68</v>
       </c>
@@ -2988,7 +3141,7 @@
       <c r="F29" s="18" t="s">
         <v>308</v>
       </c>
-      <c r="G29" s="30" t="s">
+      <c r="G29" s="19" t="s">
         <v>309</v>
       </c>
       <c r="H29" s="19" t="s">
@@ -3009,8 +3162,11 @@
       <c r="M29" s="18" t="s">
         <v>175</v>
       </c>
-    </row>
-    <row r="30" spans="1:13" ht="15.6">
+      <c r="N29" s="29" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14" ht="16.2" thickBot="1">
       <c r="A30" s="17" t="s">
         <v>71</v>
       </c>
@@ -3029,7 +3185,7 @@
       <c r="F30" s="18" t="s">
         <v>314</v>
       </c>
-      <c r="G30" s="30" t="s">
+      <c r="G30" s="19" t="s">
         <v>315</v>
       </c>
       <c r="H30" s="19" t="s">
@@ -3050,8 +3206,11 @@
       <c r="M30" s="18" t="s">
         <v>175</v>
       </c>
-    </row>
-    <row r="31" spans="1:13" ht="15.6">
+      <c r="N30" s="29" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14" ht="16.2" thickBot="1">
       <c r="A31" s="17" t="s">
         <v>73</v>
       </c>
@@ -3070,7 +3229,7 @@
       <c r="F31" s="18" t="s">
         <v>320</v>
       </c>
-      <c r="G31" s="30" t="s">
+      <c r="G31" s="19" t="s">
         <v>321</v>
       </c>
       <c r="H31" s="19" t="s">
@@ -3091,8 +3250,11 @@
       <c r="M31" s="18" t="s">
         <v>175</v>
       </c>
-    </row>
-    <row r="32" spans="1:13" ht="15.6">
+      <c r="N31" s="29" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14" ht="16.2" thickBot="1">
       <c r="A32" s="17" t="s">
         <v>74</v>
       </c>
@@ -3111,7 +3273,7 @@
       <c r="F32" s="18" t="s">
         <v>326</v>
       </c>
-      <c r="G32" s="30" t="s">
+      <c r="G32" s="19" t="s">
         <v>327</v>
       </c>
       <c r="H32" s="19" t="s">
@@ -3132,8 +3294,11 @@
       <c r="M32" s="18" t="s">
         <v>175</v>
       </c>
-    </row>
-    <row r="33" spans="1:13" ht="15.6">
+      <c r="N32" s="29" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14" ht="16.2" thickBot="1">
       <c r="A33" s="17" t="s">
         <v>76</v>
       </c>
@@ -3152,7 +3317,7 @@
       <c r="F33" s="18" t="s">
         <v>332</v>
       </c>
-      <c r="G33" s="30" t="s">
+      <c r="G33" s="19" t="s">
         <v>333</v>
       </c>
       <c r="H33" s="19" t="s">
@@ -3173,8 +3338,11 @@
       <c r="M33" s="18" t="s">
         <v>175</v>
       </c>
-    </row>
-    <row r="34" spans="1:13" ht="15.6">
+      <c r="N33" s="29" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14" ht="16.2" thickBot="1">
       <c r="A34" s="17" t="s">
         <v>78</v>
       </c>
@@ -3193,7 +3361,7 @@
       <c r="F34" s="18" t="s">
         <v>338</v>
       </c>
-      <c r="G34" s="30" t="s">
+      <c r="G34" s="19" t="s">
         <v>339</v>
       </c>
       <c r="H34" s="19" t="s">
@@ -3214,8 +3382,11 @@
       <c r="M34" s="18" t="s">
         <v>175</v>
       </c>
-    </row>
-    <row r="35" spans="1:13" ht="15.6">
+      <c r="N34" s="29" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14" ht="16.2" thickBot="1">
       <c r="A35" s="17" t="s">
         <v>80</v>
       </c>
@@ -3234,7 +3405,7 @@
       <c r="F35" s="18" t="s">
         <v>343</v>
       </c>
-      <c r="G35" s="30" t="s">
+      <c r="G35" s="19" t="s">
         <v>344</v>
       </c>
       <c r="H35" s="19" t="s">
@@ -3255,8 +3426,11 @@
       <c r="M35" s="18" t="s">
         <v>175</v>
       </c>
-    </row>
-    <row r="36" spans="1:13" ht="15.6">
+      <c r="N35" s="29" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="36" spans="1:14" ht="16.2" thickBot="1">
       <c r="A36" s="17" t="s">
         <v>82</v>
       </c>
@@ -3275,7 +3449,7 @@
       <c r="F36" s="18" t="s">
         <v>349</v>
       </c>
-      <c r="G36" s="30" t="s">
+      <c r="G36" s="19" t="s">
         <v>350</v>
       </c>
       <c r="H36" s="19" t="s">
@@ -3296,8 +3470,11 @@
       <c r="M36" s="18" t="s">
         <v>175</v>
       </c>
-    </row>
-    <row r="37" spans="1:13" ht="15.6">
+      <c r="N36" s="29" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14" ht="16.2" thickBot="1">
       <c r="A37" s="17" t="s">
         <v>87</v>
       </c>
@@ -3316,7 +3493,7 @@
       <c r="F37" s="18" t="s">
         <v>355</v>
       </c>
-      <c r="G37" s="30" t="s">
+      <c r="G37" s="19" t="s">
         <v>356</v>
       </c>
       <c r="H37" s="19" t="s">
@@ -3337,8 +3514,11 @@
       <c r="M37" s="18" t="s">
         <v>175</v>
       </c>
-    </row>
-    <row r="38" spans="1:13" ht="15.6">
+      <c r="N37" s="29" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14" ht="16.2" thickBot="1">
       <c r="A38" s="17" t="s">
         <v>89</v>
       </c>
@@ -3357,7 +3537,7 @@
       <c r="F38" s="18" t="s">
         <v>360</v>
       </c>
-      <c r="G38" s="30" t="s">
+      <c r="G38" s="19" t="s">
         <v>361</v>
       </c>
       <c r="H38" s="19" t="s">
@@ -3378,8 +3558,11 @@
       <c r="M38" s="18" t="s">
         <v>175</v>
       </c>
-    </row>
-    <row r="39" spans="1:13" ht="15.6">
+      <c r="N38" s="29" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="39" spans="1:14" ht="16.2" thickBot="1">
       <c r="A39" s="17" t="s">
         <v>92</v>
       </c>
@@ -3398,7 +3581,7 @@
       <c r="F39" s="18" t="s">
         <v>366</v>
       </c>
-      <c r="G39" s="30" t="s">
+      <c r="G39" s="19" t="s">
         <v>367</v>
       </c>
       <c r="H39" s="19" t="s">
@@ -3419,8 +3602,11 @@
       <c r="M39" s="18" t="s">
         <v>175</v>
       </c>
-    </row>
-    <row r="40" spans="1:13" ht="15.6">
+      <c r="N39" s="29" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="40" spans="1:14" ht="16.2" thickBot="1">
       <c r="A40" s="17" t="s">
         <v>94</v>
       </c>
@@ -3439,7 +3625,7 @@
       <c r="F40" s="18" t="s">
         <v>372</v>
       </c>
-      <c r="G40" s="30" t="s">
+      <c r="G40" s="19" t="s">
         <v>373</v>
       </c>
       <c r="H40" s="19" t="s">
@@ -3460,8 +3646,11 @@
       <c r="M40" s="18" t="s">
         <v>175</v>
       </c>
-    </row>
-    <row r="41" spans="1:13" ht="15.6">
+      <c r="N40" s="29" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="41" spans="1:14" ht="16.2" thickBot="1">
       <c r="A41" s="17" t="s">
         <v>97</v>
       </c>
@@ -3480,7 +3669,7 @@
       <c r="F41" s="18" t="s">
         <v>379</v>
       </c>
-      <c r="G41" s="30" t="s">
+      <c r="G41" s="19" t="s">
         <v>380</v>
       </c>
       <c r="H41" s="19" t="s">
@@ -3501,8 +3690,11 @@
       <c r="M41" s="18" t="s">
         <v>175</v>
       </c>
-    </row>
-    <row r="42" spans="1:13" ht="15.6">
+      <c r="N41" s="29" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="42" spans="1:14" ht="16.2" thickBot="1">
       <c r="A42" s="17" t="s">
         <v>99</v>
       </c>
@@ -3521,7 +3713,7 @@
       <c r="F42" s="18" t="s">
         <v>385</v>
       </c>
-      <c r="G42" s="30" t="s">
+      <c r="G42" s="19" t="s">
         <v>386</v>
       </c>
       <c r="H42" s="19" t="s">
@@ -3542,8 +3734,11 @@
       <c r="M42" s="18" t="s">
         <v>175</v>
       </c>
-    </row>
-    <row r="43" spans="1:13" ht="15.6">
+      <c r="N42" s="29" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="43" spans="1:14" ht="16.2" thickBot="1">
       <c r="A43" s="17" t="s">
         <v>101</v>
       </c>
@@ -3562,7 +3757,7 @@
       <c r="F43" s="18" t="s">
         <v>391</v>
       </c>
-      <c r="G43" s="31">
+      <c r="G43" s="18">
         <v>-7.74358755941239</v>
       </c>
       <c r="H43" s="19" t="s">
@@ -3583,8 +3778,11 @@
       <c r="M43" s="1" t="s">
         <v>105</v>
       </c>
-    </row>
-    <row r="44" spans="1:13" ht="15.6">
+      <c r="N43" s="29" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="44" spans="1:14" ht="16.2" thickBot="1">
       <c r="A44" s="17" t="s">
         <v>106</v>
       </c>
@@ -3603,7 +3801,7 @@
       <c r="F44" s="18" t="s">
         <v>395</v>
       </c>
-      <c r="G44" s="30" t="s">
+      <c r="G44" s="19" t="s">
         <v>396</v>
       </c>
       <c r="H44" s="19" t="s">
@@ -3624,8 +3822,11 @@
       <c r="M44" s="1" t="s">
         <v>105</v>
       </c>
-    </row>
-    <row r="45" spans="1:13" ht="15.6">
+      <c r="N44" s="29" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="45" spans="1:14" ht="16.2" thickBot="1">
       <c r="A45" s="17" t="s">
         <v>110</v>
       </c>
@@ -3644,7 +3845,7 @@
       <c r="F45" s="18" t="s">
         <v>400</v>
       </c>
-      <c r="G45" s="30" t="s">
+      <c r="G45" s="19" t="s">
         <v>401</v>
       </c>
       <c r="H45" s="19" t="s">
@@ -3665,8 +3866,11 @@
       <c r="M45" s="1" t="s">
         <v>105</v>
       </c>
-    </row>
-    <row r="46" spans="1:13" ht="15.6">
+      <c r="N45" s="29" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="46" spans="1:14" ht="16.2" thickBot="1">
       <c r="A46" s="17" t="s">
         <v>113</v>
       </c>
@@ -3685,7 +3889,7 @@
       <c r="F46" s="18" t="s">
         <v>405</v>
       </c>
-      <c r="G46" s="30" t="s">
+      <c r="G46" s="19" t="s">
         <v>406</v>
       </c>
       <c r="H46" s="19" t="s">
@@ -3706,8 +3910,11 @@
       <c r="M46" s="18" t="s">
         <v>175</v>
       </c>
-    </row>
-    <row r="47" spans="1:13" ht="15.6">
+      <c r="N46" s="29" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="47" spans="1:14" ht="16.2" thickBot="1">
       <c r="A47" s="17" t="s">
         <v>117</v>
       </c>
@@ -3726,7 +3933,7 @@
       <c r="F47" s="18" t="s">
         <v>410</v>
       </c>
-      <c r="G47" s="30">
+      <c r="G47" s="19">
         <v>-7.7797246321450402</v>
       </c>
       <c r="H47" s="19" t="s">
@@ -3747,8 +3954,11 @@
       <c r="M47" s="18" t="s">
         <v>175</v>
       </c>
-    </row>
-    <row r="48" spans="1:13" ht="15.6">
+      <c r="N47" s="29" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="48" spans="1:14" ht="16.2" thickBot="1">
       <c r="A48" s="17" t="s">
         <v>121</v>
       </c>
@@ -3767,7 +3977,7 @@
       <c r="F48" s="8" t="s">
         <v>412</v>
       </c>
-      <c r="G48" s="32" t="s">
+      <c r="G48" s="24" t="s">
         <v>123</v>
       </c>
       <c r="H48" s="24" t="s">
@@ -3788,8 +3998,11 @@
       <c r="M48" s="8" t="s">
         <v>175</v>
       </c>
-    </row>
-    <row r="49" spans="1:13" ht="15.6">
+      <c r="N48" s="29" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="49" spans="1:14" ht="16.2" thickBot="1">
       <c r="A49" s="17" t="s">
         <v>127</v>
       </c>
@@ -3808,7 +4021,7 @@
       <c r="F49" s="8" t="s">
         <v>414</v>
       </c>
-      <c r="G49" s="32" t="s">
+      <c r="G49" s="24" t="s">
         <v>130</v>
       </c>
       <c r="H49" s="24" t="s">
@@ -3829,8 +4042,11 @@
       <c r="M49" s="8" t="s">
         <v>175</v>
       </c>
-    </row>
-    <row r="50" spans="1:13" ht="15.6">
+      <c r="N49" s="29" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="50" spans="1:14" ht="16.2" thickBot="1">
       <c r="A50" s="17" t="s">
         <v>134</v>
       </c>
@@ -3849,7 +4065,7 @@
       <c r="F50" s="8" t="s">
         <v>415</v>
       </c>
-      <c r="G50" s="32" t="s">
+      <c r="G50" s="24" t="s">
         <v>137</v>
       </c>
       <c r="H50" s="24" t="s">
@@ -3870,8 +4086,11 @@
       <c r="M50" s="8" t="s">
         <v>175</v>
       </c>
-    </row>
-    <row r="51" spans="1:13" ht="15.6">
+      <c r="N50" s="29" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="51" spans="1:14" ht="16.2" thickBot="1">
       <c r="A51" s="17" t="s">
         <v>141</v>
       </c>
@@ -3890,7 +4109,7 @@
       <c r="F51" s="8" t="s">
         <v>416</v>
       </c>
-      <c r="G51" s="32" t="s">
+      <c r="G51" s="24" t="s">
         <v>144</v>
       </c>
       <c r="H51" s="24" t="s">
@@ -3911,8 +4130,11 @@
       <c r="M51" s="8" t="s">
         <v>175</v>
       </c>
-    </row>
-    <row r="52" spans="1:13" ht="15.6">
+      <c r="N51" s="29" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="52" spans="1:14" ht="16.2" thickBot="1">
       <c r="A52" s="17" t="s">
         <v>148</v>
       </c>
@@ -3931,7 +4153,7 @@
       <c r="F52" s="8" t="s">
         <v>417</v>
       </c>
-      <c r="G52" s="32" t="s">
+      <c r="G52" s="24" t="s">
         <v>151</v>
       </c>
       <c r="H52" s="24" t="s">
@@ -3952,6 +4174,2850 @@
       <c r="M52" s="8" t="s">
         <v>175</v>
       </c>
+      <c r="N52" s="29" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="53" spans="1:14" ht="15" thickBot="1">
+      <c r="N53" s="30"/>
+    </row>
+    <row r="54" spans="1:14" ht="15" thickBot="1">
+      <c r="N54" s="30"/>
+    </row>
+    <row r="55" spans="1:14" ht="15" thickBot="1">
+      <c r="N55" s="30"/>
+    </row>
+    <row r="56" spans="1:14" ht="15" thickBot="1">
+      <c r="N56" s="30"/>
+    </row>
+    <row r="57" spans="1:14" ht="15" thickBot="1">
+      <c r="N57" s="30"/>
+    </row>
+    <row r="58" spans="1:14" ht="15" thickBot="1">
+      <c r="N58" s="30"/>
+    </row>
+    <row r="59" spans="1:14" ht="15" thickBot="1">
+      <c r="N59" s="30"/>
+    </row>
+    <row r="60" spans="1:14" ht="15" thickBot="1">
+      <c r="N60" s="30"/>
+    </row>
+    <row r="61" spans="1:14" ht="15" thickBot="1">
+      <c r="N61" s="30"/>
+    </row>
+    <row r="62" spans="1:14" ht="15" thickBot="1">
+      <c r="N62" s="30"/>
+    </row>
+    <row r="63" spans="1:14" ht="15" thickBot="1">
+      <c r="N63" s="30"/>
+    </row>
+    <row r="64" spans="1:14" ht="15" thickBot="1">
+      <c r="N64" s="30"/>
+    </row>
+    <row r="65" spans="14:14" ht="15" thickBot="1">
+      <c r="N65" s="30"/>
+    </row>
+    <row r="66" spans="14:14" ht="15" thickBot="1">
+      <c r="N66" s="30"/>
+    </row>
+    <row r="67" spans="14:14" ht="15" thickBot="1">
+      <c r="N67" s="30"/>
+    </row>
+    <row r="68" spans="14:14" ht="15" thickBot="1">
+      <c r="N68" s="30"/>
+    </row>
+    <row r="69" spans="14:14" ht="15" thickBot="1">
+      <c r="N69" s="30"/>
+    </row>
+    <row r="70" spans="14:14" ht="15" thickBot="1">
+      <c r="N70" s="30"/>
+    </row>
+    <row r="71" spans="14:14" ht="15" thickBot="1">
+      <c r="N71" s="30"/>
+    </row>
+    <row r="72" spans="14:14" ht="15" thickBot="1">
+      <c r="N72" s="30"/>
+    </row>
+    <row r="73" spans="14:14" ht="15" thickBot="1">
+      <c r="N73" s="30"/>
+    </row>
+    <row r="74" spans="14:14" ht="15" thickBot="1">
+      <c r="N74" s="30"/>
+    </row>
+    <row r="75" spans="14:14" ht="15" thickBot="1">
+      <c r="N75" s="30"/>
+    </row>
+    <row r="76" spans="14:14" ht="15" thickBot="1">
+      <c r="N76" s="30"/>
+    </row>
+    <row r="77" spans="14:14" ht="15" thickBot="1">
+      <c r="N77" s="30"/>
+    </row>
+    <row r="78" spans="14:14" ht="15" thickBot="1">
+      <c r="N78" s="30"/>
+    </row>
+    <row r="79" spans="14:14" ht="15" thickBot="1">
+      <c r="N79" s="30"/>
+    </row>
+    <row r="80" spans="14:14" ht="15" thickBot="1">
+      <c r="N80" s="30"/>
+    </row>
+    <row r="81" spans="14:14" ht="15" thickBot="1">
+      <c r="N81" s="30"/>
+    </row>
+    <row r="82" spans="14:14" ht="15" thickBot="1">
+      <c r="N82" s="30"/>
+    </row>
+    <row r="83" spans="14:14" ht="15" thickBot="1">
+      <c r="N83" s="30"/>
+    </row>
+    <row r="84" spans="14:14" ht="15" thickBot="1">
+      <c r="N84" s="30"/>
+    </row>
+    <row r="85" spans="14:14" ht="15" thickBot="1">
+      <c r="N85" s="30"/>
+    </row>
+    <row r="86" spans="14:14" ht="15" thickBot="1">
+      <c r="N86" s="30"/>
+    </row>
+    <row r="87" spans="14:14" ht="15" thickBot="1">
+      <c r="N87" s="30"/>
+    </row>
+    <row r="88" spans="14:14" ht="15" thickBot="1">
+      <c r="N88" s="30"/>
+    </row>
+    <row r="89" spans="14:14" ht="15" thickBot="1">
+      <c r="N89" s="30"/>
+    </row>
+    <row r="90" spans="14:14" ht="15" thickBot="1">
+      <c r="N90" s="30"/>
+    </row>
+    <row r="91" spans="14:14" ht="15" thickBot="1">
+      <c r="N91" s="30"/>
+    </row>
+    <row r="92" spans="14:14" ht="15" thickBot="1">
+      <c r="N92" s="30"/>
+    </row>
+    <row r="93" spans="14:14" ht="15" thickBot="1">
+      <c r="N93" s="30"/>
+    </row>
+    <row r="94" spans="14:14" ht="15" thickBot="1">
+      <c r="N94" s="30"/>
+    </row>
+    <row r="95" spans="14:14" ht="15" thickBot="1">
+      <c r="N95" s="30"/>
+    </row>
+    <row r="96" spans="14:14" ht="15" thickBot="1">
+      <c r="N96" s="30"/>
+    </row>
+    <row r="97" spans="14:14" ht="15" thickBot="1">
+      <c r="N97" s="30"/>
+    </row>
+    <row r="98" spans="14:14" ht="15" thickBot="1">
+      <c r="N98" s="30"/>
+    </row>
+    <row r="99" spans="14:14" ht="15" thickBot="1">
+      <c r="N99" s="30"/>
+    </row>
+    <row r="100" spans="14:14" ht="15" thickBot="1">
+      <c r="N100" s="30"/>
+    </row>
+    <row r="101" spans="14:14" ht="15" thickBot="1">
+      <c r="N101" s="30"/>
+    </row>
+    <row r="102" spans="14:14" ht="15" thickBot="1">
+      <c r="N102" s="30"/>
+    </row>
+    <row r="103" spans="14:14" ht="15" thickBot="1">
+      <c r="N103" s="30"/>
+    </row>
+    <row r="104" spans="14:14" ht="15" thickBot="1">
+      <c r="N104" s="30"/>
+    </row>
+    <row r="105" spans="14:14" ht="15" thickBot="1">
+      <c r="N105" s="30"/>
+    </row>
+    <row r="106" spans="14:14" ht="15" thickBot="1">
+      <c r="N106" s="30"/>
+    </row>
+    <row r="107" spans="14:14" ht="15" thickBot="1">
+      <c r="N107" s="30"/>
+    </row>
+    <row r="108" spans="14:14" ht="15" thickBot="1">
+      <c r="N108" s="30"/>
+    </row>
+    <row r="109" spans="14:14" ht="15" thickBot="1">
+      <c r="N109" s="30"/>
+    </row>
+    <row r="110" spans="14:14" ht="15" thickBot="1">
+      <c r="N110" s="30"/>
+    </row>
+    <row r="111" spans="14:14" ht="15" thickBot="1">
+      <c r="N111" s="30"/>
+    </row>
+    <row r="112" spans="14:14" ht="15" thickBot="1">
+      <c r="N112" s="30"/>
+    </row>
+    <row r="113" spans="14:14" ht="15" thickBot="1">
+      <c r="N113" s="30"/>
+    </row>
+    <row r="114" spans="14:14" ht="15" thickBot="1">
+      <c r="N114" s="30"/>
+    </row>
+    <row r="115" spans="14:14" ht="15" thickBot="1">
+      <c r="N115" s="30"/>
+    </row>
+    <row r="116" spans="14:14" ht="15" thickBot="1">
+      <c r="N116" s="30"/>
+    </row>
+    <row r="117" spans="14:14" ht="15" thickBot="1">
+      <c r="N117" s="30"/>
+    </row>
+    <row r="118" spans="14:14" ht="15" thickBot="1">
+      <c r="N118" s="30"/>
+    </row>
+    <row r="119" spans="14:14" ht="15" thickBot="1">
+      <c r="N119" s="30"/>
+    </row>
+    <row r="120" spans="14:14" ht="15" thickBot="1">
+      <c r="N120" s="30"/>
+    </row>
+    <row r="121" spans="14:14" ht="15" thickBot="1">
+      <c r="N121" s="30"/>
+    </row>
+    <row r="122" spans="14:14" ht="15" thickBot="1">
+      <c r="N122" s="30"/>
+    </row>
+    <row r="123" spans="14:14" ht="15" thickBot="1">
+      <c r="N123" s="30"/>
+    </row>
+    <row r="124" spans="14:14" ht="15" thickBot="1">
+      <c r="N124" s="30"/>
+    </row>
+    <row r="125" spans="14:14" ht="15" thickBot="1">
+      <c r="N125" s="30"/>
+    </row>
+    <row r="126" spans="14:14" ht="15" thickBot="1">
+      <c r="N126" s="30"/>
+    </row>
+    <row r="127" spans="14:14" ht="15" thickBot="1">
+      <c r="N127" s="30"/>
+    </row>
+    <row r="128" spans="14:14" ht="15" thickBot="1">
+      <c r="N128" s="30"/>
+    </row>
+    <row r="129" spans="14:14" ht="15" thickBot="1">
+      <c r="N129" s="30"/>
+    </row>
+    <row r="130" spans="14:14" ht="15" thickBot="1">
+      <c r="N130" s="30"/>
+    </row>
+    <row r="131" spans="14:14" ht="15" thickBot="1">
+      <c r="N131" s="30"/>
+    </row>
+    <row r="132" spans="14:14" ht="15" thickBot="1">
+      <c r="N132" s="30"/>
+    </row>
+    <row r="133" spans="14:14" ht="15" thickBot="1">
+      <c r="N133" s="30"/>
+    </row>
+    <row r="134" spans="14:14" ht="15" thickBot="1">
+      <c r="N134" s="30"/>
+    </row>
+    <row r="135" spans="14:14" ht="15" thickBot="1">
+      <c r="N135" s="30"/>
+    </row>
+    <row r="136" spans="14:14" ht="15" thickBot="1">
+      <c r="N136" s="30"/>
+    </row>
+    <row r="137" spans="14:14" ht="15" thickBot="1">
+      <c r="N137" s="30"/>
+    </row>
+    <row r="138" spans="14:14" ht="15" thickBot="1">
+      <c r="N138" s="30"/>
+    </row>
+    <row r="139" spans="14:14" ht="15" thickBot="1">
+      <c r="N139" s="30"/>
+    </row>
+    <row r="140" spans="14:14" ht="15" thickBot="1">
+      <c r="N140" s="30"/>
+    </row>
+    <row r="141" spans="14:14" ht="15" thickBot="1">
+      <c r="N141" s="30"/>
+    </row>
+    <row r="142" spans="14:14" ht="15" thickBot="1">
+      <c r="N142" s="30"/>
+    </row>
+    <row r="143" spans="14:14" ht="15" thickBot="1">
+      <c r="N143" s="30"/>
+    </row>
+    <row r="144" spans="14:14" ht="15" thickBot="1">
+      <c r="N144" s="30"/>
+    </row>
+    <row r="145" spans="14:14" ht="15" thickBot="1">
+      <c r="N145" s="30"/>
+    </row>
+    <row r="146" spans="14:14" ht="15" thickBot="1">
+      <c r="N146" s="30"/>
+    </row>
+    <row r="147" spans="14:14" ht="15" thickBot="1">
+      <c r="N147" s="30"/>
+    </row>
+    <row r="148" spans="14:14" ht="15" thickBot="1">
+      <c r="N148" s="30"/>
+    </row>
+    <row r="149" spans="14:14" ht="15" thickBot="1">
+      <c r="N149" s="30"/>
+    </row>
+    <row r="150" spans="14:14" ht="15" thickBot="1">
+      <c r="N150" s="30"/>
+    </row>
+    <row r="151" spans="14:14" ht="15" thickBot="1">
+      <c r="N151" s="30"/>
+    </row>
+    <row r="152" spans="14:14" ht="15" thickBot="1">
+      <c r="N152" s="30"/>
+    </row>
+    <row r="153" spans="14:14" ht="15" thickBot="1">
+      <c r="N153" s="30"/>
+    </row>
+    <row r="154" spans="14:14" ht="15" thickBot="1">
+      <c r="N154" s="30"/>
+    </row>
+    <row r="155" spans="14:14" ht="15" thickBot="1">
+      <c r="N155" s="30"/>
+    </row>
+    <row r="156" spans="14:14" ht="15" thickBot="1">
+      <c r="N156" s="30"/>
+    </row>
+    <row r="157" spans="14:14" ht="15" thickBot="1">
+      <c r="N157" s="30"/>
+    </row>
+    <row r="158" spans="14:14" ht="15" thickBot="1">
+      <c r="N158" s="30"/>
+    </row>
+    <row r="159" spans="14:14" ht="15" thickBot="1">
+      <c r="N159" s="30"/>
+    </row>
+    <row r="160" spans="14:14" ht="15" thickBot="1">
+      <c r="N160" s="30"/>
+    </row>
+    <row r="161" spans="14:14" ht="15" thickBot="1">
+      <c r="N161" s="30"/>
+    </row>
+    <row r="162" spans="14:14" ht="15" thickBot="1">
+      <c r="N162" s="30"/>
+    </row>
+    <row r="163" spans="14:14" ht="15" thickBot="1">
+      <c r="N163" s="30"/>
+    </row>
+    <row r="164" spans="14:14" ht="15" thickBot="1">
+      <c r="N164" s="30"/>
+    </row>
+    <row r="165" spans="14:14" ht="15" thickBot="1">
+      <c r="N165" s="30"/>
+    </row>
+    <row r="166" spans="14:14" ht="15" thickBot="1">
+      <c r="N166" s="30"/>
+    </row>
+    <row r="167" spans="14:14" ht="15" thickBot="1">
+      <c r="N167" s="30"/>
+    </row>
+    <row r="168" spans="14:14" ht="15" thickBot="1">
+      <c r="N168" s="30"/>
+    </row>
+    <row r="169" spans="14:14" ht="15" thickBot="1">
+      <c r="N169" s="30"/>
+    </row>
+    <row r="170" spans="14:14" ht="15" thickBot="1">
+      <c r="N170" s="30"/>
+    </row>
+    <row r="171" spans="14:14" ht="15" thickBot="1">
+      <c r="N171" s="30"/>
+    </row>
+    <row r="172" spans="14:14" ht="15" thickBot="1">
+      <c r="N172" s="30"/>
+    </row>
+    <row r="173" spans="14:14" ht="15" thickBot="1">
+      <c r="N173" s="30"/>
+    </row>
+    <row r="174" spans="14:14" ht="15" thickBot="1">
+      <c r="N174" s="30"/>
+    </row>
+    <row r="175" spans="14:14" ht="15" thickBot="1">
+      <c r="N175" s="30"/>
+    </row>
+    <row r="176" spans="14:14" ht="15" thickBot="1">
+      <c r="N176" s="30"/>
+    </row>
+    <row r="177" spans="14:14" ht="15" thickBot="1">
+      <c r="N177" s="30"/>
+    </row>
+    <row r="178" spans="14:14" ht="15" thickBot="1">
+      <c r="N178" s="30"/>
+    </row>
+    <row r="179" spans="14:14" ht="15" thickBot="1">
+      <c r="N179" s="30"/>
+    </row>
+    <row r="180" spans="14:14" ht="15" thickBot="1">
+      <c r="N180" s="30"/>
+    </row>
+    <row r="181" spans="14:14" ht="15" thickBot="1">
+      <c r="N181" s="30"/>
+    </row>
+    <row r="182" spans="14:14" ht="15" thickBot="1">
+      <c r="N182" s="30"/>
+    </row>
+    <row r="183" spans="14:14" ht="15" thickBot="1">
+      <c r="N183" s="30"/>
+    </row>
+    <row r="184" spans="14:14" ht="15" thickBot="1">
+      <c r="N184" s="30"/>
+    </row>
+    <row r="185" spans="14:14" ht="15" thickBot="1">
+      <c r="N185" s="30"/>
+    </row>
+    <row r="186" spans="14:14" ht="15" thickBot="1">
+      <c r="N186" s="30"/>
+    </row>
+    <row r="187" spans="14:14" ht="15" thickBot="1">
+      <c r="N187" s="30"/>
+    </row>
+    <row r="188" spans="14:14" ht="15" thickBot="1">
+      <c r="N188" s="30"/>
+    </row>
+    <row r="189" spans="14:14" ht="15" thickBot="1">
+      <c r="N189" s="30"/>
+    </row>
+    <row r="190" spans="14:14" ht="15" thickBot="1">
+      <c r="N190" s="30"/>
+    </row>
+    <row r="191" spans="14:14" ht="15" thickBot="1">
+      <c r="N191" s="30"/>
+    </row>
+    <row r="192" spans="14:14" ht="15" thickBot="1">
+      <c r="N192" s="30"/>
+    </row>
+    <row r="193" spans="14:14" ht="15" thickBot="1">
+      <c r="N193" s="30"/>
+    </row>
+    <row r="194" spans="14:14" ht="15" thickBot="1">
+      <c r="N194" s="30"/>
+    </row>
+    <row r="195" spans="14:14" ht="15" thickBot="1">
+      <c r="N195" s="30"/>
+    </row>
+    <row r="196" spans="14:14" ht="15" thickBot="1">
+      <c r="N196" s="30"/>
+    </row>
+    <row r="197" spans="14:14" ht="15" thickBot="1">
+      <c r="N197" s="30"/>
+    </row>
+    <row r="198" spans="14:14" ht="15" thickBot="1">
+      <c r="N198" s="30"/>
+    </row>
+    <row r="199" spans="14:14" ht="15" thickBot="1">
+      <c r="N199" s="30"/>
+    </row>
+    <row r="200" spans="14:14" ht="15" thickBot="1">
+      <c r="N200" s="30"/>
+    </row>
+    <row r="201" spans="14:14" ht="15" thickBot="1">
+      <c r="N201" s="30"/>
+    </row>
+    <row r="202" spans="14:14" ht="15" thickBot="1">
+      <c r="N202" s="30"/>
+    </row>
+    <row r="203" spans="14:14" ht="15" thickBot="1">
+      <c r="N203" s="30"/>
+    </row>
+    <row r="204" spans="14:14" ht="15" thickBot="1">
+      <c r="N204" s="30"/>
+    </row>
+    <row r="205" spans="14:14" ht="15" thickBot="1">
+      <c r="N205" s="30"/>
+    </row>
+    <row r="206" spans="14:14" ht="15" thickBot="1">
+      <c r="N206" s="30"/>
+    </row>
+    <row r="207" spans="14:14" ht="15" thickBot="1">
+      <c r="N207" s="30"/>
+    </row>
+    <row r="208" spans="14:14" ht="15" thickBot="1">
+      <c r="N208" s="30"/>
+    </row>
+    <row r="209" spans="14:14" ht="15" thickBot="1">
+      <c r="N209" s="30"/>
+    </row>
+    <row r="210" spans="14:14" ht="15" thickBot="1">
+      <c r="N210" s="30"/>
+    </row>
+    <row r="211" spans="14:14" ht="15" thickBot="1">
+      <c r="N211" s="30"/>
+    </row>
+    <row r="212" spans="14:14" ht="15" thickBot="1">
+      <c r="N212" s="30"/>
+    </row>
+    <row r="213" spans="14:14" ht="15" thickBot="1">
+      <c r="N213" s="30"/>
+    </row>
+    <row r="214" spans="14:14" ht="15" thickBot="1">
+      <c r="N214" s="30"/>
+    </row>
+    <row r="215" spans="14:14" ht="15" thickBot="1">
+      <c r="N215" s="30"/>
+    </row>
+    <row r="216" spans="14:14" ht="15" thickBot="1">
+      <c r="N216" s="30"/>
+    </row>
+    <row r="217" spans="14:14" ht="15" thickBot="1">
+      <c r="N217" s="30"/>
+    </row>
+    <row r="218" spans="14:14" ht="15" thickBot="1">
+      <c r="N218" s="30"/>
+    </row>
+    <row r="219" spans="14:14" ht="15" thickBot="1">
+      <c r="N219" s="30"/>
+    </row>
+    <row r="220" spans="14:14" ht="15" thickBot="1">
+      <c r="N220" s="30"/>
+    </row>
+    <row r="221" spans="14:14" ht="15" thickBot="1">
+      <c r="N221" s="30"/>
+    </row>
+    <row r="222" spans="14:14" ht="15" thickBot="1">
+      <c r="N222" s="30"/>
+    </row>
+    <row r="223" spans="14:14" ht="15" thickBot="1">
+      <c r="N223" s="30"/>
+    </row>
+    <row r="224" spans="14:14" ht="15" thickBot="1">
+      <c r="N224" s="30"/>
+    </row>
+    <row r="225" spans="14:14" ht="15" thickBot="1">
+      <c r="N225" s="30"/>
+    </row>
+    <row r="226" spans="14:14" ht="15" thickBot="1">
+      <c r="N226" s="30"/>
+    </row>
+    <row r="227" spans="14:14" ht="15" thickBot="1">
+      <c r="N227" s="30"/>
+    </row>
+    <row r="228" spans="14:14" ht="15" thickBot="1">
+      <c r="N228" s="30"/>
+    </row>
+    <row r="229" spans="14:14" ht="15" thickBot="1">
+      <c r="N229" s="30"/>
+    </row>
+    <row r="230" spans="14:14" ht="15" thickBot="1">
+      <c r="N230" s="30"/>
+    </row>
+    <row r="231" spans="14:14" ht="15" thickBot="1">
+      <c r="N231" s="30"/>
+    </row>
+    <row r="232" spans="14:14" ht="15" thickBot="1">
+      <c r="N232" s="30"/>
+    </row>
+    <row r="233" spans="14:14" ht="15" thickBot="1">
+      <c r="N233" s="30"/>
+    </row>
+    <row r="234" spans="14:14" ht="15" thickBot="1">
+      <c r="N234" s="30"/>
+    </row>
+    <row r="235" spans="14:14" ht="15" thickBot="1">
+      <c r="N235" s="30"/>
+    </row>
+    <row r="236" spans="14:14" ht="15" thickBot="1">
+      <c r="N236" s="30"/>
+    </row>
+    <row r="237" spans="14:14" ht="15" thickBot="1">
+      <c r="N237" s="30"/>
+    </row>
+    <row r="238" spans="14:14" ht="15" thickBot="1">
+      <c r="N238" s="30"/>
+    </row>
+    <row r="239" spans="14:14" ht="15" thickBot="1">
+      <c r="N239" s="30"/>
+    </row>
+    <row r="240" spans="14:14" ht="15" thickBot="1">
+      <c r="N240" s="30"/>
+    </row>
+    <row r="241" spans="14:14" ht="15" thickBot="1">
+      <c r="N241" s="30"/>
+    </row>
+    <row r="242" spans="14:14" ht="15" thickBot="1">
+      <c r="N242" s="30"/>
+    </row>
+    <row r="243" spans="14:14" ht="15" thickBot="1">
+      <c r="N243" s="30"/>
+    </row>
+    <row r="244" spans="14:14" ht="15" thickBot="1">
+      <c r="N244" s="30"/>
+    </row>
+    <row r="245" spans="14:14" ht="15" thickBot="1">
+      <c r="N245" s="30"/>
+    </row>
+    <row r="246" spans="14:14" ht="15" thickBot="1">
+      <c r="N246" s="30"/>
+    </row>
+    <row r="247" spans="14:14" ht="15" thickBot="1">
+      <c r="N247" s="30"/>
+    </row>
+    <row r="248" spans="14:14" ht="15" thickBot="1">
+      <c r="N248" s="30"/>
+    </row>
+    <row r="249" spans="14:14" ht="15" thickBot="1">
+      <c r="N249" s="30"/>
+    </row>
+    <row r="250" spans="14:14" ht="15" thickBot="1">
+      <c r="N250" s="30"/>
+    </row>
+    <row r="251" spans="14:14" ht="15" thickBot="1">
+      <c r="N251" s="30"/>
+    </row>
+    <row r="252" spans="14:14" ht="15" thickBot="1">
+      <c r="N252" s="30"/>
+    </row>
+    <row r="253" spans="14:14" ht="15" thickBot="1">
+      <c r="N253" s="30"/>
+    </row>
+    <row r="254" spans="14:14" ht="15" thickBot="1">
+      <c r="N254" s="30"/>
+    </row>
+    <row r="255" spans="14:14" ht="15" thickBot="1">
+      <c r="N255" s="30"/>
+    </row>
+    <row r="256" spans="14:14" ht="15" thickBot="1">
+      <c r="N256" s="30"/>
+    </row>
+    <row r="257" spans="14:14" ht="15" thickBot="1">
+      <c r="N257" s="30"/>
+    </row>
+    <row r="258" spans="14:14" ht="15" thickBot="1">
+      <c r="N258" s="30"/>
+    </row>
+    <row r="259" spans="14:14" ht="15" thickBot="1">
+      <c r="N259" s="30"/>
+    </row>
+    <row r="260" spans="14:14" ht="15" thickBot="1">
+      <c r="N260" s="30"/>
+    </row>
+    <row r="261" spans="14:14" ht="15" thickBot="1">
+      <c r="N261" s="30"/>
+    </row>
+    <row r="262" spans="14:14" ht="15" thickBot="1">
+      <c r="N262" s="30"/>
+    </row>
+    <row r="263" spans="14:14" ht="15" thickBot="1">
+      <c r="N263" s="30"/>
+    </row>
+    <row r="264" spans="14:14" ht="15" thickBot="1">
+      <c r="N264" s="30"/>
+    </row>
+    <row r="265" spans="14:14" ht="15" thickBot="1">
+      <c r="N265" s="30"/>
+    </row>
+    <row r="266" spans="14:14" ht="15" thickBot="1">
+      <c r="N266" s="30"/>
+    </row>
+    <row r="267" spans="14:14" ht="15" thickBot="1">
+      <c r="N267" s="30"/>
+    </row>
+    <row r="268" spans="14:14" ht="15" thickBot="1">
+      <c r="N268" s="30"/>
+    </row>
+    <row r="269" spans="14:14" ht="15" thickBot="1">
+      <c r="N269" s="30"/>
+    </row>
+    <row r="270" spans="14:14" ht="15" thickBot="1">
+      <c r="N270" s="30"/>
+    </row>
+    <row r="271" spans="14:14" ht="15" thickBot="1">
+      <c r="N271" s="30"/>
+    </row>
+    <row r="272" spans="14:14" ht="15" thickBot="1">
+      <c r="N272" s="30"/>
+    </row>
+    <row r="273" spans="14:14" ht="15" thickBot="1">
+      <c r="N273" s="30"/>
+    </row>
+    <row r="274" spans="14:14" ht="15" thickBot="1">
+      <c r="N274" s="30"/>
+    </row>
+    <row r="275" spans="14:14" ht="15" thickBot="1">
+      <c r="N275" s="30"/>
+    </row>
+    <row r="276" spans="14:14" ht="15" thickBot="1">
+      <c r="N276" s="30"/>
+    </row>
+    <row r="277" spans="14:14" ht="15" thickBot="1">
+      <c r="N277" s="30"/>
+    </row>
+    <row r="278" spans="14:14" ht="15" thickBot="1">
+      <c r="N278" s="30"/>
+    </row>
+    <row r="279" spans="14:14" ht="15" thickBot="1">
+      <c r="N279" s="30"/>
+    </row>
+    <row r="280" spans="14:14" ht="15" thickBot="1">
+      <c r="N280" s="30"/>
+    </row>
+    <row r="281" spans="14:14" ht="15" thickBot="1">
+      <c r="N281" s="30"/>
+    </row>
+    <row r="282" spans="14:14" ht="15" thickBot="1">
+      <c r="N282" s="30"/>
+    </row>
+    <row r="283" spans="14:14" ht="15" thickBot="1">
+      <c r="N283" s="30"/>
+    </row>
+    <row r="284" spans="14:14" ht="15" thickBot="1">
+      <c r="N284" s="30"/>
+    </row>
+    <row r="285" spans="14:14" ht="15" thickBot="1">
+      <c r="N285" s="30"/>
+    </row>
+    <row r="286" spans="14:14" ht="15" thickBot="1">
+      <c r="N286" s="30"/>
+    </row>
+    <row r="287" spans="14:14" ht="15" thickBot="1">
+      <c r="N287" s="30"/>
+    </row>
+    <row r="288" spans="14:14" ht="15" thickBot="1">
+      <c r="N288" s="30"/>
+    </row>
+    <row r="289" spans="14:14" ht="15" thickBot="1">
+      <c r="N289" s="30"/>
+    </row>
+    <row r="290" spans="14:14" ht="15" thickBot="1">
+      <c r="N290" s="30"/>
+    </row>
+    <row r="291" spans="14:14" ht="15" thickBot="1">
+      <c r="N291" s="30"/>
+    </row>
+    <row r="292" spans="14:14" ht="15" thickBot="1">
+      <c r="N292" s="30"/>
+    </row>
+    <row r="293" spans="14:14" ht="15" thickBot="1">
+      <c r="N293" s="30"/>
+    </row>
+    <row r="294" spans="14:14" ht="15" thickBot="1">
+      <c r="N294" s="30"/>
+    </row>
+    <row r="295" spans="14:14" ht="15" thickBot="1">
+      <c r="N295" s="30"/>
+    </row>
+    <row r="296" spans="14:14" ht="15" thickBot="1">
+      <c r="N296" s="30"/>
+    </row>
+    <row r="297" spans="14:14" ht="15" thickBot="1">
+      <c r="N297" s="30"/>
+    </row>
+    <row r="298" spans="14:14" ht="15" thickBot="1">
+      <c r="N298" s="30"/>
+    </row>
+    <row r="299" spans="14:14" ht="15" thickBot="1">
+      <c r="N299" s="30"/>
+    </row>
+    <row r="300" spans="14:14" ht="15" thickBot="1">
+      <c r="N300" s="30"/>
+    </row>
+    <row r="301" spans="14:14" ht="15" thickBot="1">
+      <c r="N301" s="30"/>
+    </row>
+    <row r="302" spans="14:14" ht="15" thickBot="1">
+      <c r="N302" s="30"/>
+    </row>
+    <row r="303" spans="14:14" ht="15" thickBot="1">
+      <c r="N303" s="30"/>
+    </row>
+    <row r="304" spans="14:14" ht="15" thickBot="1">
+      <c r="N304" s="30"/>
+    </row>
+    <row r="305" spans="14:14" ht="15" thickBot="1">
+      <c r="N305" s="30"/>
+    </row>
+    <row r="306" spans="14:14" ht="15" thickBot="1">
+      <c r="N306" s="30"/>
+    </row>
+    <row r="307" spans="14:14" ht="15" thickBot="1">
+      <c r="N307" s="30"/>
+    </row>
+    <row r="308" spans="14:14" ht="15" thickBot="1">
+      <c r="N308" s="30"/>
+    </row>
+    <row r="309" spans="14:14" ht="15" thickBot="1">
+      <c r="N309" s="30"/>
+    </row>
+    <row r="310" spans="14:14" ht="15" thickBot="1">
+      <c r="N310" s="30"/>
+    </row>
+    <row r="311" spans="14:14" ht="15" thickBot="1">
+      <c r="N311" s="30"/>
+    </row>
+    <row r="312" spans="14:14" ht="15" thickBot="1">
+      <c r="N312" s="30"/>
+    </row>
+    <row r="313" spans="14:14" ht="15" thickBot="1">
+      <c r="N313" s="30"/>
+    </row>
+    <row r="314" spans="14:14" ht="15" thickBot="1">
+      <c r="N314" s="30"/>
+    </row>
+    <row r="315" spans="14:14" ht="15" thickBot="1">
+      <c r="N315" s="30"/>
+    </row>
+    <row r="316" spans="14:14" ht="15" thickBot="1">
+      <c r="N316" s="30"/>
+    </row>
+    <row r="317" spans="14:14" ht="15" thickBot="1">
+      <c r="N317" s="30"/>
+    </row>
+    <row r="318" spans="14:14" ht="15" thickBot="1">
+      <c r="N318" s="30"/>
+    </row>
+    <row r="319" spans="14:14" ht="15" thickBot="1">
+      <c r="N319" s="30"/>
+    </row>
+    <row r="320" spans="14:14" ht="15" thickBot="1">
+      <c r="N320" s="30"/>
+    </row>
+    <row r="321" spans="14:14" ht="15" thickBot="1">
+      <c r="N321" s="30"/>
+    </row>
+    <row r="322" spans="14:14" ht="15" thickBot="1">
+      <c r="N322" s="30"/>
+    </row>
+    <row r="323" spans="14:14" ht="15" thickBot="1">
+      <c r="N323" s="30"/>
+    </row>
+    <row r="324" spans="14:14" ht="15" thickBot="1">
+      <c r="N324" s="30"/>
+    </row>
+    <row r="325" spans="14:14" ht="15" thickBot="1">
+      <c r="N325" s="30"/>
+    </row>
+    <row r="326" spans="14:14" ht="15" thickBot="1">
+      <c r="N326" s="30"/>
+    </row>
+    <row r="327" spans="14:14" ht="15" thickBot="1">
+      <c r="N327" s="30"/>
+    </row>
+    <row r="328" spans="14:14" ht="15" thickBot="1">
+      <c r="N328" s="30"/>
+    </row>
+    <row r="329" spans="14:14" ht="15" thickBot="1">
+      <c r="N329" s="30"/>
+    </row>
+    <row r="330" spans="14:14" ht="15" thickBot="1">
+      <c r="N330" s="30"/>
+    </row>
+    <row r="331" spans="14:14" ht="15" thickBot="1">
+      <c r="N331" s="30"/>
+    </row>
+    <row r="332" spans="14:14" ht="15" thickBot="1">
+      <c r="N332" s="30"/>
+    </row>
+    <row r="333" spans="14:14" ht="15" thickBot="1">
+      <c r="N333" s="30"/>
+    </row>
+    <row r="334" spans="14:14" ht="15" thickBot="1">
+      <c r="N334" s="30"/>
+    </row>
+    <row r="335" spans="14:14" ht="15" thickBot="1">
+      <c r="N335" s="30"/>
+    </row>
+    <row r="336" spans="14:14" ht="15" thickBot="1">
+      <c r="N336" s="30"/>
+    </row>
+    <row r="337" spans="14:14" ht="15" thickBot="1">
+      <c r="N337" s="30"/>
+    </row>
+    <row r="338" spans="14:14" ht="15" thickBot="1">
+      <c r="N338" s="30"/>
+    </row>
+    <row r="339" spans="14:14" ht="15" thickBot="1">
+      <c r="N339" s="30"/>
+    </row>
+    <row r="340" spans="14:14" ht="15" thickBot="1">
+      <c r="N340" s="30"/>
+    </row>
+    <row r="341" spans="14:14" ht="15" thickBot="1">
+      <c r="N341" s="30"/>
+    </row>
+    <row r="342" spans="14:14" ht="15" thickBot="1">
+      <c r="N342" s="30"/>
+    </row>
+    <row r="343" spans="14:14" ht="15" thickBot="1">
+      <c r="N343" s="30"/>
+    </row>
+    <row r="344" spans="14:14" ht="15" thickBot="1">
+      <c r="N344" s="30"/>
+    </row>
+    <row r="345" spans="14:14" ht="15" thickBot="1">
+      <c r="N345" s="30"/>
+    </row>
+    <row r="346" spans="14:14" ht="15" thickBot="1">
+      <c r="N346" s="30"/>
+    </row>
+    <row r="347" spans="14:14" ht="15" thickBot="1">
+      <c r="N347" s="30"/>
+    </row>
+    <row r="348" spans="14:14" ht="15" thickBot="1">
+      <c r="N348" s="30"/>
+    </row>
+    <row r="349" spans="14:14" ht="15" thickBot="1">
+      <c r="N349" s="30"/>
+    </row>
+    <row r="350" spans="14:14" ht="15" thickBot="1">
+      <c r="N350" s="30"/>
+    </row>
+    <row r="351" spans="14:14" ht="15" thickBot="1">
+      <c r="N351" s="30"/>
+    </row>
+    <row r="352" spans="14:14" ht="15" thickBot="1">
+      <c r="N352" s="30"/>
+    </row>
+    <row r="353" spans="14:14" ht="15" thickBot="1">
+      <c r="N353" s="30"/>
+    </row>
+    <row r="354" spans="14:14" ht="15" thickBot="1">
+      <c r="N354" s="30"/>
+    </row>
+    <row r="355" spans="14:14" ht="15" thickBot="1">
+      <c r="N355" s="30"/>
+    </row>
+    <row r="356" spans="14:14" ht="15" thickBot="1">
+      <c r="N356" s="30"/>
+    </row>
+    <row r="357" spans="14:14" ht="15" thickBot="1">
+      <c r="N357" s="30"/>
+    </row>
+    <row r="358" spans="14:14" ht="15" thickBot="1">
+      <c r="N358" s="30"/>
+    </row>
+    <row r="359" spans="14:14" ht="15" thickBot="1">
+      <c r="N359" s="30"/>
+    </row>
+    <row r="360" spans="14:14" ht="15" thickBot="1">
+      <c r="N360" s="30"/>
+    </row>
+    <row r="361" spans="14:14" ht="15" thickBot="1">
+      <c r="N361" s="30"/>
+    </row>
+    <row r="362" spans="14:14" ht="15" thickBot="1">
+      <c r="N362" s="30"/>
+    </row>
+    <row r="363" spans="14:14" ht="15" thickBot="1">
+      <c r="N363" s="30"/>
+    </row>
+    <row r="364" spans="14:14" ht="15" thickBot="1">
+      <c r="N364" s="30"/>
+    </row>
+    <row r="365" spans="14:14" ht="15" thickBot="1">
+      <c r="N365" s="30"/>
+    </row>
+    <row r="366" spans="14:14" ht="15" thickBot="1">
+      <c r="N366" s="30"/>
+    </row>
+    <row r="367" spans="14:14" ht="15" thickBot="1">
+      <c r="N367" s="30"/>
+    </row>
+    <row r="368" spans="14:14" ht="15" thickBot="1">
+      <c r="N368" s="30"/>
+    </row>
+    <row r="369" spans="14:14" ht="15" thickBot="1">
+      <c r="N369" s="30"/>
+    </row>
+    <row r="370" spans="14:14" ht="15" thickBot="1">
+      <c r="N370" s="30"/>
+    </row>
+    <row r="371" spans="14:14" ht="15" thickBot="1">
+      <c r="N371" s="30"/>
+    </row>
+    <row r="372" spans="14:14" ht="15" thickBot="1">
+      <c r="N372" s="30"/>
+    </row>
+    <row r="373" spans="14:14" ht="15" thickBot="1">
+      <c r="N373" s="30"/>
+    </row>
+    <row r="374" spans="14:14" ht="15" thickBot="1">
+      <c r="N374" s="30"/>
+    </row>
+    <row r="375" spans="14:14" ht="15" thickBot="1">
+      <c r="N375" s="30"/>
+    </row>
+    <row r="376" spans="14:14" ht="15" thickBot="1">
+      <c r="N376" s="30"/>
+    </row>
+    <row r="377" spans="14:14" ht="15" thickBot="1">
+      <c r="N377" s="30"/>
+    </row>
+    <row r="378" spans="14:14" ht="15" thickBot="1">
+      <c r="N378" s="30"/>
+    </row>
+    <row r="379" spans="14:14" ht="15" thickBot="1">
+      <c r="N379" s="30"/>
+    </row>
+    <row r="380" spans="14:14" ht="15" thickBot="1">
+      <c r="N380" s="30"/>
+    </row>
+    <row r="381" spans="14:14" ht="15" thickBot="1">
+      <c r="N381" s="30"/>
+    </row>
+    <row r="382" spans="14:14" ht="15" thickBot="1">
+      <c r="N382" s="30"/>
+    </row>
+    <row r="383" spans="14:14" ht="15" thickBot="1">
+      <c r="N383" s="30"/>
+    </row>
+    <row r="384" spans="14:14" ht="15" thickBot="1">
+      <c r="N384" s="30"/>
+    </row>
+    <row r="385" spans="14:14" ht="15" thickBot="1">
+      <c r="N385" s="30"/>
+    </row>
+    <row r="386" spans="14:14" ht="15" thickBot="1">
+      <c r="N386" s="30"/>
+    </row>
+    <row r="387" spans="14:14" ht="15" thickBot="1">
+      <c r="N387" s="30"/>
+    </row>
+    <row r="388" spans="14:14" ht="15" thickBot="1">
+      <c r="N388" s="30"/>
+    </row>
+    <row r="389" spans="14:14" ht="15" thickBot="1">
+      <c r="N389" s="30"/>
+    </row>
+    <row r="390" spans="14:14" ht="15" thickBot="1">
+      <c r="N390" s="30"/>
+    </row>
+    <row r="391" spans="14:14" ht="15" thickBot="1">
+      <c r="N391" s="30"/>
+    </row>
+    <row r="392" spans="14:14" ht="15" thickBot="1">
+      <c r="N392" s="30"/>
+    </row>
+    <row r="393" spans="14:14" ht="15" thickBot="1">
+      <c r="N393" s="30"/>
+    </row>
+    <row r="394" spans="14:14" ht="15" thickBot="1">
+      <c r="N394" s="30"/>
+    </row>
+    <row r="395" spans="14:14" ht="15" thickBot="1">
+      <c r="N395" s="30"/>
+    </row>
+    <row r="396" spans="14:14" ht="15" thickBot="1">
+      <c r="N396" s="30"/>
+    </row>
+    <row r="397" spans="14:14" ht="15" thickBot="1">
+      <c r="N397" s="30"/>
+    </row>
+    <row r="398" spans="14:14" ht="15" thickBot="1">
+      <c r="N398" s="30"/>
+    </row>
+    <row r="399" spans="14:14" ht="15" thickBot="1">
+      <c r="N399" s="30"/>
+    </row>
+    <row r="400" spans="14:14" ht="15" thickBot="1">
+      <c r="N400" s="30"/>
+    </row>
+    <row r="401" spans="14:14" ht="15" thickBot="1">
+      <c r="N401" s="30"/>
+    </row>
+    <row r="402" spans="14:14" ht="15" thickBot="1">
+      <c r="N402" s="30"/>
+    </row>
+    <row r="403" spans="14:14" ht="15" thickBot="1">
+      <c r="N403" s="30"/>
+    </row>
+    <row r="404" spans="14:14" ht="15" thickBot="1">
+      <c r="N404" s="30"/>
+    </row>
+    <row r="405" spans="14:14" ht="15" thickBot="1">
+      <c r="N405" s="30"/>
+    </row>
+    <row r="406" spans="14:14" ht="15" thickBot="1">
+      <c r="N406" s="30"/>
+    </row>
+    <row r="407" spans="14:14" ht="15" thickBot="1">
+      <c r="N407" s="30"/>
+    </row>
+    <row r="408" spans="14:14" ht="15" thickBot="1">
+      <c r="N408" s="30"/>
+    </row>
+    <row r="409" spans="14:14" ht="15" thickBot="1">
+      <c r="N409" s="30"/>
+    </row>
+    <row r="410" spans="14:14" ht="15" thickBot="1">
+      <c r="N410" s="30"/>
+    </row>
+    <row r="411" spans="14:14" ht="15" thickBot="1">
+      <c r="N411" s="30"/>
+    </row>
+    <row r="412" spans="14:14" ht="15" thickBot="1">
+      <c r="N412" s="30"/>
+    </row>
+    <row r="413" spans="14:14" ht="15" thickBot="1">
+      <c r="N413" s="30"/>
+    </row>
+    <row r="414" spans="14:14" ht="15" thickBot="1">
+      <c r="N414" s="30"/>
+    </row>
+    <row r="415" spans="14:14" ht="15" thickBot="1">
+      <c r="N415" s="30"/>
+    </row>
+    <row r="416" spans="14:14" ht="15" thickBot="1">
+      <c r="N416" s="30"/>
+    </row>
+    <row r="417" spans="14:14" ht="15" thickBot="1">
+      <c r="N417" s="30"/>
+    </row>
+    <row r="418" spans="14:14" ht="15" thickBot="1">
+      <c r="N418" s="30"/>
+    </row>
+    <row r="419" spans="14:14" ht="15" thickBot="1">
+      <c r="N419" s="30"/>
+    </row>
+    <row r="420" spans="14:14" ht="15" thickBot="1">
+      <c r="N420" s="30"/>
+    </row>
+    <row r="421" spans="14:14" ht="15" thickBot="1">
+      <c r="N421" s="30"/>
+    </row>
+    <row r="422" spans="14:14" ht="15" thickBot="1">
+      <c r="N422" s="30"/>
+    </row>
+    <row r="423" spans="14:14" ht="15" thickBot="1">
+      <c r="N423" s="30"/>
+    </row>
+    <row r="424" spans="14:14" ht="15" thickBot="1">
+      <c r="N424" s="30"/>
+    </row>
+    <row r="425" spans="14:14" ht="15" thickBot="1">
+      <c r="N425" s="30"/>
+    </row>
+    <row r="426" spans="14:14" ht="15" thickBot="1">
+      <c r="N426" s="30"/>
+    </row>
+    <row r="427" spans="14:14" ht="15" thickBot="1">
+      <c r="N427" s="30"/>
+    </row>
+    <row r="428" spans="14:14" ht="15" thickBot="1">
+      <c r="N428" s="30"/>
+    </row>
+    <row r="429" spans="14:14" ht="15" thickBot="1">
+      <c r="N429" s="30"/>
+    </row>
+    <row r="430" spans="14:14" ht="15" thickBot="1">
+      <c r="N430" s="30"/>
+    </row>
+    <row r="431" spans="14:14" ht="15" thickBot="1">
+      <c r="N431" s="30"/>
+    </row>
+    <row r="432" spans="14:14" ht="15" thickBot="1">
+      <c r="N432" s="30"/>
+    </row>
+    <row r="433" spans="14:14" ht="15" thickBot="1">
+      <c r="N433" s="30"/>
+    </row>
+    <row r="434" spans="14:14" ht="15" thickBot="1">
+      <c r="N434" s="30"/>
+    </row>
+    <row r="435" spans="14:14" ht="15" thickBot="1">
+      <c r="N435" s="30"/>
+    </row>
+    <row r="436" spans="14:14" ht="15" thickBot="1">
+      <c r="N436" s="30"/>
+    </row>
+    <row r="437" spans="14:14" ht="15" thickBot="1">
+      <c r="N437" s="30"/>
+    </row>
+    <row r="438" spans="14:14" ht="15" thickBot="1">
+      <c r="N438" s="30"/>
+    </row>
+    <row r="439" spans="14:14" ht="15" thickBot="1">
+      <c r="N439" s="30"/>
+    </row>
+    <row r="440" spans="14:14" ht="15" thickBot="1">
+      <c r="N440" s="30"/>
+    </row>
+    <row r="441" spans="14:14" ht="15" thickBot="1">
+      <c r="N441" s="30"/>
+    </row>
+    <row r="442" spans="14:14" ht="15" thickBot="1">
+      <c r="N442" s="30"/>
+    </row>
+    <row r="443" spans="14:14" ht="15" thickBot="1">
+      <c r="N443" s="30"/>
+    </row>
+    <row r="444" spans="14:14" ht="15" thickBot="1">
+      <c r="N444" s="30"/>
+    </row>
+    <row r="445" spans="14:14" ht="15" thickBot="1">
+      <c r="N445" s="30"/>
+    </row>
+    <row r="446" spans="14:14" ht="15" thickBot="1">
+      <c r="N446" s="30"/>
+    </row>
+    <row r="447" spans="14:14" ht="15" thickBot="1">
+      <c r="N447" s="30"/>
+    </row>
+    <row r="448" spans="14:14" ht="15" thickBot="1">
+      <c r="N448" s="30"/>
+    </row>
+    <row r="449" spans="14:14" ht="15" thickBot="1">
+      <c r="N449" s="30"/>
+    </row>
+    <row r="450" spans="14:14" ht="15" thickBot="1">
+      <c r="N450" s="30"/>
+    </row>
+    <row r="451" spans="14:14" ht="15" thickBot="1">
+      <c r="N451" s="30"/>
+    </row>
+    <row r="452" spans="14:14" ht="15" thickBot="1">
+      <c r="N452" s="30"/>
+    </row>
+    <row r="453" spans="14:14" ht="15" thickBot="1">
+      <c r="N453" s="30"/>
+    </row>
+    <row r="454" spans="14:14" ht="15" thickBot="1">
+      <c r="N454" s="30"/>
+    </row>
+    <row r="455" spans="14:14" ht="15" thickBot="1">
+      <c r="N455" s="30"/>
+    </row>
+    <row r="456" spans="14:14" ht="15" thickBot="1">
+      <c r="N456" s="30"/>
+    </row>
+    <row r="457" spans="14:14" ht="15" thickBot="1">
+      <c r="N457" s="30"/>
+    </row>
+    <row r="458" spans="14:14" ht="15" thickBot="1">
+      <c r="N458" s="30"/>
+    </row>
+    <row r="459" spans="14:14" ht="15" thickBot="1">
+      <c r="N459" s="30"/>
+    </row>
+    <row r="460" spans="14:14" ht="15" thickBot="1">
+      <c r="N460" s="30"/>
+    </row>
+    <row r="461" spans="14:14" ht="15" thickBot="1">
+      <c r="N461" s="30"/>
+    </row>
+    <row r="462" spans="14:14" ht="15" thickBot="1">
+      <c r="N462" s="30"/>
+    </row>
+    <row r="463" spans="14:14" ht="15" thickBot="1">
+      <c r="N463" s="30"/>
+    </row>
+    <row r="464" spans="14:14" ht="15" thickBot="1">
+      <c r="N464" s="30"/>
+    </row>
+    <row r="465" spans="14:14" ht="15" thickBot="1">
+      <c r="N465" s="30"/>
+    </row>
+    <row r="466" spans="14:14" ht="15" thickBot="1">
+      <c r="N466" s="30"/>
+    </row>
+    <row r="467" spans="14:14" ht="15" thickBot="1">
+      <c r="N467" s="30"/>
+    </row>
+    <row r="468" spans="14:14" ht="15" thickBot="1">
+      <c r="N468" s="30"/>
+    </row>
+    <row r="469" spans="14:14" ht="15" thickBot="1">
+      <c r="N469" s="30"/>
+    </row>
+    <row r="470" spans="14:14" ht="15" thickBot="1">
+      <c r="N470" s="30"/>
+    </row>
+    <row r="471" spans="14:14" ht="15" thickBot="1">
+      <c r="N471" s="30"/>
+    </row>
+    <row r="472" spans="14:14" ht="15" thickBot="1">
+      <c r="N472" s="30"/>
+    </row>
+    <row r="473" spans="14:14" ht="15" thickBot="1">
+      <c r="N473" s="30"/>
+    </row>
+    <row r="474" spans="14:14" ht="15" thickBot="1">
+      <c r="N474" s="30"/>
+    </row>
+    <row r="475" spans="14:14" ht="15" thickBot="1">
+      <c r="N475" s="30"/>
+    </row>
+    <row r="476" spans="14:14" ht="15" thickBot="1">
+      <c r="N476" s="30"/>
+    </row>
+    <row r="477" spans="14:14" ht="15" thickBot="1">
+      <c r="N477" s="30"/>
+    </row>
+    <row r="478" spans="14:14" ht="15" thickBot="1">
+      <c r="N478" s="30"/>
+    </row>
+    <row r="479" spans="14:14" ht="15" thickBot="1">
+      <c r="N479" s="30"/>
+    </row>
+    <row r="480" spans="14:14" ht="15" thickBot="1">
+      <c r="N480" s="30"/>
+    </row>
+    <row r="481" spans="14:14" ht="15" thickBot="1">
+      <c r="N481" s="30"/>
+    </row>
+    <row r="482" spans="14:14" ht="15" thickBot="1">
+      <c r="N482" s="30"/>
+    </row>
+    <row r="483" spans="14:14" ht="15" thickBot="1">
+      <c r="N483" s="30"/>
+    </row>
+    <row r="484" spans="14:14" ht="15" thickBot="1">
+      <c r="N484" s="30"/>
+    </row>
+    <row r="485" spans="14:14" ht="15" thickBot="1">
+      <c r="N485" s="30"/>
+    </row>
+    <row r="486" spans="14:14" ht="15" thickBot="1">
+      <c r="N486" s="30"/>
+    </row>
+    <row r="487" spans="14:14" ht="15" thickBot="1">
+      <c r="N487" s="30"/>
+    </row>
+    <row r="488" spans="14:14" ht="15" thickBot="1">
+      <c r="N488" s="30"/>
+    </row>
+    <row r="489" spans="14:14" ht="15" thickBot="1">
+      <c r="N489" s="30"/>
+    </row>
+    <row r="490" spans="14:14" ht="15" thickBot="1">
+      <c r="N490" s="30"/>
+    </row>
+    <row r="491" spans="14:14" ht="15" thickBot="1">
+      <c r="N491" s="30"/>
+    </row>
+    <row r="492" spans="14:14" ht="15" thickBot="1">
+      <c r="N492" s="30"/>
+    </row>
+    <row r="493" spans="14:14" ht="15" thickBot="1">
+      <c r="N493" s="30"/>
+    </row>
+    <row r="494" spans="14:14" ht="15" thickBot="1">
+      <c r="N494" s="30"/>
+    </row>
+    <row r="495" spans="14:14" ht="15" thickBot="1">
+      <c r="N495" s="30"/>
+    </row>
+    <row r="496" spans="14:14" ht="15" thickBot="1">
+      <c r="N496" s="30"/>
+    </row>
+    <row r="497" spans="14:14" ht="15" thickBot="1">
+      <c r="N497" s="30"/>
+    </row>
+    <row r="498" spans="14:14" ht="15" thickBot="1">
+      <c r="N498" s="30"/>
+    </row>
+    <row r="499" spans="14:14" ht="15" thickBot="1">
+      <c r="N499" s="30"/>
+    </row>
+    <row r="500" spans="14:14" ht="15" thickBot="1">
+      <c r="N500" s="30"/>
+    </row>
+    <row r="501" spans="14:14" ht="15" thickBot="1">
+      <c r="N501" s="30"/>
+    </row>
+    <row r="502" spans="14:14" ht="15" thickBot="1">
+      <c r="N502" s="30"/>
+    </row>
+    <row r="503" spans="14:14" ht="15" thickBot="1">
+      <c r="N503" s="30"/>
+    </row>
+    <row r="504" spans="14:14" ht="15" thickBot="1">
+      <c r="N504" s="30"/>
+    </row>
+    <row r="505" spans="14:14" ht="15" thickBot="1">
+      <c r="N505" s="30"/>
+    </row>
+    <row r="506" spans="14:14" ht="15" thickBot="1">
+      <c r="N506" s="30"/>
+    </row>
+    <row r="507" spans="14:14" ht="15" thickBot="1">
+      <c r="N507" s="30"/>
+    </row>
+    <row r="508" spans="14:14" ht="15" thickBot="1">
+      <c r="N508" s="30"/>
+    </row>
+    <row r="509" spans="14:14" ht="15" thickBot="1">
+      <c r="N509" s="30"/>
+    </row>
+    <row r="510" spans="14:14" ht="15" thickBot="1">
+      <c r="N510" s="30"/>
+    </row>
+    <row r="511" spans="14:14" ht="15" thickBot="1">
+      <c r="N511" s="30"/>
+    </row>
+    <row r="512" spans="14:14" ht="15" thickBot="1">
+      <c r="N512" s="30"/>
+    </row>
+    <row r="513" spans="14:14" ht="15" thickBot="1">
+      <c r="N513" s="30"/>
+    </row>
+    <row r="514" spans="14:14" ht="15" thickBot="1">
+      <c r="N514" s="30"/>
+    </row>
+    <row r="515" spans="14:14" ht="15" thickBot="1">
+      <c r="N515" s="30"/>
+    </row>
+    <row r="516" spans="14:14" ht="15" thickBot="1">
+      <c r="N516" s="30"/>
+    </row>
+    <row r="517" spans="14:14" ht="15" thickBot="1">
+      <c r="N517" s="30"/>
+    </row>
+    <row r="518" spans="14:14" ht="15" thickBot="1">
+      <c r="N518" s="30"/>
+    </row>
+    <row r="519" spans="14:14" ht="15" thickBot="1">
+      <c r="N519" s="30"/>
+    </row>
+    <row r="520" spans="14:14" ht="15" thickBot="1">
+      <c r="N520" s="30"/>
+    </row>
+    <row r="521" spans="14:14" ht="15" thickBot="1">
+      <c r="N521" s="30"/>
+    </row>
+    <row r="522" spans="14:14" ht="15" thickBot="1">
+      <c r="N522" s="30"/>
+    </row>
+    <row r="523" spans="14:14" ht="15" thickBot="1">
+      <c r="N523" s="30"/>
+    </row>
+    <row r="524" spans="14:14" ht="15" thickBot="1">
+      <c r="N524" s="30"/>
+    </row>
+    <row r="525" spans="14:14" ht="15" thickBot="1">
+      <c r="N525" s="30"/>
+    </row>
+    <row r="526" spans="14:14" ht="15" thickBot="1">
+      <c r="N526" s="30"/>
+    </row>
+    <row r="527" spans="14:14" ht="15" thickBot="1">
+      <c r="N527" s="30"/>
+    </row>
+    <row r="528" spans="14:14" ht="15" thickBot="1">
+      <c r="N528" s="30"/>
+    </row>
+    <row r="529" spans="14:14" ht="15" thickBot="1">
+      <c r="N529" s="30"/>
+    </row>
+    <row r="530" spans="14:14" ht="15" thickBot="1">
+      <c r="N530" s="30"/>
+    </row>
+    <row r="531" spans="14:14" ht="15" thickBot="1">
+      <c r="N531" s="30"/>
+    </row>
+    <row r="532" spans="14:14" ht="15" thickBot="1">
+      <c r="N532" s="30"/>
+    </row>
+    <row r="533" spans="14:14" ht="15" thickBot="1">
+      <c r="N533" s="30"/>
+    </row>
+    <row r="534" spans="14:14" ht="15" thickBot="1">
+      <c r="N534" s="30"/>
+    </row>
+    <row r="535" spans="14:14" ht="15" thickBot="1">
+      <c r="N535" s="30"/>
+    </row>
+    <row r="536" spans="14:14" ht="15" thickBot="1">
+      <c r="N536" s="30"/>
+    </row>
+    <row r="537" spans="14:14" ht="15" thickBot="1">
+      <c r="N537" s="30"/>
+    </row>
+    <row r="538" spans="14:14" ht="15" thickBot="1">
+      <c r="N538" s="30"/>
+    </row>
+    <row r="539" spans="14:14" ht="15" thickBot="1">
+      <c r="N539" s="30"/>
+    </row>
+    <row r="540" spans="14:14" ht="15" thickBot="1">
+      <c r="N540" s="30"/>
+    </row>
+    <row r="541" spans="14:14" ht="15" thickBot="1">
+      <c r="N541" s="30"/>
+    </row>
+    <row r="542" spans="14:14" ht="15" thickBot="1">
+      <c r="N542" s="30"/>
+    </row>
+    <row r="543" spans="14:14" ht="15" thickBot="1">
+      <c r="N543" s="30"/>
+    </row>
+    <row r="544" spans="14:14" ht="15" thickBot="1">
+      <c r="N544" s="30"/>
+    </row>
+    <row r="545" spans="14:14" ht="15" thickBot="1">
+      <c r="N545" s="30"/>
+    </row>
+    <row r="546" spans="14:14" ht="15" thickBot="1">
+      <c r="N546" s="30"/>
+    </row>
+    <row r="547" spans="14:14" ht="15" thickBot="1">
+      <c r="N547" s="30"/>
+    </row>
+    <row r="548" spans="14:14" ht="15" thickBot="1">
+      <c r="N548" s="30"/>
+    </row>
+    <row r="549" spans="14:14" ht="15" thickBot="1">
+      <c r="N549" s="30"/>
+    </row>
+    <row r="550" spans="14:14" ht="15" thickBot="1">
+      <c r="N550" s="30"/>
+    </row>
+    <row r="551" spans="14:14" ht="15" thickBot="1">
+      <c r="N551" s="30"/>
+    </row>
+    <row r="552" spans="14:14" ht="15" thickBot="1">
+      <c r="N552" s="30"/>
+    </row>
+    <row r="553" spans="14:14" ht="15" thickBot="1">
+      <c r="N553" s="30"/>
+    </row>
+    <row r="554" spans="14:14" ht="15" thickBot="1">
+      <c r="N554" s="30"/>
+    </row>
+    <row r="555" spans="14:14" ht="15" thickBot="1">
+      <c r="N555" s="30"/>
+    </row>
+    <row r="556" spans="14:14" ht="15" thickBot="1">
+      <c r="N556" s="30"/>
+    </row>
+    <row r="557" spans="14:14" ht="15" thickBot="1">
+      <c r="N557" s="30"/>
+    </row>
+    <row r="558" spans="14:14" ht="15" thickBot="1">
+      <c r="N558" s="30"/>
+    </row>
+    <row r="559" spans="14:14" ht="15" thickBot="1">
+      <c r="N559" s="30"/>
+    </row>
+    <row r="560" spans="14:14" ht="15" thickBot="1">
+      <c r="N560" s="30"/>
+    </row>
+    <row r="561" spans="14:14" ht="15" thickBot="1">
+      <c r="N561" s="30"/>
+    </row>
+    <row r="562" spans="14:14" ht="15" thickBot="1">
+      <c r="N562" s="30"/>
+    </row>
+    <row r="563" spans="14:14" ht="15" thickBot="1">
+      <c r="N563" s="30"/>
+    </row>
+    <row r="564" spans="14:14" ht="15" thickBot="1">
+      <c r="N564" s="30"/>
+    </row>
+    <row r="565" spans="14:14" ht="15" thickBot="1">
+      <c r="N565" s="30"/>
+    </row>
+    <row r="566" spans="14:14" ht="15" thickBot="1">
+      <c r="N566" s="30"/>
+    </row>
+    <row r="567" spans="14:14" ht="15" thickBot="1">
+      <c r="N567" s="30"/>
+    </row>
+    <row r="568" spans="14:14" ht="15" thickBot="1">
+      <c r="N568" s="30"/>
+    </row>
+    <row r="569" spans="14:14" ht="15" thickBot="1">
+      <c r="N569" s="30"/>
+    </row>
+    <row r="570" spans="14:14" ht="15" thickBot="1">
+      <c r="N570" s="30"/>
+    </row>
+    <row r="571" spans="14:14" ht="15" thickBot="1">
+      <c r="N571" s="30"/>
+    </row>
+    <row r="572" spans="14:14" ht="15" thickBot="1">
+      <c r="N572" s="30"/>
+    </row>
+    <row r="573" spans="14:14" ht="15" thickBot="1">
+      <c r="N573" s="30"/>
+    </row>
+    <row r="574" spans="14:14" ht="15" thickBot="1">
+      <c r="N574" s="30"/>
+    </row>
+    <row r="575" spans="14:14" ht="15" thickBot="1">
+      <c r="N575" s="30"/>
+    </row>
+    <row r="576" spans="14:14" ht="15" thickBot="1">
+      <c r="N576" s="30"/>
+    </row>
+    <row r="577" spans="14:14" ht="15" thickBot="1">
+      <c r="N577" s="30"/>
+    </row>
+    <row r="578" spans="14:14" ht="15" thickBot="1">
+      <c r="N578" s="30"/>
+    </row>
+    <row r="579" spans="14:14" ht="15" thickBot="1">
+      <c r="N579" s="30"/>
+    </row>
+    <row r="580" spans="14:14" ht="15" thickBot="1">
+      <c r="N580" s="30"/>
+    </row>
+    <row r="581" spans="14:14" ht="15" thickBot="1">
+      <c r="N581" s="30"/>
+    </row>
+    <row r="582" spans="14:14" ht="15" thickBot="1">
+      <c r="N582" s="30"/>
+    </row>
+    <row r="583" spans="14:14" ht="15" thickBot="1">
+      <c r="N583" s="30"/>
+    </row>
+    <row r="584" spans="14:14" ht="15" thickBot="1">
+      <c r="N584" s="30"/>
+    </row>
+    <row r="585" spans="14:14" ht="15" thickBot="1">
+      <c r="N585" s="30"/>
+    </row>
+    <row r="586" spans="14:14" ht="15" thickBot="1">
+      <c r="N586" s="30"/>
+    </row>
+    <row r="587" spans="14:14" ht="15" thickBot="1">
+      <c r="N587" s="30"/>
+    </row>
+    <row r="588" spans="14:14" ht="15" thickBot="1">
+      <c r="N588" s="30"/>
+    </row>
+    <row r="589" spans="14:14" ht="15" thickBot="1">
+      <c r="N589" s="30"/>
+    </row>
+    <row r="590" spans="14:14" ht="15" thickBot="1">
+      <c r="N590" s="30"/>
+    </row>
+    <row r="591" spans="14:14" ht="15" thickBot="1">
+      <c r="N591" s="30"/>
+    </row>
+    <row r="592" spans="14:14" ht="15" thickBot="1">
+      <c r="N592" s="30"/>
+    </row>
+    <row r="593" spans="14:14" ht="15" thickBot="1">
+      <c r="N593" s="30"/>
+    </row>
+    <row r="594" spans="14:14" ht="15" thickBot="1">
+      <c r="N594" s="30"/>
+    </row>
+    <row r="595" spans="14:14" ht="15" thickBot="1">
+      <c r="N595" s="30"/>
+    </row>
+    <row r="596" spans="14:14" ht="15" thickBot="1">
+      <c r="N596" s="30"/>
+    </row>
+    <row r="597" spans="14:14" ht="15" thickBot="1">
+      <c r="N597" s="30"/>
+    </row>
+    <row r="598" spans="14:14" ht="15" thickBot="1">
+      <c r="N598" s="30"/>
+    </row>
+    <row r="599" spans="14:14" ht="15" thickBot="1">
+      <c r="N599" s="30"/>
+    </row>
+    <row r="600" spans="14:14" ht="15" thickBot="1">
+      <c r="N600" s="30"/>
+    </row>
+    <row r="601" spans="14:14" ht="15" thickBot="1">
+      <c r="N601" s="30"/>
+    </row>
+    <row r="602" spans="14:14" ht="15" thickBot="1">
+      <c r="N602" s="30"/>
+    </row>
+    <row r="603" spans="14:14" ht="15" thickBot="1">
+      <c r="N603" s="30"/>
+    </row>
+    <row r="604" spans="14:14" ht="15" thickBot="1">
+      <c r="N604" s="30"/>
+    </row>
+    <row r="605" spans="14:14" ht="15" thickBot="1">
+      <c r="N605" s="30"/>
+    </row>
+    <row r="606" spans="14:14" ht="15" thickBot="1">
+      <c r="N606" s="30"/>
+    </row>
+    <row r="607" spans="14:14" ht="15" thickBot="1">
+      <c r="N607" s="30"/>
+    </row>
+    <row r="608" spans="14:14" ht="15" thickBot="1">
+      <c r="N608" s="30"/>
+    </row>
+    <row r="609" spans="14:14" ht="15" thickBot="1">
+      <c r="N609" s="30"/>
+    </row>
+    <row r="610" spans="14:14" ht="15" thickBot="1">
+      <c r="N610" s="30"/>
+    </row>
+    <row r="611" spans="14:14" ht="15" thickBot="1">
+      <c r="N611" s="30"/>
+    </row>
+    <row r="612" spans="14:14" ht="15" thickBot="1">
+      <c r="N612" s="30"/>
+    </row>
+    <row r="613" spans="14:14" ht="15" thickBot="1">
+      <c r="N613" s="30"/>
+    </row>
+    <row r="614" spans="14:14" ht="15" thickBot="1">
+      <c r="N614" s="30"/>
+    </row>
+    <row r="615" spans="14:14" ht="15" thickBot="1">
+      <c r="N615" s="30"/>
+    </row>
+    <row r="616" spans="14:14" ht="15" thickBot="1">
+      <c r="N616" s="30"/>
+    </row>
+    <row r="617" spans="14:14" ht="15" thickBot="1">
+      <c r="N617" s="30"/>
+    </row>
+    <row r="618" spans="14:14" ht="15" thickBot="1">
+      <c r="N618" s="30"/>
+    </row>
+    <row r="619" spans="14:14" ht="15" thickBot="1">
+      <c r="N619" s="30"/>
+    </row>
+    <row r="620" spans="14:14" ht="15" thickBot="1">
+      <c r="N620" s="30"/>
+    </row>
+    <row r="621" spans="14:14" ht="15" thickBot="1">
+      <c r="N621" s="30"/>
+    </row>
+    <row r="622" spans="14:14" ht="15" thickBot="1">
+      <c r="N622" s="30"/>
+    </row>
+    <row r="623" spans="14:14" ht="15" thickBot="1">
+      <c r="N623" s="30"/>
+    </row>
+    <row r="624" spans="14:14" ht="15" thickBot="1">
+      <c r="N624" s="30"/>
+    </row>
+    <row r="625" spans="14:14" ht="15" thickBot="1">
+      <c r="N625" s="30"/>
+    </row>
+    <row r="626" spans="14:14" ht="15" thickBot="1">
+      <c r="N626" s="30"/>
+    </row>
+    <row r="627" spans="14:14" ht="15" thickBot="1">
+      <c r="N627" s="30"/>
+    </row>
+    <row r="628" spans="14:14" ht="15" thickBot="1">
+      <c r="N628" s="30"/>
+    </row>
+    <row r="629" spans="14:14" ht="15" thickBot="1">
+      <c r="N629" s="30"/>
+    </row>
+    <row r="630" spans="14:14" ht="15" thickBot="1">
+      <c r="N630" s="30"/>
+    </row>
+    <row r="631" spans="14:14" ht="15" thickBot="1">
+      <c r="N631" s="30"/>
+    </row>
+    <row r="632" spans="14:14" ht="15" thickBot="1">
+      <c r="N632" s="30"/>
+    </row>
+    <row r="633" spans="14:14" ht="15" thickBot="1">
+      <c r="N633" s="30"/>
+    </row>
+    <row r="634" spans="14:14" ht="15" thickBot="1">
+      <c r="N634" s="30"/>
+    </row>
+    <row r="635" spans="14:14" ht="15" thickBot="1">
+      <c r="N635" s="30"/>
+    </row>
+    <row r="636" spans="14:14" ht="15" thickBot="1">
+      <c r="N636" s="30"/>
+    </row>
+    <row r="637" spans="14:14" ht="15" thickBot="1">
+      <c r="N637" s="30"/>
+    </row>
+    <row r="638" spans="14:14" ht="15" thickBot="1">
+      <c r="N638" s="30"/>
+    </row>
+    <row r="639" spans="14:14" ht="15" thickBot="1">
+      <c r="N639" s="30"/>
+    </row>
+    <row r="640" spans="14:14" ht="15" thickBot="1">
+      <c r="N640" s="30"/>
+    </row>
+    <row r="641" spans="14:14" ht="15" thickBot="1">
+      <c r="N641" s="30"/>
+    </row>
+    <row r="642" spans="14:14" ht="15" thickBot="1">
+      <c r="N642" s="30"/>
+    </row>
+    <row r="643" spans="14:14" ht="15" thickBot="1">
+      <c r="N643" s="30"/>
+    </row>
+    <row r="644" spans="14:14" ht="15" thickBot="1">
+      <c r="N644" s="30"/>
+    </row>
+    <row r="645" spans="14:14" ht="15" thickBot="1">
+      <c r="N645" s="30"/>
+    </row>
+    <row r="646" spans="14:14" ht="15" thickBot="1">
+      <c r="N646" s="30"/>
+    </row>
+    <row r="647" spans="14:14" ht="15" thickBot="1">
+      <c r="N647" s="30"/>
+    </row>
+    <row r="648" spans="14:14" ht="15" thickBot="1">
+      <c r="N648" s="30"/>
+    </row>
+    <row r="649" spans="14:14" ht="15" thickBot="1">
+      <c r="N649" s="30"/>
+    </row>
+    <row r="650" spans="14:14" ht="15" thickBot="1">
+      <c r="N650" s="30"/>
+    </row>
+    <row r="651" spans="14:14" ht="15" thickBot="1">
+      <c r="N651" s="30"/>
+    </row>
+    <row r="652" spans="14:14" ht="15" thickBot="1">
+      <c r="N652" s="30"/>
+    </row>
+    <row r="653" spans="14:14" ht="15" thickBot="1">
+      <c r="N653" s="30"/>
+    </row>
+    <row r="654" spans="14:14" ht="15" thickBot="1">
+      <c r="N654" s="30"/>
+    </row>
+    <row r="655" spans="14:14" ht="15" thickBot="1">
+      <c r="N655" s="30"/>
+    </row>
+    <row r="656" spans="14:14" ht="15" thickBot="1">
+      <c r="N656" s="30"/>
+    </row>
+    <row r="657" spans="14:14" ht="15" thickBot="1">
+      <c r="N657" s="30"/>
+    </row>
+    <row r="658" spans="14:14" ht="15" thickBot="1">
+      <c r="N658" s="30"/>
+    </row>
+    <row r="659" spans="14:14" ht="15" thickBot="1">
+      <c r="N659" s="30"/>
+    </row>
+    <row r="660" spans="14:14" ht="15" thickBot="1">
+      <c r="N660" s="30"/>
+    </row>
+    <row r="661" spans="14:14" ht="15" thickBot="1">
+      <c r="N661" s="30"/>
+    </row>
+    <row r="662" spans="14:14" ht="15" thickBot="1">
+      <c r="N662" s="30"/>
+    </row>
+    <row r="663" spans="14:14" ht="15" thickBot="1">
+      <c r="N663" s="30"/>
+    </row>
+    <row r="664" spans="14:14" ht="15" thickBot="1">
+      <c r="N664" s="30"/>
+    </row>
+    <row r="665" spans="14:14" ht="15" thickBot="1">
+      <c r="N665" s="30"/>
+    </row>
+    <row r="666" spans="14:14" ht="15" thickBot="1">
+      <c r="N666" s="30"/>
+    </row>
+    <row r="667" spans="14:14" ht="15" thickBot="1">
+      <c r="N667" s="30"/>
+    </row>
+    <row r="668" spans="14:14" ht="15" thickBot="1">
+      <c r="N668" s="30"/>
+    </row>
+    <row r="669" spans="14:14" ht="15" thickBot="1">
+      <c r="N669" s="30"/>
+    </row>
+    <row r="670" spans="14:14" ht="15" thickBot="1">
+      <c r="N670" s="30"/>
+    </row>
+    <row r="671" spans="14:14" ht="15" thickBot="1">
+      <c r="N671" s="30"/>
+    </row>
+    <row r="672" spans="14:14" ht="15" thickBot="1">
+      <c r="N672" s="30"/>
+    </row>
+    <row r="673" spans="14:14" ht="15" thickBot="1">
+      <c r="N673" s="30"/>
+    </row>
+    <row r="674" spans="14:14" ht="15" thickBot="1">
+      <c r="N674" s="30"/>
+    </row>
+    <row r="675" spans="14:14" ht="15" thickBot="1">
+      <c r="N675" s="30"/>
+    </row>
+    <row r="676" spans="14:14" ht="15" thickBot="1">
+      <c r="N676" s="30"/>
+    </row>
+    <row r="677" spans="14:14" ht="15" thickBot="1">
+      <c r="N677" s="30"/>
+    </row>
+    <row r="678" spans="14:14" ht="15" thickBot="1">
+      <c r="N678" s="30"/>
+    </row>
+    <row r="679" spans="14:14" ht="15" thickBot="1">
+      <c r="N679" s="30"/>
+    </row>
+    <row r="680" spans="14:14" ht="15" thickBot="1">
+      <c r="N680" s="30"/>
+    </row>
+    <row r="681" spans="14:14" ht="15" thickBot="1">
+      <c r="N681" s="30"/>
+    </row>
+    <row r="682" spans="14:14" ht="15" thickBot="1">
+      <c r="N682" s="30"/>
+    </row>
+    <row r="683" spans="14:14" ht="15" thickBot="1">
+      <c r="N683" s="30"/>
+    </row>
+    <row r="684" spans="14:14" ht="15" thickBot="1">
+      <c r="N684" s="30"/>
+    </row>
+    <row r="685" spans="14:14" ht="15" thickBot="1">
+      <c r="N685" s="30"/>
+    </row>
+    <row r="686" spans="14:14" ht="15" thickBot="1">
+      <c r="N686" s="30"/>
+    </row>
+    <row r="687" spans="14:14" ht="15" thickBot="1">
+      <c r="N687" s="30"/>
+    </row>
+    <row r="688" spans="14:14" ht="15" thickBot="1">
+      <c r="N688" s="30"/>
+    </row>
+    <row r="689" spans="14:14" ht="15" thickBot="1">
+      <c r="N689" s="30"/>
+    </row>
+    <row r="690" spans="14:14" ht="15" thickBot="1">
+      <c r="N690" s="30"/>
+    </row>
+    <row r="691" spans="14:14" ht="15" thickBot="1">
+      <c r="N691" s="30"/>
+    </row>
+    <row r="692" spans="14:14" ht="15" thickBot="1">
+      <c r="N692" s="30"/>
+    </row>
+    <row r="693" spans="14:14" ht="15" thickBot="1">
+      <c r="N693" s="30"/>
+    </row>
+    <row r="694" spans="14:14" ht="15" thickBot="1">
+      <c r="N694" s="30"/>
+    </row>
+    <row r="695" spans="14:14" ht="15" thickBot="1">
+      <c r="N695" s="30"/>
+    </row>
+    <row r="696" spans="14:14" ht="15" thickBot="1">
+      <c r="N696" s="30"/>
+    </row>
+    <row r="697" spans="14:14" ht="15" thickBot="1">
+      <c r="N697" s="30"/>
+    </row>
+    <row r="698" spans="14:14" ht="15" thickBot="1">
+      <c r="N698" s="30"/>
+    </row>
+    <row r="699" spans="14:14" ht="15" thickBot="1">
+      <c r="N699" s="30"/>
+    </row>
+    <row r="700" spans="14:14" ht="15" thickBot="1">
+      <c r="N700" s="30"/>
+    </row>
+    <row r="701" spans="14:14" ht="15" thickBot="1">
+      <c r="N701" s="30"/>
+    </row>
+    <row r="702" spans="14:14" ht="15" thickBot="1">
+      <c r="N702" s="30"/>
+    </row>
+    <row r="703" spans="14:14" ht="15" thickBot="1">
+      <c r="N703" s="30"/>
+    </row>
+    <row r="704" spans="14:14" ht="15" thickBot="1">
+      <c r="N704" s="30"/>
+    </row>
+    <row r="705" spans="14:14" ht="15" thickBot="1">
+      <c r="N705" s="30"/>
+    </row>
+    <row r="706" spans="14:14" ht="15" thickBot="1">
+      <c r="N706" s="30"/>
+    </row>
+    <row r="707" spans="14:14" ht="15" thickBot="1">
+      <c r="N707" s="30"/>
+    </row>
+    <row r="708" spans="14:14" ht="15" thickBot="1">
+      <c r="N708" s="30"/>
+    </row>
+    <row r="709" spans="14:14" ht="15" thickBot="1">
+      <c r="N709" s="30"/>
+    </row>
+    <row r="710" spans="14:14" ht="15" thickBot="1">
+      <c r="N710" s="30"/>
+    </row>
+    <row r="711" spans="14:14" ht="15" thickBot="1">
+      <c r="N711" s="30"/>
+    </row>
+    <row r="712" spans="14:14" ht="15" thickBot="1">
+      <c r="N712" s="30"/>
+    </row>
+    <row r="713" spans="14:14" ht="15" thickBot="1">
+      <c r="N713" s="30"/>
+    </row>
+    <row r="714" spans="14:14" ht="15" thickBot="1">
+      <c r="N714" s="30"/>
+    </row>
+    <row r="715" spans="14:14" ht="15" thickBot="1">
+      <c r="N715" s="30"/>
+    </row>
+    <row r="716" spans="14:14" ht="15" thickBot="1">
+      <c r="N716" s="30"/>
+    </row>
+    <row r="717" spans="14:14" ht="15" thickBot="1">
+      <c r="N717" s="30"/>
+    </row>
+    <row r="718" spans="14:14" ht="15" thickBot="1">
+      <c r="N718" s="30"/>
+    </row>
+    <row r="719" spans="14:14" ht="15" thickBot="1">
+      <c r="N719" s="30"/>
+    </row>
+    <row r="720" spans="14:14" ht="15" thickBot="1">
+      <c r="N720" s="30"/>
+    </row>
+    <row r="721" spans="14:14" ht="15" thickBot="1">
+      <c r="N721" s="30"/>
+    </row>
+    <row r="722" spans="14:14" ht="15" thickBot="1">
+      <c r="N722" s="30"/>
+    </row>
+    <row r="723" spans="14:14" ht="15" thickBot="1">
+      <c r="N723" s="30"/>
+    </row>
+    <row r="724" spans="14:14" ht="15" thickBot="1">
+      <c r="N724" s="30"/>
+    </row>
+    <row r="725" spans="14:14" ht="15" thickBot="1">
+      <c r="N725" s="30"/>
+    </row>
+    <row r="726" spans="14:14" ht="15" thickBot="1">
+      <c r="N726" s="30"/>
+    </row>
+    <row r="727" spans="14:14" ht="15" thickBot="1">
+      <c r="N727" s="30"/>
+    </row>
+    <row r="728" spans="14:14" ht="15" thickBot="1">
+      <c r="N728" s="30"/>
+    </row>
+    <row r="729" spans="14:14" ht="15" thickBot="1">
+      <c r="N729" s="30"/>
+    </row>
+    <row r="730" spans="14:14" ht="15" thickBot="1">
+      <c r="N730" s="30"/>
+    </row>
+    <row r="731" spans="14:14" ht="15" thickBot="1">
+      <c r="N731" s="30"/>
+    </row>
+    <row r="732" spans="14:14" ht="15" thickBot="1">
+      <c r="N732" s="30"/>
+    </row>
+    <row r="733" spans="14:14" ht="15" thickBot="1">
+      <c r="N733" s="30"/>
+    </row>
+    <row r="734" spans="14:14" ht="15" thickBot="1">
+      <c r="N734" s="30"/>
+    </row>
+    <row r="735" spans="14:14" ht="15" thickBot="1">
+      <c r="N735" s="30"/>
+    </row>
+    <row r="736" spans="14:14" ht="15" thickBot="1">
+      <c r="N736" s="30"/>
+    </row>
+    <row r="737" spans="14:14" ht="15" thickBot="1">
+      <c r="N737" s="30"/>
+    </row>
+    <row r="738" spans="14:14" ht="15" thickBot="1">
+      <c r="N738" s="30"/>
+    </row>
+    <row r="739" spans="14:14" ht="15" thickBot="1">
+      <c r="N739" s="30"/>
+    </row>
+    <row r="740" spans="14:14" ht="15" thickBot="1">
+      <c r="N740" s="30"/>
+    </row>
+    <row r="741" spans="14:14" ht="15" thickBot="1">
+      <c r="N741" s="30"/>
+    </row>
+    <row r="742" spans="14:14" ht="15" thickBot="1">
+      <c r="N742" s="30"/>
+    </row>
+    <row r="743" spans="14:14" ht="15" thickBot="1">
+      <c r="N743" s="30"/>
+    </row>
+    <row r="744" spans="14:14" ht="15" thickBot="1">
+      <c r="N744" s="30"/>
+    </row>
+    <row r="745" spans="14:14" ht="15" thickBot="1">
+      <c r="N745" s="30"/>
+    </row>
+    <row r="746" spans="14:14" ht="15" thickBot="1">
+      <c r="N746" s="30"/>
+    </row>
+    <row r="747" spans="14:14" ht="15" thickBot="1">
+      <c r="N747" s="30"/>
+    </row>
+    <row r="748" spans="14:14" ht="15" thickBot="1">
+      <c r="N748" s="30"/>
+    </row>
+    <row r="749" spans="14:14" ht="15" thickBot="1">
+      <c r="N749" s="30"/>
+    </row>
+    <row r="750" spans="14:14" ht="15" thickBot="1">
+      <c r="N750" s="30"/>
+    </row>
+    <row r="751" spans="14:14" ht="15" thickBot="1">
+      <c r="N751" s="30"/>
+    </row>
+    <row r="752" spans="14:14" ht="15" thickBot="1">
+      <c r="N752" s="30"/>
+    </row>
+    <row r="753" spans="14:14" ht="15" thickBot="1">
+      <c r="N753" s="30"/>
+    </row>
+    <row r="754" spans="14:14" ht="15" thickBot="1">
+      <c r="N754" s="30"/>
+    </row>
+    <row r="755" spans="14:14" ht="15" thickBot="1">
+      <c r="N755" s="30"/>
+    </row>
+    <row r="756" spans="14:14" ht="15" thickBot="1">
+      <c r="N756" s="30"/>
+    </row>
+    <row r="757" spans="14:14" ht="15" thickBot="1">
+      <c r="N757" s="30"/>
+    </row>
+    <row r="758" spans="14:14" ht="15" thickBot="1">
+      <c r="N758" s="30"/>
+    </row>
+    <row r="759" spans="14:14" ht="15" thickBot="1">
+      <c r="N759" s="30"/>
+    </row>
+    <row r="760" spans="14:14" ht="15" thickBot="1">
+      <c r="N760" s="30"/>
+    </row>
+    <row r="761" spans="14:14" ht="15" thickBot="1">
+      <c r="N761" s="30"/>
+    </row>
+    <row r="762" spans="14:14" ht="15" thickBot="1">
+      <c r="N762" s="30"/>
+    </row>
+    <row r="763" spans="14:14" ht="15" thickBot="1">
+      <c r="N763" s="30"/>
+    </row>
+    <row r="764" spans="14:14" ht="15" thickBot="1">
+      <c r="N764" s="30"/>
+    </row>
+    <row r="765" spans="14:14" ht="15" thickBot="1">
+      <c r="N765" s="30"/>
+    </row>
+    <row r="766" spans="14:14" ht="15" thickBot="1">
+      <c r="N766" s="30"/>
+    </row>
+    <row r="767" spans="14:14" ht="15" thickBot="1">
+      <c r="N767" s="30"/>
+    </row>
+    <row r="768" spans="14:14" ht="15" thickBot="1">
+      <c r="N768" s="30"/>
+    </row>
+    <row r="769" spans="14:14" ht="15" thickBot="1">
+      <c r="N769" s="30"/>
+    </row>
+    <row r="770" spans="14:14" ht="15" thickBot="1">
+      <c r="N770" s="30"/>
+    </row>
+    <row r="771" spans="14:14" ht="15" thickBot="1">
+      <c r="N771" s="30"/>
+    </row>
+    <row r="772" spans="14:14" ht="15" thickBot="1">
+      <c r="N772" s="30"/>
+    </row>
+    <row r="773" spans="14:14" ht="15" thickBot="1">
+      <c r="N773" s="30"/>
+    </row>
+    <row r="774" spans="14:14" ht="15" thickBot="1">
+      <c r="N774" s="30"/>
+    </row>
+    <row r="775" spans="14:14" ht="15" thickBot="1">
+      <c r="N775" s="30"/>
+    </row>
+    <row r="776" spans="14:14" ht="15" thickBot="1">
+      <c r="N776" s="30"/>
+    </row>
+    <row r="777" spans="14:14" ht="15" thickBot="1">
+      <c r="N777" s="30"/>
+    </row>
+    <row r="778" spans="14:14" ht="15" thickBot="1">
+      <c r="N778" s="30"/>
+    </row>
+    <row r="779" spans="14:14" ht="15" thickBot="1">
+      <c r="N779" s="30"/>
+    </row>
+    <row r="780" spans="14:14" ht="15" thickBot="1">
+      <c r="N780" s="30"/>
+    </row>
+    <row r="781" spans="14:14" ht="15" thickBot="1">
+      <c r="N781" s="30"/>
+    </row>
+    <row r="782" spans="14:14" ht="15" thickBot="1">
+      <c r="N782" s="30"/>
+    </row>
+    <row r="783" spans="14:14" ht="15" thickBot="1">
+      <c r="N783" s="30"/>
+    </row>
+    <row r="784" spans="14:14" ht="15" thickBot="1">
+      <c r="N784" s="30"/>
+    </row>
+    <row r="785" spans="14:14" ht="15" thickBot="1">
+      <c r="N785" s="30"/>
+    </row>
+    <row r="786" spans="14:14" ht="15" thickBot="1">
+      <c r="N786" s="30"/>
+    </row>
+    <row r="787" spans="14:14" ht="15" thickBot="1">
+      <c r="N787" s="30"/>
+    </row>
+    <row r="788" spans="14:14" ht="15" thickBot="1">
+      <c r="N788" s="30"/>
+    </row>
+    <row r="789" spans="14:14" ht="15" thickBot="1">
+      <c r="N789" s="30"/>
+    </row>
+    <row r="790" spans="14:14" ht="15" thickBot="1">
+      <c r="N790" s="30"/>
+    </row>
+    <row r="791" spans="14:14" ht="15" thickBot="1">
+      <c r="N791" s="30"/>
+    </row>
+    <row r="792" spans="14:14" ht="15" thickBot="1">
+      <c r="N792" s="30"/>
+    </row>
+    <row r="793" spans="14:14" ht="15" thickBot="1">
+      <c r="N793" s="30"/>
+    </row>
+    <row r="794" spans="14:14" ht="15" thickBot="1">
+      <c r="N794" s="30"/>
+    </row>
+    <row r="795" spans="14:14" ht="15" thickBot="1">
+      <c r="N795" s="30"/>
+    </row>
+    <row r="796" spans="14:14" ht="15" thickBot="1">
+      <c r="N796" s="30"/>
+    </row>
+    <row r="797" spans="14:14" ht="15" thickBot="1">
+      <c r="N797" s="30"/>
+    </row>
+    <row r="798" spans="14:14" ht="15" thickBot="1">
+      <c r="N798" s="30"/>
+    </row>
+    <row r="799" spans="14:14" ht="15" thickBot="1">
+      <c r="N799" s="30"/>
+    </row>
+    <row r="800" spans="14:14" ht="15" thickBot="1">
+      <c r="N800" s="30"/>
+    </row>
+    <row r="801" spans="14:14" ht="15" thickBot="1">
+      <c r="N801" s="30"/>
+    </row>
+    <row r="802" spans="14:14" ht="15" thickBot="1">
+      <c r="N802" s="30"/>
+    </row>
+    <row r="803" spans="14:14" ht="15" thickBot="1">
+      <c r="N803" s="30"/>
+    </row>
+    <row r="804" spans="14:14" ht="15" thickBot="1">
+      <c r="N804" s="30"/>
+    </row>
+    <row r="805" spans="14:14" ht="15" thickBot="1">
+      <c r="N805" s="30"/>
+    </row>
+    <row r="806" spans="14:14" ht="15" thickBot="1">
+      <c r="N806" s="30"/>
+    </row>
+    <row r="807" spans="14:14" ht="15" thickBot="1">
+      <c r="N807" s="30"/>
+    </row>
+    <row r="808" spans="14:14" ht="15" thickBot="1">
+      <c r="N808" s="30"/>
+    </row>
+    <row r="809" spans="14:14" ht="15" thickBot="1">
+      <c r="N809" s="30"/>
+    </row>
+    <row r="810" spans="14:14" ht="15" thickBot="1">
+      <c r="N810" s="30"/>
+    </row>
+    <row r="811" spans="14:14" ht="15" thickBot="1">
+      <c r="N811" s="30"/>
+    </row>
+    <row r="812" spans="14:14" ht="15" thickBot="1">
+      <c r="N812" s="30"/>
+    </row>
+    <row r="813" spans="14:14" ht="15" thickBot="1">
+      <c r="N813" s="30"/>
+    </row>
+    <row r="814" spans="14:14" ht="15" thickBot="1">
+      <c r="N814" s="30"/>
+    </row>
+    <row r="815" spans="14:14" ht="15" thickBot="1">
+      <c r="N815" s="30"/>
+    </row>
+    <row r="816" spans="14:14" ht="15" thickBot="1">
+      <c r="N816" s="30"/>
+    </row>
+    <row r="817" spans="14:14" ht="15" thickBot="1">
+      <c r="N817" s="30"/>
+    </row>
+    <row r="818" spans="14:14" ht="15" thickBot="1">
+      <c r="N818" s="30"/>
+    </row>
+    <row r="819" spans="14:14" ht="15" thickBot="1">
+      <c r="N819" s="30"/>
+    </row>
+    <row r="820" spans="14:14" ht="15" thickBot="1">
+      <c r="N820" s="30"/>
+    </row>
+    <row r="821" spans="14:14" ht="15" thickBot="1">
+      <c r="N821" s="30"/>
+    </row>
+    <row r="822" spans="14:14" ht="15" thickBot="1">
+      <c r="N822" s="30"/>
+    </row>
+    <row r="823" spans="14:14" ht="15" thickBot="1">
+      <c r="N823" s="30"/>
+    </row>
+    <row r="824" spans="14:14" ht="15" thickBot="1">
+      <c r="N824" s="30"/>
+    </row>
+    <row r="825" spans="14:14" ht="15" thickBot="1">
+      <c r="N825" s="30"/>
+    </row>
+    <row r="826" spans="14:14" ht="15" thickBot="1">
+      <c r="N826" s="30"/>
+    </row>
+    <row r="827" spans="14:14" ht="15" thickBot="1">
+      <c r="N827" s="30"/>
+    </row>
+    <row r="828" spans="14:14" ht="15" thickBot="1">
+      <c r="N828" s="30"/>
+    </row>
+    <row r="829" spans="14:14" ht="15" thickBot="1">
+      <c r="N829" s="30"/>
+    </row>
+    <row r="830" spans="14:14" ht="15" thickBot="1">
+      <c r="N830" s="30"/>
+    </row>
+    <row r="831" spans="14:14" ht="15" thickBot="1">
+      <c r="N831" s="30"/>
+    </row>
+    <row r="832" spans="14:14" ht="15" thickBot="1">
+      <c r="N832" s="30"/>
+    </row>
+    <row r="833" spans="14:14" ht="15" thickBot="1">
+      <c r="N833" s="30"/>
+    </row>
+    <row r="834" spans="14:14" ht="15" thickBot="1">
+      <c r="N834" s="30"/>
+    </row>
+    <row r="835" spans="14:14" ht="15" thickBot="1">
+      <c r="N835" s="30"/>
+    </row>
+    <row r="836" spans="14:14" ht="15" thickBot="1">
+      <c r="N836" s="30"/>
+    </row>
+    <row r="837" spans="14:14" ht="15" thickBot="1">
+      <c r="N837" s="30"/>
+    </row>
+    <row r="838" spans="14:14" ht="15" thickBot="1">
+      <c r="N838" s="30"/>
+    </row>
+    <row r="839" spans="14:14" ht="15" thickBot="1">
+      <c r="N839" s="30"/>
+    </row>
+    <row r="840" spans="14:14" ht="15" thickBot="1">
+      <c r="N840" s="30"/>
+    </row>
+    <row r="841" spans="14:14" ht="15" thickBot="1">
+      <c r="N841" s="30"/>
+    </row>
+    <row r="842" spans="14:14" ht="15" thickBot="1">
+      <c r="N842" s="30"/>
+    </row>
+    <row r="843" spans="14:14" ht="15" thickBot="1">
+      <c r="N843" s="30"/>
+    </row>
+    <row r="844" spans="14:14" ht="15" thickBot="1">
+      <c r="N844" s="30"/>
+    </row>
+    <row r="845" spans="14:14" ht="15" thickBot="1">
+      <c r="N845" s="30"/>
+    </row>
+    <row r="846" spans="14:14" ht="15" thickBot="1">
+      <c r="N846" s="30"/>
+    </row>
+    <row r="847" spans="14:14" ht="15" thickBot="1">
+      <c r="N847" s="30"/>
+    </row>
+    <row r="848" spans="14:14" ht="15" thickBot="1">
+      <c r="N848" s="30"/>
+    </row>
+    <row r="849" spans="14:14" ht="15" thickBot="1">
+      <c r="N849" s="30"/>
+    </row>
+    <row r="850" spans="14:14" ht="15" thickBot="1">
+      <c r="N850" s="30"/>
+    </row>
+    <row r="851" spans="14:14" ht="15" thickBot="1">
+      <c r="N851" s="30"/>
+    </row>
+    <row r="852" spans="14:14" ht="15" thickBot="1">
+      <c r="N852" s="30"/>
+    </row>
+    <row r="853" spans="14:14" ht="15" thickBot="1">
+      <c r="N853" s="30"/>
+    </row>
+    <row r="854" spans="14:14" ht="15" thickBot="1">
+      <c r="N854" s="30"/>
+    </row>
+    <row r="855" spans="14:14" ht="15" thickBot="1">
+      <c r="N855" s="30"/>
+    </row>
+    <row r="856" spans="14:14" ht="15" thickBot="1">
+      <c r="N856" s="30"/>
+    </row>
+    <row r="857" spans="14:14" ht="15" thickBot="1">
+      <c r="N857" s="30"/>
+    </row>
+    <row r="858" spans="14:14" ht="15" thickBot="1">
+      <c r="N858" s="30"/>
+    </row>
+    <row r="859" spans="14:14" ht="15" thickBot="1">
+      <c r="N859" s="30"/>
+    </row>
+    <row r="860" spans="14:14" ht="15" thickBot="1">
+      <c r="N860" s="30"/>
+    </row>
+    <row r="861" spans="14:14" ht="15" thickBot="1">
+      <c r="N861" s="30"/>
+    </row>
+    <row r="862" spans="14:14" ht="15" thickBot="1">
+      <c r="N862" s="30"/>
+    </row>
+    <row r="863" spans="14:14" ht="15" thickBot="1">
+      <c r="N863" s="30"/>
+    </row>
+    <row r="864" spans="14:14" ht="15" thickBot="1">
+      <c r="N864" s="30"/>
+    </row>
+    <row r="865" spans="14:14" ht="15" thickBot="1">
+      <c r="N865" s="30"/>
+    </row>
+    <row r="866" spans="14:14" ht="15" thickBot="1">
+      <c r="N866" s="30"/>
+    </row>
+    <row r="867" spans="14:14" ht="15" thickBot="1">
+      <c r="N867" s="30"/>
+    </row>
+    <row r="868" spans="14:14" ht="15" thickBot="1">
+      <c r="N868" s="30"/>
+    </row>
+    <row r="869" spans="14:14" ht="15" thickBot="1">
+      <c r="N869" s="30"/>
+    </row>
+    <row r="870" spans="14:14" ht="15" thickBot="1">
+      <c r="N870" s="30"/>
+    </row>
+    <row r="871" spans="14:14" ht="15" thickBot="1">
+      <c r="N871" s="30"/>
+    </row>
+    <row r="872" spans="14:14" ht="15" thickBot="1">
+      <c r="N872" s="30"/>
+    </row>
+    <row r="873" spans="14:14" ht="15" thickBot="1">
+      <c r="N873" s="30"/>
+    </row>
+    <row r="874" spans="14:14" ht="15" thickBot="1">
+      <c r="N874" s="30"/>
+    </row>
+    <row r="875" spans="14:14" ht="15" thickBot="1">
+      <c r="N875" s="30"/>
+    </row>
+    <row r="876" spans="14:14" ht="15" thickBot="1">
+      <c r="N876" s="30"/>
+    </row>
+    <row r="877" spans="14:14" ht="15" thickBot="1">
+      <c r="N877" s="30"/>
+    </row>
+    <row r="878" spans="14:14" ht="15" thickBot="1">
+      <c r="N878" s="30"/>
+    </row>
+    <row r="879" spans="14:14" ht="15" thickBot="1">
+      <c r="N879" s="30"/>
+    </row>
+    <row r="880" spans="14:14" ht="15" thickBot="1">
+      <c r="N880" s="30"/>
+    </row>
+    <row r="881" spans="14:14" ht="15" thickBot="1">
+      <c r="N881" s="30"/>
+    </row>
+    <row r="882" spans="14:14" ht="15" thickBot="1">
+      <c r="N882" s="30"/>
+    </row>
+    <row r="883" spans="14:14" ht="15" thickBot="1">
+      <c r="N883" s="30"/>
+    </row>
+    <row r="884" spans="14:14" ht="15" thickBot="1">
+      <c r="N884" s="30"/>
+    </row>
+    <row r="885" spans="14:14" ht="15" thickBot="1">
+      <c r="N885" s="30"/>
+    </row>
+    <row r="886" spans="14:14" ht="15" thickBot="1">
+      <c r="N886" s="30"/>
+    </row>
+    <row r="887" spans="14:14" ht="15" thickBot="1">
+      <c r="N887" s="30"/>
+    </row>
+    <row r="888" spans="14:14" ht="15" thickBot="1">
+      <c r="N888" s="30"/>
+    </row>
+    <row r="889" spans="14:14" ht="15" thickBot="1">
+      <c r="N889" s="30"/>
+    </row>
+    <row r="890" spans="14:14" ht="15" thickBot="1">
+      <c r="N890" s="30"/>
+    </row>
+    <row r="891" spans="14:14" ht="15" thickBot="1">
+      <c r="N891" s="30"/>
+    </row>
+    <row r="892" spans="14:14" ht="15" thickBot="1">
+      <c r="N892" s="30"/>
+    </row>
+    <row r="893" spans="14:14" ht="15" thickBot="1">
+      <c r="N893" s="30"/>
+    </row>
+    <row r="894" spans="14:14" ht="15" thickBot="1">
+      <c r="N894" s="30"/>
+    </row>
+    <row r="895" spans="14:14" ht="15" thickBot="1">
+      <c r="N895" s="30"/>
+    </row>
+    <row r="896" spans="14:14" ht="15" thickBot="1">
+      <c r="N896" s="30"/>
+    </row>
+    <row r="897" spans="14:14" ht="15" thickBot="1">
+      <c r="N897" s="30"/>
+    </row>
+    <row r="898" spans="14:14" ht="15" thickBot="1">
+      <c r="N898" s="30"/>
+    </row>
+    <row r="899" spans="14:14" ht="15" thickBot="1">
+      <c r="N899" s="30"/>
+    </row>
+    <row r="900" spans="14:14" ht="15" thickBot="1">
+      <c r="N900" s="30"/>
+    </row>
+    <row r="901" spans="14:14" ht="15" thickBot="1">
+      <c r="N901" s="30"/>
+    </row>
+    <row r="902" spans="14:14" ht="15" thickBot="1">
+      <c r="N902" s="30"/>
+    </row>
+    <row r="903" spans="14:14" ht="15" thickBot="1">
+      <c r="N903" s="30"/>
+    </row>
+    <row r="904" spans="14:14" ht="15" thickBot="1">
+      <c r="N904" s="30"/>
+    </row>
+    <row r="905" spans="14:14" ht="15" thickBot="1">
+      <c r="N905" s="30"/>
+    </row>
+    <row r="906" spans="14:14" ht="15" thickBot="1">
+      <c r="N906" s="30"/>
+    </row>
+    <row r="907" spans="14:14" ht="15" thickBot="1">
+      <c r="N907" s="30"/>
+    </row>
+    <row r="908" spans="14:14" ht="15" thickBot="1">
+      <c r="N908" s="30"/>
+    </row>
+    <row r="909" spans="14:14" ht="15" thickBot="1">
+      <c r="N909" s="30"/>
+    </row>
+    <row r="910" spans="14:14" ht="15" thickBot="1">
+      <c r="N910" s="30"/>
+    </row>
+    <row r="911" spans="14:14" ht="15" thickBot="1">
+      <c r="N911" s="30"/>
+    </row>
+    <row r="912" spans="14:14" ht="15" thickBot="1">
+      <c r="N912" s="30"/>
+    </row>
+    <row r="913" spans="14:14" ht="15" thickBot="1">
+      <c r="N913" s="30"/>
+    </row>
+    <row r="914" spans="14:14" ht="15" thickBot="1">
+      <c r="N914" s="30"/>
+    </row>
+    <row r="915" spans="14:14" ht="15" thickBot="1">
+      <c r="N915" s="30"/>
+    </row>
+    <row r="916" spans="14:14" ht="15" thickBot="1">
+      <c r="N916" s="30"/>
+    </row>
+    <row r="917" spans="14:14" ht="15" thickBot="1">
+      <c r="N917" s="30"/>
+    </row>
+    <row r="918" spans="14:14" ht="15" thickBot="1">
+      <c r="N918" s="30"/>
+    </row>
+    <row r="919" spans="14:14" ht="15" thickBot="1">
+      <c r="N919" s="30"/>
+    </row>
+    <row r="920" spans="14:14" ht="15" thickBot="1">
+      <c r="N920" s="30"/>
+    </row>
+    <row r="921" spans="14:14" ht="15" thickBot="1">
+      <c r="N921" s="30"/>
+    </row>
+    <row r="922" spans="14:14" ht="15" thickBot="1">
+      <c r="N922" s="30"/>
+    </row>
+    <row r="923" spans="14:14" ht="15" thickBot="1">
+      <c r="N923" s="30"/>
+    </row>
+    <row r="924" spans="14:14" ht="15" thickBot="1">
+      <c r="N924" s="30"/>
+    </row>
+    <row r="925" spans="14:14" ht="15" thickBot="1">
+      <c r="N925" s="30"/>
+    </row>
+    <row r="926" spans="14:14" ht="15" thickBot="1">
+      <c r="N926" s="30"/>
+    </row>
+    <row r="927" spans="14:14" ht="15" thickBot="1">
+      <c r="N927" s="30"/>
+    </row>
+    <row r="928" spans="14:14" ht="15" thickBot="1">
+      <c r="N928" s="30"/>
+    </row>
+    <row r="929" spans="14:14" ht="15" thickBot="1">
+      <c r="N929" s="30"/>
+    </row>
+    <row r="930" spans="14:14" ht="15" thickBot="1">
+      <c r="N930" s="30"/>
+    </row>
+    <row r="931" spans="14:14" ht="15" thickBot="1">
+      <c r="N931" s="30"/>
+    </row>
+    <row r="932" spans="14:14" ht="15" thickBot="1">
+      <c r="N932" s="30"/>
+    </row>
+    <row r="933" spans="14:14" ht="15" thickBot="1">
+      <c r="N933" s="30"/>
+    </row>
+    <row r="934" spans="14:14" ht="15" thickBot="1">
+      <c r="N934" s="30"/>
+    </row>
+    <row r="935" spans="14:14" ht="15" thickBot="1">
+      <c r="N935" s="30"/>
+    </row>
+    <row r="936" spans="14:14" ht="15" thickBot="1">
+      <c r="N936" s="30"/>
+    </row>
+    <row r="937" spans="14:14" ht="15" thickBot="1">
+      <c r="N937" s="30"/>
+    </row>
+    <row r="938" spans="14:14" ht="15" thickBot="1">
+      <c r="N938" s="30"/>
+    </row>
+    <row r="939" spans="14:14" ht="15" thickBot="1">
+      <c r="N939" s="30"/>
+    </row>
+    <row r="940" spans="14:14" ht="15" thickBot="1">
+      <c r="N940" s="30"/>
+    </row>
+    <row r="941" spans="14:14" ht="15" thickBot="1">
+      <c r="N941" s="30"/>
+    </row>
+    <row r="942" spans="14:14" ht="15" thickBot="1">
+      <c r="N942" s="30"/>
+    </row>
+    <row r="943" spans="14:14" ht="15" thickBot="1">
+      <c r="N943" s="30"/>
+    </row>
+    <row r="944" spans="14:14" ht="15" thickBot="1">
+      <c r="N944" s="30"/>
+    </row>
+    <row r="945" spans="14:14" ht="15" thickBot="1">
+      <c r="N945" s="30"/>
+    </row>
+    <row r="946" spans="14:14" ht="15" thickBot="1">
+      <c r="N946" s="30"/>
+    </row>
+    <row r="947" spans="14:14" ht="15" thickBot="1">
+      <c r="N947" s="30"/>
+    </row>
+    <row r="948" spans="14:14" ht="15" thickBot="1">
+      <c r="N948" s="30"/>
+    </row>
+    <row r="949" spans="14:14" ht="15" thickBot="1">
+      <c r="N949" s="30"/>
+    </row>
+    <row r="950" spans="14:14" ht="15" thickBot="1">
+      <c r="N950" s="30"/>
+    </row>
+    <row r="951" spans="14:14" ht="15" thickBot="1">
+      <c r="N951" s="30"/>
+    </row>
+    <row r="952" spans="14:14" ht="15" thickBot="1">
+      <c r="N952" s="30"/>
+    </row>
+    <row r="953" spans="14:14" ht="15" thickBot="1">
+      <c r="N953" s="30"/>
+    </row>
+    <row r="954" spans="14:14" ht="15" thickBot="1">
+      <c r="N954" s="30"/>
+    </row>
+    <row r="955" spans="14:14" ht="15" thickBot="1">
+      <c r="N955" s="30"/>
+    </row>
+    <row r="956" spans="14:14" ht="15" thickBot="1">
+      <c r="N956" s="30"/>
+    </row>
+    <row r="957" spans="14:14" ht="15" thickBot="1">
+      <c r="N957" s="30"/>
+    </row>
+    <row r="958" spans="14:14" ht="15" thickBot="1">
+      <c r="N958" s="30"/>
+    </row>
+    <row r="959" spans="14:14" ht="15" thickBot="1">
+      <c r="N959" s="30"/>
+    </row>
+    <row r="960" spans="14:14" ht="15" thickBot="1">
+      <c r="N960" s="30"/>
+    </row>
+    <row r="961" spans="14:14" ht="15" thickBot="1">
+      <c r="N961" s="30"/>
+    </row>
+    <row r="962" spans="14:14" ht="15" thickBot="1">
+      <c r="N962" s="30"/>
+    </row>
+    <row r="963" spans="14:14" ht="15" thickBot="1">
+      <c r="N963" s="30"/>
+    </row>
+    <row r="964" spans="14:14" ht="15" thickBot="1">
+      <c r="N964" s="30"/>
+    </row>
+    <row r="965" spans="14:14" ht="15" thickBot="1">
+      <c r="N965" s="30"/>
+    </row>
+    <row r="966" spans="14:14" ht="15" thickBot="1">
+      <c r="N966" s="30"/>
+    </row>
+    <row r="967" spans="14:14" ht="15" thickBot="1">
+      <c r="N967" s="30"/>
+    </row>
+    <row r="968" spans="14:14" ht="15" thickBot="1">
+      <c r="N968" s="30"/>
+    </row>
+    <row r="969" spans="14:14" ht="15" thickBot="1">
+      <c r="N969" s="30"/>
+    </row>
+    <row r="970" spans="14:14" ht="15" thickBot="1">
+      <c r="N970" s="30"/>
+    </row>
+    <row r="971" spans="14:14" ht="15" thickBot="1">
+      <c r="N971" s="30"/>
+    </row>
+    <row r="972" spans="14:14" ht="15" thickBot="1">
+      <c r="N972" s="30"/>
+    </row>
+    <row r="973" spans="14:14" ht="15" thickBot="1">
+      <c r="N973" s="30"/>
+    </row>
+    <row r="974" spans="14:14" ht="15" thickBot="1">
+      <c r="N974" s="30"/>
+    </row>
+    <row r="975" spans="14:14" ht="15" thickBot="1">
+      <c r="N975" s="30"/>
+    </row>
+    <row r="976" spans="14:14" ht="15" thickBot="1">
+      <c r="N976" s="30"/>
+    </row>
+    <row r="977" spans="14:14" ht="15" thickBot="1">
+      <c r="N977" s="30"/>
+    </row>
+    <row r="978" spans="14:14" ht="15" thickBot="1">
+      <c r="N978" s="30"/>
+    </row>
+    <row r="979" spans="14:14" ht="15" thickBot="1">
+      <c r="N979" s="30"/>
+    </row>
+    <row r="980" spans="14:14" ht="15" thickBot="1">
+      <c r="N980" s="30"/>
+    </row>
+    <row r="981" spans="14:14" ht="15" thickBot="1">
+      <c r="N981" s="30"/>
+    </row>
+    <row r="982" spans="14:14" ht="15" thickBot="1">
+      <c r="N982" s="30"/>
+    </row>
+    <row r="983" spans="14:14" ht="15" thickBot="1">
+      <c r="N983" s="30"/>
+    </row>
+    <row r="984" spans="14:14" ht="15" thickBot="1">
+      <c r="N984" s="30"/>
+    </row>
+    <row r="985" spans="14:14" ht="15" thickBot="1">
+      <c r="N985" s="30"/>
+    </row>
+    <row r="986" spans="14:14" ht="15" thickBot="1">
+      <c r="N986" s="30"/>
+    </row>
+    <row r="987" spans="14:14" ht="15" thickBot="1">
+      <c r="N987" s="30"/>
+    </row>
+    <row r="988" spans="14:14" ht="15" thickBot="1">
+      <c r="N988" s="30"/>
+    </row>
+    <row r="989" spans="14:14" ht="15" thickBot="1">
+      <c r="N989" s="30"/>
+    </row>
+    <row r="990" spans="14:14" ht="15" thickBot="1">
+      <c r="N990" s="30"/>
+    </row>
+    <row r="991" spans="14:14" ht="15" thickBot="1">
+      <c r="N991" s="30"/>
+    </row>
+    <row r="992" spans="14:14" ht="15" thickBot="1">
+      <c r="N992" s="30"/>
+    </row>
+    <row r="993" spans="14:14" ht="15" thickBot="1">
+      <c r="N993" s="30"/>
+    </row>
+    <row r="994" spans="14:14" ht="15" thickBot="1">
+      <c r="N994" s="30"/>
+    </row>
+    <row r="995" spans="14:14" ht="15" thickBot="1">
+      <c r="N995" s="30"/>
+    </row>
+    <row r="996" spans="14:14" ht="15" thickBot="1">
+      <c r="N996" s="30"/>
+    </row>
+    <row r="997" spans="14:14" ht="15" thickBot="1">
+      <c r="N997" s="30"/>
+    </row>
+    <row r="998" spans="14:14" ht="15" thickBot="1">
+      <c r="N998" s="30"/>
+    </row>
+    <row r="999" spans="14:14" ht="15" thickBot="1">
+      <c r="N999" s="30"/>
     </row>
   </sheetData>
   <hyperlinks>
